--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -2005,14 +2005,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="B2:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2020,7 +2019,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -2035,7 +2033,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -2043,13 +2040,8 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Tabs: WACC / Scenarios / Revenue Drivers / NOPAT Bridge / DCF / Comps</t>
-        </is>
-      </c>
+      <c r="B9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="6" t="n"/>
@@ -2060,7 +2052,6 @@
     <row r="12">
       <c r="B12" s="8" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="B14" s="5" t="n"/>
     </row>
@@ -2071,13 +2062,8 @@
       <c r="B16" s="5" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>LULU_Assumptions_Memo.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
+      <c r="B17" s="10" t="n"/>
+    </row>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2113,17 +2099,15 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="11" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2190,7 +2174,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -2205,7 +2188,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>100</v>
+        <v>100.61</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -2260,7 +2243,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -2383,7 +2365,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -2412,7 +2393,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
@@ -2819,7 +2799,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4822,7 +4801,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4880,7 +4858,6 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4888,7 +4865,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5977,13 +5953,8 @@
       <c r="H1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>FY2025A = FY25 10-K historical anchors (blue). FY26-30 = red operational assumptions. Consolidated revenue cross-checks to Scenarios base case.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" s="26" t="n"/>
+    </row>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -6501,7 +6472,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6876,7 +6846,6 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7036,7 +7005,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7301,7 +7269,6 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7474,11 +7441,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="26" t="inlineStr">
-        <is>
-          <t>Note: DCF / Scenarios consolidated revenue is the valuation anchor - drivers do not feed the DCF. A small variance vs Scenarios means the bottom-up path still hangs together, so the Scenarios case stays viable. Bigger gaps = revisit drivers or Scenarios assumptions.</t>
-        </is>
-      </c>
+      <c r="A59" s="26" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7522,7 +7485,7 @@
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>NOPAT NORMALIZATION PIPELINE (BASE CASE)</t>
+          <t>NOPAT RECONCILIATION (BASE CASE)</t>
         </is>
       </c>
       <c r="B1" s="13" t="n"/>
@@ -7574,7 +7537,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7608,11 +7570,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>Forecast NOPAT uses Scenarios EBIT with SBC expensed. DCF implied value uses basic shares (111.4M).</t>
-        </is>
-      </c>
+      <c r="A8" s="26" t="n"/>
     </row>
     <row r="9" ht="70" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -7739,7 +7697,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8413,7 +8370,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -8604,38 +8560,17 @@
       </c>
       <c r="H2" s="81" t="inlineStr">
         <is>
-          <t>Delta vs Scenarios</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="82" t="inlineStr">
-        <is>
-          <t>Forecast drivers linked to Scenarios tab to Base case (column G)</t>
-        </is>
-      </c>
-      <c r="B3" s="83" t="inlineStr">
-        <is>
-          <t>10-K</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https: / www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-        </is>
-      </c>
-      <c r="H3" s="84" t="inlineStr">
-        <is>
-          <t>(should be 0)</t>
-        </is>
-      </c>
+      <c r="A3" s="82" t="n"/>
+      <c r="B3" s="83" t="n"/>
+      <c r="H3" s="84" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
-        <is>
-          <t>LULU_Assumptions_Memo.pdf</t>
-        </is>
-      </c>
+      <c r="A4" s="38" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -9060,7 +8995,7 @@
     <row r="19">
       <c r="A19" s="52" t="inlineStr">
         <is>
-          <t>Working capital schedule (driver-based) [click - to collapse detail]</t>
+          <t>Working capital schedule</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9576,7 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Scenarios linkage summary (column K should all read OK)</t>
+          <t>Scenarios linkage</t>
         </is>
       </c>
       <c r="H40" s="92">
@@ -9753,11 +9688,6 @@
       <c r="B50" s="74" t="n">
         <v>1807202</v>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>https: / www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-        </is>
-      </c>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
@@ -9768,11 +9698,6 @@
       <c r="B51" s="74" t="n">
         <v>-1798441</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>https: / www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="26" t="inlineStr">
@@ -9784,7 +9709,7 @@
     <row r="53">
       <c r="A53" s="26" t="inlineStr">
         <is>
-          <t>UFCF is pre-interest; rent stays in opex. We subtract lease liabilities in the bridge but do not add back implied lease interest to EBIT (simplified treatment).</t>
+          <t>UFCF pre-interest; ASC 842 lease debt in EV bridge.</t>
         </is>
       </c>
     </row>
@@ -9808,11 +9733,6 @@
       <c r="B55" s="74" t="n">
         <v>111380</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>https: / www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="23" t="inlineStr">
@@ -9836,12 +9756,7 @@
         </is>
       </c>
       <c r="B57" s="97" t="n">
-        <v>100</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>https: / www.nasdaq.com/market-activity/stocks/lulu</t>
-        </is>
+        <v>100.61</v>
       </c>
     </row>
     <row r="58">
@@ -9877,11 +9792,7 @@
       <c r="B62" s="13" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="inlineStr">
-        <is>
-          <t>Guardrail: implied value per share above still divides equity value by Day-1 shares (E55 = 111,380k). This schedule does not change intrinsic DCF per share.</t>
-        </is>
-      </c>
+      <c r="A63" s="26" t="n"/>
     </row>
     <row r="64"/>
     <row r="65">
@@ -10037,7 +9948,7 @@
         </is>
       </c>
       <c r="B72" s="99" t="n">
-        <v>100</v>
+        <v>100.61</v>
       </c>
       <c r="C72" s="99">
         <f>B72*(1+$B$66)</f>
@@ -10490,29 +10401,23 @@
     <row r="104" ht="28" customHeight="1"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -10568,11 +10473,6 @@
       <c r="B4" s="74" t="n">
         <v>11102600</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https: / www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -10605,11 +10505,6 @@
       <c r="B7" s="97" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https: / corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-        </is>
-      </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -10620,11 +10515,6 @@
       <c r="B8" s="74" t="n">
         <v>1807202</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https: / www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -10635,11 +10525,6 @@
       <c r="B9" s="74" t="n">
         <v>111380</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https: / www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -10648,12 +10533,7 @@
         </is>
       </c>
       <c r="B10" s="97" t="n">
-        <v>100</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https: / www.nasdaq.com/market-activity/stocks/lulu</t>
-        </is>
+        <v>100.61</v>
       </c>
     </row>
     <row r="11">
@@ -10925,11 +10805,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>Column E on the next two rows is $bn, not EV/EBITDA. The black formula is implied EV/Sales on an unclosed ask.</t>
-        </is>
-      </c>
+      <c r="A32" s="26" t="n"/>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
@@ -10940,11 +10816,6 @@
       <c r="B33" s="117" t="n">
         <v>10</v>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https: / www.reuters.com/markets/deals/alo-yoga-parent-seeks-investment-10-bln-valuation-sources-2023-10-30/</t>
-        </is>
-      </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
@@ -10954,11 +10825,6 @@
       </c>
       <c r="B34" s="117" t="n">
         <v>2</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https: / www.forbes.com/sites/jemimamcevoy/2025/04/01/the-founders-of-this-lululemon-rival-are-worth-nearly-5-billion-each/</t>
-        </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
@@ -11017,7 +10883,7 @@
     <row r="41">
       <c r="A41" s="107" t="inlineStr">
         <is>
-          <t>We do not average peers for terminal value, and we do not use Alo 5.0x EV/Sales as EV/EBITDA.</t>
+          <t>Peer multiples illustrative; terminal value from DCF exit multiple.</t>
         </is>
       </c>
     </row>
@@ -11228,12 +11094,7 @@
         </is>
       </c>
       <c r="B62" s="125" t="n">
-        <v>100</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>https: / www.nasdaq.com/market-activity/stocks/lulu</t>
-        </is>
+        <v>100.61</v>
       </c>
     </row>
     <row r="63">
@@ -11244,16 +11105,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId8"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -10400,25 +10400,6 @@
     </row>
     <row r="104" ht="28" customHeight="1"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId17"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -2005,13 +2005,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2019,6 +2020,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -2033,6 +2035,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -2040,6 +2043,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="n"/>
     </row>
@@ -2052,6 +2056,7 @@
     <row r="12">
       <c r="B12" s="8" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="5" t="n"/>
     </row>
@@ -2064,6 +2069,7 @@
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="10" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2099,6 +2105,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="B25" s="11" t="n"/>
     </row>
@@ -2174,6 +2181,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -2243,6 +2251,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -2365,6 +2374,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -2393,6 +2403,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
@@ -2799,6 +2810,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4801,6 +4813,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4858,6 +4871,7 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4865,6 +4879,7 @@
         </is>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5955,6 +5970,7 @@
     <row r="2">
       <c r="A2" s="26" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -6472,6 +6488,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6846,6 +6863,7 @@
         <v>122</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7005,6 +7023,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7269,6 +7288,7 @@
         <v>0.13</v>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7537,6 +7557,7 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7697,6 +7718,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8370,6 +8392,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="WACC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DCF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Comps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2002,17 +2002,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="B2:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2020,7 +2019,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -2035,7 +2033,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -2043,7 +2040,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="n"/>
     </row>
@@ -2056,7 +2052,6 @@
     <row r="12">
       <c r="B12" s="8" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="B14" s="5" t="n"/>
     </row>
@@ -2069,7 +2064,6 @@
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="10" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2105,7 +2099,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="11" t="n"/>
     </row>
@@ -2123,16 +2116,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
-    <col outlineLevel="1" width="18" customWidth="1" min="3" max="3"/>
-    <col outlineLevel="1" width="40" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2181,7 +2174,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -2251,7 +2243,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -2374,7 +2365,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -2403,7 +2393,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
@@ -2455,16 +2444,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
-    <col outlineLevel="1" width="16" customWidth="1" min="3" max="3"/>
-    <col outlineLevel="1" width="38" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -2810,7 +2799,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4813,7 +4801,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4871,7 +4858,6 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4879,7 +4865,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5933,7 +5918,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H59"/>
@@ -5947,10 +5932,10 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col outlineLevel="1" width="40" customWidth="1" min="9" max="9"/>
-    <col outlineLevel="1" width="28" customWidth="1" min="10" max="10"/>
-    <col outlineLevel="1" width="16" customWidth="1" min="11" max="11"/>
-    <col outlineLevel="1" width="36" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5970,7 +5955,6 @@
     <row r="2">
       <c r="A2" s="26" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -6488,7 +6472,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6863,7 +6846,6 @@
         <v>122</v>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7023,7 +7005,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7288,7 +7269,6 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7484,16 +7464,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
-    <col outlineLevel="1" width="22" customWidth="1" min="2" max="2"/>
-    <col outlineLevel="1" width="28" customWidth="1" min="3" max="3"/>
-    <col outlineLevel="1" width="28" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -7557,7 +7537,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7718,15 +7697,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15" outlineLevel="1">
+    <row r="15">
       <c r="A15" s="73" t="inlineStr">
         <is>
           <t>EBIT adjustments</t>
         </is>
       </c>
     </row>
-    <row r="16" outlineLevel="1" ht="28" customHeight="1">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Reported operating income (EBIT)</t>
@@ -7756,7 +7734,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" outlineLevel="1" ht="28" customHeight="1">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>+ Impairment / intangible amortization (add-back)</t>
@@ -7781,7 +7759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" outlineLevel="1" ht="28" customHeight="1">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>+ Restructuring costs (add-back)</t>
@@ -7806,7 +7784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" outlineLevel="1" ht="28" customHeight="1">
+    <row r="19" ht="28" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>+ Legal / M&amp;A one-offs (add-back)</t>
@@ -7831,7 +7809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" outlineLevel="1" ht="42" customHeight="1">
+    <row r="20" ht="42" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>+ Stock-based compensation (add-back only if flag = 1)</t>
@@ -7862,7 +7840,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" outlineLevel="1" ht="28" customHeight="1">
+    <row r="21" ht="28" customHeight="1">
       <c r="A21" s="23">
         <f> Adjusted EBIT (Phase 1)</f>
         <v/>
@@ -7888,14 +7866,14 @@
         <v/>
       </c>
     </row>
-    <row r="22" outlineLevel="1">
+    <row r="22">
       <c r="A22" s="73" t="inlineStr">
         <is>
           <t>Lease &amp; capitalization</t>
         </is>
       </c>
     </row>
-    <row r="23" outlineLevel="1" ht="42" customHeight="1">
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>+ Implied lease interest expense (reclass from rent)</t>
@@ -7925,7 +7903,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" outlineLevel="1" ht="28" customHeight="1">
+    <row r="24" ht="28" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t>+ Capitalize R&amp;D / software (current-year expense)</t>
@@ -7950,7 +7928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" outlineLevel="1" ht="28" customHeight="1">
+    <row r="25" ht="28" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Amortization of prior capitalized intangibles</t>
@@ -7975,7 +7953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" outlineLevel="1" ht="28" customHeight="1">
+    <row r="26" ht="28" customHeight="1">
       <c r="A26" s="23">
         <f> EBIT after lease &amp; capitalization (Phase 2)</f>
         <v/>
@@ -8001,14 +7979,14 @@
         <v/>
       </c>
     </row>
-    <row r="27" outlineLevel="1">
+    <row r="27">
       <c r="A27" s="73" t="inlineStr">
         <is>
           <t>Segment EBIT bridge</t>
         </is>
       </c>
     </row>
-    <row r="28" outlineLevel="1" ht="28" customHeight="1">
+    <row r="28" ht="28" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Store-channel revenue</t>
@@ -8038,7 +8016,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" outlineLevel="1" ht="28" customHeight="1">
+    <row r="29" ht="28" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>E-commerce revenue</t>
@@ -8068,7 +8046,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" outlineLevel="1" ht="28" customHeight="1">
+    <row r="30" ht="28" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Other channels revenue</t>
@@ -8098,7 +8076,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" outlineLevel="1" ht="70" customHeight="1">
+    <row r="31" ht="70" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Store-channel EBIT (= Rev x store margin)</t>
@@ -8128,7 +8106,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" outlineLevel="1" ht="70" customHeight="1">
+    <row r="32" ht="70" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
           <t>E-commerce EBIT (= Rev x e-comm margin)</t>
@@ -8158,7 +8136,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" outlineLevel="1" ht="56" customHeight="1">
+    <row r="33" ht="56" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Other-channels EBIT (= Rev x other margin)</t>
@@ -8188,7 +8166,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" outlineLevel="1" ht="28" customHeight="1">
+    <row r="34" ht="28" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
         <is>
           <t>Channel EBIT (sum of sector EBIT)</t>
@@ -8215,7 +8193,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" outlineLevel="1" ht="28" customHeight="1">
+    <row r="35" ht="28" customHeight="1">
       <c r="A35" s="23">
         <f> EBIT after channel mix (Phase 3)</f>
         <v/>
@@ -8244,7 +8222,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" outlineLevel="1" ht="28" customHeight="1">
+    <row r="36" ht="28" customHeight="1">
       <c r="A36" s="23">
         <f> Normalized EBIT (tax base for NOPAT)</f>
         <v/>
@@ -8274,7 +8252,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" outlineLevel="1">
+    <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Check vs Scenarios EBIT (base case)</t>
@@ -8301,14 +8279,14 @@
         <v/>
       </c>
     </row>
-    <row r="38" outlineLevel="1">
+    <row r="38">
       <c r="A38" s="73" t="inlineStr">
         <is>
           <t>Tax normalization</t>
         </is>
       </c>
     </row>
-    <row r="39" outlineLevel="1" ht="70" customHeight="1">
+    <row r="39" ht="70" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Operating effective tax rate (t_operating)</t>
@@ -8338,7 +8316,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" outlineLevel="1" ht="28" customHeight="1">
+    <row r="40" ht="28" customHeight="1">
       <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Unlevered tax on normalized EBIT</t>
@@ -8365,7 +8343,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" outlineLevel="1" ht="28" customHeight="1">
+    <row r="41" ht="28" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
           <t>NORMALIZED NOPAT</t>
@@ -8392,7 +8370,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -8516,16 +8493,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
-    <col outlineLevel="1" width="16" customWidth="1" min="3" max="3"/>
-    <col outlineLevel="1" width="36" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -8533,8 +8510,8 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col outlineLevel="1" width="16" customWidth="1" min="12" max="12"/>
-    <col outlineLevel="1" width="36" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -9022,7 +8999,7 @@
         </is>
       </c>
     </row>
-    <row r="20" outlineLevel="1" ht="150" customHeight="1">
+    <row r="20" ht="150" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>DSO (days) - flat vs FY25</t>
@@ -9056,7 +9033,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" outlineLevel="1" ht="98" customHeight="1">
+    <row r="21" ht="98" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Accounts receivable, net</t>
@@ -9090,7 +9067,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" outlineLevel="1" ht="150" customHeight="1">
+    <row r="22" ht="150" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>DIO (days) - FY25 anchor, -1 day/yr</t>
@@ -9124,7 +9101,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" outlineLevel="1" ht="112" customHeight="1">
+    <row r="23" ht="112" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Inventories</t>
@@ -9158,7 +9135,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" outlineLevel="1" ht="84" customHeight="1">
+    <row r="24" ht="84" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t>DPO (days) - flat vs FY25</t>
@@ -9192,7 +9169,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" outlineLevel="1" ht="84" customHeight="1">
+    <row r="25" ht="84" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Accounts payable</t>
@@ -9226,7 +9203,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" outlineLevel="1" ht="84" customHeight="1">
+    <row r="26" ht="84" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Prepaid expenses (% of revenue)</t>
@@ -9256,7 +9233,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" outlineLevel="1" ht="84" customHeight="1">
+    <row r="27" ht="84" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Prepaid expenses (other current assets)</t>
@@ -9290,7 +9267,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" outlineLevel="1" ht="84" customHeight="1">
+    <row r="28" ht="84" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Accrued liabilities (% of revenue)</t>
@@ -9320,7 +9297,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" outlineLevel="1" ht="84" customHeight="1">
+    <row r="29" ht="84" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Accrued liabilities and other</t>
@@ -9354,7 +9331,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" outlineLevel="1" ht="42" customHeight="1">
+    <row r="30" ht="42" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Current operating assets (AR + inv + prepaids)</t>
@@ -9385,7 +9362,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" outlineLevel="1" ht="42" customHeight="1">
+    <row r="31" ht="42" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Current operating liabilities (AP + accruals)</t>
@@ -9416,7 +9393,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" outlineLevel="1" ht="42" customHeight="1">
+    <row r="32" ht="42" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
           <t>Net working capital</t>
@@ -9595,7 +9572,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -9804,8 +9780,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -9817,7 +9791,6 @@
     <row r="63">
       <c r="A63" s="26" t="n"/>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -9878,7 +9851,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -9963,7 +9935,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10084,7 +10055,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10145,7 +10115,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -10215,7 +10184,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -10261,8 +10229,6 @@
         </is>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -10431,16 +10397,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
-    <col outlineLevel="1" width="18" customWidth="1" min="3" max="3"/>
-    <col outlineLevel="1" width="44" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -10460,7 +10426,6 @@
       <c r="D1" s="13" t="n"/>
       <c r="E1" s="13" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -10562,7 +10527,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -10800,7 +10764,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -10854,7 +10817,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -10891,7 +10853,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -10981,7 +10942,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -11090,7 +11050,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -2005,13 +2005,14 @@
     <outlinePr summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -2019,6 +2020,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -2033,6 +2035,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -2040,6 +2043,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="n"/>
     </row>
@@ -2052,6 +2056,7 @@
     <row r="12">
       <c r="B12" s="8" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="5" t="n"/>
     </row>
@@ -2064,6 +2069,7 @@
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="10" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -2099,6 +2105,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="B25" s="11" t="n"/>
     </row>
@@ -2174,6 +2181,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -2243,6 +2251,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -2365,6 +2374,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -2393,6 +2403,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
@@ -2799,6 +2810,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4801,6 +4813,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4858,13 +4871,11 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
-      <c r="A135" s="26" t="inlineStr">
-        <is>
-          <t>Current price $100.00; cash $1,807,202 k; lease debt $1,798,441 k; funded debt $0; net cash $8,761 k.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A135" s="26" t="n"/>
+    </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5955,6 +5966,7 @@
     <row r="2">
       <c r="A2" s="26" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -6472,6 +6484,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6846,6 +6859,7 @@
         <v>122</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7005,6 +7019,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7269,6 +7284,7 @@
         <v>0.13</v>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7537,6 +7553,7 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7697,6 +7714,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8255,7 +8273,7 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>Check vs Scenarios EBIT (base case)</t>
+          <t>EBIT variance vs Scenarios ($000)</t>
         </is>
       </c>
       <c r="C37" s="75">
@@ -8370,6 +8388,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -8457,18 +8476,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="26" t="inlineStr">
-        <is>
-          <t>Steps 1-4: DCF unchanged on FY26. Step 5 changes NOPAT only (tax). Step 6 changes FY26 EBIT (+ tariff).</t>
-        </is>
-      </c>
+      <c r="A51" s="26" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
-        <is>
-          <t>Scenarios base-case NOPAT (col G) links to NORMALIZED NOPAT above. Bear/bull apply the same t_operating to their EBIT paths.</t>
-        </is>
-      </c>
+      <c r="A52" s="26" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8496,7 +8507,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8558,16 +8569,10 @@
           <t>FY2030E</t>
         </is>
       </c>
-      <c r="H2" s="81" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="82" t="n"/>
       <c r="B3" s="83" t="n"/>
-      <c r="H3" s="84" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="38" t="n"/>
@@ -8601,10 +8606,6 @@
         <f>Scenarios!D29</f>
         <v/>
       </c>
-      <c r="H5" s="86">
-        <f>IF(MAX(ABS(C5-Scenarios!$D$25),ABS(D5-Scenarios!$D$26),ABS(E5-Scenarios!$D$27),ABS(F5-Scenarios!$D$28),ABS(G5-Scenarios!$D$29))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -8692,10 +8693,6 @@
         <f>Scenarios!D39</f>
         <v/>
       </c>
-      <c r="H8" s="86">
-        <f>IF(MAX(ABS(C8-Scenarios!$D$35),ABS(D8-Scenarios!$D$36),ABS(E8-Scenarios!$D$37),ABS(F8-Scenarios!$D$38),ABS(G8-Scenarios!$D$39))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -8723,10 +8720,6 @@
         <f>Scenarios!D44</f>
         <v/>
       </c>
-      <c r="H9" s="86">
-        <f>IF(MAX(ABS(C9-Scenarios!$D$40),ABS(D9-Scenarios!$D$41),ABS(E9-Scenarios!$D$42),ABS(F9-Scenarios!$D$43),ABS(G9-Scenarios!$D$44))&lt;0.0001,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -8783,10 +8776,6 @@
         <f>Scenarios!D49</f>
         <v/>
       </c>
-      <c r="H11" s="87">
-        <f>IF(MAX(ABS(C11-Scenarios!$D$45),ABS(D11-Scenarios!$D$46),ABS(E11-Scenarios!$D$47),ABS(F11-Scenarios!$D$48),ABS(G11-Scenarios!$D$49))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -8871,10 +8860,6 @@
         <f>Scenarios!D54</f>
         <v/>
       </c>
-      <c r="H14" s="87">
-        <f>IF(MAX(ABS(C14-Scenarios!$D$50),ABS(D14-Scenarios!$D$51),ABS(E14-Scenarios!$D$52),ABS(F14-Scenarios!$D$53),ABS(G14-Scenarios!$D$54))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
@@ -8929,10 +8914,6 @@
         <f>Scenarios!D59</f>
         <v/>
       </c>
-      <c r="H16" s="86">
-        <f>IF(MAX(ABS(C16-Scenarios!$D$55),ABS(D16-Scenarios!$D$56),ABS(E16-Scenarios!$D$57),ABS(F16-Scenarios!$D$58),ABS(G16-Scenarios!$D$59))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -8987,15 +8968,11 @@
         <f>-Scenarios!D64</f>
         <v/>
       </c>
-      <c r="H18" s="86">
-        <f>IF(MAX(ABS(C18+Scenarios!$D$60),ABS(D18+Scenarios!$D$61),ABS(E18+Scenarios!$D$62),ABS(F18+Scenarios!$D$63),ABS(G18+Scenarios!$D$64))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="52" t="inlineStr">
         <is>
-          <t>Working capital schedule</t>
+          <t>Working capital</t>
         </is>
       </c>
     </row>
@@ -9028,10 +9005,6 @@
         <f>Scenarios!D69</f>
         <v/>
       </c>
-      <c r="H20" s="86">
-        <f>IF(MAX(ABS(C20-Scenarios!$D$65),ABS(D20-Scenarios!$D$66),ABS(E20-Scenarios!$D$67),ABS(F20-Scenarios!$D$68),ABS(G20-Scenarios!$D$69))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="21" ht="98" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -9062,10 +9035,6 @@
         <f>Scenarios!D74</f>
         <v/>
       </c>
-      <c r="H21" s="86">
-        <f>IF(MAX(ABS(C21-Scenarios!$D$70),ABS(D21-Scenarios!$D$71),ABS(E21-Scenarios!$D$72),ABS(F21-Scenarios!$D$73),ABS(G21-Scenarios!$D$74))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -9096,10 +9065,6 @@
         <f>Scenarios!D79</f>
         <v/>
       </c>
-      <c r="H22" s="86">
-        <f>IF(MAX(ABS(C22-Scenarios!$D$75),ABS(D22-Scenarios!$D$76),ABS(E22-Scenarios!$D$77),ABS(F22-Scenarios!$D$78),ABS(G22-Scenarios!$D$79))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="23" ht="112" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
@@ -9130,10 +9095,6 @@
         <f>Scenarios!D84</f>
         <v/>
       </c>
-      <c r="H23" s="86">
-        <f>IF(MAX(ABS(C23-Scenarios!$D$80),ABS(D23-Scenarios!$D$81),ABS(E23-Scenarios!$D$82),ABS(F23-Scenarios!$D$83),ABS(G23-Scenarios!$D$84))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="24" ht="84" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -9164,10 +9125,6 @@
         <f>Scenarios!D89</f>
         <v/>
       </c>
-      <c r="H24" s="86">
-        <f>IF(MAX(ABS(C24-Scenarios!$D$85),ABS(D24-Scenarios!$D$86),ABS(E24-Scenarios!$D$87),ABS(F24-Scenarios!$D$88),ABS(G24-Scenarios!$D$89))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="25" ht="84" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -9198,10 +9155,6 @@
         <f>Scenarios!D94</f>
         <v/>
       </c>
-      <c r="H25" s="86">
-        <f>IF(MAX(ABS(C25-Scenarios!$D$90),ABS(D25-Scenarios!$D$91),ABS(E25-Scenarios!$D$92),ABS(F25-Scenarios!$D$93),ABS(G25-Scenarios!$D$94))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="26" ht="84" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -9262,10 +9215,6 @@
         <f>Scenarios!D99</f>
         <v/>
       </c>
-      <c r="H27" s="86">
-        <f>IF(MAX(ABS(C27-Scenarios!$D$95),ABS(D27-Scenarios!$D$96),ABS(E27-Scenarios!$D$97),ABS(F27-Scenarios!$D$98),ABS(G27-Scenarios!$D$99))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="28" ht="84" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
@@ -9326,10 +9275,6 @@
         <f>Scenarios!D104</f>
         <v/>
       </c>
-      <c r="H29" s="86">
-        <f>IF(MAX(ABS(C29-Scenarios!$D$100),ABS(D29-Scenarios!$D$101),ABS(E29-Scenarios!$D$102),ABS(F29-Scenarios!$D$103),ABS(G29-Scenarios!$D$104))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
@@ -9357,10 +9302,6 @@
         <f>Scenarios!D109</f>
         <v/>
       </c>
-      <c r="H30" s="86">
-        <f>IF(MAX(ABS(C30-Scenarios!$D$105),ABS(D30-Scenarios!$D$106),ABS(E30-Scenarios!$D$107),ABS(F30-Scenarios!$D$108),ABS(G30-Scenarios!$D$109))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="31" ht="42" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
@@ -9388,10 +9329,6 @@
         <f>Scenarios!D114</f>
         <v/>
       </c>
-      <c r="H31" s="86">
-        <f>IF(MAX(ABS(C31-Scenarios!$D$110),ABS(D31-Scenarios!$D$111),ABS(E31-Scenarios!$D$112),ABS(F31-Scenarios!$D$113),ABS(G31-Scenarios!$D$114))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
@@ -9422,10 +9359,6 @@
         <f>Scenarios!D119</f>
         <v/>
       </c>
-      <c r="H32" s="87">
-        <f>IF(MAX(ABS(C32-Scenarios!$D$115),ABS(D32-Scenarios!$D$116),ABS(E32-Scenarios!$D$117),ABS(F32-Scenarios!$D$118),ABS(G32-Scenarios!$D$119))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="33" ht="56" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
@@ -9453,17 +9386,9 @@
         <f>Scenarios!D124</f>
         <v/>
       </c>
-      <c r="H33" s="87">
-        <f>IF(MAX(ABS(C33-Scenarios!$D$120),ABS(D33-Scenarios!$D$121),ABS(E33-Scenarios!$D$122),ABS(F33-Scenarios!$D$123),ABS(G33-Scenarios!$D$124))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
-        <is>
-          <t>driver-based NWC. Delta NWC = prior-year NWC - current-year NWC; added to UFCF (NWC build = cash outflow).</t>
-        </is>
-      </c>
+      <c r="A34" s="26" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
@@ -9491,10 +9416,6 @@
         <f>Scenarios!D129</f>
         <v/>
       </c>
-      <c r="H35" s="87">
-        <f>IF(MAX(ABS(C35-Scenarios!$D$125),ABS(D35-Scenarios!$D$126),ABS(E35-Scenarios!$D$127),ABS(F35-Scenarios!$D$128),ABS(G35-Scenarios!$D$129))&lt;0.5,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -9572,15 +9493,12 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>Scenarios linkage</t>
-        </is>
-      </c>
-      <c r="H40" s="92">
-        <f>IF(COUNTIF(H5:H35,"CHECK")=0,"ALL OK","REVIEW")</f>
-        <v/>
+          <t>Scenarios tie-out</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -9699,16 +9617,12 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
-        <is>
-          <t>funded term debt $0. Operating leases $298,724k current + $1,499,717k non-current = $1,798,441k (ASC 842 debt equivalent).</t>
-        </is>
-      </c>
+      <c r="A52" s="26" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="26" t="inlineStr">
         <is>
-          <t>UFCF pre-interest; ASC 842 lease debt in EV bridge.</t>
+          <t>Enterprise value bridge</t>
         </is>
       </c>
     </row>
@@ -9743,10 +9657,6 @@
         <f>B54/B55</f>
         <v/>
       </c>
-      <c r="H56" s="87">
-        <f>IF(ABS(B56-Scenarios!$D$132)&lt;0.05,"OK","CHECK")</f>
-        <v/>
-      </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
@@ -9780,6 +9690,8 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -9791,6 +9703,7 @@
     <row r="63">
       <c r="A63" s="26" t="n"/>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -9851,6 +9764,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -9935,6 +9849,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10055,6 +9970,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10115,6 +10031,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -10123,11 +10040,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
-        <is>
-          <t>Exit multiple is the Gordon identity - not a peer pick or an average</t>
-        </is>
-      </c>
+      <c r="A81" s="15" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="16" t="inlineStr">
@@ -10184,6 +10097,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -10229,6 +10143,8 @@
         </is>
       </c>
     </row>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -10426,6 +10342,7 @@
       <c r="D1" s="13" t="n"/>
       <c r="E1" s="13" t="n"/>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -10527,6 +10444,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -10544,16 +10462,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>PITCHBOOK PUBCOMPS - daily EV / TTM EBITDA as of 04-Sep-2026 ($000)</t>
+          <t>Peer EV/EBITDA (PitchBook, Sep-2026)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
-        <is>
-          <t>EV/EBITDA is a black formula (I/J). UAA is shown but excluded from averages (negative TTM EBITDA).</t>
-        </is>
-      </c>
+      <c r="A17" s="26" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="113" t="inlineStr">
@@ -10764,6 +10678,7 @@
         <v>407521</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -10817,6 +10732,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -10847,12 +10763,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="107" t="inlineStr">
-        <is>
-          <t>Peer multiples illustrative; terminal value from DCF exit multiple.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A41" s="107" t="n"/>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -10896,52 +10809,29 @@
     <row r="47">
       <c r="A47" s="68" t="inlineStr">
         <is>
-          <t>Rationale for selected exit (Gordon identity, not a peer pick)</t>
+          <t>Selected exit multiple (Gordon growth)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="41" t="inlineStr">
-        <is>
-          <t>/ Selected exit = Gordon TV / FY30 EBITDA. Identity: (UFCF/EBITDA)x(1+g)/(WACC-g). Live formula, not a typed 8.0x</t>
-        </is>
-      </c>
+      <c r="A48" s="41" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="41" t="inlineStr">
-        <is>
-          <t>/ At base WACC ~9.0% and g 2.25% that identity is ~7.4x FY30 EBITDA - not a peer average</t>
-        </is>
-      </c>
+      <c r="A49" s="41" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="41" t="inlineStr">
-        <is>
-          <t>/ PitchBook pubcomps (04-Sep-2026) are the current tape: each multiple is daily EV / TTM EBITDA</t>
-        </is>
-      </c>
+      <c r="A50" s="41" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="41" t="inlineStr">
-        <is>
-          <t>/ That tape is a check, not the exit. A 2.25% g / 15.5% OM year is not today's NKE/WSM multiple</t>
-        </is>
-      </c>
+      <c r="A51" s="41" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="41" t="inlineStr">
-        <is>
-          <t>/ Alo has no EV/EBITDA print. Implied 5.0x is EV/Sales (unclosed $10bn ask / ~$2bn parent sales) - not the FY30 exit</t>
-        </is>
-      </c>
+      <c r="A52" s="41" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="41" t="inlineStr">
-        <is>
-          <t>/ PitchBook LULU is ~4.7x TTM. Gordon ~7.4x is a partial recovery, not a re-rate to WSM ~15x</t>
-        </is>
-      </c>
-    </row>
+      <c r="A53" s="41" t="n"/>
+    </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -11050,6 +10940,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>
@@ -11061,11 +10952,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="inlineStr">
-        <is>
-          <t>Note: pubcomps are PitchBook 04-Sep-2026 (EV/EBITDA = daily EV / TTM EBITDA). UAA excluded from the mean. Selected TV is Gordon implied, not the PitchBook average. Alo EV/EBITDA is n.a.</t>
-        </is>
-      </c>
+      <c r="A63" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -5914,11 +5914,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="26" t="inlineStr">
-        <is>
-          <t>pitch deck Pitch deck reads base/bull scenario columns.</t>
-        </is>
-      </c>
+      <c r="A193" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10137,11 +10133,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="68" t="inlineStr">
-        <is>
-          <t>Sanity check: multiples within +/-1.5 turns?</t>
-        </is>
-      </c>
+      <c r="A94" s="68" t="n"/>
     </row>
     <row r="95"/>
     <row r="96"/>
@@ -10682,7 +10674,7 @@
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
-          <t>ALO YOGA BUILD - no source prints EV/EBITDA (Reuters + Forbes)</t>
+          <t>Alo Yoga implied valuation (reference only)</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10728,7 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Averages (live Excel AVERAGE - shown so TV is not a blended print)</t>
+          <t>Averages</t>
         </is>
       </c>
     </row>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -976,7 +976,7 @@
     </comment>
     <comment ref="F9" authorId="0" shapeId="0">
       <text>
-        <t>Model cross-reference. WACC tab → green cell = rf 4.8% + relevered β × ERP 6.0% Lease-adjusted WACC; base case for DCF and sensitivity.</t>
+        <t>Model cross-reference. WACC tab to green cell = rf 4.8% + relevered β × ERP 6.0% Lease-adjusted WACC; base case for DCF and sensitivity.</t>
       </text>
     </comment>
     <comment ref="F10" authorId="0" shapeId="0">
@@ -1021,17 +1021,17 @@
     </comment>
     <comment ref="F18" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 331,421 ($000) → 4,818,468 ($000) Not % of revenue; DPO ≈ 25.1 days. Working-capital driver; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 331,421 ($000) to 4,818,468 ($000) Not % of revenue; DPO ≈ 25.1 days. Working-capital driver; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="F19" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 211,620 ($000) → 352,469 ($000) 5.1% of revenue (flat). Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 211,620 ($000) to 352,469 ($000) 5.1% of revenue (flat). Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="F20" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 662,982 ($000) → 11,102,600 ($000) 6.0% of revenue (flat). Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 662,982 ($000) to 11,102,600 ($000) 6.0% of revenue (flat). Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
   </commentList>
@@ -1251,7 +1251,7 @@
     </comment>
     <comment ref="E20" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 62,203 ($000) FY25 reference. High-conviction analyst overlay on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 62,203 ($000) FY25 reference. High-conviction analyst overlay on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -1261,7 +1261,7 @@
     </comment>
     <comment ref="E23" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 1,028 ($000) supplemental cash-flow disclosure. ASC 842 lease debt equivalent in capital structure. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 1,028 ($000) supplemental cash-flow disclosure. ASC 842 lease debt equivalent in capital structure. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -1281,17 +1281,17 @@
     </comment>
     <comment ref="E28" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. Revenue Drivers tab → store-channel revenue row. Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. Revenue Drivers tab to store-channel revenue row. Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E29" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. Revenue Drivers tab → e-commerce revenue row. Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. Revenue Drivers tab to e-commerce revenue row. Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. Revenue Drivers tab → other channels revenue row. Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. Revenue Drivers tab to other channels revenue row. Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -1456,32 +1456,32 @@
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 331,421 ($000) → 4,818,468 ($000) Not % of revenue; DPO ≈ 25.1 days. Working-capital driver; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 331,421 ($000) to 4,818,468 ($000) Not % of revenue; DPO ≈ 25.1 days. Working-capital driver; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E25" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 331,421 ($000) → 11,102,600 ($000) Implied ~3.0% of revenue (= 331,421 ÷ 11,102,600);… High-conviction analyst overlay on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 331,421 ($000) to 11,102,600 ($000) Implied ~3.0% of revenue (= 331,421 ÷ 11,102,600);… High-conviction analyst overlay on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E26" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 211,620 ($000) → 352,469 ($000) 5.1% of revenue (flat). Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 211,620 ($000) to 352,469 ($000) 5.1% of revenue (flat). Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E27" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 211,620 ($000) → 352,469 ($000) 5.1% of revenue (flat). High-conviction analyst overlay on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 211,620 ($000) to 352,469 ($000) 5.1% of revenue (flat). High-conviction analyst overlay on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E28" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 662,982 ($000) → 11,102,600 ($000) 6.0% of revenue (flat). Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 662,982 ($000) to 11,102,600 ($000) 6.0% of revenue (flat). Operating assumption with durable cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E29" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. → 662,982 ($000) → 11,102,600 ($000) 6.0% of revenue (flat). High-conviction analyst overlay on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K anchor. to 662,982 ($000) to 11,102,600 ($000) 6.0% of revenue (flat). High-conviction analyst overlay on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -1541,27 +1541,27 @@
     </comment>
     <comment ref="E99" authorId="0" shapeId="0">
       <text>
-        <t>Damodaran implied ERP reference. WACC tab → green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline. Source: https://www.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html</t>
+        <t>Damodaran implied ERP reference. WACC tab to green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline. Source: https://www.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html</t>
       </text>
     </comment>
     <comment ref="E100" authorId="0" shapeId="0">
       <text>
-        <t>0.1 WACC tab → green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline.</t>
+        <t>0.1 WACC tab to green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline.</t>
       </text>
     </comment>
     <comment ref="E101" authorId="0" shapeId="0">
       <text>
-        <t>0.105 WACC tab → green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline.</t>
+        <t>0.105 WACC tab to green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline.</t>
       </text>
     </comment>
     <comment ref="E102" authorId="0" shapeId="0">
       <text>
-        <t>0.11 WACC tab → green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline.</t>
+        <t>0.11 WACC tab to green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline.</t>
       </text>
     </comment>
     <comment ref="E103" authorId="0" shapeId="0">
       <text>
-        <t>0.115 WACC tab → green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline.</t>
+        <t>0.115 WACC tab to green WACC cell ~9.0%. High-conviction analyst overlay on reported baseline.</t>
       </text>
     </comment>
   </commentList>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Women's mix fades 62.5%→60% as men's penetrates; FY25.</t>
+          <t>Women's mix fades 62.5% to 60% as men's penetrates; FY25.</t>
         </is>
       </c>
       <c r="J49" s="126" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Men's mix rises 24.5%→27%; FY25 men's grew 4%.</t>
+          <t>Men's mix rises 24.5% to 27%; FY25 men's grew 4%.</t>
         </is>
       </c>
       <c r="J50" s="126" t="inlineStr">

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -9934,7 +9934,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -10101,23 +10101,23 @@
         <v>0.5659999999999999</v>
       </c>
       <c r="E7" s="136">
-        <f>Scenarios!$H$14</f>
+        <f>Scenarios!$F$14</f>
         <v/>
       </c>
       <c r="F7" s="136">
-        <f>Scenarios!$H$14</f>
+        <f>Scenarios!$F$14</f>
         <v/>
       </c>
       <c r="G7" s="136">
-        <f>Scenarios!$H$14</f>
+        <f>Scenarios!$F$14</f>
         <v/>
       </c>
       <c r="H7" s="136">
-        <f>Scenarios!$H$14</f>
+        <f>Scenarios!$F$14</f>
         <v/>
       </c>
       <c r="I7" s="136">
-        <f>Scenarios!$H$14</f>
+        <f>Scenarios!$F$14</f>
         <v/>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="138">
-        <f>Scenarios!$H$7</f>
+        <f>Scenarios!$F$7</f>
         <v/>
       </c>
       <c r="F10" s="22" t="n">
@@ -10355,23 +10355,23 @@
         </is>
       </c>
       <c r="E15" s="136">
-        <f>Scenarios!$H$12</f>
+        <f>Scenarios!$F$12</f>
         <v/>
       </c>
       <c r="F15" s="136">
-        <f>Scenarios!$H$12</f>
+        <f>Scenarios!$F$12</f>
         <v/>
       </c>
       <c r="G15" s="136">
-        <f>Scenarios!$H$12</f>
+        <f>Scenarios!$F$12</f>
         <v/>
       </c>
       <c r="H15" s="136">
-        <f>Scenarios!$H$12</f>
+        <f>Scenarios!$F$12</f>
         <v/>
       </c>
       <c r="I15" s="136">
-        <f>Scenarios!$H$12</f>
+        <f>Scenarios!$F$12</f>
         <v/>
       </c>
     </row>
@@ -10419,23 +10419,23 @@
         </is>
       </c>
       <c r="E17" s="136">
-        <f>Scenarios!$H$13</f>
+        <f>Scenarios!$F$13</f>
         <v/>
       </c>
       <c r="F17" s="136">
-        <f>Scenarios!$H$13</f>
+        <f>Scenarios!$F$13</f>
         <v/>
       </c>
       <c r="G17" s="136">
-        <f>Scenarios!$H$13</f>
+        <f>Scenarios!$F$13</f>
         <v/>
       </c>
       <c r="H17" s="136">
-        <f>Scenarios!$H$13</f>
+        <f>Scenarios!$F$13</f>
         <v/>
       </c>
       <c r="I17" s="136">
-        <f>Scenarios!$H$13</f>
+        <f>Scenarios!$F$13</f>
         <v/>
       </c>
     </row>
@@ -10743,23 +10743,23 @@
         <v>0.051</v>
       </c>
       <c r="E26" s="136">
-        <f>Scenarios!$H$19</f>
+        <f>Scenarios!$F$19</f>
         <v/>
       </c>
       <c r="F26" s="136">
-        <f>Scenarios!$H$19</f>
+        <f>Scenarios!$F$19</f>
         <v/>
       </c>
       <c r="G26" s="136">
-        <f>Scenarios!$H$19</f>
+        <f>Scenarios!$F$19</f>
         <v/>
       </c>
       <c r="H26" s="136">
-        <f>Scenarios!$H$19</f>
+        <f>Scenarios!$F$19</f>
         <v/>
       </c>
       <c r="I26" s="136">
-        <f>Scenarios!$H$19</f>
+        <f>Scenarios!$F$19</f>
         <v/>
       </c>
     </row>
@@ -10823,23 +10823,23 @@
         <v>0.06</v>
       </c>
       <c r="E28" s="136">
-        <f>Scenarios!$H$20</f>
+        <f>Scenarios!$F$20</f>
         <v/>
       </c>
       <c r="F28" s="136">
-        <f>Scenarios!$H$20</f>
+        <f>Scenarios!$F$20</f>
         <v/>
       </c>
       <c r="G28" s="136">
-        <f>Scenarios!$H$20</f>
+        <f>Scenarios!$F$20</f>
         <v/>
       </c>
       <c r="H28" s="136">
-        <f>Scenarios!$H$20</f>
+        <f>Scenarios!$F$20</f>
         <v/>
       </c>
       <c r="I28" s="136">
-        <f>Scenarios!$H$20</f>
+        <f>Scenarios!$F$20</f>
         <v/>
       </c>
     </row>
@@ -11093,23 +11093,23 @@
         </is>
       </c>
       <c r="E37" s="147">
-        <f>1/(1+Scenarios!$H$9)^E36</f>
+        <f>1/(1+Scenarios!$F$9)^E36</f>
         <v/>
       </c>
       <c r="F37" s="147">
-        <f>1/(1+Scenarios!$H$9)^F36</f>
+        <f>1/(1+Scenarios!$F$9)^F36</f>
         <v/>
       </c>
       <c r="G37" s="147">
-        <f>1/(1+Scenarios!$H$9)^G36</f>
+        <f>1/(1+Scenarios!$F$9)^G36</f>
         <v/>
       </c>
       <c r="H37" s="147">
-        <f>1/(1+Scenarios!$H$9)^H36</f>
+        <f>1/(1+Scenarios!$F$9)^H36</f>
         <v/>
       </c>
       <c r="I37" s="147">
-        <f>1/(1+Scenarios!$H$9)^I36</f>
+        <f>1/(1+Scenarios!$F$9)^I36</f>
         <v/>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="D43" s="136">
-        <f>Scenarios!$H$10</f>
+        <f>Scenarios!$F$10</f>
         <v/>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
         </is>
       </c>
       <c r="D45" s="138">
-        <f>I35*(1+Scenarios!$H$10)/(Scenarios!$H$9-Scenarios!$H$10)</f>
+        <f>I35*(1+Scenarios!$F$10)/(Scenarios!$F$9-Scenarios!$F$10)</f>
         <v/>
       </c>
     </row>
@@ -11227,7 +11227,7 @@
         </is>
       </c>
       <c r="D47" s="148">
-        <f>I35/D44*(1+Scenarios!$H$10)/(Scenarios!$H$9-Scenarios!$H$10)</f>
+        <f>I35/D44*(1+Scenarios!$F$10)/(Scenarios!$F$9-Scenarios!$F$10)</f>
         <v/>
       </c>
     </row>
@@ -11238,7 +11238,7 @@
         </is>
       </c>
       <c r="D48" s="138">
-        <f>D45/(1+Scenarios!$H$9)^I36</f>
+        <f>D45/(1+Scenarios!$F$9)^I36</f>
         <v/>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
         </is>
       </c>
       <c r="D84" s="138">
-        <f>D83/(1+Scenarios!$H$9)^I36</f>
+        <f>D83/(1+Scenarios!$F$9)^I36</f>
         <v/>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -423,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="164">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -875,6 +875,15 @@
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -960,546 +969,6 @@
   <commentList>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
-        <t>FRED macro anchor. AAA blue-chip proxy; for unlevered FCF. Source: https://fred.stlouisfed.org/series/DGS10</t>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0" shapeId="0">
-      <text>
-        <t>Damodaran implied ERP reference. Conservative ERP overlay vs implied market ERP. Source: https://www.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html</t>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0">
-      <text>
-        <t>Q2 FY26 management guidance. Cash tax assumption for Hamada relever and NOPAT. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>NASDAQ last-sale cross-check. Market equity input for capital structure and beta relever. Source: https://www.nasdaq.com/market-activity/stocks/lulu</t>
-      </text>
-    </comment>
-    <comment ref="D9" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D10" authorId="0" shapeId="0">
-      <text>
-        <t>Share price row × shares outstanding row on this tab. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="D11" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. ASC 842 lease debt equivalent in capital structure. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. ASC 842 lease debt equivalent in capital structure. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D16" authorId="0" shapeId="0">
-      <text>
-        <t>Yahoo Finance market-data cross-check. Hamada beta chain; discount rate input. Source: https://finance.yahoo.com/quote/LULU/key-statistics/</t>
-      </text>
-    </comment>
-    <comment ref="D17" authorId="0" shapeId="0">
-      <text>
-        <t>Yahoo Finance market-data cross-check. ASC 842 lease debt equivalent in capital structure. Source: https://finance.yahoo.com/quote/LULU/key-statistics/</t>
-      </text>
-    </comment>
-    <comment ref="D18" authorId="0" shapeId="0">
-      <text>
-        <t>Yahoo Finance market-data cross-check. Market equity input for capital structure and beta relever. Source: https://finance.yahoo.com/quote/LULU/key-statistics/</t>
-      </text>
-    </comment>
-    <comment ref="D19" authorId="0" shapeId="0">
-      <text>
-        <t>Yahoo Finance market-data cross-check. Formula: D/E = E[Yahoo debt mrq] ÷ E[Yahoo market cap]. Market equity input for capital structure and beta relever. Source: https://finance.yahoo.com/quote/LULU/key-statistics/</t>
-      </text>
-    </comment>
-    <comment ref="D20" authorId="0" shapeId="0">
-      <text>
-        <t>Yahoo Finance market-data cross-check. on reported baseline. Source: https://finance.yahoo.com/quote/LULU/key-statistics/</t>
-      </text>
-    </comment>
-    <comment ref="D21" authorId="0" shapeId="0">
-      <text>
-        <t>Yahoo Finance market-data cross-check. βu = E[βL] ÷ (1 + 0.70 × E[D/E Yahoo]). Hamada beta chain; discount rate input.</t>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="0" shapeId="0">
-      <text>
-        <t>D/E = E[FY25 lease debt] ÷ E[market cap]. ASC 842 lease debt equivalent in capital structure.</t>
-      </text>
-    </comment>
-    <comment ref="D23" authorId="0" shapeId="0">
-      <text>
-        <t>Damodaran implied ERP reference. Hamada beta chain; discount rate input. Source: https://www.stern.nyu.edu/~adamodar/New_Home_Page/datafile/Betas.html</t>
-      </text>
-    </comment>
-    <comment ref="D24" authorId="0" shapeId="0">
-      <text>
-        <t>YAHOO KEY STATISTICS; βL + debt + equity on ONE page (No vendor publishes the D/E… Hamada beta chain; discount rate input.</t>
-      </text>
-    </comment>
-    <comment ref="D30" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. ASC 842 lease debt equivalent in capital structure. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D34" authorId="0" shapeId="0">
-      <text>
-        <t>Equity weight = market cap ÷ (market cap + lease debt). on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="D35" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Debt weight = lease liabilities ÷ (market cap + lease debt). ASC 842 lease debt equivalent in capital structure. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Analyst</author>
-  </authors>
-  <commentList>
-    <comment ref="F4" authorId="0" shapeId="0">
-      <text>
-        <t>Q2 FY26 management guidance. cash-flow read-through. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-      </text>
-    </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
-      <text>
-        <t>StockAnalysis consensus forecast. cash-flow read-through. Source: https://stockanalysis.com/stocks/lulu/statistics/</t>
-      </text>
-    </comment>
-    <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>Q2 FY26 management guidance. cash-flow read-through. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>Q2 FY26 management guidance. on reported baseline. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="F9" authorId="0" shapeId="0">
-      <text>
-        <t>WACC tab to green cell = rf 4.8% + relevered β × ERP 6.0% Lease-adjusted WACC; base case for DCF and sensitivity.</t>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
-      <text>
-        <t>FRED macro anchor. on reported baseline. Source: https://fred.stlouisfed.org/series/GDPC1</t>
-      </text>
-    </comment>
-    <comment ref="F11" authorId="0" shapeId="0">
-      <text>
-        <t>Q2 FY26 management guidance. Cash tax assumption for Hamada relever and NOPAT. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-      </text>
-    </comment>
-    <comment ref="F12" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="F13" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. FY25 actual (10-K) 680.8 / 11,102.6 = 6.1% FY26 capex (10-K) FY26 sales (earnings) 7.0%… cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="F14" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. 56.6% of revenue (gross margin). cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not % of revenue; DSO (days), flat ~6.3. ; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="F16" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not % of revenue; DIO (days). ; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="F17" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not % of revenue; DIO −1 day/yr (−5 days FY26–30). ; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="F18" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 331,421 ($000) to 4,818,468 ($000) Not % of revenue; DPO ≈ 25.1 days. ; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="F19" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 211,620 ($000) to 352,469 ($000) 5.1% of revenue (flat). cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="F20" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 662,982 ($000) to 11,102,600 ($000) 6.0% of revenue (flat). cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Analyst</author>
-  </authors>
-  <commentList>
-    <comment ref="C7" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C19" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C24" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C25" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C26" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C27" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C28" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C31" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C32" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C33" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C34" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C38" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C39" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C40" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C41" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C45" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C46" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C47" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C48" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C49" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C50" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C51" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C55" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="C56" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Analyst</author>
-  </authors>
-  <commentList>
-    <comment ref="E9" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not consolidated EBIT margin; EBIT ÷ store revenue only (cf. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not consolidated EBIT margin; EBIT ÷ e-commerce revenue only (cf. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not consolidated EBIT margin; EBIT ÷ other-channel revenue only (cf. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
-      <text>
-        <t>Q2 FY26 management guidance. Cash tax assumption for Hamada relever and NOPAT. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-      </text>
-    </comment>
-    <comment ref="E13" authorId="0" shapeId="0">
-      <text>
-        <t>Driver tab linkage. Amortization period if R&amp;D capitalized (3–5 yr convention). on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E16" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E18" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E19" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. One-off legal/M&amp;A fees in SG&amp;A; none identified FY25. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E20" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 62,203 ($000) FY25 reference. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E21" authorId="0" shapeId="0">
-      <text>
-        <t>Driver tab linkage. Sum of reported EBIT + Phase 1 add-backs on this tab. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E23" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 1,028 ($000) supplemental cash-flow disclosure. ASC 842 lease debt equivalent in capital structure. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E24" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. R&amp;D / software capitalization; LULU immaterial; held at $0. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E25" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Amortization of prior capitalized intangibles; netted in D&amp;A line. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E26" authorId="0" shapeId="0">
-      <text>
-        <t>Driver tab linkage. Phase 1 + lease interest + R&amp;D cap − amortization. ASC 842 lease debt equivalent in capital structure.</t>
-      </text>
-    </comment>
-    <comment ref="E28" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Revenue Drivers tab to store-channel revenue row. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E29" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Revenue Drivers tab to e-commerce revenue row. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E30" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Revenue Drivers tab to other channels revenue row. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E31" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not consolidated EBIT margin; store EBIT ÷ store revenue only. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E32" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not consolidated EBIT margin; e-commerce EBIT ÷ e-commerce revenue only. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E33" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not consolidated EBIT margin; other-channel EBIT ÷ other revenue only. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E34" authorId="0" shapeId="0">
-      <text>
-        <t>Driver tab linkage. Sum of sector EBIT rows. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E35" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Channel EBIT subtotal (Phase 3). on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E36" authorId="0" shapeId="0">
-      <text>
-        <t>Scenarios tab: base-case EBIT (forecast) FY25: Phase 1–2 formula. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E39" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. t_operating = (tax + interest×30%) ÷ (EBT + interest). Cash tax assumption for Hamada relever and NOPAT. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E40" authorId="0" shapeId="0">
-      <text>
-        <t>Driver tab linkage. Normalized EBIT × t_operating; unlevered tax (no debt shield). on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E41" authorId="0" shapeId="0">
-      <text>
-        <t>Driver tab linkage. EBIT_norm − unlevered tax. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E45" authorId="0" shapeId="0">
-      <text>
-        <t>EBIT = 13.2% × rev + tariff; SBC stays expensed (flag = 0). DCF unchanged. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E46" authorId="0" shapeId="0">
-      <text>
-        <t>R&amp;D/software expensed in full each year ($0 for LULU). DCF unchanged. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E47" authorId="0" shapeId="0">
-      <text>
-        <t>Rent in opex; no implied lease-interest add-back. DCF unchanged. ASC 842 lease debt equivalent in capital structure.</t>
-      </text>
-    </comment>
-    <comment ref="E48" authorId="0" shapeId="0">
-      <text>
-        <t>DCF uses consolidated 13.2% on total revenue (+ tariff). DCF unchanged. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E49" authorId="0" shapeId="0">
-      <text>
-        <t>NOPAT = EBIT × (1 − 30%) flat sc_tax. NOPAT = EBIT × (1 − t_operating) — same EBIT, slightly higher NOPAT. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E50" authorId="0" shapeId="0">
-      <text>
-        <t>EBIT = Rev × 13.2% only (no refund). + $134,500k in FY26 — DCF uses this. on reported baseline.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Analyst</author>
-  </authors>
-  <commentList>
-    <comment ref="D3" authorId="0" shapeId="0">
-      <text>
         <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
@@ -1508,29 +977,9 @@
         <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0">
-      <text>
-        <t>Q2 FY26 management guidance. Also: cash-flow read-through. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. 56.6% of revenue (gross margin). cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
     <comment ref="E8" authorId="0" shapeId="0">
       <text>
         <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E9" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Also: cash-flow read-through. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733 Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E11" authorId="0" shapeId="0">
@@ -1541,126 +990,6 @@
     <comment ref="E12" authorId="0" shapeId="0">
       <text>
         <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E15" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. FY25 actual (10-K) 680.8 / 11,102.6 = 6.1% FY26 capex (10-K) FY26 sales (earnings) 7.0%… cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E20" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not % of revenue; DSO (days), flat ~6.3. ; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E21" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Implied ~1.7% of revenue (= 190,657 ÷ 11,102,600); not a direct % plug. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E22" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not % of revenue; DIO (days). ; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E23" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not % of revenue; Inventories_t = (DIO_t ÷ 365) × COGS_t. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E24" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 331,421 ($000) to 4,818,468 ($000) Not % of revenue; DPO ≈ 25.1 days. ; supports unlevered FCF bridge. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E25" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 331,421 ($000) to 11,102,600 ($000) Implied ~3.0% of revenue (= 331,421 ÷ 11,102,600);… on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E26" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 211,620 ($000) to 352,469 ($000) 5.1% of revenue (flat). cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E27" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 211,620 ($000) to 352,469 ($000) 5.1% of revenue (flat). on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E28" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 662,982 ($000) to 11,102,600 ($000) 6.0% of revenue (flat). cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E29" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. to 662,982 ($000) to 11,102,600 ($000) 6.0% of revenue (flat). on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E30" authorId="0" shapeId="0">
-      <text>
-        <t>Scenarios tab: AR + inventory + prepaids Not one % of revenue; sum of line items. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E31" authorId="0" shapeId="0">
-      <text>
-        <t>Scenarios tab: AP + accrued liabilities Not one % of revenue; sum of line items. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E32" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. Not one % of revenue; net balance. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="E33" authorId="0" shapeId="0">
-      <text>
-        <t>Scenarios tab: NWC roll-forward (driver schedule) Not % of revenue; $ change year-over-year. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="D43" authorId="0" shapeId="0">
-      <text>
-        <t>FRED macro anchor. on reported baseline. Source: https://fred.stlouisfed.org/series/GDPC1</t>
-      </text>
-    </comment>
-    <comment ref="D50" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D51" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. ASC 842 lease debt equivalent in capital structure. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D55" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>NASDAQ last-sale cross-check. Market equity input for capital structure and beta relever. Source: https://www.nasdaq.com/market-activity/stocks/lulu</t>
-      </text>
-    </comment>
-    <comment ref="D82" authorId="0" shapeId="0">
-      <text>
-        <t>DCF: Gordon implied exit (TV / FY30 EBITDA) No peer on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="E98" authorId="0" shapeId="0">
-      <text>
-        <t>FRED macro anchor. Lease-adjusted WACC; base case for DCF and sensitivity. Source: https://fred.stlouisfed.org/series/GDPC1</t>
-      </text>
-    </comment>
-    <comment ref="E99" authorId="0" shapeId="0">
-      <text>
-        <t>Damodaran implied ERP reference. WACC tab to green WACC cell ~9.0%. on reported baseline. Source: https://www.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html</t>
       </text>
     </comment>
     <comment ref="E100" authorId="0" shapeId="0">
@@ -1687,155 +1016,20 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Analyst</author>
   </authors>
   <commentList>
-    <comment ref="D4" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="0" shapeId="0">
-      <text>
-        <t>↳ DCF base case on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>Q2 FY26 management guidance. ; supports unlevered FCF bridge. Source: https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D9" authorId="0" shapeId="0">
-      <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="D10" authorId="0" shapeId="0">
-      <text>
-        <t>NASDAQ last-sale cross-check. Market equity input for capital structure and beta relever. Source: https://www.nasdaq.com/market-activity/stocks/lulu</t>
-      </text>
-    </comment>
     <comment ref="D18" authorId="0" shapeId="0">
       <text>
         <t>Source on reported baseline.</t>
       </text>
     </comment>
-    <comment ref="D19" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D20" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D21" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D22" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D23" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D24" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D25" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D26" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D27" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D28" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D29" authorId="0" shapeId="0">
-      <text>
-        <t>PitchBook comps set (EV / TTM EBITDA). No public HTML. Peer multiple reference; not the selected terminal value.</t>
-      </text>
-    </comment>
-    <comment ref="D33" authorId="0" shapeId="0">
-      <text>
-        <t>Reuters: Alo parent $10bn Moelis ask Also: Reuters: Alo 2023 process; no deal on reported baseline. Source: https://www.reuters.com/markets/deals/alo-yoga-parent-seeks-investment-10-bln-valuation-sources-2023-10-30/</t>
-      </text>
-    </comment>
-    <comment ref="D34" authorId="0" shapeId="0">
-      <text>
-        <t>Forbes: Color Image nearly $2bn sales on reported baseline. Source: https://www.forbes.com/sites/jemimamcevoy/2025/04/01/the-founders-of-this-lululemon-rival-are-worth-nearly-5-billion-each/</t>
-      </text>
-    </comment>
-    <comment ref="D35" authorId="0" shapeId="0">
-      <text>
-        <t>Comps: Alo ask / parent sales No on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="D36" authorId="0" shapeId="0">
-      <text>
-        <t>None — no EBITDA source on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="D39" authorId="0" shapeId="0">
-      <text>
-        <t>Derived: Excel AVERAGE of the seven core prints Each E cell is I/J from the PitchBook extract. on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="D40" authorId="0" shapeId="0">
-      <text>
-        <t>Derived: Excel AVERAGE of every positive-EBITDA row UAA omitted because TTM EBITDA is negative. on reported baseline.</t>
-      </text>
-    </comment>
     <comment ref="D56" authorId="0" shapeId="0">
       <text>
         <t>Source on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="D57" authorId="0" shapeId="0">
-      <text>
-        <t>StockAnalysis consensus forecast. Lo: Hi: on reported baseline. Source: https://stockanalysis.com/stocks/lulu/statistics/</t>
-      </text>
-    </comment>
-    <comment ref="D58" authorId="0" shapeId="0">
-      <text>
-        <t>DCF: Gordon implied exit (TV / FY30 EBITDA) No peer on reported baseline.</t>
-      </text>
-    </comment>
-    <comment ref="D59" authorId="0" shapeId="0">
-      <text>
-        <t>StockAnalysis consensus forecast. Lo: Hi: on reported baseline. Source: https://stockanalysis.com/stocks/lulu/statistics/</t>
-      </text>
-    </comment>
-    <comment ref="D62" authorId="0" shapeId="0">
-      <text>
-        <t>NASDAQ last-sale cross-check. on reported baseline. Source: https://www.nasdaq.com/market-activity/stocks/lulu</t>
       </text>
     </comment>
   </commentList>
@@ -2192,7 +1386,7 @@
     <row r="16">
       <c r="B16" s="5" t="n"/>
     </row>
-    <row r="17" ht="36" customHeight="1">
+    <row r="17" ht="15" customHeight="1">
       <c r="B17" s="10" t="n"/>
     </row>
     <row r="18"/>
@@ -2203,28 +1397,28 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="B20" s="10" t="inlineStr">
         <is>
           <t>SEC EDGAR filings, CIK 0001397187 (Form 10-K, FY2025)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="15" customHeight="1">
       <c r="B21" s="10" t="inlineStr">
         <is>
           <t>FY2025 Form 10-K (ended Feb 1, 2026)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Market data &amp; Q2 FY2026 results (Sep 3, 2026 earnings release)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="15" customHeight="1">
       <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Current share price (NASDAQ: LULU)</t>
@@ -2252,7 +1446,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2298,7 +1492,7 @@
           <t>Current 10Y UST</t>
         </is>
       </c>
-      <c r="C3" s="128" t="inlineStr">
+      <c r="C3" s="164" t="inlineStr">
         <is>
           <t>FRED: 10Y Treasury (DGS10)</t>
         </is>
@@ -2318,7 +1512,7 @@
           <t>Damodaran ERP + overlay</t>
         </is>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="164" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
@@ -2338,7 +1532,7 @@
           <t>Q2 FY26 guide ~30%</t>
         </is>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="164" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
@@ -2366,7 +1560,7 @@
           <t>NASDAQ last sale</t>
         </is>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="164" t="inlineStr">
         <is>
           <t>NASDAQ LULU last sale (current price)</t>
         </is>
@@ -2386,7 +1580,7 @@
           <t>FY25 10-K shares</t>
         </is>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: shares outstanding</t>
         </is>
@@ -2406,7 +1600,7 @@
           <t>Px × shares</t>
         </is>
       </c>
-      <c r="C10" s="126" t="inlineStr">
+      <c r="C10" s="165" t="inlineStr">
         <is>
           <t>WACC tab: price × shares</t>
         </is>
@@ -2427,7 +1621,7 @@
           <t>FY25 lease debt (10-K)</t>
         </is>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: operating lease liabilities</t>
         </is>
@@ -2462,7 +1656,7 @@
           <t>Total debt equivalents</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C13" s="166" t="inlineStr">
         <is>
           <t>Lease + funded debt (above)</t>
         </is>
@@ -2511,7 +1705,7 @@
           <t>Yahoo total debt</t>
         </is>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="164" t="inlineStr">
         <is>
           <t>Yahoo Finance: LULU Total Debt (mrq)</t>
         </is>
@@ -2531,7 +1725,7 @@
           <t>Yahoo Market Cap = $11.14B on the same.</t>
         </is>
       </c>
-      <c r="C18" s="128" t="inlineStr">
+      <c r="C18" s="164" t="inlineStr">
         <is>
           <t>Yahoo Finance: LULU Market Cap</t>
         </is>
@@ -2551,7 +1745,7 @@
           <t>Unlever D/E = Yahoo debt (mrq) ÷ Yahoo.</t>
         </is>
       </c>
-      <c r="C19" s="128" t="inlineStr">
+      <c r="C19" s="164" t="inlineStr">
         <is>
           <t>Yahoo Finance: debt (mrq) ÷ market cap</t>
         </is>
@@ -2572,7 +1766,7 @@
           <t>Yahoo Total Debt/Equity (mrq) = 44.69% is book.</t>
         </is>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="164" t="inlineStr">
         <is>
           <t>Yahoo Finance: Total Debt/Equity (mrq)</t>
         </is>
@@ -2592,7 +1786,7 @@
           <t>βu = 0.86 ÷ [1 + 0.70 ×.</t>
         </is>
       </c>
-      <c r="C21" s="126" t="inlineStr">
+      <c r="C21" s="165" t="inlineStr">
         <is>
           <t>WACC tab: Hamada unlever (Yahoo market D/E)</t>
         </is>
@@ -2613,7 +1807,7 @@
           <t>FY25 lease D/E</t>
         </is>
       </c>
-      <c r="C22" s="126" t="inlineStr">
+      <c r="C22" s="165" t="inlineStr">
         <is>
           <t>WACC tab: FY25 lease debt / market equity</t>
         </is>
@@ -2634,7 +1828,7 @@
           <t>Benchmark only: Damodaran unlevered Retail (Special Lines) βu.</t>
         </is>
       </c>
-      <c r="C23" s="128" t="inlineStr">
+      <c r="C23" s="164" t="inlineStr">
         <is>
           <t>Damodaran: US betas by sector (Jan 2026)</t>
         </is>
@@ -2654,7 +1848,7 @@
           <t>Relevered β</t>
         </is>
       </c>
-      <c r="C24" s="126" t="inlineStr">
+      <c r="C24" s="165" t="inlineStr">
         <is>
           <t>WACC tab: Hamada relever (total D/E incl. leases)</t>
         </is>
@@ -2664,7 +1858,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="150" customHeight="1">
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="26" t="n"/>
     </row>
     <row r="26">
@@ -2789,7 +1983,7 @@
           <t>Debt weight</t>
         </is>
       </c>
-      <c r="C35" s="128" t="inlineStr">
+      <c r="C35" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: operating lease liabilities</t>
         </is>
@@ -2836,7 +2030,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2914,7 +2107,7 @@
           <t>Q2 FY26 rev guide</t>
         </is>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="164" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release</t>
         </is>
@@ -2940,7 +2133,7 @@
           <t>2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast.</t>
         </is>
       </c>
-      <c r="C5" s="128" t="inlineStr">
+      <c r="C5" s="164" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU 3Y revenue forecast</t>
         </is>
@@ -2966,7 +2159,7 @@
           <t>Q2 FY26 run-rate OM</t>
         </is>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="164" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs</t>
         </is>
@@ -2992,7 +2185,7 @@
           <t>FY26 tariff refund</t>
         </is>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="164" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
         </is>
@@ -3018,7 +2211,7 @@
           <t>Partial OM recovery</t>
         </is>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: Operating margin 19.9% (one hit)</t>
         </is>
@@ -3044,7 +2237,7 @@
           <t>Links to WACC tab</t>
         </is>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="164" t="inlineStr">
         <is>
           <t>WACC tab: CAPM build</t>
         </is>
@@ -3071,7 +2264,7 @@
           <t>FRED GDPC1 ~2.1%</t>
         </is>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="164" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -3097,7 +2290,7 @@
           <t>Q2 FY26 guide ~30%</t>
         </is>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="164" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
@@ -3123,7 +2316,7 @@
           <t>FY25 D&amp;A / sales</t>
         </is>
       </c>
-      <c r="C12" s="128" t="inlineStr">
+      <c r="C12" s="164" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)</t>
         </is>
@@ -3138,7 +2331,7 @@
         <v>0.045</v>
       </c>
     </row>
-    <row r="13" ht="150" customHeight="1">
+    <row r="13" ht="15" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Capex % of revenue</t>
@@ -3149,7 +2342,7 @@
           <t>Capex fade to 5.5%</t>
         </is>
       </c>
-      <c r="C13" s="128" t="inlineStr">
+      <c r="C13" s="164" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
         </is>
@@ -3164,7 +2357,7 @@
         <v>0.045</v>
       </c>
     </row>
-    <row r="14" ht="112" customHeight="1">
+    <row r="14" ht="15" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
@@ -3175,7 +2368,7 @@
           <t>Flat vs FY25</t>
         </is>
       </c>
-      <c r="C14" s="128" t="inlineStr">
+      <c r="C14" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
         </is>
@@ -3190,7 +2383,7 @@
         <v>0.575</v>
       </c>
     </row>
-    <row r="15" ht="150" customHeight="1">
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>DSO (days) - flat vs FY25</t>
@@ -3201,7 +2394,7 @@
           <t>Not % of revenue; DSO (days), flat ~6.3..</t>
         </is>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
@@ -3216,7 +2409,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="16" ht="140" customHeight="1">
+    <row r="16" ht="15" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>FY25 DIO anchor (days)</t>
@@ -3227,7 +2420,7 @@
           <t>FY25 DIO −1d/yr</t>
         </is>
       </c>
-      <c r="C16" s="128" t="inlineStr">
+      <c r="C16" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories &amp; COGS</t>
         </is>
@@ -3242,7 +2435,7 @@
         <v>128.8</v>
       </c>
     </row>
-    <row r="17" ht="70" customHeight="1">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>DIO decline (days / forecast yr)</t>
@@ -3253,7 +2446,7 @@
           <t>−1 day / yr</t>
         </is>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: inventory &amp; markdown outlook</t>
         </is>
@@ -3268,7 +2461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="84" customHeight="1">
+    <row r="18" ht="15" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>DPO (days) - flat vs FY25</t>
@@ -3279,7 +2472,7 @@
           <t>Not % of revenue; DPO (days), flat ~25.1..</t>
         </is>
       </c>
-      <c r="C18" s="128" t="inlineStr">
+      <c r="C18" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
         </is>
@@ -3294,7 +2487,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="19" ht="84" customHeight="1">
+    <row r="19" ht="15" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Prepaid expenses (% of revenue)</t>
@@ -3305,7 +2498,7 @@
           <t>FY25 prepaids % rev</t>
         </is>
       </c>
-      <c r="C19" s="128" t="inlineStr">
+      <c r="C19" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
@@ -3320,7 +2513,7 @@
         <v>0.051</v>
       </c>
     </row>
-    <row r="20" ht="84" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Accrued liabilities (% of revenue)</t>
@@ -3331,7 +2524,7 @@
           <t>FY25 accrued % rev</t>
         </is>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
@@ -6505,7 +5698,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -6648,7 +5840,7 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J6" s="126" t="inlineStr">
+      <c r="J6" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
         </is>
@@ -6685,7 +5877,7 @@
           <t>Store openings skew to China (+20 FY26) vs.</t>
         </is>
       </c>
-      <c r="J7" s="128" t="inlineStr">
+      <c r="J7" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
         </is>
@@ -6722,7 +5914,7 @@
           <t>Closures assume 2–3 per mature region annually as.</t>
         </is>
       </c>
-      <c r="J8" s="128" t="inlineStr">
+      <c r="J8" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
         </is>
@@ -6767,7 +5959,7 @@
           <t>Simple roll-forward: where you started, plus openings, minus.</t>
         </is>
       </c>
-      <c r="J9" s="126" t="inlineStr">
+      <c r="J9" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
         </is>
@@ -6812,7 +6004,7 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J10" s="126" t="inlineStr">
+      <c r="J10" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
         </is>
@@ -6849,7 +6041,7 @@
           <t>Store openings skew to China (+20 FY26) vs.</t>
         </is>
       </c>
-      <c r="J11" s="128" t="inlineStr">
+      <c r="J11" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
         </is>
@@ -6886,7 +6078,7 @@
           <t>Closures assume 2–3 per mature region annually as.</t>
         </is>
       </c>
-      <c r="J12" s="128" t="inlineStr">
+      <c r="J12" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
         </is>
@@ -6931,7 +6123,7 @@
           <t>Simple roll-forward: where you started, plus openings, minus.</t>
         </is>
       </c>
-      <c r="J13" s="126" t="inlineStr">
+      <c r="J13" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
         </is>
@@ -6976,7 +6168,7 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J14" s="126" t="inlineStr">
+      <c r="J14" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
         </is>
@@ -7013,7 +6205,7 @@
           <t>Store openings skew to China (+20 FY26) vs.</t>
         </is>
       </c>
-      <c r="J15" s="128" t="inlineStr">
+      <c r="J15" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
         </is>
@@ -7050,7 +6242,7 @@
           <t>Closures assume 2–3 per mature region annually as.</t>
         </is>
       </c>
-      <c r="J16" s="128" t="inlineStr">
+      <c r="J16" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
         </is>
@@ -7095,7 +6287,7 @@
           <t>Simple roll-forward: where you started, plus openings, minus.</t>
         </is>
       </c>
-      <c r="J17" s="126" t="inlineStr">
+      <c r="J17" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
         </is>
@@ -7135,7 +6327,7 @@
           <t>Add up Americas + China + RoW ending.</t>
         </is>
       </c>
-      <c r="J18" s="126" t="inlineStr">
+      <c r="J18" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-stores formula</t>
         </is>
@@ -7175,7 +6367,7 @@
           <t>4,367 avg sq ft/store = implied FY25 total.</t>
         </is>
       </c>
-      <c r="J19" s="128" t="inlineStr">
+      <c r="J19" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: sales per square foot</t>
         </is>
@@ -7221,7 +6413,7 @@
           <t>Ending stores times avg sq ft per box..</t>
         </is>
       </c>
-      <c r="J20" s="126" t="inlineStr">
+      <c r="J20" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-sqft formula</t>
         </is>
@@ -7321,7 +6513,7 @@
           <t>FY26 SPSF $1,380 reflects Americas traffic/conversion pressure; recovers.</t>
         </is>
       </c>
-      <c r="J24" s="128" t="inlineStr">
+      <c r="J24" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: comparable sales &amp; SPSF</t>
         </is>
@@ -7361,7 +6553,7 @@
           <t>FY25 Americas comp −3% per 10-K (traffic, conversion,.</t>
         </is>
       </c>
-      <c r="J25" s="128" t="inlineStr">
+      <c r="J25" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: Americas comparable sales</t>
         </is>
@@ -7401,7 +6593,7 @@
           <t>FY25 China comp +20% (+19% CCY) per 10-K..</t>
         </is>
       </c>
-      <c r="J26" s="128" t="inlineStr">
+      <c r="J26" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: China Mainland comparable sales</t>
         </is>
@@ -7441,7 +6633,7 @@
           <t>FY25 RoW comp +9% (+7% CCY) per 10-K..</t>
         </is>
       </c>
-      <c r="J27" s="128" t="inlineStr">
+      <c r="J27" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: Rest of World comparable sales</t>
         </is>
@@ -7486,7 +6678,7 @@
           <t>Last year's total store-channel revenue; the base you're.</t>
         </is>
       </c>
-      <c r="J28" s="126" t="inlineStr">
+      <c r="J28" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: prior store-rev formula</t>
         </is>
@@ -7526,7 +6718,7 @@
           <t>Existing-store sales only; prior store rev grown by.</t>
         </is>
       </c>
-      <c r="J29" s="126" t="inlineStr">
+      <c r="J29" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: comp-store formula</t>
         </is>
@@ -7566,7 +6758,7 @@
           <t>Net new doors × sq ft × $/sq.</t>
         </is>
       </c>
-      <c r="J30" s="126" t="inlineStr">
+      <c r="J30" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: net-new-store formula</t>
         </is>
@@ -7606,7 +6798,7 @@
           <t>Brick-and-mortar channel = comp store sales plus whatever.</t>
         </is>
       </c>
-      <c r="J31" s="126" t="inlineStr">
+      <c r="J31" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: store-channel formula</t>
         </is>
@@ -7646,7 +6838,7 @@
           <t>Fleet traffic memo line; not a separate FCF.</t>
         </is>
       </c>
-      <c r="J32" s="128" t="inlineStr">
+      <c r="J32" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: store traffic commentary</t>
         </is>
@@ -7681,7 +6873,7 @@
           <t>In-store conversion memo; 10-K cites lower conversion in.</t>
         </is>
       </c>
-      <c r="J33" s="128" t="inlineStr">
+      <c r="J33" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: conversion rate commentary</t>
         </is>
@@ -7716,7 +6908,7 @@
           <t>In-store average transaction $115–$122; supports SPSF and comp-sales.</t>
         </is>
       </c>
-      <c r="J34" s="128" t="inlineStr">
+      <c r="J34" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: average order value commentary</t>
         </is>
@@ -7816,7 +7008,7 @@
           <t>485M FY25 sessions implied from reported e-comm revenue.</t>
         </is>
       </c>
-      <c r="J38" s="128" t="inlineStr">
+      <c r="J38" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
         </is>
@@ -7851,7 +7043,7 @@
           <t>3.3% FY26 digital conversion vs 3.5% pressure cited.</t>
         </is>
       </c>
-      <c r="J39" s="128" t="inlineStr">
+      <c r="J39" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: digital / traffic commentary</t>
         </is>
@@ -7886,7 +7078,7 @@
           <t>AOV $305 FY26 on promo intensity; steps to.</t>
         </is>
       </c>
-      <c r="J40" s="128" t="inlineStr">
+      <c r="J40" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
         </is>
@@ -7926,7 +7118,7 @@
           <t>Traffic × conversion × AOV is dollars. ×1M.</t>
         </is>
       </c>
-      <c r="J41" s="126" t="inlineStr">
+      <c r="J41" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: e-comm formula</t>
         </is>
@@ -8031,13 +7223,13 @@
           <t>Other channels (wholesale/license/outlets) held at FY25 $1.13B base;.</t>
         </is>
       </c>
-      <c r="J45" s="128" t="inlineStr">
+      <c r="J45" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: channel revenue table</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="70" customHeight="1">
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="41" t="inlineStr">
         <is>
           <t>Americas net revenue ($000)</t>
@@ -8076,13 +7268,13 @@
           <t>Geographic split scales with consolidated growth; FY25 Americas.</t>
         </is>
       </c>
-      <c r="J46" s="128" t="inlineStr">
+      <c r="J46" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="70" customHeight="1">
+    <row r="47" ht="15" customHeight="1">
       <c r="A47" s="41" t="inlineStr">
         <is>
           <t>China Mainland net revenue ($000)</t>
@@ -8121,13 +7313,13 @@
           <t>China 15.8% of FY25 revenue; fastest comp and.</t>
         </is>
       </c>
-      <c r="J47" s="128" t="inlineStr">
+      <c r="J47" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="70" customHeight="1">
+    <row r="48" ht="15" customHeight="1">
       <c r="A48" s="41" t="inlineStr">
         <is>
           <t>Rest of World net revenue ($000)</t>
@@ -8166,7 +7358,7 @@
           <t>Rest of World 13.5% of FY25 revenue; mid-single-digit.</t>
         </is>
       </c>
-      <c r="J48" s="128" t="inlineStr">
+      <c r="J48" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
         </is>
@@ -8201,7 +7393,7 @@
           <t>Women's mix fades 62.5% to 60% as men's penetrates; FY25.</t>
         </is>
       </c>
-      <c r="J49" s="128" t="inlineStr">
+      <c r="J49" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
         </is>
@@ -8236,7 +7428,7 @@
           <t>Men's mix rises 24.5% to 27%; FY25 men's grew 4%.</t>
         </is>
       </c>
-      <c r="J50" s="128" t="inlineStr">
+      <c r="J50" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
         </is>
@@ -8271,7 +7463,7 @@
           <t>Accessories steady at 13% of revenue; FY25 accessories.</t>
         </is>
       </c>
-      <c r="J51" s="128" t="inlineStr">
+      <c r="J51" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
         </is>
@@ -8371,7 +7563,7 @@
           <t>Bottom-up total = store channel + e-comm +.</t>
         </is>
       </c>
-      <c r="J55" s="126" t="inlineStr">
+      <c r="J55" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-rev formula</t>
         </is>
@@ -8411,7 +7603,7 @@
           <t>Pulls the Scenarios base-case revenue path; that's still.</t>
         </is>
       </c>
-      <c r="J56" s="128" t="inlineStr">
+      <c r="J56" s="164" t="inlineStr">
         <is>
           <t>Scenarios tab: base revenue</t>
         </is>
@@ -8452,7 +7644,7 @@
           <t>Driver-built revenue minus Scenarios revenue. Shows you how.</t>
         </is>
       </c>
-      <c r="J57" s="126" t="inlineStr">
+      <c r="J57" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance formula</t>
         </is>
@@ -8493,7 +7685,7 @@
           <t>Variance as a percent of Scenarios revenue. Easy.</t>
         </is>
       </c>
-      <c r="J58" s="126" t="inlineStr">
+      <c r="J58" s="165" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance % formula</t>
         </is>
@@ -8541,7 +7733,6 @@
     <hyperlink ref="J56" location="'Scenarios'!F25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -8639,7 +7830,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>SBC add-back flag (0 = expensed)</t>
@@ -8667,7 +7858,7 @@
     <row r="8">
       <c r="A8" s="26" t="n"/>
     </row>
-    <row r="9" ht="70" customHeight="1">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Store-channel EBIT margin %</t>
@@ -8678,7 +7869,7 @@
           <t>Not % of consolidated revenue; EBIT as %.</t>
         </is>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: company-operated stores net revenue</t>
         </is>
@@ -8702,7 +7893,7 @@
         <v>0.186</v>
       </c>
     </row>
-    <row r="10" ht="70" customHeight="1">
+    <row r="10" ht="15" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>E-commerce EBIT margin %</t>
@@ -8713,7 +7904,7 @@
           <t>Not % of consolidated revenue; EBIT as %.</t>
         </is>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce net revenue</t>
         </is>
@@ -8737,7 +7928,7 @@
         <v>0.236</v>
       </c>
     </row>
-    <row r="11" ht="70" customHeight="1">
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Other-channels EBIT margin %</t>
@@ -8748,7 +7939,7 @@
           <t>Not % of consolidated revenue; EBIT as %.</t>
         </is>
       </c>
-      <c r="C11" s="128" t="inlineStr">
+      <c r="C11" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: other channels (residual)</t>
         </is>
@@ -8783,7 +7974,7 @@
           <t>30% statutory marginal rate. t_operating transitions here over.</t>
         </is>
       </c>
-      <c r="C12" s="128" t="inlineStr">
+      <c r="C12" s="164" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
@@ -8818,7 +8009,7 @@
           <t>Not % of revenue; amortization period (years) if.</t>
         </is>
       </c>
-      <c r="C13" s="126" t="inlineStr">
+      <c r="C13" s="165" t="inlineStr">
         <is>
           <t>NOPAT Bridge: capitalization convention</t>
         </is>
@@ -8861,7 +8052,7 @@
           <t>10-K EBIT / Scenarios forecast.</t>
         </is>
       </c>
-      <c r="C16" s="128" t="inlineStr">
+      <c r="C16" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Income from operations</t>
         </is>
@@ -8901,7 +8092,7 @@
           <t>Run-rate intangible amort add-back.</t>
         </is>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: amortization of intangible assets</t>
         </is>
@@ -8936,7 +8127,7 @@
           <t>Non-recurring restructuring add-back.</t>
         </is>
       </c>
-      <c r="C18" s="128" t="inlineStr">
+      <c r="C18" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: restructuring charges</t>
         </is>
@@ -8971,7 +8162,7 @@
           <t>One-off legal / M&amp;A strip.</t>
         </is>
       </c>
-      <c r="C19" s="128" t="inlineStr">
+      <c r="C19" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: SG&amp;A one-offs</t>
         </is>
@@ -8995,7 +8186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>+ Stock-based compensation (add-back only if flag = 1)</t>
@@ -9006,7 +8197,7 @@
           <t>SBC add-back (if flag = 1).</t>
         </is>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="164" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K): stock-based compensation</t>
         </is>
@@ -9046,7 +8237,7 @@
           <t>Reported EBIT plus non-recurring add-backs.</t>
         </is>
       </c>
-      <c r="C21" s="126" t="inlineStr">
+      <c r="C21" s="165" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab: Phase 1 subtotal</t>
         </is>
@@ -9079,7 +8270,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>+ Implied lease interest expense (reclass from rent)</t>
@@ -9090,7 +8281,7 @@
           <t>Lease interest reclass (memo).</t>
         </is>
       </c>
-      <c r="C23" s="128" t="inlineStr">
+      <c r="C23" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: interest on lease liabilities (supplemental)</t>
         </is>
@@ -9130,7 +8321,7 @@
           <t>R&amp;D cap immaterial this yr.</t>
         </is>
       </c>
-      <c r="C24" s="128" t="inlineStr">
+      <c r="C24" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: R&amp;D / software expense</t>
         </is>
@@ -9165,7 +8356,7 @@
           <t>Amortization of prior capitalized intangibles. LULU: flows through.</t>
         </is>
       </c>
-      <c r="C25" s="128" t="inlineStr">
+      <c r="C25" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: intangible amortization</t>
         </is>
@@ -9199,7 +8390,7 @@
           <t>Phase 1 plus lease / R&amp;D adjustments.</t>
         </is>
       </c>
-      <c r="C26" s="126" t="inlineStr">
+      <c r="C26" s="165" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab: Phase 2 subtotal</t>
         </is>
@@ -9243,7 +8434,7 @@
           <t>Store rev from Revenue Drivers.</t>
         </is>
       </c>
-      <c r="C28" s="128" t="inlineStr">
+      <c r="C28" s="164" t="inlineStr">
         <is>
           <t>Revenue Drivers tab: store-channel revenue</t>
         </is>
@@ -9283,7 +8474,7 @@
           <t>E-comm rev from Revenue Drivers.</t>
         </is>
       </c>
-      <c r="C29" s="128" t="inlineStr">
+      <c r="C29" s="164" t="inlineStr">
         <is>
           <t>Revenue Drivers tab: e-commerce revenue</t>
         </is>
@@ -9323,7 +8514,7 @@
           <t>Other rev from Revenue Drivers.</t>
         </is>
       </c>
-      <c r="C30" s="128" t="inlineStr">
+      <c r="C30" s="164" t="inlineStr">
         <is>
           <t>Revenue Drivers tab: other channels revenue</t>
         </is>
@@ -9352,7 +8543,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="70" customHeight="1">
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Store-channel EBIT (= Rev x store margin)</t>
@@ -9363,7 +8554,7 @@
           <t>Not % of consolidated revenue; store EBIT ÷.</t>
         </is>
       </c>
-      <c r="C31" s="128" t="inlineStr">
+      <c r="C31" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: company-operated stores net revenue</t>
         </is>
@@ -9392,7 +8583,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="70" customHeight="1">
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
           <t>E-commerce EBIT (= Rev x e-comm margin)</t>
@@ -9403,7 +8594,7 @@
           <t>Not % of consolidated revenue; e-commerce EBIT ÷.</t>
         </is>
       </c>
-      <c r="C32" s="128" t="inlineStr">
+      <c r="C32" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce net revenue</t>
         </is>
@@ -9432,7 +8623,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Other-channels EBIT (= Rev x other margin)</t>
@@ -9443,7 +8634,7 @@
           <t>Not % of consolidated revenue; other-channel EBIT ÷.</t>
         </is>
       </c>
-      <c r="C33" s="128" t="inlineStr">
+      <c r="C33" s="164" t="inlineStr">
         <is>
           <t>FY2025 10-K: other channels (residual)</t>
         </is>
@@ -9483,7 +8674,7 @@
           <t>Sum of sector EBIT (Phase 3).</t>
         </is>
       </c>
-      <c r="C34" s="126" t="inlineStr">
+      <c r="C34" s="165" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab: sector EBIT subtotal</t>
         </is>
@@ -9519,7 +8710,7 @@
           <t>Channel-mix EBIT output (Phase 3).</t>
         </is>
       </c>
-      <c r="C35" s="126" t="inlineStr">
+      <c r="C35" s="165" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab: Phase 3 subtotal</t>
         </is>
@@ -9558,7 +8749,7 @@
           <t>FY25 walk-through Phases 1–2.</t>
         </is>
       </c>
-      <c r="C36" s="126" t="inlineStr">
+      <c r="C36" s="165" t="inlineStr">
         <is>
           <t>Scenarios tab: base-case EBIT (forecast)</t>
         </is>
@@ -9622,7 +8813,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="70" customHeight="1">
+    <row r="39" ht="15" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Operating effective tax rate (t_operating)</t>
@@ -9633,7 +8824,7 @@
           <t>Operating ETR with interest shield.</t>
         </is>
       </c>
-      <c r="C39" s="128" t="inlineStr">
+      <c r="C39" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: income tax &amp; interest expense</t>
         </is>
@@ -9673,7 +8864,7 @@
           <t>Normalized EBIT × t_operating.</t>
         </is>
       </c>
-      <c r="C40" s="126" t="inlineStr">
+      <c r="C40" s="165" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab: unlevered tax expense</t>
         </is>
@@ -9710,7 +8901,7 @@
           <t>EBIT_norm × (1 − t_operating).</t>
         </is>
       </c>
-      <c r="C41" s="126" t="inlineStr">
+      <c r="C41" s="165" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab: normalized NOPAT</t>
         </is>
@@ -9924,7 +9115,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -9934,7 +9124,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I103"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -10011,7 +9201,7 @@
       <c r="A3" s="82" t="n"/>
       <c r="D3" s="83" t="n"/>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="38" t="n"/>
     </row>
     <row r="5">
@@ -10044,7 +9234,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="15" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Revenue growth %</t>
@@ -10055,7 +9245,7 @@
           <t>−6.1% FY2026 revenue growth matches company guidance midpoint.</t>
         </is>
       </c>
-      <c r="C6" s="128" t="inlineStr">
+      <c r="C6" s="164" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release Also: StockAnalysis: LULU 3Y revenue forecast</t>
         </is>
@@ -10081,7 +9271,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" ht="112" customHeight="1">
+    <row r="7" ht="15" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
@@ -10092,7 +9282,7 @@
           <t>56.6% of revenue (gross margin). Isolates COGS for.</t>
         </is>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
         </is>
@@ -10151,7 +9341,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" ht="15" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Clean / run-rate EBIT margin %</t>
@@ -10162,7 +9352,7 @@
           <t>13.2% is the real/run-rate OM: Q2 18.8% minus.</t>
         </is>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="164" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs Also: FY2025 10-K: Operating margin 19.9% (one hit)</t>
         </is>
@@ -10199,7 +9389,7 @@
           <t>Add back $134.5M in FY26 only; already recognized.</t>
         </is>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="164" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
         </is>
@@ -10349,7 +9539,7 @@
           <t>4.5% D&amp;A / sales = FY25 496,228 /.</t>
         </is>
       </c>
-      <c r="C15" s="128" t="inlineStr">
+      <c r="C15" s="164" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)</t>
         </is>
@@ -10402,7 +9592,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" ht="150" customHeight="1">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Capex % of revenue</t>
@@ -10413,7 +9603,7 @@
           <t>FY26 7.0% is $735M on $10.4B sales, not.</t>
         </is>
       </c>
-      <c r="C17" s="128" t="inlineStr">
+      <c r="C17" s="164" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
         </is>
@@ -10483,7 +9673,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="150" customHeight="1">
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>DSO (days) - flat vs FY25</t>
@@ -10494,7 +9684,7 @@
           <t>Not % of revenue; DSO (days), flat ~6.3..</t>
         </is>
       </c>
-      <c r="C20" s="128" t="inlineStr">
+      <c r="C20" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
@@ -10523,7 +9713,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="98" customHeight="1">
+    <row r="21" ht="15" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Accounts receivable, net</t>
@@ -10534,7 +9724,7 @@
           <t>Implied ~1.7% of revenue (not a direct %.</t>
         </is>
       </c>
-      <c r="C21" s="128" t="inlineStr">
+      <c r="C21" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
@@ -10563,7 +9753,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="150" customHeight="1">
+    <row r="22" ht="15" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>DIO (days) - FY25 anchor, -1 day/yr</t>
@@ -10574,7 +9764,7 @@
           <t>Not % of revenue; DIO (days). FY25 anchor:.</t>
         </is>
       </c>
-      <c r="C22" s="128" t="inlineStr">
+      <c r="C22" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories &amp; COGS Also: LULU FY2025 10-K: inventory &amp; markdown outlook</t>
         </is>
@@ -10603,7 +9793,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" ht="112" customHeight="1">
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Inventories</t>
@@ -10614,7 +9804,7 @@
           <t>Not % of revenue; $ balance (not a.</t>
         </is>
       </c>
-      <c r="C23" s="128" t="inlineStr">
+      <c r="C23" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories</t>
         </is>
@@ -10643,7 +9833,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" ht="84" customHeight="1">
+    <row r="24" ht="15" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t>DPO (days) - flat vs FY25</t>
@@ -10654,7 +9844,7 @@
           <t>Not % of revenue; DPO (days), flat ~25.1..</t>
         </is>
       </c>
-      <c r="C24" s="128" t="inlineStr">
+      <c r="C24" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
         </is>
@@ -10683,7 +9873,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="84" customHeight="1">
+    <row r="25" ht="15" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Accounts payable</t>
@@ -10694,7 +9884,7 @@
           <t>Implied ~3.0% of revenue (not a direct %.</t>
         </is>
       </c>
-      <c r="C25" s="128" t="inlineStr">
+      <c r="C25" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable</t>
         </is>
@@ -10723,7 +9913,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" ht="84" customHeight="1">
+    <row r="26" ht="15" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Prepaid expenses (% of revenue)</t>
@@ -10734,7 +9924,7 @@
           <t>5.1% of revenue (flat). FY25 other current assets.</t>
         </is>
       </c>
-      <c r="C26" s="128" t="inlineStr">
+      <c r="C26" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
@@ -10763,7 +9953,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="84" customHeight="1">
+    <row r="27" ht="15" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Prepaid expenses (other current assets)</t>
@@ -10774,7 +9964,7 @@
           <t>5.1% of revenue (flat). FY25 other current assets.</t>
         </is>
       </c>
-      <c r="C27" s="128" t="inlineStr">
+      <c r="C27" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
@@ -10803,7 +9993,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" ht="84" customHeight="1">
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Accrued liabilities (% of revenue)</t>
@@ -10814,7 +10004,7 @@
           <t>6.0% of revenue (flat). FY25 accrued liabilities ÷.</t>
         </is>
       </c>
-      <c r="C28" s="128" t="inlineStr">
+      <c r="C28" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
@@ -10843,7 +10033,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="84" customHeight="1">
+    <row r="29" ht="15" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Accrued liabilities and other</t>
@@ -10854,7 +10044,7 @@
           <t>6.0% of revenue (flat). FY25 accrued liabilities ÷.</t>
         </is>
       </c>
-      <c r="C29" s="128" t="inlineStr">
+      <c r="C29" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
@@ -10883,7 +10073,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="42" customHeight="1">
+    <row r="30" ht="15" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Current operating assets (AR + inv + prepaids)</t>
@@ -10894,7 +10084,7 @@
           <t>Not one %; sum ≈22.1% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C30" s="128" t="inlineStr">
+      <c r="C30" s="164" t="inlineStr">
         <is>
           <t>Scenarios tab: AR + inventory + prepaids</t>
         </is>
@@ -10920,7 +10110,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" ht="42" customHeight="1">
+    <row r="31" ht="15" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Current operating liabilities (AP + accruals)</t>
@@ -10931,7 +10121,7 @@
           <t>Not one %; sum ≈9.0% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C31" s="128" t="inlineStr">
+      <c r="C31" s="164" t="inlineStr">
         <is>
           <t>Scenarios tab: AP + accrued liabilities</t>
         </is>
@@ -10957,7 +10147,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" ht="42" customHeight="1">
+    <row r="32" ht="15" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
           <t>Net working capital</t>
@@ -10968,7 +10158,7 @@
           <t>Not one %; net ≈13.2% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C32" s="128" t="inlineStr">
+      <c r="C32" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: working-capital components</t>
         </is>
@@ -10997,7 +10187,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" ht="56" customHeight="1">
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="23" t="inlineStr">
         <is>
           <t>Delta NWC (prior yr - current yr)</t>
@@ -11008,7 +10198,7 @@
           <t>Not % of revenue; $ change in NWC.</t>
         </is>
       </c>
-      <c r="C33" s="128" t="inlineStr">
+      <c r="C33" s="164" t="inlineStr">
         <is>
           <t>Scenarios tab: NWC roll-forward (driver schedule)</t>
         </is>
@@ -11177,7 +10367,7 @@
           <t>2.25% terminal g sits next to FRED GDPC1.</t>
         </is>
       </c>
-      <c r="C43" s="128" t="inlineStr">
+      <c r="C43" s="164" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -11259,7 +10449,7 @@
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C50" s="128" t="inlineStr">
+      <c r="C50" s="164" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -11279,7 +10469,7 @@
           <t>Subtract ASC 842 operating lease liabilities as debt.</t>
         </is>
       </c>
-      <c r="C51" s="128" t="inlineStr">
+      <c r="C51" s="164" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: operating lease liabilities</t>
         </is>
@@ -11315,7 +10505,7 @@
           <t>Shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C55" s="128" t="inlineStr">
+      <c r="C55" s="164" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -11341,7 +10531,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C57" s="128" t="inlineStr">
+      <c r="C57" s="164" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -11735,7 +10925,7 @@
           <t>Selected exit is Gordon TV / FY30 EBITDA..</t>
         </is>
       </c>
-      <c r="C82" s="128" t="inlineStr">
+      <c r="C82" s="164" t="inlineStr">
         <is>
           <t>DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
         </is>
@@ -11879,7 +11069,7 @@
           <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by.</t>
         </is>
       </c>
-      <c r="C98" s="128" t="inlineStr">
+      <c r="C98" s="164" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -11904,7 +11094,7 @@
       <c r="A99" s="109" t="n">
         <v>0.095</v>
       </c>
-      <c r="C99" s="128" t="inlineStr">
+      <c r="C99" s="164" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
@@ -12125,7 +11315,7 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="128" t="inlineStr">
+      <c r="C4" s="164" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -12167,7 +11357,7 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C7" s="128" t="inlineStr">
+      <c r="C7" s="164" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
@@ -12182,7 +11372,7 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="128" t="inlineStr">
+      <c r="C8" s="164" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -12197,7 +11387,7 @@
           <t>Shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C9" s="128" t="inlineStr">
+      <c r="C9" s="164" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -12212,7 +11402,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C10" s="128" t="inlineStr">
+      <c r="C10" s="164" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -12321,7 +11511,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C19" s="126" t="inlineStr">
+      <c r="C19" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12348,7 +11538,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C20" s="126" t="inlineStr">
+      <c r="C20" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12375,7 +11565,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C21" s="126" t="inlineStr">
+      <c r="C21" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12402,7 +11592,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C22" s="126" t="inlineStr">
+      <c r="C22" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12429,7 +11619,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C23" s="126" t="inlineStr">
+      <c r="C23" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12456,7 +11646,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C24" s="126" t="inlineStr">
+      <c r="C24" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12483,7 +11673,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C25" s="126" t="inlineStr">
+      <c r="C25" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12510,7 +11700,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C26" s="126" t="inlineStr">
+      <c r="C26" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12537,7 +11727,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C27" s="126" t="inlineStr">
+      <c r="C27" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12564,7 +11754,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C28" s="126" t="inlineStr">
+      <c r="C28" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12591,7 +11781,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C29" s="126" t="inlineStr">
+      <c r="C29" s="165" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -12618,7 +11808,7 @@
     <row r="32">
       <c r="A32" s="26" t="n"/>
     </row>
-    <row r="33" ht="42" customHeight="1">
+    <row r="33" ht="15" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Alo / Color Image 2023 Moelis ask ($bn)</t>
@@ -12629,7 +11819,7 @@
           <t>Reuters: about $10 billion Moelis ask for Color.</t>
         </is>
       </c>
-      <c r="C33" s="128" t="inlineStr">
+      <c r="C33" s="164" t="inlineStr">
         <is>
           <t>Reuters: Alo parent $10bn Moelis ask Also: Reuters: Alo 2023 process; no deal</t>
         </is>
@@ -12649,7 +11839,7 @@
           <t>Forbes estimates Color Image parent sales nearly $2.</t>
         </is>
       </c>
-      <c r="C34" s="128" t="inlineStr">
+      <c r="C34" s="164" t="inlineStr">
         <is>
           <t>Forbes: Color Image nearly $2bn sales</t>
         </is>
@@ -12669,7 +11859,7 @@
           <t>5.0x = 10 / 2. Implied EV/Sales on.</t>
         </is>
       </c>
-      <c r="C35" s="128" t="inlineStr">
+      <c r="C35" s="164" t="inlineStr">
         <is>
           <t>Comps: Alo ask / parent sales</t>
         </is>
@@ -12690,7 +11880,7 @@
           <t>No page prints Alo or Color Image EBITDA..</t>
         </is>
       </c>
-      <c r="C36" s="126" t="inlineStr">
+      <c r="C36" s="165" t="inlineStr">
         <is>
           <t>None — no EBITDA source</t>
         </is>
@@ -12875,7 +12065,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="42" customHeight="1">
+    <row r="57" ht="15" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
         <is>
           <t>EV / EBITDA (FY2030E terminal)</t>
@@ -12887,7 +12077,7 @@
 Hi 8.0x DECK high-end cap.</t>
         </is>
       </c>
-      <c r="C57" s="128" t="inlineStr">
+      <c r="C57" s="164" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA Hi: StockAnalysis: DECK EV/EBITDA</t>
         </is>
@@ -12918,7 +12108,7 @@
           <t>Gordon TV / FY30 EBITDA exit.</t>
         </is>
       </c>
-      <c r="C58" s="128" t="inlineStr">
+      <c r="C58" s="164" t="inlineStr">
         <is>
           <t>DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
         </is>
@@ -12932,7 +12122,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" ht="42" customHeight="1">
+    <row r="59" ht="15" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
         <is>
           <t>P / E (FY2026E EPS)</t>
@@ -12944,7 +12134,7 @@
 Hi 18x FY26E EPS recovery.</t>
         </is>
       </c>
-      <c r="C59" s="128" t="inlineStr">
+      <c r="C59" s="164" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E Hi: StockAnalysis: NKE Forward P/E</t>
         </is>
@@ -12988,7 +12178,7 @@
           <t>Current price</t>
         </is>
       </c>
-      <c r="C62" s="128" t="inlineStr">
+      <c r="C62" s="164" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -1325,14 +1325,13 @@
     <outlinePr summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="B2:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1340,7 +1339,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1355,7 +1353,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1363,7 +1360,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="n"/>
     </row>
@@ -1376,7 +1372,6 @@
     <row r="12">
       <c r="B12" s="8" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="B14" s="5" t="n"/>
     </row>
@@ -1389,7 +1384,6 @@
     <row r="17" ht="15" customHeight="1">
       <c r="B17" s="10" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1425,7 +1419,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="11" t="n"/>
     </row>
@@ -1446,7 +1439,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1566,7 +1559,7 @@
         </is>
       </c>
       <c r="D8" s="157" t="n">
-        <v>100.61</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
@@ -1772,7 +1765,7 @@
         </is>
       </c>
       <c r="D20" s="27" t="n">
-        <v>0.447</v>
+        <v>0.4469</v>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
@@ -2273,7 +2266,7 @@
         <v>0.015</v>
       </c>
       <c r="F10" s="129" t="n">
-        <v>0.022</v>
+        <v>0.0225</v>
       </c>
       <c r="G10" s="129" t="n">
         <v>0.03</v>
@@ -2400,13 +2393,13 @@
         </is>
       </c>
       <c r="E15" s="159" t="n">
-        <v>6.3</v>
+        <v>6.267883648875038</v>
       </c>
       <c r="F15" s="159" t="n">
-        <v>6.3</v>
+        <v>6.267883648875038</v>
       </c>
       <c r="G15" s="159" t="n">
-        <v>6.3</v>
+        <v>6.267883648875038</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
@@ -2426,13 +2419,13 @@
         </is>
       </c>
       <c r="E16" s="159" t="n">
-        <v>128.8</v>
+        <v>128.8324100108167</v>
       </c>
       <c r="F16" s="159" t="n">
-        <v>128.8</v>
+        <v>128.8324100108167</v>
       </c>
       <c r="G16" s="159" t="n">
-        <v>128.8</v>
+        <v>128.8324100108167</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -2478,13 +2471,13 @@
         </is>
       </c>
       <c r="E18" s="159" t="n">
-        <v>25.1</v>
+        <v>25.10521290169407</v>
       </c>
       <c r="F18" s="159" t="n">
-        <v>25.1</v>
+        <v>25.10521290169407</v>
       </c>
       <c r="G18" s="159" t="n">
-        <v>25.1</v>
+        <v>25.10521290169407</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
@@ -2504,13 +2497,13 @@
         </is>
       </c>
       <c r="E19" s="129" t="n">
-        <v>0.051</v>
+        <v>0.05080692810692991</v>
       </c>
       <c r="F19" s="129" t="n">
-        <v>0.051</v>
+        <v>0.05080692810692991</v>
       </c>
       <c r="G19" s="129" t="n">
-        <v>0.051</v>
+        <v>0.05080692810692991</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
@@ -2530,13 +2523,13 @@
         </is>
       </c>
       <c r="E20" s="129" t="n">
-        <v>0.06</v>
+        <v>0.05971412101669879</v>
       </c>
       <c r="F20" s="129" t="n">
-        <v>0.06</v>
+        <v>0.05971412101669879</v>
       </c>
       <c r="G20" s="129" t="n">
-        <v>0.06</v>
+        <v>0.05971412101669879</v>
       </c>
     </row>
     <row r="21">
@@ -8560,7 +8553,7 @@
         </is>
       </c>
       <c r="D31" s="22" t="n">
-        <v>939252.38</v>
+        <v>939252.384</v>
       </c>
       <c r="E31" s="75">
         <f>E28*D$9</f>
@@ -8600,7 +8593,7 @@
         </is>
       </c>
       <c r="D32" s="22" t="n">
-        <v>1160812.49</v>
+        <v>1160812.492</v>
       </c>
       <c r="E32" s="75">
         <f>E29*D$10</f>
@@ -8640,7 +8633,7 @@
         </is>
       </c>
       <c r="D33" s="22" t="n">
-        <v>103208.47</v>
+        <v>103208.469</v>
       </c>
       <c r="E33" s="75">
         <f>E30*D$11</f>
@@ -8716,7 +8709,7 @@
         </is>
       </c>
       <c r="D35" s="160" t="n">
-        <v>2203273</v>
+        <v>2203273.345</v>
       </c>
       <c r="E35" s="130">
         <f>E34</f>
@@ -8830,7 +8823,7 @@
         </is>
       </c>
       <c r="D39" s="129" t="n">
-        <v>0.295</v>
+        <v>0.2946847649213503</v>
       </c>
       <c r="E39" s="32">
         <f>0.29468476492135026+(E$12-0.29468476492135026)*1/5</f>
@@ -9124,7 +9117,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9288,7 +9281,7 @@
         </is>
       </c>
       <c r="D7" s="129" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.566005440167168</v>
       </c>
       <c r="E7" s="136">
         <f>Scenarios!$F$14</f>
@@ -9451,7 +9444,7 @@
         </is>
       </c>
       <c r="D12" s="129" t="n">
-        <v>0.199</v>
+        <v>0.1991078666258354</v>
       </c>
       <c r="E12" s="32">
         <f>E11/E5</f>
@@ -9690,7 +9683,7 @@
         </is>
       </c>
       <c r="D20" s="159" t="n">
-        <v>6.3</v>
+        <v>6.267883648875038</v>
       </c>
       <c r="E20" s="145">
         <f>Scenarios!F65</f>
@@ -9770,7 +9763,7 @@
         </is>
       </c>
       <c r="D22" s="159" t="n">
-        <v>128.8</v>
+        <v>128.8324100108167</v>
       </c>
       <c r="E22" s="145">
         <f>Scenarios!F75</f>
@@ -9850,7 +9843,7 @@
         </is>
       </c>
       <c r="D24" s="159" t="n">
-        <v>25.1</v>
+        <v>25.10521290169407</v>
       </c>
       <c r="E24" s="145">
         <f>Scenarios!F85</f>
@@ -9930,7 +9923,7 @@
         </is>
       </c>
       <c r="D26" s="129" t="n">
-        <v>0.051</v>
+        <v>0.05080692810692991</v>
       </c>
       <c r="E26" s="136">
         <f>Scenarios!$F$19</f>
@@ -10010,7 +10003,7 @@
         </is>
       </c>
       <c r="D28" s="129" t="n">
-        <v>0.06</v>
+        <v>0.05971412101669879</v>
       </c>
       <c r="E28" s="136">
         <f>Scenarios!$F$20</f>
@@ -10537,7 +10530,7 @@
         </is>
       </c>
       <c r="D57" s="157" t="n">
-        <v>100.61</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58">
@@ -10729,7 +10722,7 @@
         </is>
       </c>
       <c r="D72" s="157" t="n">
-        <v>100.61</v>
+        <v>100</v>
       </c>
       <c r="E72" s="99">
         <f>D72*(1+$D$66)</f>
@@ -10880,7 +10873,7 @@
         </is>
       </c>
       <c r="D78" s="161" t="n">
-        <v>14.18</v>
+        <v>14.1783354282636</v>
       </c>
       <c r="E78" s="150">
         <f>E77/E75</f>
@@ -11363,7 +11356,7 @@
         </is>
       </c>
       <c r="D7" s="159" t="n">
-        <v>9.6</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -11408,7 +11401,7 @@
         </is>
       </c>
       <c r="D10" s="157" t="n">
-        <v>100.61</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -12184,7 +12177,7 @@
         </is>
       </c>
       <c r="D62" s="21" t="n">
-        <v>100.61</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63">

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -1534,7 +1534,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1659,7 +1658,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -1887,7 +1885,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -1931,7 +1928,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
@@ -2564,7 +2560,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4567,7 +4562,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4625,11 +4619,9 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="n"/>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5734,7 +5726,6 @@
     <row r="2">
       <c r="A2" s="26" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -6412,7 +6403,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6907,7 +6897,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7117,7 +7106,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7462,7 +7450,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7815,7 +7802,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -8026,7 +8012,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8920,7 +8905,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -10323,7 +10307,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -10555,8 +10538,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -10568,7 +10549,6 @@
     <row r="63">
       <c r="A63" s="26" t="n"/>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10629,7 +10609,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10714,7 +10693,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10835,7 +10813,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10896,7 +10873,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -10972,7 +10948,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -11038,8 +11013,6 @@
     <row r="94">
       <c r="A94" s="68" t="n"/>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -11074,7 +11047,7 @@
         <v>0.02</v>
       </c>
       <c r="G98" s="151" t="n">
-        <v>0.022</v>
+        <v>0.0225</v>
       </c>
       <c r="H98" s="151" t="n">
         <v>0.025</v>
@@ -11426,7 +11399,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11790,7 +11762,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -11884,7 +11855,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -11947,7 +11917,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -12013,7 +11982,6 @@
     <row r="53">
       <c r="A53" s="41" t="n"/>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -12164,7 +12132,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Damodaran ERP + overlay</t>
+          <t>Damodaran ERP plus 177 bps US risk premium.</t>
         </is>
       </c>
       <c r="C4" s="164" t="inlineStr">
@@ -1534,6 +1534,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1658,6 +1659,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -1885,6 +1887,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -1928,6 +1931,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
@@ -2328,7 +2332,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Capex fade to 5.5%</t>
+          <t>5.5% model rate; FY26 7% capex guide fades down.</t>
         </is>
       </c>
       <c r="C13" s="164" t="inlineStr">
@@ -2380,7 +2384,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Not % of revenue; DSO (days), flat ~6.3..</t>
+          <t>6.3 days DSO held flat vs FY25 actual.</t>
         </is>
       </c>
       <c r="C15" s="164" t="inlineStr">
@@ -2458,7 +2462,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Not % of revenue; DPO (days), flat ~25.1..</t>
+          <t>25.1 days DPO held flat vs FY25 actual.</t>
         </is>
       </c>
       <c r="C18" s="164" t="inlineStr">
@@ -2560,6 +2564,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4562,6 +4567,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4619,9 +4625,11 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="n"/>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5726,6 +5734,7 @@
     <row r="2">
       <c r="A2" s="26" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -6403,6 +6412,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6897,6 +6907,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7106,6 +7117,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7450,6 +7462,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7802,6 +7815,7 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -8012,6 +8026,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8905,6 +8920,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -9219,7 +9235,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>−6.1% FY2026 revenue growth matches company guidance midpoint.</t>
+          <t>Minus 6.1% FY26 revenue per company guidance midpoint.</t>
         </is>
       </c>
       <c r="C6" s="164" t="inlineStr">
@@ -9256,7 +9272,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.6% of revenue (gross margin). Isolates COGS for.</t>
+          <t>56.6% FY25 gross margin held flat in forecast.</t>
         </is>
       </c>
       <c r="C7" s="164" t="inlineStr">
@@ -9326,7 +9342,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13.2% is the real/run-rate OM: Q2 18.8% minus.</t>
+          <t>13.2% clean OM from Q2 run-rate ex tariff.</t>
         </is>
       </c>
       <c r="C9" s="164" t="inlineStr">
@@ -9363,7 +9379,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Add back $134.5M in FY26 only; already recognized.</t>
+          <t>Add back 134.5M tariff refund in FY26 only.</t>
         </is>
       </c>
       <c r="C10" s="164" t="inlineStr">
@@ -9513,7 +9529,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.5% D&amp;A / sales = FY25 496,228 /.</t>
+          <t>4.5% of sales from FY25 D&amp;A over revenue.</t>
         </is>
       </c>
       <c r="C15" s="164" t="inlineStr">
@@ -9577,7 +9593,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FY26 7.0% is $735M on $10.4B sales, not.</t>
+          <t>5.5% model rate; FY26 7% capex guide fades down.</t>
         </is>
       </c>
       <c r="C17" s="164" t="inlineStr">
@@ -9641,7 +9657,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Not one %; net ≈13.2% of FY25 sales.</t>
+          <t>NWC schedule nets to 13.2% of FY25 sales.</t>
         </is>
       </c>
       <c r="C19" s="128" t="inlineStr">
@@ -9658,7 +9674,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Not % of revenue; DSO (days), flat ~6.3..</t>
+          <t>6.3 days DSO held flat vs FY25 actual.</t>
         </is>
       </c>
       <c r="C20" s="164" t="inlineStr">
@@ -9698,7 +9714,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Implied ~1.7% of revenue (not a direct %.</t>
+          <t>AR 1.7% of sales from FY25 balance sheet.</t>
         </is>
       </c>
       <c r="C21" s="164" t="inlineStr">
@@ -9738,7 +9754,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Not % of revenue; DIO (days). FY25 anchor:.</t>
+          <t>128.8 day DIO anchor; minus 1 day per year.</t>
         </is>
       </c>
       <c r="C22" s="164" t="inlineStr">
@@ -9778,7 +9794,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Not % of revenue; $ balance (not a.</t>
+          <t>Inventory dollar balance driven by DIO times COGS.</t>
         </is>
       </c>
       <c r="C23" s="164" t="inlineStr">
@@ -9818,7 +9834,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Not % of revenue; DPO (days), flat ~25.1..</t>
+          <t>25.1 days DPO held flat vs FY25 actual.</t>
         </is>
       </c>
       <c r="C24" s="164" t="inlineStr">
@@ -9858,7 +9874,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Implied ~3.0% of revenue (not a direct %.</t>
+          <t>AP 3.0% of sales from FY25 payables balance.</t>
         </is>
       </c>
       <c r="C25" s="164" t="inlineStr">
@@ -9898,7 +9914,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5.1% of revenue (flat). FY25 other current assets.</t>
+          <t>5.1% of revenue from FY25 other current assets.</t>
         </is>
       </c>
       <c r="C26" s="164" t="inlineStr">
@@ -9938,7 +9954,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5.1% of revenue (flat). FY25 other current assets.</t>
+          <t>5.1% of revenue from FY25 other current assets.</t>
         </is>
       </c>
       <c r="C27" s="164" t="inlineStr">
@@ -9978,7 +9994,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>6.0% of revenue (flat). FY25 accrued liabilities ÷.</t>
+          <t>6.0% of revenue from FY25 accrued liabilities balance.</t>
         </is>
       </c>
       <c r="C28" s="164" t="inlineStr">
@@ -10018,7 +10034,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6.0% of revenue (flat). FY25 accrued liabilities ÷.</t>
+          <t>6.0% of revenue from FY25 accrued liabilities balance.</t>
         </is>
       </c>
       <c r="C29" s="164" t="inlineStr">
@@ -10058,7 +10074,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Not one %; sum ≈22.1% of FY25 sales.</t>
+          <t>Operating assets sum to 22.1% of FY25 sales.</t>
         </is>
       </c>
       <c r="C30" s="164" t="inlineStr">
@@ -10095,7 +10111,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Not one %; sum ≈9.0% of FY25 sales.</t>
+          <t>Operating liabilities sum to 9.0% of FY25 sales.</t>
         </is>
       </c>
       <c r="C31" s="164" t="inlineStr">
@@ -10132,7 +10148,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Not one %; net ≈13.2% of FY25 sales.</t>
+          <t>Net working capital equals 13.2% of FY25 sales.</t>
         </is>
       </c>
       <c r="C32" s="164" t="inlineStr">
@@ -10172,7 +10188,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Not % of revenue; $ change in NWC.</t>
+          <t>Year-over-year dollar change in net working capital schedule.</t>
         </is>
       </c>
       <c r="C33" s="164" t="inlineStr">
@@ -10307,6 +10323,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -10340,7 +10357,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.25% terminal g sits next to FRED GDPC1.</t>
+          <t>2.25% terminal g anchored to FRED GDPC1 macro series.</t>
         </is>
       </c>
       <c r="C43" s="164" t="inlineStr">
@@ -10538,6 +10555,8 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -10549,6 +10568,7 @@
     <row r="63">
       <c r="A63" s="26" t="n"/>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10609,6 +10629,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10693,6 +10714,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10813,6 +10835,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10873,6 +10896,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -10891,7 +10915,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Selected exit is Gordon TV / FY30 EBITDA..</t>
+          <t>Gordon terminal value divided by FY30 EBITDA multiple.</t>
         </is>
       </c>
       <c r="C82" s="164" t="inlineStr">
@@ -10948,6 +10972,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -11013,6 +11038,8 @@
     <row r="94">
       <c r="A94" s="68" t="n"/>
     </row>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -11032,7 +11059,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Terminal-g axis 1.5–3.0% brackets 2.25% base; bounded by.</t>
+          <t>Sensitivity grid; terminal g spans 1.5% to 3.0%.</t>
         </is>
       </c>
       <c r="C98" s="164" t="inlineStr">
@@ -11399,6 +11426,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11762,6 +11790,7 @@
         <v>407521</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -11855,6 +11884,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -11917,6 +11947,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -11982,6 +12013,7 @@
     <row r="53">
       <c r="A53" s="41" t="n"/>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -12132,6 +12164,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scratch" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +32,7 @@
     <numFmt numFmtId="169" formatCode="0.0x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="60">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -364,8 +365,28 @@
       <color rgb="000000CC"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Garamond"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Garamond"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -397,6 +418,11 @@
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF99"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -423,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -885,6 +911,23 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -969,47 +1012,47 @@
   <commentList>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Line item — FY25 10-K. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Net revenue FY25 10-K. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E8" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>COGS FY25 10-K. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E11" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. on reported baseline. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>EBIT incl. FY26 refund FY25 10-K. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E12" authorId="0" shapeId="0">
       <text>
-        <t>FY25 10-K anchor. cash-flow read-through. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Reported EBIT margin FY25 10-K. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
     <comment ref="E100" authorId="0" shapeId="0">
       <text>
-        <t>0.1 WACC tab to green WACC cell ~9.0%. on reported baseline.</t>
+        <t>WACC sensitivity −100 bps vs base.</t>
       </text>
     </comment>
     <comment ref="E101" authorId="0" shapeId="0">
       <text>
-        <t>0.105 WACC tab to green WACC cell ~9.0%. on reported baseline.</t>
+        <t>WACC sensitivity −50 bps vs base.</t>
       </text>
     </comment>
     <comment ref="E102" authorId="0" shapeId="0">
       <text>
-        <t>0.11 WACC tab to green WACC cell ~9.0%. on reported baseline.</t>
+        <t>WACC sensitivity +50 bps vs base.</t>
       </text>
     </comment>
     <comment ref="E103" authorId="0" shapeId="0">
       <text>
-        <t>0.115 WACC tab to green WACC cell ~9.0%. on reported baseline.</t>
+        <t>WACC sensitivity +100 bps vs base.</t>
       </text>
     </comment>
   </commentList>
@@ -1024,12 +1067,12 @@
   <commentList>
     <comment ref="D18" authorId="0" shapeId="0">
       <text>
-        <t>Source on reported baseline.</t>
+        <t>Peer EV/EBITDA from PitchBook.</t>
       </text>
     </comment>
     <comment ref="D56" authorId="0" shapeId="0">
       <text>
-        <t>Source on reported baseline.</t>
+        <t>Football-field range from comp set.</t>
       </text>
     </comment>
   </commentList>
@@ -1325,13 +1368,14 @@
     <outlinePr summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1339,6 +1383,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1353,6 +1398,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1360,6 +1406,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="n"/>
     </row>
@@ -1372,6 +1419,7 @@
     <row r="12">
       <c r="B12" s="8" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="B14" s="5" t="n"/>
     </row>
@@ -1384,6 +1432,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="B17" s="10" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1419,6 +1468,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="B25" s="11" t="n"/>
     </row>
@@ -1485,7 +1535,7 @@
           <t>Current 10Y UST</t>
         </is>
       </c>
-      <c r="C3" s="164" t="inlineStr">
+      <c r="C3" s="167" t="inlineStr">
         <is>
           <t>FRED: 10Y Treasury (DGS10)</t>
         </is>
@@ -1505,7 +1555,7 @@
           <t>Damodaran ERP plus 177 bps US risk premium.</t>
         </is>
       </c>
-      <c r="C4" s="164" t="inlineStr">
+      <c r="C4" s="167" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
@@ -1525,7 +1575,7 @@
           <t>Q2 FY26 guide ~30%</t>
         </is>
       </c>
-      <c r="C5" s="164" t="inlineStr">
+      <c r="C5" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
@@ -1553,7 +1603,7 @@
           <t>NASDAQ last sale</t>
         </is>
       </c>
-      <c r="C8" s="164" t="inlineStr">
+      <c r="C8" s="167" t="inlineStr">
         <is>
           <t>NASDAQ LULU last sale (current price)</t>
         </is>
@@ -1573,7 +1623,7 @@
           <t>FY25 10-K shares</t>
         </is>
       </c>
-      <c r="C9" s="164" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: shares outstanding</t>
         </is>
@@ -1593,7 +1643,7 @@
           <t>Px × shares</t>
         </is>
       </c>
-      <c r="C10" s="165" t="inlineStr">
+      <c r="C10" s="168" t="inlineStr">
         <is>
           <t>WACC tab: price × shares</t>
         </is>
@@ -1614,7 +1664,7 @@
           <t>FY25 lease debt (10-K)</t>
         </is>
       </c>
-      <c r="C11" s="164" t="inlineStr">
+      <c r="C11" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: operating lease liabilities</t>
         </is>
@@ -1649,7 +1699,7 @@
           <t>Total debt equivalents</t>
         </is>
       </c>
-      <c r="C13" s="166" t="inlineStr">
+      <c r="C13" s="169" t="inlineStr">
         <is>
           <t>Lease + funded debt (above)</t>
         </is>
@@ -1698,7 +1748,7 @@
           <t>Yahoo total debt</t>
         </is>
       </c>
-      <c r="C17" s="164" t="inlineStr">
+      <c r="C17" s="167" t="inlineStr">
         <is>
           <t>Yahoo Finance: LULU Total Debt (mrq)</t>
         </is>
@@ -1718,7 +1768,7 @@
           <t>Yahoo Market Cap = $11.14B on the same.</t>
         </is>
       </c>
-      <c r="C18" s="164" t="inlineStr">
+      <c r="C18" s="167" t="inlineStr">
         <is>
           <t>Yahoo Finance: LULU Market Cap</t>
         </is>
@@ -1738,7 +1788,7 @@
           <t>Unlever D/E = Yahoo debt (mrq) ÷ Yahoo.</t>
         </is>
       </c>
-      <c r="C19" s="164" t="inlineStr">
+      <c r="C19" s="167" t="inlineStr">
         <is>
           <t>Yahoo Finance: debt (mrq) ÷ market cap</t>
         </is>
@@ -1759,7 +1809,7 @@
           <t>Yahoo Total Debt/Equity (mrq) = 44.69% is book.</t>
         </is>
       </c>
-      <c r="C20" s="164" t="inlineStr">
+      <c r="C20" s="167" t="inlineStr">
         <is>
           <t>Yahoo Finance: Total Debt/Equity (mrq)</t>
         </is>
@@ -1779,7 +1829,7 @@
           <t>βu = 0.86 ÷ [1 + 0.70 ×.</t>
         </is>
       </c>
-      <c r="C21" s="165" t="inlineStr">
+      <c r="C21" s="168" t="inlineStr">
         <is>
           <t>WACC tab: Hamada unlever (Yahoo market D/E)</t>
         </is>
@@ -1800,7 +1850,7 @@
           <t>FY25 lease D/E</t>
         </is>
       </c>
-      <c r="C22" s="165" t="inlineStr">
+      <c r="C22" s="168" t="inlineStr">
         <is>
           <t>WACC tab: FY25 lease debt / market equity</t>
         </is>
@@ -1821,7 +1871,7 @@
           <t>Benchmark only: Damodaran unlevered Retail (Special Lines) βu.</t>
         </is>
       </c>
-      <c r="C23" s="164" t="inlineStr">
+      <c r="C23" s="167" t="inlineStr">
         <is>
           <t>Damodaran: US betas by sector (Jan 2026)</t>
         </is>
@@ -1841,7 +1891,7 @@
           <t>Relevered β</t>
         </is>
       </c>
-      <c r="C24" s="165" t="inlineStr">
+      <c r="C24" s="168" t="inlineStr">
         <is>
           <t>WACC tab: Hamada relever (total D/E incl. leases)</t>
         </is>
@@ -1976,7 +2026,7 @@
           <t>Debt weight</t>
         </is>
       </c>
-      <c r="C35" s="164" t="inlineStr">
+      <c r="C35" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: operating lease liabilities</t>
         </is>
@@ -2032,7 +2082,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:I193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2092,7 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -2088,6 +2139,11 @@
           <t>Source</t>
         </is>
       </c>
+      <c r="I3" s="170" t="inlineStr">
+        <is>
+          <t>spot check</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -2100,7 +2156,7 @@
           <t>Q2 FY26 rev guide</t>
         </is>
       </c>
-      <c r="C4" s="164" t="inlineStr">
+      <c r="C4" s="167" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release</t>
         </is>
@@ -2108,12 +2164,16 @@
       <c r="E4" s="129" t="n">
         <v>-0.09</v>
       </c>
-      <c r="F4" s="129" t="n">
+      <c r="F4" s="171" t="n">
         <v>-0.061</v>
       </c>
       <c r="G4" s="129" t="n">
         <v>-0.04</v>
       </c>
+      <c r="I4" s="172">
+        <f>F25*F4</f>
+        <v/>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -2126,7 +2186,7 @@
           <t>2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast.</t>
         </is>
       </c>
-      <c r="C5" s="164" t="inlineStr">
+      <c r="C5" s="167" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU 3Y revenue forecast</t>
         </is>
@@ -2152,7 +2212,7 @@
           <t>Q2 FY26 run-rate OM</t>
         </is>
       </c>
-      <c r="C6" s="164" t="inlineStr">
+      <c r="C6" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs</t>
         </is>
@@ -2178,7 +2238,7 @@
           <t>FY26 tariff refund</t>
         </is>
       </c>
-      <c r="C7" s="164" t="inlineStr">
+      <c r="C7" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
         </is>
@@ -2204,7 +2264,7 @@
           <t>Partial OM recovery</t>
         </is>
       </c>
-      <c r="C8" s="164" t="inlineStr">
+      <c r="C8" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: Operating margin 19.9% (one hit)</t>
         </is>
@@ -2230,7 +2290,7 @@
           <t>Links to WACC tab</t>
         </is>
       </c>
-      <c r="C9" s="164" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>WACC tab: CAPM build</t>
         </is>
@@ -2257,7 +2317,7 @@
           <t>FRED GDPC1 ~2.1%</t>
         </is>
       </c>
-      <c r="C10" s="164" t="inlineStr">
+      <c r="C10" s="167" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -2265,7 +2325,7 @@
       <c r="E10" s="129" t="n">
         <v>0.015</v>
       </c>
-      <c r="F10" s="129" t="n">
+      <c r="F10" s="171" t="n">
         <v>0.0225</v>
       </c>
       <c r="G10" s="129" t="n">
@@ -2283,7 +2343,7 @@
           <t>Q2 FY26 guide ~30%</t>
         </is>
       </c>
-      <c r="C11" s="164" t="inlineStr">
+      <c r="C11" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
@@ -2309,7 +2369,7 @@
           <t>FY25 D&amp;A / sales</t>
         </is>
       </c>
-      <c r="C12" s="164" t="inlineStr">
+      <c r="C12" s="167" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)</t>
         </is>
@@ -2335,7 +2395,7 @@
           <t>5.5% model rate; FY26 7% capex guide fades down.</t>
         </is>
       </c>
-      <c r="C13" s="164" t="inlineStr">
+      <c r="C13" s="167" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
         </is>
@@ -2343,7 +2403,7 @@
       <c r="E13" s="129" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F13" s="129" t="n">
+      <c r="F13" s="171" t="n">
         <v>0.055</v>
       </c>
       <c r="G13" s="129" t="n">
@@ -2361,7 +2421,7 @@
           <t>Flat vs FY25</t>
         </is>
       </c>
-      <c r="C14" s="164" t="inlineStr">
+      <c r="C14" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
         </is>
@@ -2387,7 +2447,7 @@
           <t>6.3 days DSO held flat vs FY25 actual.</t>
         </is>
       </c>
-      <c r="C15" s="164" t="inlineStr">
+      <c r="C15" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
@@ -2413,7 +2473,7 @@
           <t>FY25 DIO −1d/yr</t>
         </is>
       </c>
-      <c r="C16" s="164" t="inlineStr">
+      <c r="C16" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories &amp; COGS</t>
         </is>
@@ -2439,7 +2499,7 @@
           <t>−1 day / yr</t>
         </is>
       </c>
-      <c r="C17" s="164" t="inlineStr">
+      <c r="C17" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: inventory &amp; markdown outlook</t>
         </is>
@@ -2465,7 +2525,7 @@
           <t>25.1 days DPO held flat vs FY25 actual.</t>
         </is>
       </c>
-      <c r="C18" s="164" t="inlineStr">
+      <c r="C18" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
         </is>
@@ -2491,7 +2551,7 @@
           <t>FY25 prepaids % rev</t>
         </is>
       </c>
-      <c r="C19" s="164" t="inlineStr">
+      <c r="C19" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
@@ -2517,7 +2577,7 @@
           <t>FY25 accrued % rev</t>
         </is>
       </c>
-      <c r="C20" s="164" t="inlineStr">
+      <c r="C20" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
@@ -5833,7 +5893,7 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J6" s="165" t="inlineStr">
+      <c r="J6" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
         </is>
@@ -5870,7 +5930,7 @@
           <t>Store openings skew to China (+20 FY26) vs.</t>
         </is>
       </c>
-      <c r="J7" s="164" t="inlineStr">
+      <c r="J7" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
         </is>
@@ -5907,7 +5967,7 @@
           <t>Closures assume 2–3 per mature region annually as.</t>
         </is>
       </c>
-      <c r="J8" s="164" t="inlineStr">
+      <c r="J8" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
         </is>
@@ -5952,7 +6012,7 @@
           <t>Simple roll-forward: where you started, plus openings, minus.</t>
         </is>
       </c>
-      <c r="J9" s="165" t="inlineStr">
+      <c r="J9" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
         </is>
@@ -5997,7 +6057,7 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J10" s="165" t="inlineStr">
+      <c r="J10" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
         </is>
@@ -6034,7 +6094,7 @@
           <t>Store openings skew to China (+20 FY26) vs.</t>
         </is>
       </c>
-      <c r="J11" s="164" t="inlineStr">
+      <c r="J11" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
         </is>
@@ -6071,7 +6131,7 @@
           <t>Closures assume 2–3 per mature region annually as.</t>
         </is>
       </c>
-      <c r="J12" s="164" t="inlineStr">
+      <c r="J12" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
         </is>
@@ -6116,7 +6176,7 @@
           <t>Simple roll-forward: where you started, plus openings, minus.</t>
         </is>
       </c>
-      <c r="J13" s="165" t="inlineStr">
+      <c r="J13" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
         </is>
@@ -6161,7 +6221,7 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J14" s="165" t="inlineStr">
+      <c r="J14" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
         </is>
@@ -6198,7 +6258,7 @@
           <t>Store openings skew to China (+20 FY26) vs.</t>
         </is>
       </c>
-      <c r="J15" s="164" t="inlineStr">
+      <c r="J15" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
         </is>
@@ -6235,7 +6295,7 @@
           <t>Closures assume 2–3 per mature region annually as.</t>
         </is>
       </c>
-      <c r="J16" s="164" t="inlineStr">
+      <c r="J16" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
         </is>
@@ -6280,7 +6340,7 @@
           <t>Simple roll-forward: where you started, plus openings, minus.</t>
         </is>
       </c>
-      <c r="J17" s="165" t="inlineStr">
+      <c r="J17" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
         </is>
@@ -6320,7 +6380,7 @@
           <t>Add up Americas + China + RoW ending.</t>
         </is>
       </c>
-      <c r="J18" s="165" t="inlineStr">
+      <c r="J18" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-stores formula</t>
         </is>
@@ -6360,7 +6420,7 @@
           <t>4,367 avg sq ft/store = implied FY25 total.</t>
         </is>
       </c>
-      <c r="J19" s="164" t="inlineStr">
+      <c r="J19" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: sales per square foot</t>
         </is>
@@ -6406,7 +6466,7 @@
           <t>Ending stores times avg sq ft per box..</t>
         </is>
       </c>
-      <c r="J20" s="165" t="inlineStr">
+      <c r="J20" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-sqft formula</t>
         </is>
@@ -6506,7 +6566,7 @@
           <t>FY26 SPSF $1,380 reflects Americas traffic/conversion pressure; recovers.</t>
         </is>
       </c>
-      <c r="J24" s="164" t="inlineStr">
+      <c r="J24" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: comparable sales &amp; SPSF</t>
         </is>
@@ -6546,7 +6606,7 @@
           <t>FY25 Americas comp −3% per 10-K (traffic, conversion,.</t>
         </is>
       </c>
-      <c r="J25" s="164" t="inlineStr">
+      <c r="J25" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: Americas comparable sales</t>
         </is>
@@ -6586,7 +6646,7 @@
           <t>FY25 China comp +20% (+19% CCY) per 10-K..</t>
         </is>
       </c>
-      <c r="J26" s="164" t="inlineStr">
+      <c r="J26" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: China Mainland comparable sales</t>
         </is>
@@ -6626,7 +6686,7 @@
           <t>FY25 RoW comp +9% (+7% CCY) per 10-K..</t>
         </is>
       </c>
-      <c r="J27" s="164" t="inlineStr">
+      <c r="J27" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: Rest of World comparable sales</t>
         </is>
@@ -6671,7 +6731,7 @@
           <t>Last year's total store-channel revenue; the base you're.</t>
         </is>
       </c>
-      <c r="J28" s="165" t="inlineStr">
+      <c r="J28" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: prior store-rev formula</t>
         </is>
@@ -6711,7 +6771,7 @@
           <t>Existing-store sales only; prior store rev grown by.</t>
         </is>
       </c>
-      <c r="J29" s="165" t="inlineStr">
+      <c r="J29" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: comp-store formula</t>
         </is>
@@ -6751,7 +6811,7 @@
           <t>Net new doors × sq ft × $/sq.</t>
         </is>
       </c>
-      <c r="J30" s="165" t="inlineStr">
+      <c r="J30" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: net-new-store formula</t>
         </is>
@@ -6791,7 +6851,7 @@
           <t>Brick-and-mortar channel = comp store sales plus whatever.</t>
         </is>
       </c>
-      <c r="J31" s="165" t="inlineStr">
+      <c r="J31" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: store-channel formula</t>
         </is>
@@ -6831,7 +6891,7 @@
           <t>Fleet traffic memo line; not a separate FCF.</t>
         </is>
       </c>
-      <c r="J32" s="164" t="inlineStr">
+      <c r="J32" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: store traffic commentary</t>
         </is>
@@ -6866,7 +6926,7 @@
           <t>In-store conversion memo; 10-K cites lower conversion in.</t>
         </is>
       </c>
-      <c r="J33" s="164" t="inlineStr">
+      <c r="J33" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: conversion rate commentary</t>
         </is>
@@ -6901,7 +6961,7 @@
           <t>In-store average transaction $115–$122; supports SPSF and comp-sales.</t>
         </is>
       </c>
-      <c r="J34" s="164" t="inlineStr">
+      <c r="J34" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: average order value commentary</t>
         </is>
@@ -7001,7 +7061,7 @@
           <t>485M FY25 sessions implied from reported e-comm revenue.</t>
         </is>
       </c>
-      <c r="J38" s="164" t="inlineStr">
+      <c r="J38" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
         </is>
@@ -7036,7 +7096,7 @@
           <t>3.3% FY26 digital conversion vs 3.5% pressure cited.</t>
         </is>
       </c>
-      <c r="J39" s="164" t="inlineStr">
+      <c r="J39" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: digital / traffic commentary</t>
         </is>
@@ -7071,7 +7131,7 @@
           <t>AOV $305 FY26 on promo intensity; steps to.</t>
         </is>
       </c>
-      <c r="J40" s="164" t="inlineStr">
+      <c r="J40" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
         </is>
@@ -7111,7 +7171,7 @@
           <t>Traffic × conversion × AOV is dollars. ×1M.</t>
         </is>
       </c>
-      <c r="J41" s="165" t="inlineStr">
+      <c r="J41" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: e-comm formula</t>
         </is>
@@ -7216,7 +7276,7 @@
           <t>Other channels (wholesale/license/outlets) held at FY25 $1.13B base;.</t>
         </is>
       </c>
-      <c r="J45" s="164" t="inlineStr">
+      <c r="J45" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: channel revenue table</t>
         </is>
@@ -7261,7 +7321,7 @@
           <t>Geographic split scales with consolidated growth; FY25 Americas.</t>
         </is>
       </c>
-      <c r="J46" s="164" t="inlineStr">
+      <c r="J46" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
         </is>
@@ -7306,7 +7366,7 @@
           <t>China 15.8% of FY25 revenue; fastest comp and.</t>
         </is>
       </c>
-      <c r="J47" s="164" t="inlineStr">
+      <c r="J47" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
         </is>
@@ -7351,7 +7411,7 @@
           <t>Rest of World 13.5% of FY25 revenue; mid-single-digit.</t>
         </is>
       </c>
-      <c r="J48" s="164" t="inlineStr">
+      <c r="J48" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
         </is>
@@ -7386,7 +7446,7 @@
           <t>Women's mix fades 62.5% to 60% as men's penetrates; FY25.</t>
         </is>
       </c>
-      <c r="J49" s="164" t="inlineStr">
+      <c r="J49" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
         </is>
@@ -7421,7 +7481,7 @@
           <t>Men's mix rises 24.5% to 27%; FY25 men's grew 4%.</t>
         </is>
       </c>
-      <c r="J50" s="164" t="inlineStr">
+      <c r="J50" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
         </is>
@@ -7456,7 +7516,7 @@
           <t>Accessories steady at 13% of revenue; FY25 accessories.</t>
         </is>
       </c>
-      <c r="J51" s="164" t="inlineStr">
+      <c r="J51" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
         </is>
@@ -7556,7 +7616,7 @@
           <t>Bottom-up total = store channel + e-comm +.</t>
         </is>
       </c>
-      <c r="J55" s="165" t="inlineStr">
+      <c r="J55" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-rev formula</t>
         </is>
@@ -7596,7 +7656,7 @@
           <t>Pulls the Scenarios base-case revenue path; that's still.</t>
         </is>
       </c>
-      <c r="J56" s="164" t="inlineStr">
+      <c r="J56" s="167" t="inlineStr">
         <is>
           <t>Scenarios tab: base revenue</t>
         </is>
@@ -7637,7 +7697,7 @@
           <t>Driver-built revenue minus Scenarios revenue. Shows you how.</t>
         </is>
       </c>
-      <c r="J57" s="165" t="inlineStr">
+      <c r="J57" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance formula</t>
         </is>
@@ -7678,7 +7738,7 @@
           <t>Variance as a percent of Scenarios revenue. Easy.</t>
         </is>
       </c>
-      <c r="J58" s="165" t="inlineStr">
+      <c r="J58" s="168" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance % formula</t>
         </is>
@@ -7862,7 +7922,7 @@
           <t>Not % of consolidated revenue; EBIT as %.</t>
         </is>
       </c>
-      <c r="C9" s="164" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: company-operated stores net revenue</t>
         </is>
@@ -7897,7 +7957,7 @@
           <t>Not % of consolidated revenue; EBIT as %.</t>
         </is>
       </c>
-      <c r="C10" s="164" t="inlineStr">
+      <c r="C10" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce net revenue</t>
         </is>
@@ -7932,7 +7992,7 @@
           <t>Not % of consolidated revenue; EBIT as %.</t>
         </is>
       </c>
-      <c r="C11" s="164" t="inlineStr">
+      <c r="C11" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: other channels (residual)</t>
         </is>
@@ -7967,7 +8027,7 @@
           <t>30% statutory marginal rate. t_operating transitions here over.</t>
         </is>
       </c>
-      <c r="C12" s="164" t="inlineStr">
+      <c r="C12" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
@@ -8002,7 +8062,7 @@
           <t>Not % of revenue; amortization period (years) if.</t>
         </is>
       </c>
-      <c r="C13" s="165" t="inlineStr">
+      <c r="C13" s="168" t="inlineStr">
         <is>
           <t>NOPAT Bridge: capitalization convention</t>
         </is>
@@ -8045,7 +8105,7 @@
           <t>10-K EBIT / Scenarios forecast.</t>
         </is>
       </c>
-      <c r="C16" s="164" t="inlineStr">
+      <c r="C16" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Income from operations</t>
         </is>
@@ -8085,7 +8145,7 @@
           <t>Run-rate intangible amort add-back.</t>
         </is>
       </c>
-      <c r="C17" s="164" t="inlineStr">
+      <c r="C17" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: amortization of intangible assets</t>
         </is>
@@ -8120,7 +8180,7 @@
           <t>Non-recurring restructuring add-back.</t>
         </is>
       </c>
-      <c r="C18" s="164" t="inlineStr">
+      <c r="C18" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: restructuring charges</t>
         </is>
@@ -8155,7 +8215,7 @@
           <t>One-off legal / M&amp;A strip.</t>
         </is>
       </c>
-      <c r="C19" s="164" t="inlineStr">
+      <c r="C19" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: SG&amp;A one-offs</t>
         </is>
@@ -8190,7 +8250,7 @@
           <t>SBC add-back (if flag = 1).</t>
         </is>
       </c>
-      <c r="C20" s="164" t="inlineStr">
+      <c r="C20" s="167" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K): stock-based compensation</t>
         </is>
@@ -8227,12 +8287,12 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Reported EBIT plus non-recurring add-backs.</t>
-        </is>
-      </c>
-      <c r="C21" s="165" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: Phase 1 subtotal</t>
+          <t>Reported EBIT plus all listed non-recurring add-backs above.</t>
+        </is>
+      </c>
+      <c r="C21" s="168" t="inlineStr">
+        <is>
+          <t>Sum of reported EBIT and add-backs above.</t>
         </is>
       </c>
       <c r="E21" s="130">
@@ -8274,7 +8334,7 @@
           <t>Lease interest reclass (memo).</t>
         </is>
       </c>
-      <c r="C23" s="164" t="inlineStr">
+      <c r="C23" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: interest on lease liabilities (supplemental)</t>
         </is>
@@ -8314,7 +8374,7 @@
           <t>R&amp;D cap immaterial this yr.</t>
         </is>
       </c>
-      <c r="C24" s="164" t="inlineStr">
+      <c r="C24" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: R&amp;D / software expense</t>
         </is>
@@ -8349,7 +8409,7 @@
           <t>Amortization of prior capitalized intangibles. LULU: flows through.</t>
         </is>
       </c>
-      <c r="C25" s="164" t="inlineStr">
+      <c r="C25" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: intangible amortization</t>
         </is>
@@ -8380,12 +8440,12 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Phase 1 plus lease / R&amp;D adjustments.</t>
-        </is>
-      </c>
-      <c r="C26" s="165" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: Phase 2 subtotal</t>
+          <t>Reported EBIT plus lease interest and R&amp;D adjustments.</t>
+        </is>
+      </c>
+      <c r="C26" s="168" t="inlineStr">
+        <is>
+          <t>Sum after lease and R&amp;D adjustments above.</t>
         </is>
       </c>
       <c r="E26" s="130">
@@ -8427,7 +8487,7 @@
           <t>Store rev from Revenue Drivers.</t>
         </is>
       </c>
-      <c r="C28" s="164" t="inlineStr">
+      <c r="C28" s="167" t="inlineStr">
         <is>
           <t>Revenue Drivers tab: store-channel revenue</t>
         </is>
@@ -8467,7 +8527,7 @@
           <t>E-comm rev from Revenue Drivers.</t>
         </is>
       </c>
-      <c r="C29" s="164" t="inlineStr">
+      <c r="C29" s="167" t="inlineStr">
         <is>
           <t>Revenue Drivers tab: e-commerce revenue</t>
         </is>
@@ -8507,7 +8567,7 @@
           <t>Other rev from Revenue Drivers.</t>
         </is>
       </c>
-      <c r="C30" s="164" t="inlineStr">
+      <c r="C30" s="167" t="inlineStr">
         <is>
           <t>Revenue Drivers tab: other channels revenue</t>
         </is>
@@ -8547,7 +8607,7 @@
           <t>Not % of consolidated revenue; store EBIT ÷.</t>
         </is>
       </c>
-      <c r="C31" s="164" t="inlineStr">
+      <c r="C31" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: company-operated stores net revenue</t>
         </is>
@@ -8587,7 +8647,7 @@
           <t>Not % of consolidated revenue; e-commerce EBIT ÷.</t>
         </is>
       </c>
-      <c r="C32" s="164" t="inlineStr">
+      <c r="C32" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce net revenue</t>
         </is>
@@ -8627,7 +8687,7 @@
           <t>Not % of consolidated revenue; other-channel EBIT ÷.</t>
         </is>
       </c>
-      <c r="C33" s="164" t="inlineStr">
+      <c r="C33" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: other channels (residual)</t>
         </is>
@@ -8664,12 +8724,12 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Sum of sector EBIT (Phase 3).</t>
-        </is>
-      </c>
-      <c r="C34" s="165" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: sector EBIT subtotal</t>
+          <t>Sum of store, e-comm, and other channel EBIT lines.</t>
+        </is>
+      </c>
+      <c r="C34" s="168" t="inlineStr">
+        <is>
+          <t>Sum of channel EBIT lines above.</t>
         </is>
       </c>
       <c r="E34" s="138">
@@ -8700,12 +8760,12 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Channel-mix EBIT output (Phase 3).</t>
-        </is>
-      </c>
-      <c r="C35" s="165" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: Phase 3 subtotal</t>
+          <t>Channel-mix EBIT output line before tax normalization step.</t>
+        </is>
+      </c>
+      <c r="C35" s="168" t="inlineStr">
+        <is>
+          <t>Sum of channel EBIT lines above.</t>
         </is>
       </c>
       <c r="D35" s="160" t="n">
@@ -8742,7 +8802,7 @@
           <t>FY25 walk-through Phases 1–2.</t>
         </is>
       </c>
-      <c r="C36" s="165" t="inlineStr">
+      <c r="C36" s="168" t="inlineStr">
         <is>
           <t>Scenarios tab: base-case EBIT (forecast)</t>
         </is>
@@ -8817,7 +8877,7 @@
           <t>Operating ETR with interest shield.</t>
         </is>
       </c>
-      <c r="C39" s="164" t="inlineStr">
+      <c r="C39" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: income tax &amp; interest expense</t>
         </is>
@@ -8857,7 +8917,7 @@
           <t>Normalized EBIT × t_operating.</t>
         </is>
       </c>
-      <c r="C40" s="165" t="inlineStr">
+      <c r="C40" s="168" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab: unlevered tax expense</t>
         </is>
@@ -8894,7 +8954,7 @@
           <t>EBIT_norm × (1 − t_operating).</t>
         </is>
       </c>
-      <c r="C41" s="165" t="inlineStr">
+      <c r="C41" s="168" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab: normalized NOPAT</t>
         </is>
@@ -9238,7 +9298,7 @@
           <t>Minus 6.1% FY26 revenue per company guidance midpoint.</t>
         </is>
       </c>
-      <c r="C6" s="164" t="inlineStr">
+      <c r="C6" s="167" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release Also: StockAnalysis: LULU 3Y revenue forecast</t>
         </is>
@@ -9275,7 +9335,7 @@
           <t>56.6% FY25 gross margin held flat in forecast.</t>
         </is>
       </c>
-      <c r="C7" s="164" t="inlineStr">
+      <c r="C7" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
         </is>
@@ -9345,7 +9405,7 @@
           <t>13.2% clean OM from Q2 run-rate ex tariff.</t>
         </is>
       </c>
-      <c r="C9" s="164" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs Also: FY2025 10-K: Operating margin 19.9% (one hit)</t>
         </is>
@@ -9382,7 +9442,7 @@
           <t>Add back 134.5M tariff refund in FY26 only.</t>
         </is>
       </c>
-      <c r="C10" s="164" t="inlineStr">
+      <c r="C10" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
         </is>
@@ -9532,7 +9592,7 @@
           <t>4.5% of sales from FY25 D&amp;A over revenue.</t>
         </is>
       </c>
-      <c r="C15" s="164" t="inlineStr">
+      <c r="C15" s="167" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)</t>
         </is>
@@ -9596,7 +9656,7 @@
           <t>5.5% model rate; FY26 7% capex guide fades down.</t>
         </is>
       </c>
-      <c r="C17" s="164" t="inlineStr">
+      <c r="C17" s="167" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
         </is>
@@ -9677,7 +9737,7 @@
           <t>6.3 days DSO held flat vs FY25 actual.</t>
         </is>
       </c>
-      <c r="C20" s="164" t="inlineStr">
+      <c r="C20" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
@@ -9717,7 +9777,7 @@
           <t>AR 1.7% of sales from FY25 balance sheet.</t>
         </is>
       </c>
-      <c r="C21" s="164" t="inlineStr">
+      <c r="C21" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
@@ -9757,7 +9817,7 @@
           <t>128.8 day DIO anchor; minus 1 day per year.</t>
         </is>
       </c>
-      <c r="C22" s="164" t="inlineStr">
+      <c r="C22" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories &amp; COGS Also: LULU FY2025 10-K: inventory &amp; markdown outlook</t>
         </is>
@@ -9797,7 +9857,7 @@
           <t>Inventory dollar balance driven by DIO times COGS.</t>
         </is>
       </c>
-      <c r="C23" s="164" t="inlineStr">
+      <c r="C23" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories</t>
         </is>
@@ -9837,7 +9897,7 @@
           <t>25.1 days DPO held flat vs FY25 actual.</t>
         </is>
       </c>
-      <c r="C24" s="164" t="inlineStr">
+      <c r="C24" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
         </is>
@@ -9877,7 +9937,7 @@
           <t>AP 3.0% of sales from FY25 payables balance.</t>
         </is>
       </c>
-      <c r="C25" s="164" t="inlineStr">
+      <c r="C25" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable</t>
         </is>
@@ -9917,7 +9977,7 @@
           <t>5.1% of revenue from FY25 other current assets.</t>
         </is>
       </c>
-      <c r="C26" s="164" t="inlineStr">
+      <c r="C26" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
@@ -9957,7 +10017,7 @@
           <t>5.1% of revenue from FY25 other current assets.</t>
         </is>
       </c>
-      <c r="C27" s="164" t="inlineStr">
+      <c r="C27" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
@@ -9997,7 +10057,7 @@
           <t>6.0% of revenue from FY25 accrued liabilities balance.</t>
         </is>
       </c>
-      <c r="C28" s="164" t="inlineStr">
+      <c r="C28" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
@@ -10037,7 +10097,7 @@
           <t>6.0% of revenue from FY25 accrued liabilities balance.</t>
         </is>
       </c>
-      <c r="C29" s="164" t="inlineStr">
+      <c r="C29" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
@@ -10077,7 +10137,7 @@
           <t>Operating assets sum to 22.1% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C30" s="164" t="inlineStr">
+      <c r="C30" s="167" t="inlineStr">
         <is>
           <t>Scenarios tab: AR + inventory + prepaids</t>
         </is>
@@ -10114,7 +10174,7 @@
           <t>Operating liabilities sum to 9.0% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C31" s="164" t="inlineStr">
+      <c r="C31" s="167" t="inlineStr">
         <is>
           <t>Scenarios tab: AP + accrued liabilities</t>
         </is>
@@ -10151,7 +10211,7 @@
           <t>Net working capital equals 13.2% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C32" s="164" t="inlineStr">
+      <c r="C32" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: working-capital components</t>
         </is>
@@ -10191,7 +10251,7 @@
           <t>Year-over-year dollar change in net working capital schedule.</t>
         </is>
       </c>
-      <c r="C33" s="164" t="inlineStr">
+      <c r="C33" s="167" t="inlineStr">
         <is>
           <t>Scenarios tab: NWC roll-forward (driver schedule)</t>
         </is>
@@ -10360,7 +10420,7 @@
           <t>2.25% terminal g anchored to FRED GDPC1 macro series.</t>
         </is>
       </c>
-      <c r="C43" s="164" t="inlineStr">
+      <c r="C43" s="167" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -10442,7 +10502,7 @@
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="C50" s="164" t="inlineStr">
+      <c r="C50" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -10462,7 +10522,7 @@
           <t>Subtract ASC 842 operating lease liabilities as debt.</t>
         </is>
       </c>
-      <c r="C51" s="164" t="inlineStr">
+      <c r="C51" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: operating lease liabilities</t>
         </is>
@@ -10498,7 +10558,7 @@
           <t>Shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C55" s="164" t="inlineStr">
+      <c r="C55" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -10524,7 +10584,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C57" s="164" t="inlineStr">
+      <c r="C57" s="167" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -10918,7 +10978,7 @@
           <t>Gordon terminal value divided by FY30 EBITDA multiple.</t>
         </is>
       </c>
-      <c r="C82" s="164" t="inlineStr">
+      <c r="C82" s="167" t="inlineStr">
         <is>
           <t>DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
         </is>
@@ -11062,7 +11122,7 @@
           <t>Sensitivity grid; terminal g spans 1.5% to 3.0%.</t>
         </is>
       </c>
-      <c r="C98" s="164" t="inlineStr">
+      <c r="C98" s="167" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -11087,7 +11147,7 @@
       <c r="A99" s="109" t="n">
         <v>0.095</v>
       </c>
-      <c r="C99" s="164" t="inlineStr">
+      <c r="C99" s="167" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
@@ -11308,7 +11368,7 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="C4" s="164" t="inlineStr">
+      <c r="C4" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -11350,7 +11410,7 @@
           <t>FY2026E diluted EPS (guidance midpoint)</t>
         </is>
       </c>
-      <c r="C7" s="164" t="inlineStr">
+      <c r="C7" s="167" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
@@ -11365,7 +11425,7 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C8" s="164" t="inlineStr">
+      <c r="C8" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -11380,7 +11440,7 @@
           <t>Shares outstanding (000)</t>
         </is>
       </c>
-      <c r="C9" s="164" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -11395,7 +11455,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="C10" s="164" t="inlineStr">
+      <c r="C10" s="167" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -11504,7 +11564,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C19" s="165" t="inlineStr">
+      <c r="C19" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11531,7 +11591,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C20" s="165" t="inlineStr">
+      <c r="C20" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11558,7 +11618,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C21" s="165" t="inlineStr">
+      <c r="C21" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11585,7 +11645,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C22" s="165" t="inlineStr">
+      <c r="C22" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11612,7 +11672,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C23" s="165" t="inlineStr">
+      <c r="C23" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11639,7 +11699,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C24" s="165" t="inlineStr">
+      <c r="C24" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11666,7 +11726,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C25" s="165" t="inlineStr">
+      <c r="C25" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11693,7 +11753,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C26" s="165" t="inlineStr">
+      <c r="C26" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11720,7 +11780,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C27" s="165" t="inlineStr">
+      <c r="C27" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11747,7 +11807,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C28" s="165" t="inlineStr">
+      <c r="C28" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11774,7 +11834,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C29" s="165" t="inlineStr">
+      <c r="C29" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -11812,7 +11872,7 @@
           <t>Reuters: about $10 billion Moelis ask for Color.</t>
         </is>
       </c>
-      <c r="C33" s="164" t="inlineStr">
+      <c r="C33" s="167" t="inlineStr">
         <is>
           <t>Reuters: Alo parent $10bn Moelis ask Also: Reuters: Alo 2023 process; no deal</t>
         </is>
@@ -11832,7 +11892,7 @@
           <t>Forbes estimates Color Image parent sales nearly $2.</t>
         </is>
       </c>
-      <c r="C34" s="164" t="inlineStr">
+      <c r="C34" s="167" t="inlineStr">
         <is>
           <t>Forbes: Color Image nearly $2bn sales</t>
         </is>
@@ -11852,7 +11912,7 @@
           <t>5.0x = 10 / 2. Implied EV/Sales on.</t>
         </is>
       </c>
-      <c r="C35" s="164" t="inlineStr">
+      <c r="C35" s="167" t="inlineStr">
         <is>
           <t>Comps: Alo ask / parent sales</t>
         </is>
@@ -11873,7 +11933,7 @@
           <t>No page prints Alo or Color Image EBITDA..</t>
         </is>
       </c>
-      <c r="C36" s="165" t="inlineStr">
+      <c r="C36" s="168" t="inlineStr">
         <is>
           <t>None — no EBITDA source</t>
         </is>
@@ -12070,7 +12130,7 @@
 Hi 8.0x DECK high-end cap.</t>
         </is>
       </c>
-      <c r="C57" s="164" t="inlineStr">
+      <c r="C57" s="167" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA Hi: StockAnalysis: DECK EV/EBITDA</t>
         </is>
@@ -12101,7 +12161,7 @@
           <t>Gordon TV / FY30 EBITDA exit.</t>
         </is>
       </c>
-      <c r="C58" s="164" t="inlineStr">
+      <c r="C58" s="167" t="inlineStr">
         <is>
           <t>DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
         </is>
@@ -12127,7 +12187,7 @@
 Hi 18x FY26E EPS recovery.</t>
         </is>
       </c>
-      <c r="C59" s="164" t="inlineStr">
+      <c r="C59" s="167" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E Hi: StockAnalysis: NKE Forward P/E</t>
         </is>
@@ -12171,7 +12231,7 @@
           <t>Current price</t>
         </is>
       </c>
-      <c r="C62" s="164" t="inlineStr">
+      <c r="C62" s="167" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -12202,4 +12262,74 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="173" t="inlineStr">
+        <is>
+          <t>Quick checks (not in model)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="174" t="inlineStr">
+        <is>
+          <t>Mkt cap ($k)</t>
+        </is>
+      </c>
+      <c r="B3" s="175">
+        <f>WACC!D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="174" t="inlineStr">
+        <is>
+          <t>FY26 rev growth check</t>
+        </is>
+      </c>
+      <c r="B4" s="175">
+        <f>Scenarios!F4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="174" t="inlineStr">
+        <is>
+          <t>Terminal g</t>
+        </is>
+      </c>
+      <c r="B5" s="175">
+        <f>Scenarios!F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="174" t="inlineStr">
+        <is>
+          <t>Implied px (DCF)</t>
+        </is>
+      </c>
+      <c r="B6" s="175">
+        <f>DCF!D56</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -1368,14 +1368,13 @@
     <outlinePr summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="B2:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1383,7 +1382,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1398,7 +1396,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1406,7 +1403,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="n"/>
     </row>
@@ -1419,7 +1415,6 @@
     <row r="12">
       <c r="B12" s="8" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="B14" s="5" t="n"/>
     </row>
@@ -1432,7 +1427,6 @@
     <row r="17" ht="15" customHeight="1">
       <c r="B17" s="10" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -1468,7 +1462,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="B25" s="11" t="n"/>
     </row>
@@ -1584,7 +1577,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1709,7 +1701,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -1937,7 +1928,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -1981,7 +1971,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
@@ -2624,7 +2613,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4627,7 +4615,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4685,11 +4672,9 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="n"/>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5794,7 +5779,6 @@
     <row r="2">
       <c r="A2" s="26" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -6472,7 +6456,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6967,7 +6950,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7177,7 +7159,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7522,7 +7503,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7875,7 +7855,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -8086,7 +8065,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8980,7 +8958,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -10383,7 +10360,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -10615,8 +10591,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -10628,7 +10602,6 @@
     <row r="63">
       <c r="A63" s="26" t="n"/>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10689,7 +10662,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10774,7 +10746,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10895,7 +10866,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10956,7 +10926,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -11032,7 +11001,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -11042,6 +11010,21 @@
     </row>
     <row r="89">
       <c r="A89" s="103" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Gordon Growth</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="23" t="inlineStr">
@@ -11050,11 +11033,15 @@
         </is>
       </c>
       <c r="B90">
-        <f>E45</f>
+        <f>D45</f>
         <v/>
       </c>
       <c r="C90" s="126">
-        <f>E83</f>
+        <f>D83</f>
+        <v/>
+      </c>
+      <c r="D90">
+        <f>B90-C90</f>
         <v/>
       </c>
     </row>
@@ -11065,11 +11052,15 @@
         </is>
       </c>
       <c r="B91">
-        <f>E46</f>
+        <f>D46</f>
         <v/>
       </c>
       <c r="C91" s="126">
-        <f>E82</f>
+        <f>D82</f>
+        <v/>
+      </c>
+      <c r="D91">
+        <f>B91-C91</f>
         <v/>
       </c>
     </row>
@@ -11079,6 +11070,10 @@
           <t>Terminal value variance (%)</t>
         </is>
       </c>
+      <c r="D92">
+        <f>(B90-C90)/B90</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="23" t="inlineStr">
@@ -11087,19 +11082,34 @@
         </is>
       </c>
       <c r="B93">
-        <f>E56</f>
+        <f>D56</f>
         <v/>
       </c>
       <c r="C93" s="126">
-        <f>E86</f>
+        <f>D86</f>
+        <v/>
+      </c>
+      <c r="D93">
+        <f>B93-C93</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="68" t="n"/>
-    </row>
-    <row r="95"/>
-    <row r="96"/>
+      <c r="B94">
+        <f>IF(ABS(D91)&lt;=1.5,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+      <c r="C94">
+        <f>TEXT(D91,"0.0")&amp;"x spread vs Gordon-implied exit"</f>
+        <v/>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Selected exit is the Gordon identity, so spread should be 0</t>
+        </is>
+      </c>
+    </row>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -11486,7 +11496,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11850,7 +11859,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -11944,7 +11952,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -12007,7 +12014,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -12073,7 +12079,6 @@
     <row r="53">
       <c r="A53" s="41" t="n"/>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -12224,7 +12229,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>
@@ -12284,7 +12288,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="174" t="inlineStr">
         <is>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -1577,6 +1577,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1635,11 +1636,7 @@
           <t>Px × shares</t>
         </is>
       </c>
-      <c r="C10" s="168" t="inlineStr">
-        <is>
-          <t>WACC tab: price × shares</t>
-        </is>
-      </c>
+      <c r="C10" s="168" t="n"/>
       <c r="D10" s="130">
         <f>D8*D9</f>
         <v/>
@@ -1701,6 +1698,7 @@
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -1928,6 +1926,7 @@
         <v/>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -1971,6 +1970,7 @@
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
@@ -2613,6 +2613,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4615,6 +4616,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4672,9 +4674,11 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="n"/>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5779,6 +5783,7 @@
     <row r="2">
       <c r="A2" s="26" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -5877,11 +5882,7 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J6" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: beginning-stores formula</t>
-        </is>
-      </c>
+      <c r="J6" s="168" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="41" t="inlineStr">
@@ -5911,7 +5912,7 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>Store openings skew to China (+20 FY26) vs.</t>
+          <t>China plus twenty store openings FY26; Americas and RoW open slower.</t>
         </is>
       </c>
       <c r="J7" s="167" t="inlineStr">
@@ -5948,7 +5949,7 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>Closures assume 2–3 per mature region annually as.</t>
+          <t>Assume two to three store closures per mature region annually.</t>
         </is>
       </c>
       <c r="J8" s="167" t="inlineStr">
@@ -5993,14 +5994,10 @@
       </c>
       <c r="I9" s="9" t="inlineStr">
         <is>
-          <t>Simple roll-forward: where you started, plus openings, minus.</t>
-        </is>
-      </c>
-      <c r="J9" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: ending-stores formula</t>
-        </is>
-      </c>
+          <t>Beginning stores plus regional openings minus closures each year.</t>
+        </is>
+      </c>
+      <c r="J9" s="168" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="41" t="inlineStr">
@@ -6041,11 +6038,7 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J10" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: beginning-stores formula</t>
-        </is>
-      </c>
+      <c r="J10" s="168" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="41" t="inlineStr">
@@ -6075,7 +6068,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Store openings skew to China (+20 FY26) vs.</t>
+          <t>China plus twenty store openings FY26; Americas and RoW open slower.</t>
         </is>
       </c>
       <c r="J11" s="167" t="inlineStr">
@@ -6112,7 +6105,7 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Closures assume 2–3 per mature region annually as.</t>
+          <t>Assume two to three store closures per mature region annually.</t>
         </is>
       </c>
       <c r="J12" s="167" t="inlineStr">
@@ -6157,14 +6150,10 @@
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>Simple roll-forward: where you started, plus openings, minus.</t>
-        </is>
-      </c>
-      <c r="J13" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: ending-stores formula</t>
-        </is>
-      </c>
+          <t>Beginning stores plus regional openings minus closures each year.</t>
+        </is>
+      </c>
+      <c r="J13" s="168" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="41" t="inlineStr">
@@ -6205,11 +6194,7 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J14" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: beginning-stores formula</t>
-        </is>
-      </c>
+      <c r="J14" s="168" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="41" t="inlineStr">
@@ -6239,7 +6224,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>Store openings skew to China (+20 FY26) vs.</t>
+          <t>China plus twenty store openings FY26; Americas and RoW open slower.</t>
         </is>
       </c>
       <c r="J15" s="167" t="inlineStr">
@@ -6276,7 +6261,7 @@
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Closures assume 2–3 per mature region annually as.</t>
+          <t>Assume two to three store closures per mature region annually.</t>
         </is>
       </c>
       <c r="J16" s="167" t="inlineStr">
@@ -6321,14 +6306,10 @@
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
-          <t>Simple roll-forward: where you started, plus openings, minus.</t>
-        </is>
-      </c>
-      <c r="J17" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: ending-stores formula</t>
-        </is>
-      </c>
+          <t>Beginning stores plus regional openings minus closures each year.</t>
+        </is>
+      </c>
+      <c r="J17" s="168" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="61" t="inlineStr">
@@ -6364,11 +6345,7 @@
           <t>Add up Americas + China + RoW ending.</t>
         </is>
       </c>
-      <c r="J18" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: total-stores formula</t>
-        </is>
-      </c>
+      <c r="J18" s="168" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="41" t="inlineStr">
@@ -6447,15 +6424,12 @@
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>Ending stores times avg sq ft per box..</t>
-        </is>
-      </c>
-      <c r="J20" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: total-sqft formula</t>
-        </is>
-      </c>
-    </row>
+          <t>Total sq ft equals ending store count times average box size.</t>
+        </is>
+      </c>
+      <c r="J20" s="168" t="n"/>
+    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6626,7 +6600,7 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>FY25 China comp +20% (+19% CCY) per 10-K..</t>
+          <t>FY25 China comparable sales plus twenty percent per FY25 10-K.</t>
         </is>
       </c>
       <c r="J26" s="167" t="inlineStr">
@@ -6666,7 +6640,7 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>FY25 RoW comp +9% (+7% CCY) per 10-K..</t>
+          <t>FY25 rest of world comp plus nine percent per FY25 10-K.</t>
         </is>
       </c>
       <c r="J27" s="167" t="inlineStr">
@@ -6714,11 +6688,7 @@
           <t>Last year's total store-channel revenue; the base you're.</t>
         </is>
       </c>
-      <c r="J28" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: prior store-rev formula</t>
-        </is>
-      </c>
+      <c r="J28" s="168" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="41" t="inlineStr">
@@ -6754,11 +6724,7 @@
           <t>Existing-store sales only; prior store rev grown by.</t>
         </is>
       </c>
-      <c r="J29" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: comp-store formula</t>
-        </is>
-      </c>
+      <c r="J29" s="168" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="41" t="inlineStr">
@@ -6794,11 +6760,7 @@
           <t>Net new doors × sq ft × $/sq.</t>
         </is>
       </c>
-      <c r="J30" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: net-new-store formula</t>
-        </is>
-      </c>
+      <c r="J30" s="168" t="n"/>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="61" t="inlineStr">
@@ -6834,11 +6796,7 @@
           <t>Brick-and-mortar channel = comp store sales plus whatever.</t>
         </is>
       </c>
-      <c r="J31" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: store-channel formula</t>
-        </is>
-      </c>
+      <c r="J31" s="168" t="n"/>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="41" t="inlineStr">
@@ -6950,6 +6908,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7153,12 +7112,9 @@
           <t>Traffic × conversion × AOV is dollars. ×1M.</t>
         </is>
       </c>
-      <c r="J41" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: e-comm formula</t>
-        </is>
-      </c>
-    </row>
+      <c r="J41" s="168" t="n"/>
+    </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7503,6 +7459,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7596,11 +7553,7 @@
           <t>Bottom-up total = store channel + e-comm +.</t>
         </is>
       </c>
-      <c r="J55" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: total-rev formula</t>
-        </is>
-      </c>
+      <c r="J55" s="168" t="n"/>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="41" t="inlineStr">
@@ -7677,11 +7630,7 @@
           <t>Driver-built revenue minus Scenarios revenue. Shows you how.</t>
         </is>
       </c>
-      <c r="J57" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: variance formula</t>
-        </is>
-      </c>
+      <c r="J57" s="168" t="n"/>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="41" t="inlineStr">
@@ -7718,11 +7667,7 @@
           <t>Variance as a percent of Scenarios revenue. Easy.</t>
         </is>
       </c>
-      <c r="J58" s="168" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: variance % formula</t>
-        </is>
-      </c>
+      <c r="J58" s="168" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="26" t="n"/>
@@ -7855,6 +7800,7 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -8065,6 +8011,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8582,7 +8529,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Not % of consolidated revenue; store EBIT ÷.</t>
+          <t>Store EBIT margin applied to store channel revenue only.</t>
         </is>
       </c>
       <c r="C31" s="167" t="inlineStr">
@@ -8622,7 +8569,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Not % of consolidated revenue; e-commerce EBIT ÷.</t>
+          <t>E-commerce EBIT margin applied to e-comm channel revenue only.</t>
         </is>
       </c>
       <c r="C32" s="167" t="inlineStr">
@@ -8662,7 +8609,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Not % of consolidated revenue; other-channel EBIT ÷.</t>
+          <t>Other-channel EBIT margin applied to other channel revenue only.</t>
         </is>
       </c>
       <c r="C33" s="167" t="inlineStr">
@@ -8895,11 +8842,7 @@
           <t>Normalized EBIT × t_operating.</t>
         </is>
       </c>
-      <c r="C40" s="168" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: unlevered tax expense</t>
-        </is>
-      </c>
+      <c r="C40" s="168" t="n"/>
       <c r="E40" s="75">
         <f>E36*E39</f>
         <v/>
@@ -8932,11 +8875,7 @@
           <t>EBIT_norm × (1 − t_operating).</t>
         </is>
       </c>
-      <c r="C41" s="168" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: normalized NOPAT</t>
-        </is>
-      </c>
+      <c r="C41" s="168" t="n"/>
       <c r="E41" s="130">
         <f>E36-E40</f>
         <v/>
@@ -8958,6 +8897,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -10360,6 +10300,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -10591,6 +10532,8 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -10602,6 +10545,7 @@
     <row r="63">
       <c r="A63" s="26" t="n"/>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10662,6 +10606,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10746,6 +10691,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10866,6 +10812,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10926,6 +10873,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -11001,6 +10949,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -11110,6 +11059,8 @@
         </is>
       </c>
     </row>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -11496,6 +11447,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11859,6 +11811,7 @@
         <v>407521</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -11938,7 +11891,7 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>No page prints Alo or Color Image EBITDA..</t>
+          <t>Alo Yoga excluded from comp set; no reliable EBITDA on pages.</t>
         </is>
       </c>
       <c r="C36" s="168" t="inlineStr">
@@ -11952,6 +11905,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -12014,6 +11968,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -12079,6 +12034,7 @@
     <row r="53">
       <c r="A53" s="41" t="n"/>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -12229,6 +12185,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -1577,7 +1577,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1698,7 +1697,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
@@ -1754,7 +1752,7 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Yahoo Market Cap = $11.14B on the same.</t>
+          <t>Yahoo market cap from same page as beta and debt.</t>
         </is>
       </c>
       <c r="C18" s="167" t="inlineStr">
@@ -1774,7 +1772,7 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Unlever D/E = Yahoo debt (mrq) ÷ Yahoo.</t>
+          <t>Yahoo total debt divided by Yahoo market cap ratio.</t>
         </is>
       </c>
       <c r="C19" s="167" t="inlineStr">
@@ -1815,7 +1813,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>βu = 0.86 ÷ [1 + 0.70 ×.</t>
+          <t>Hamada unlever beta using Yahoo market D/E and tax rate.</t>
         </is>
       </c>
       <c r="C21" s="168" t="inlineStr">
@@ -1926,7 +1924,6 @@
         <v/>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
         <is>
@@ -1970,7 +1967,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
@@ -2128,11 +2124,7 @@
           <t>Source</t>
         </is>
       </c>
-      <c r="I3" s="170" t="inlineStr">
-        <is>
-          <t>spot check</t>
-        </is>
-      </c>
+      <c r="I3" s="170" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -2159,10 +2151,7 @@
       <c r="G4" s="129" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I4" s="172">
-        <f>F25*F4</f>
-        <v/>
-      </c>
+      <c r="I4" s="172" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -2613,7 +2602,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -2628,15 +2616,15 @@
         </is>
       </c>
       <c r="E25" s="75">
-        <f>11102600*(1+E4)</f>
+        <f>DCF!$D$5*(1+E4)</f>
         <v/>
       </c>
       <c r="F25" s="75">
-        <f>11102600*(1+F4)</f>
+        <f>DCF!$D$5*(1+F4)</f>
         <v/>
       </c>
       <c r="G25" s="75">
-        <f>11102600*(1+G4)</f>
+        <f>DCF!$D$5*(1+G4)</f>
         <v/>
       </c>
     </row>
@@ -4616,7 +4604,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4674,11 +4661,9 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="n"/>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5783,7 +5768,6 @@
     <row r="2">
       <c r="A2" s="26" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="52" t="inlineStr">
         <is>
@@ -6429,7 +6413,6 @@
       </c>
       <c r="J20" s="168" t="n"/>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6908,7 +6891,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -7114,7 +7096,6 @@
       </c>
       <c r="J41" s="168" t="n"/>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7459,7 +7440,6 @@
         </is>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7800,7 +7780,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -8011,7 +7990,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8206,9 +8184,10 @@
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="23">
-        <f> Adjusted EBIT (Phase 1)</f>
-        <v/>
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Adjusted EBIT (Phase 1)</t>
+        </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
@@ -8359,9 +8338,10 @@
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="23">
-        <f> EBIT after lease &amp; capitalization (Phase 2)</f>
-        <v/>
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>EBIT after lease &amp; capitalization (Phase 2)</t>
+        </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
@@ -8679,9 +8659,10 @@
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="23">
-        <f> EBIT after channel mix (Phase 3)</f>
-        <v/>
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>EBIT after channel mix (Phase 3)</t>
+        </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
@@ -8718,9 +8699,10 @@
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="23">
-        <f> Normalized EBIT (tax base for NOPAT)</f>
-        <v/>
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Normalized EBIT (tax base for NOPAT)</t>
+        </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
@@ -8897,7 +8879,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>
@@ -10300,7 +10281,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -10532,8 +10512,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -10545,7 +10523,6 @@
     <row r="63">
       <c r="A63" s="26" t="n"/>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10606,7 +10583,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10691,7 +10667,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10812,7 +10787,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10873,7 +10847,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -10949,7 +10922,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -11059,8 +11031,6 @@
         </is>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -11345,7 +11315,7 @@
         </is>
       </c>
       <c r="D5" s="75">
-        <f>2210615+496228</f>
+        <f>DCF!D11+496228</f>
         <v/>
       </c>
     </row>
@@ -11447,7 +11417,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11811,7 +11780,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -11905,7 +11873,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -11968,7 +11935,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -12034,7 +12000,6 @@
     <row r="53">
       <c r="A53" s="41" t="n"/>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -12185,7 +12150,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -5233,15 +5233,15 @@
         </is>
       </c>
       <c r="E168" s="75">
-        <f>8456743*E25/11102600</f>
+        <f>8456743*E25/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F168" s="75">
-        <f>8456743*F25/11102600</f>
+        <f>8456743*F25/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G168" s="75">
-        <f>8456743*G25/11102600</f>
+        <f>8456743*G25/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5252,15 +5252,15 @@
         </is>
       </c>
       <c r="E169" s="75">
-        <f>8456743*E26/11102600</f>
+        <f>8456743*E26/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F169" s="75">
-        <f>8456743*F26/11102600</f>
+        <f>8456743*F26/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G169" s="75">
-        <f>8456743*G26/11102600</f>
+        <f>8456743*G26/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5271,15 +5271,15 @@
         </is>
       </c>
       <c r="E170" s="75">
-        <f>8456743*E27/11102600</f>
+        <f>8456743*E27/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F170" s="75">
-        <f>8456743*F27/11102600</f>
+        <f>8456743*F27/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G170" s="75">
-        <f>8456743*G27/11102600</f>
+        <f>8456743*G27/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5290,15 +5290,15 @@
         </is>
       </c>
       <c r="E171" s="75">
-        <f>8456743*E28/11102600</f>
+        <f>8456743*E28/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F171" s="75">
-        <f>8456743*F28/11102600</f>
+        <f>8456743*F28/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G171" s="75">
-        <f>8456743*G28/11102600</f>
+        <f>8456743*G28/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5309,15 +5309,15 @@
         </is>
       </c>
       <c r="E172" s="75">
-        <f>8456743*E29/11102600</f>
+        <f>8456743*E29/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F172" s="75">
-        <f>8456743*F29/11102600</f>
+        <f>8456743*F29/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G172" s="75">
-        <f>8456743*G29/11102600</f>
+        <f>8456743*G29/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5328,15 +5328,15 @@
         </is>
       </c>
       <c r="E173" s="75">
-        <f>3494903*E25/11102600</f>
+        <f>3494903*E25/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F173" s="75">
-        <f>3494903*F25/11102600</f>
+        <f>3494903*F25/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G173" s="75">
-        <f>3494903*G25/11102600</f>
+        <f>3494903*G25/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5347,15 +5347,15 @@
         </is>
       </c>
       <c r="E174" s="75">
-        <f>3494903*E26/11102600</f>
+        <f>3494903*E26/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F174" s="75">
-        <f>3494903*F26/11102600</f>
+        <f>3494903*F26/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G174" s="75">
-        <f>3494903*G26/11102600</f>
+        <f>3494903*G26/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5366,15 +5366,15 @@
         </is>
       </c>
       <c r="E175" s="75">
-        <f>3494903*E27/11102600</f>
+        <f>3494903*E27/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F175" s="75">
-        <f>3494903*F27/11102600</f>
+        <f>3494903*F27/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G175" s="75">
-        <f>3494903*G27/11102600</f>
+        <f>3494903*G27/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5385,15 +5385,15 @@
         </is>
       </c>
       <c r="E176" s="75">
-        <f>3494903*E28/11102600</f>
+        <f>3494903*E28/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F176" s="75">
-        <f>3494903*F28/11102600</f>
+        <f>3494903*F28/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G176" s="75">
-        <f>3494903*G28/11102600</f>
+        <f>3494903*G28/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5404,15 +5404,15 @@
         </is>
       </c>
       <c r="E177" s="75">
-        <f>3494903*E29/11102600</f>
+        <f>3494903*E29/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F177" s="75">
-        <f>3494903*F29/11102600</f>
+        <f>3494903*F29/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G177" s="75">
-        <f>3494903*G29/11102600</f>
+        <f>3494903*G29/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5423,15 +5423,15 @@
         </is>
       </c>
       <c r="E178" s="75">
-        <f>4961840*E25/11102600</f>
+        <f>4961840*E25/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F178" s="75">
-        <f>4961840*F25/11102600</f>
+        <f>4961840*F25/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G178" s="75">
-        <f>4961840*G25/11102600</f>
+        <f>4961840*G25/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5442,15 +5442,15 @@
         </is>
       </c>
       <c r="E179" s="75">
-        <f>4961840*E26/11102600</f>
+        <f>4961840*E26/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F179" s="75">
-        <f>4961840*F26/11102600</f>
+        <f>4961840*F26/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G179" s="75">
-        <f>4961840*G26/11102600</f>
+        <f>4961840*G26/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5461,15 +5461,15 @@
         </is>
       </c>
       <c r="E180" s="75">
-        <f>4961840*E27/11102600</f>
+        <f>4961840*E27/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F180" s="75">
-        <f>4961840*F27/11102600</f>
+        <f>4961840*F27/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G180" s="75">
-        <f>4961840*G27/11102600</f>
+        <f>4961840*G27/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5480,15 +5480,15 @@
         </is>
       </c>
       <c r="E181" s="75">
-        <f>4961840*E28/11102600</f>
+        <f>4961840*E28/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F181" s="75">
-        <f>4961840*F28/11102600</f>
+        <f>4961840*F28/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G181" s="75">
-        <f>4961840*G28/11102600</f>
+        <f>4961840*G28/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -5499,15 +5499,15 @@
         </is>
       </c>
       <c r="E182" s="75">
-        <f>4961840*E29/11102600</f>
+        <f>4961840*E29/DCF!$D$5</f>
         <v/>
       </c>
       <c r="F182" s="75">
-        <f>4961840*F29/11102600</f>
+        <f>4961840*F29/DCF!$D$5</f>
         <v/>
       </c>
       <c r="G182" s="75">
-        <f>4961840*G29/11102600</f>
+        <f>4961840*G29/DCF!$D$5</f>
         <v/>
       </c>
     </row>
@@ -7780,6 +7780,7 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7990,6 +7991,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8163,30 +8165,30 @@
         <v/>
       </c>
       <c r="E20" s="138">
-        <f>Scenarios!F25/11102600*62203*$D$7</f>
+        <f>Scenarios!F25/DCF!$D$5*62203*$D$7</f>
         <v/>
       </c>
       <c r="F20" s="138">
-        <f>Scenarios!F26/11102600*62203*$D$7</f>
+        <f>Scenarios!F26/DCF!$D$5*62203*$D$7</f>
         <v/>
       </c>
       <c r="G20" s="138">
-        <f>Scenarios!F27/11102600*62203*$D$7</f>
+        <f>Scenarios!F27/DCF!$D$5*62203*$D$7</f>
         <v/>
       </c>
       <c r="H20" s="138">
-        <f>Scenarios!F28/11102600*62203*$D$7</f>
+        <f>Scenarios!F28/DCF!$D$5*62203*$D$7</f>
         <v/>
       </c>
       <c r="I20" s="138">
-        <f>Scenarios!F29/11102600*62203*$D$7</f>
+        <f>Scenarios!F29/DCF!$D$5*62203*$D$7</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>Adjusted EBIT (Phase 1)</t>
+          <t>Adjusted EBIT</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -8247,23 +8249,23 @@
         <v>1028</v>
       </c>
       <c r="E23" s="138">
-        <f>1028*(Scenarios!F25/11102600)</f>
+        <f>1028*(Scenarios!F25/DCF!$D$5)</f>
         <v/>
       </c>
       <c r="F23" s="138">
-        <f>1028*(Scenarios!F26/11102600)</f>
+        <f>1028*(Scenarios!F26/DCF!$D$5)</f>
         <v/>
       </c>
       <c r="G23" s="138">
-        <f>1028*(Scenarios!F27/11102600)</f>
+        <f>1028*(Scenarios!F27/DCF!$D$5)</f>
         <v/>
       </c>
       <c r="H23" s="138">
-        <f>1028*(Scenarios!F28/11102600)</f>
+        <f>1028*(Scenarios!F28/DCF!$D$5)</f>
         <v/>
       </c>
       <c r="I23" s="138">
-        <f>1028*(Scenarios!F29/11102600)</f>
+        <f>1028*(Scenarios!F29/DCF!$D$5)</f>
         <v/>
       </c>
     </row>
@@ -8340,7 +8342,7 @@
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>EBIT after lease &amp; capitalization (Phase 2)</t>
+          <t>EBIT after lease &amp; capitalization</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -8661,7 +8663,7 @@
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>EBIT after channel mix (Phase 3)</t>
+          <t>EBIT after channel mix</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -8879,6 +8881,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="73" t="inlineStr">
         <is>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -1730,7 +1730,7 @@
           <t>Current 10Y UST</t>
         </is>
       </c>
-      <c r="C3" s="185" t="inlineStr">
+      <c r="C3" s="167" t="inlineStr">
         <is>
           <t>FRED: 10Y Treasury (DGS10)</t>
         </is>
@@ -1750,7 +1750,7 @@
           <t>Damodaran ERP plus 177 bps US risk premium.</t>
         </is>
       </c>
-      <c r="C4" s="185" t="inlineStr">
+      <c r="C4" s="167" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
@@ -1770,7 +1770,7 @@
           <t>Q2 FY26 guide ~30%</t>
         </is>
       </c>
-      <c r="C5" s="185" t="inlineStr">
+      <c r="C5" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
@@ -1806,7 +1806,7 @@
           <t>NASDAQ last sale</t>
         </is>
       </c>
-      <c r="C8" s="185" t="inlineStr">
+      <c r="C8" s="167" t="inlineStr">
         <is>
           <t>NASDAQ LULU last sale (current price)</t>
         </is>
@@ -1826,7 +1826,7 @@
           <t>FY25 10-K shares</t>
         </is>
       </c>
-      <c r="C9" s="185" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: shares outstanding</t>
         </is>
@@ -1846,9 +1846,9 @@
           <t>Px × shares</t>
         </is>
       </c>
-      <c r="C10" s="169" t="inlineStr">
-        <is>
-          <t>Px × shares (above)</t>
+      <c r="C10" s="168" t="inlineStr">
+        <is>
+          <t>WACC tab: price × shares</t>
         </is>
       </c>
       <c r="D10" s="130">
@@ -1867,7 +1867,7 @@
           <t>FY25 lease debt (10-K)</t>
         </is>
       </c>
-      <c r="C11" s="185" t="inlineStr">
+      <c r="C11" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: operating lease liabilities</t>
         </is>
@@ -1887,7 +1887,7 @@
           <t>No funded debt (10-K)</t>
         </is>
       </c>
-      <c r="C12" s="188" t="inlineStr">
+      <c r="C12" s="128" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K (no funded debt)</t>
         </is>
@@ -1940,7 +1940,7 @@
           <t>Yahoo Beta (5Y Monthly) = 0.86. Levered equity.</t>
         </is>
       </c>
-      <c r="C16" s="188" t="inlineStr">
+      <c r="C16" s="128" t="inlineStr">
         <is>
           <t>Yahoo Finance: LULU Beta (5Y Monthly)</t>
         </is>
@@ -1960,7 +1960,7 @@
           <t>Yahoo total debt</t>
         </is>
       </c>
-      <c r="C17" s="185" t="inlineStr">
+      <c r="C17" s="167" t="inlineStr">
         <is>
           <t>Yahoo Finance: LULU Total Debt (mrq)</t>
         </is>
@@ -1980,7 +1980,7 @@
           <t>Yahoo market cap from same page as beta and debt.</t>
         </is>
       </c>
-      <c r="C18" s="185" t="inlineStr">
+      <c r="C18" s="167" t="inlineStr">
         <is>
           <t>Yahoo Finance: LULU Market Cap</t>
         </is>
@@ -2000,7 +2000,7 @@
           <t>Yahoo total debt divided by Yahoo market cap ratio.</t>
         </is>
       </c>
-      <c r="C19" s="185" t="inlineStr">
+      <c r="C19" s="167" t="inlineStr">
         <is>
           <t>Yahoo Finance: debt (mrq) ÷ market cap</t>
         </is>
@@ -2021,7 +2021,7 @@
           <t>Yahoo Total Debt/Equity (mrq) = 44.69% is book.</t>
         </is>
       </c>
-      <c r="C20" s="185" t="inlineStr">
+      <c r="C20" s="167" t="inlineStr">
         <is>
           <t>Yahoo Finance: Total Debt/Equity (mrq)</t>
         </is>
@@ -2041,7 +2041,7 @@
           <t>Hamada unlever beta using Yahoo market D/E and tax rate.</t>
         </is>
       </c>
-      <c r="C21" s="185" t="inlineStr">
+      <c r="C21" s="168" t="inlineStr">
         <is>
           <t>WACC tab: Hamada unlever (Yahoo market D/E)</t>
         </is>
@@ -2062,7 +2062,7 @@
           <t>FY25 lease D/E</t>
         </is>
       </c>
-      <c r="C22" s="185" t="inlineStr">
+      <c r="C22" s="168" t="inlineStr">
         <is>
           <t>WACC tab: FY25 lease debt / market equity</t>
         </is>
@@ -2083,7 +2083,7 @@
           <t>Benchmark only: Damodaran unlevered Retail (Special Lines) βu.</t>
         </is>
       </c>
-      <c r="C23" s="185" t="inlineStr">
+      <c r="C23" s="167" t="inlineStr">
         <is>
           <t>Damodaran: US betas by sector (Jan 2026)</t>
         </is>
@@ -2103,7 +2103,7 @@
           <t>Relevered β</t>
         </is>
       </c>
-      <c r="C24" s="185" t="inlineStr">
+      <c r="C24" s="168" t="inlineStr">
         <is>
           <t>WACC tab: Hamada relever (total D/E incl. leases)</t>
         </is>
@@ -2181,7 +2181,7 @@
           <t>Lease-equivalent kd</t>
         </is>
       </c>
-      <c r="C30" s="188" t="inlineStr">
+      <c r="C30" s="128" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: lease liabilities &amp; no funded debt</t>
         </is>
@@ -2238,7 +2238,7 @@
           <t>Equity weight</t>
         </is>
       </c>
-      <c r="C34" s="188" t="inlineStr">
+      <c r="C34" s="126" t="inlineStr">
         <is>
           <t>WACC tab: capital structure</t>
         </is>
@@ -2259,7 +2259,7 @@
           <t>Debt weight</t>
         </is>
       </c>
-      <c r="C35" s="185" t="inlineStr">
+      <c r="C35" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: operating lease liabilities</t>
         </is>
@@ -2401,7 +2401,7 @@
           <t>Q2 FY26 rev guide</t>
         </is>
       </c>
-      <c r="C4" s="185" t="inlineStr">
+      <c r="C4" s="167" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release</t>
         </is>
@@ -2430,7 +2430,7 @@
           <t>2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast.</t>
         </is>
       </c>
-      <c r="C5" s="185" t="inlineStr">
+      <c r="C5" s="167" t="inlineStr">
         <is>
           <t>StockAnalysis: LULU 3Y revenue forecast</t>
         </is>
@@ -2459,7 +2459,7 @@
           <t>Q2 FY26 run-rate OM</t>
         </is>
       </c>
-      <c r="C6" s="185" t="inlineStr">
+      <c r="C6" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs</t>
         </is>
@@ -2488,7 +2488,7 @@
           <t>FY26 tariff refund</t>
         </is>
       </c>
-      <c r="C7" s="185" t="inlineStr">
+      <c r="C7" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
         </is>
@@ -2517,7 +2517,7 @@
           <t>Partial OM recovery</t>
         </is>
       </c>
-      <c r="C8" s="185" t="inlineStr">
+      <c r="C8" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: Operating margin 19.9% (one hit)</t>
         </is>
@@ -2546,7 +2546,7 @@
           <t>Links to WACC tab</t>
         </is>
       </c>
-      <c r="C9" s="185" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>WACC tab: CAPM build</t>
         </is>
@@ -2576,7 +2576,7 @@
           <t>FRED GDPC1 ~2.1%</t>
         </is>
       </c>
-      <c r="C10" s="185" t="inlineStr">
+      <c r="C10" s="167" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -2605,7 +2605,7 @@
           <t>Q2 FY26 guide ~30%</t>
         </is>
       </c>
-      <c r="C11" s="185" t="inlineStr">
+      <c r="C11" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
@@ -2634,7 +2634,7 @@
           <t>FY25 D&amp;A / sales</t>
         </is>
       </c>
-      <c r="C12" s="185" t="inlineStr">
+      <c r="C12" s="167" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)</t>
         </is>
@@ -2663,7 +2663,7 @@
           <t>5.5% model rate; FY26 7% capex guide fades down.</t>
         </is>
       </c>
-      <c r="C13" s="185" t="inlineStr">
+      <c r="C13" s="167" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
         </is>
@@ -2692,7 +2692,7 @@
           <t>Flat vs FY25</t>
         </is>
       </c>
-      <c r="C14" s="185" t="inlineStr">
+      <c r="C14" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
         </is>
@@ -2721,7 +2721,7 @@
           <t>6.3 days DSO held flat vs FY25 actual.</t>
         </is>
       </c>
-      <c r="C15" s="185" t="inlineStr">
+      <c r="C15" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
@@ -2750,7 +2750,7 @@
           <t>FY25 DIO −1d/yr</t>
         </is>
       </c>
-      <c r="C16" s="185" t="inlineStr">
+      <c r="C16" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories &amp; COGS</t>
         </is>
@@ -2779,7 +2779,7 @@
           <t>−1 day / yr</t>
         </is>
       </c>
-      <c r="C17" s="185" t="inlineStr">
+      <c r="C17" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: inventory &amp; markdown outlook</t>
         </is>
@@ -2808,7 +2808,7 @@
           <t>25.1 days DPO held flat vs FY25 actual.</t>
         </is>
       </c>
-      <c r="C18" s="185" t="inlineStr">
+      <c r="C18" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
         </is>
@@ -2837,7 +2837,7 @@
           <t>FY25 prepaids % rev</t>
         </is>
       </c>
-      <c r="C19" s="185" t="inlineStr">
+      <c r="C19" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
@@ -2866,7 +2866,7 @@
           <t>FY25 accrued % rev</t>
         </is>
       </c>
-      <c r="C20" s="185" t="inlineStr">
+      <c r="C20" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
@@ -7068,7 +7068,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="J5" s="176" t="inlineStr">
+      <c r="J5" s="126" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -7113,9 +7113,9 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J6" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, Item 2 — Americas 462 company-operated stores</t>
+      <c r="J6" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: beginning-stores formula</t>
         </is>
       </c>
     </row>
@@ -7151,7 +7151,7 @@
           <t>China plus twenty store openings FY26; Americas and RoW open slower.</t>
         </is>
       </c>
-      <c r="J7" s="185" t="inlineStr">
+      <c r="J7" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
         </is>
@@ -7189,7 +7189,7 @@
           <t>Assume two to three store closures per mature region annually.</t>
         </is>
       </c>
-      <c r="J8" s="185" t="inlineStr">
+      <c r="J8" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
         </is>
@@ -7234,9 +7234,9 @@
           <t>Beginning stores plus regional openings minus closures each year.</t>
         </is>
       </c>
-      <c r="J9" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, store roll-forward — Americas ending 476 stores</t>
+      <c r="J9" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: ending-stores formula</t>
         </is>
       </c>
     </row>
@@ -7279,9 +7279,9 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J10" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, Item 2 — China Mainland 151 stores</t>
+      <c r="J10" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: beginning-stores formula</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
           <t>China plus twenty store openings FY26; Americas and RoW open slower.</t>
         </is>
       </c>
-      <c r="J11" s="185" t="inlineStr">
+      <c r="J11" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
         </is>
@@ -7355,7 +7355,7 @@
           <t>Assume two to three store closures per mature region annually.</t>
         </is>
       </c>
-      <c r="J12" s="185" t="inlineStr">
+      <c r="J12" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
         </is>
@@ -7400,9 +7400,9 @@
           <t>Beginning stores plus regional openings minus closures each year.</t>
         </is>
       </c>
-      <c r="J13" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, store roll-forward — China ending 172 stores</t>
+      <c r="J13" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: ending-stores formula</t>
         </is>
       </c>
     </row>
@@ -7445,9 +7445,9 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J14" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, Item 2 — Rest of World 154 stores</t>
+      <c r="J14" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: beginning-stores formula</t>
         </is>
       </c>
     </row>
@@ -7483,7 +7483,7 @@
           <t>China plus twenty store openings FY26; Americas and RoW open slower.</t>
         </is>
       </c>
-      <c r="J15" s="185" t="inlineStr">
+      <c r="J15" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
         </is>
@@ -7521,7 +7521,7 @@
           <t>Assume two to three store closures per mature region annually.</t>
         </is>
       </c>
-      <c r="J16" s="185" t="inlineStr">
+      <c r="J16" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
         </is>
@@ -7566,9 +7566,9 @@
           <t>Beginning stores plus regional openings minus closures each year.</t>
         </is>
       </c>
-      <c r="J17" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, store roll-forward — RoW ending 163 stores</t>
+      <c r="J17" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: ending-stores formula</t>
         </is>
       </c>
     </row>
@@ -7607,9 +7607,9 @@
           <t>Add up Americas + China + RoW ending.</t>
         </is>
       </c>
-      <c r="J18" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, Item 2 — Total company-operated 811 stores</t>
+      <c r="J18" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: total-stores formula</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
           <t>4,367 avg sq ft/store = implied FY25 total.</t>
         </is>
       </c>
-      <c r="J19" s="185" t="inlineStr">
+      <c r="J19" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: sales per square foot</t>
         </is>
@@ -7693,7 +7693,11 @@
           <t>Total sq ft equals ending store count times average box size.</t>
         </is>
       </c>
-      <c r="J20" s="185" t="n"/>
+      <c r="J20" s="168" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: total-sqft formula</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="176" t="n"/>
@@ -7769,7 +7773,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="J23" s="188" t="inlineStr">
+      <c r="J23" s="126" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -7809,7 +7813,7 @@
           <t>FY26 SPSF $1,380 reflects Americas traffic/conversion pressure; recovers.</t>
         </is>
       </c>
-      <c r="J24" s="185" t="inlineStr">
+      <c r="J24" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: comparable sales &amp; SPSF</t>
         </is>
@@ -7849,7 +7853,7 @@
           <t>FY25 Americas comp −3% per 10-K (traffic, conversion,.</t>
         </is>
       </c>
-      <c r="J25" s="185" t="inlineStr">
+      <c r="J25" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: Americas comparable sales</t>
         </is>
@@ -7889,7 +7893,7 @@
           <t>FY25 China comparable sales plus twenty percent per FY25 10-K.</t>
         </is>
       </c>
-      <c r="J26" s="185" t="inlineStr">
+      <c r="J26" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: China Mainland comparable sales</t>
         </is>
@@ -7929,7 +7933,7 @@
           <t>FY25 rest of world comp plus nine percent per FY25 10-K.</t>
         </is>
       </c>
-      <c r="J27" s="185" t="inlineStr">
+      <c r="J27" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: Rest of World comparable sales</t>
         </is>
@@ -7974,9 +7978,9 @@
           <t>Last year's total store-channel revenue; the base you're.</t>
         </is>
       </c>
-      <c r="J28" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, company-operated stores net revenue ($5,049.7M)</t>
+      <c r="J28" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: prior store-rev formula</t>
         </is>
       </c>
     </row>
@@ -8015,9 +8019,9 @@
           <t>Existing-store sales only; prior store rev grown by.</t>
         </is>
       </c>
-      <c r="J29" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, comparable store sales base (prior-year store rev)</t>
+      <c r="J29" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: comp-store formula</t>
         </is>
       </c>
     </row>
@@ -8056,9 +8060,9 @@
           <t>Net new doors × sq ft × $/sq.</t>
         </is>
       </c>
-      <c r="J30" s="169" t="inlineStr">
-        <is>
-          <t>Revenue Drivers tab — net-new-store calc; FY25 anchor $0</t>
+      <c r="J30" s="168" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: net-new-store formula</t>
         </is>
       </c>
     </row>
@@ -8097,9 +8101,9 @@
           <t>Brick-and-mortar channel = comp store sales plus whatever.</t>
         </is>
       </c>
-      <c r="J31" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, company-operated stores net revenue ($5,049.7M)</t>
+      <c r="J31" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: store-channel formula</t>
         </is>
       </c>
     </row>
@@ -8137,7 +8141,7 @@
           <t>Fleet traffic memo line; not a separate FCF.</t>
         </is>
       </c>
-      <c r="J32" s="185" t="inlineStr">
+      <c r="J32" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: store traffic commentary</t>
         </is>
@@ -8173,7 +8177,7 @@
           <t>In-store conversion memo; 10-K cites lower conversion in.</t>
         </is>
       </c>
-      <c r="J33" s="185" t="inlineStr">
+      <c r="J33" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: conversion rate commentary</t>
         </is>
@@ -8209,7 +8213,7 @@
           <t>In-store average transaction $115–$122; supports SPSF and comp-sales.</t>
         </is>
       </c>
-      <c r="J34" s="185" t="inlineStr">
+      <c r="J34" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: average order value commentary</t>
         </is>
@@ -8289,7 +8293,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="J37" s="188" t="inlineStr">
+      <c r="J37" s="126" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -8329,7 +8333,7 @@
           <t>485M FY25 sessions implied from reported e-comm revenue.</t>
         </is>
       </c>
-      <c r="J38" s="185" t="inlineStr">
+      <c r="J38" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
         </is>
@@ -8365,7 +8369,7 @@
           <t>3.3% FY26 digital conversion vs 3.5% pressure cited.</t>
         </is>
       </c>
-      <c r="J39" s="185" t="inlineStr">
+      <c r="J39" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: digital / traffic commentary</t>
         </is>
@@ -8401,7 +8405,7 @@
           <t>AOV $305 FY26 on promo intensity; steps to.</t>
         </is>
       </c>
-      <c r="J40" s="185" t="inlineStr">
+      <c r="J40" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
         </is>
@@ -8442,9 +8446,9 @@
           <t>Traffic × conversion × AOV is dollars. ×1M.</t>
         </is>
       </c>
-      <c r="J41" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, e-commerce net revenue ($4,918.7M)</t>
+      <c r="J41" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: e-comm formula</t>
         </is>
       </c>
     </row>
@@ -8522,7 +8526,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="J44" s="188" t="inlineStr">
+      <c r="J44" s="126" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -8567,7 +8571,7 @@
           <t>Other channels (wholesale/license/outlets) held at FY25 $1.13B base;.</t>
         </is>
       </c>
-      <c r="J45" s="185" t="inlineStr">
+      <c r="J45" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: channel revenue table</t>
         </is>
@@ -8612,7 +8616,7 @@
           <t>Geographic split scales with consolidated growth; FY25 Americas.</t>
         </is>
       </c>
-      <c r="J46" s="185" t="inlineStr">
+      <c r="J46" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
         </is>
@@ -8657,7 +8661,7 @@
           <t>China 15.8% of FY25 revenue; fastest comp and.</t>
         </is>
       </c>
-      <c r="J47" s="185" t="inlineStr">
+      <c r="J47" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
         </is>
@@ -8702,7 +8706,7 @@
           <t>Rest of World 13.5% of FY25 revenue; mid-single-digit.</t>
         </is>
       </c>
-      <c r="J48" s="185" t="inlineStr">
+      <c r="J48" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
         </is>
@@ -8738,7 +8742,7 @@
           <t>Women's mix fades 62.5% to 60% as men's penetrates; FY25.</t>
         </is>
       </c>
-      <c r="J49" s="185" t="inlineStr">
+      <c r="J49" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
         </is>
@@ -8774,7 +8778,7 @@
           <t>Men's mix rises 24.5% to 27%; FY25 men's grew 4%.</t>
         </is>
       </c>
-      <c r="J50" s="185" t="inlineStr">
+      <c r="J50" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
         </is>
@@ -8810,7 +8814,7 @@
           <t>Accessories steady at 13% of revenue; FY25 accessories.</t>
         </is>
       </c>
-      <c r="J51" s="185" t="inlineStr">
+      <c r="J51" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
         </is>
@@ -8890,7 +8894,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="J54" s="188" t="inlineStr">
+      <c r="J54" s="126" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -8931,9 +8935,9 @@
           <t>Bottom-up total = store channel + e-comm +.</t>
         </is>
       </c>
-      <c r="J55" s="169" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K, consolidated net revenue ($11,102.6M)</t>
+      <c r="J55" s="167" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: total-rev formula</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8976,7 @@
           <t>Pulls the Scenarios base-case revenue path; that's still.</t>
         </is>
       </c>
-      <c r="J56" s="185" t="inlineStr">
+      <c r="J56" s="167" t="inlineStr">
         <is>
           <t>Scenarios tab: base revenue</t>
         </is>
@@ -9014,7 +9018,11 @@
           <t>Driver-built revenue minus Scenarios revenue. Shows you how.</t>
         </is>
       </c>
-      <c r="J57" s="185" t="n"/>
+      <c r="J57" s="168" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: variance formula</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="41" t="inlineStr">
@@ -9052,7 +9060,11 @@
           <t>Variance as a percent of Scenarios revenue. Easy.</t>
         </is>
       </c>
-      <c r="J58" s="185" t="n"/>
+      <c r="J58" s="168" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: variance % formula</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="26" t="n"/>
@@ -9068,40 +9080,52 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId46"/>
     <hyperlink ref="J56" location="'Scenarios'!F25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9288,7 +9312,7 @@
           <t>Not % of consolidated revenue; EBIT as %.</t>
         </is>
       </c>
-      <c r="C9" s="185" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: company-operated stores net revenue</t>
         </is>
@@ -9323,7 +9347,7 @@
           <t>Not % of consolidated revenue; EBIT as %.</t>
         </is>
       </c>
-      <c r="C10" s="185" t="inlineStr">
+      <c r="C10" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce net revenue</t>
         </is>
@@ -9358,7 +9382,7 @@
           <t>Not % of consolidated revenue; EBIT as %.</t>
         </is>
       </c>
-      <c r="C11" s="185" t="inlineStr">
+      <c r="C11" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: other channels (residual)</t>
         </is>
@@ -9393,7 +9417,7 @@
           <t>30% statutory marginal rate. t_operating transitions here over.</t>
         </is>
       </c>
-      <c r="C12" s="185" t="inlineStr">
+      <c r="C12" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
         </is>
@@ -9428,7 +9452,7 @@
           <t>Not % of revenue; amortization period (years) if.</t>
         </is>
       </c>
-      <c r="C13" s="185" t="inlineStr">
+      <c r="C13" s="168" t="inlineStr">
         <is>
           <t>NOPAT Bridge: capitalization convention</t>
         </is>
@@ -9489,7 +9513,7 @@
           <t>10-K EBIT / Scenarios forecast.</t>
         </is>
       </c>
-      <c r="C16" s="185" t="inlineStr">
+      <c r="C16" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Income from operations</t>
         </is>
@@ -9529,7 +9553,7 @@
           <t>Run-rate intangible amort add-back.</t>
         </is>
       </c>
-      <c r="C17" s="185" t="inlineStr">
+      <c r="C17" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: amortization of intangible assets</t>
         </is>
@@ -9564,7 +9588,7 @@
           <t>Non-recurring restructuring add-back.</t>
         </is>
       </c>
-      <c r="C18" s="185" t="inlineStr">
+      <c r="C18" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: restructuring charges</t>
         </is>
@@ -9599,7 +9623,7 @@
           <t>One-off legal / M&amp;A strip.</t>
         </is>
       </c>
-      <c r="C19" s="185" t="inlineStr">
+      <c r="C19" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: SG&amp;A one-offs</t>
         </is>
@@ -9634,7 +9658,7 @@
           <t>SBC add-back (if flag = 1).</t>
         </is>
       </c>
-      <c r="C20" s="185" t="inlineStr">
+      <c r="C20" s="167" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K): stock-based compensation</t>
         </is>
@@ -9675,9 +9699,9 @@
           <t>Reported EBIT plus all listed non-recurring add-backs above.</t>
         </is>
       </c>
-      <c r="C21" s="185" t="inlineStr">
-        <is>
-          <t>Sum of reported EBIT and add-backs above.</t>
+      <c r="C21" s="168" t="inlineStr">
+        <is>
+          <t>NOPAT Bridge tab: Phase 1 subtotal</t>
         </is>
       </c>
       <c r="D21" s="176" t="n"/>
@@ -9728,7 +9752,7 @@
           <t>Lease interest reclass (memo).</t>
         </is>
       </c>
-      <c r="C23" s="185" t="inlineStr">
+      <c r="C23" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: interest on lease liabilities (supplemental)</t>
         </is>
@@ -9768,7 +9792,7 @@
           <t>R&amp;D cap immaterial this yr.</t>
         </is>
       </c>
-      <c r="C24" s="185" t="inlineStr">
+      <c r="C24" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: R&amp;D / software expense</t>
         </is>
@@ -9803,7 +9827,7 @@
           <t>Amortization of prior capitalized intangibles. LULU: flows through.</t>
         </is>
       </c>
-      <c r="C25" s="185" t="inlineStr">
+      <c r="C25" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: intangible amortization</t>
         </is>
@@ -9838,9 +9862,9 @@
           <t>Reported EBIT plus lease interest and R&amp;D adjustments.</t>
         </is>
       </c>
-      <c r="C26" s="185" t="inlineStr">
-        <is>
-          <t>Sum after lease and R&amp;D adjustments above.</t>
+      <c r="C26" s="168" t="inlineStr">
+        <is>
+          <t>NOPAT Bridge tab: Phase 2 subtotal</t>
         </is>
       </c>
       <c r="D26" s="176" t="n"/>
@@ -9891,7 +9915,7 @@
           <t>Store rev from Revenue Drivers.</t>
         </is>
       </c>
-      <c r="C28" s="185" t="inlineStr">
+      <c r="C28" s="167" t="inlineStr">
         <is>
           <t>Revenue Drivers tab: store-channel revenue</t>
         </is>
@@ -9931,7 +9955,7 @@
           <t>E-comm rev from Revenue Drivers.</t>
         </is>
       </c>
-      <c r="C29" s="185" t="inlineStr">
+      <c r="C29" s="167" t="inlineStr">
         <is>
           <t>Revenue Drivers tab: e-commerce revenue</t>
         </is>
@@ -9971,7 +9995,7 @@
           <t>Other rev from Revenue Drivers.</t>
         </is>
       </c>
-      <c r="C30" s="185" t="inlineStr">
+      <c r="C30" s="167" t="inlineStr">
         <is>
           <t>Revenue Drivers tab: other channels revenue</t>
         </is>
@@ -10011,7 +10035,7 @@
           <t>Store EBIT margin applied to store channel revenue only.</t>
         </is>
       </c>
-      <c r="C31" s="185" t="inlineStr">
+      <c r="C31" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: company-operated stores net revenue</t>
         </is>
@@ -10051,7 +10075,7 @@
           <t>E-commerce EBIT margin applied to e-comm channel revenue only.</t>
         </is>
       </c>
-      <c r="C32" s="185" t="inlineStr">
+      <c r="C32" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce net revenue</t>
         </is>
@@ -10091,7 +10115,7 @@
           <t>Other-channel EBIT margin applied to other channel revenue only.</t>
         </is>
       </c>
-      <c r="C33" s="185" t="inlineStr">
+      <c r="C33" s="167" t="inlineStr">
         <is>
           <t>FY2025 10-K: other channels (residual)</t>
         </is>
@@ -10131,9 +10155,9 @@
           <t>Sum of store, e-comm, and other channel EBIT lines.</t>
         </is>
       </c>
-      <c r="C34" s="185" t="inlineStr">
-        <is>
-          <t>Sum of channel EBIT lines above.</t>
+      <c r="C34" s="168" t="inlineStr">
+        <is>
+          <t>NOPAT Bridge tab: sector EBIT subtotal</t>
         </is>
       </c>
       <c r="D34" s="176" t="n"/>
@@ -10169,9 +10193,9 @@
           <t>Channel-mix EBIT output line before tax normalization step.</t>
         </is>
       </c>
-      <c r="C35" s="185" t="inlineStr">
-        <is>
-          <t>Sum of channel EBIT lines above.</t>
+      <c r="C35" s="168" t="inlineStr">
+        <is>
+          <t>NOPAT Bridge tab: Phase 3 subtotal</t>
         </is>
       </c>
       <c r="D35" s="197" t="n">
@@ -10209,7 +10233,7 @@
           <t>FY25 walk-through Phases 1–2.</t>
         </is>
       </c>
-      <c r="C36" s="185" t="inlineStr">
+      <c r="C36" s="168" t="inlineStr">
         <is>
           <t>Scenarios tab: base-case EBIT (forecast)</t>
         </is>
@@ -10295,7 +10319,7 @@
           <t>Operating ETR with interest shield.</t>
         </is>
       </c>
-      <c r="C39" s="185" t="inlineStr">
+      <c r="C39" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: income tax &amp; interest expense</t>
         </is>
@@ -10335,7 +10359,11 @@
           <t>Normalized EBIT × t_operating.</t>
         </is>
       </c>
-      <c r="C40" s="185" t="n"/>
+      <c r="C40" s="168" t="inlineStr">
+        <is>
+          <t>NOPAT Bridge tab: unlevered tax expense</t>
+        </is>
+      </c>
       <c r="D40" s="176" t="n"/>
       <c r="E40" s="75">
         <f>E36*E39</f>
@@ -10369,7 +10397,11 @@
           <t>EBIT_norm × (1 − t_operating).</t>
         </is>
       </c>
-      <c r="C41" s="185" t="n"/>
+      <c r="C41" s="168" t="inlineStr">
+        <is>
+          <t>NOPAT Bridge tab: normalized NOPAT</t>
+        </is>
+      </c>
       <c r="D41" s="176" t="n"/>
       <c r="E41" s="130">
         <f>E36-E40</f>
@@ -10444,7 +10476,7 @@
           <t>SEC 10-K income statement</t>
         </is>
       </c>
-      <c r="C45" s="188" t="inlineStr">
+      <c r="C45" s="126" t="inlineStr">
         <is>
           <t>EBIT = 13.2% × rev + tariff; SBC stays expensed (flag = 0).</t>
         </is>
@@ -10471,7 +10503,7 @@
           <t>SG&amp;A footnotes</t>
         </is>
       </c>
-      <c r="C46" s="188" t="inlineStr">
+      <c r="C46" s="126" t="inlineStr">
         <is>
           <t>R&amp;D/software expensed in full each year ($0 for LULU).</t>
         </is>
@@ -10498,7 +10530,7 @@
           <t>ASC 842 lease footnote</t>
         </is>
       </c>
-      <c r="C47" s="188" t="inlineStr">
+      <c r="C47" s="126" t="inlineStr">
         <is>
           <t>Rent in opex; no implied lease-interest add-back.</t>
         </is>
@@ -10525,7 +10557,7 @@
           <t>Revenue Drivers tab</t>
         </is>
       </c>
-      <c r="C48" s="188" t="inlineStr">
+      <c r="C48" s="126" t="inlineStr">
         <is>
           <t>DCF uses consolidated 13.2% on total revenue (+ tariff).</t>
         </is>
@@ -10552,7 +10584,7 @@
           <t>Normalized EBIT &amp; t_operating</t>
         </is>
       </c>
-      <c r="C49" s="188" t="inlineStr">
+      <c r="C49" s="126" t="inlineStr">
         <is>
           <t>NOPAT = EBIT × (1 − 30%) flat sc_tax.</t>
         </is>
@@ -10579,7 +10611,7 @@
           <t>Q2 FY2026 earnings release</t>
         </is>
       </c>
-      <c r="C50" s="188" t="inlineStr">
+      <c r="C50" s="126" t="inlineStr">
         <is>
           <t>EBIT = Rev × 13.2% only (no refund).</t>
         </is>
@@ -10802,7 +10834,7 @@
           <t>Minus 6.1% FY26 revenue per company guidance midpoint.</t>
         </is>
       </c>
-      <c r="C6" s="185" t="inlineStr">
+      <c r="C6" s="167" t="inlineStr">
         <is>
           <t>LULU Q2 FY2026 earnings release Also: StockAnalysis: LULU 3Y revenue forecast</t>
         </is>
@@ -10840,7 +10872,7 @@
           <t>56.6% FY25 gross margin held flat in forecast.</t>
         </is>
       </c>
-      <c r="C7" s="185" t="inlineStr">
+      <c r="C7" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
         </is>
@@ -10912,7 +10944,7 @@
           <t>13.2% clean OM from Q2 run-rate ex tariff.</t>
         </is>
       </c>
-      <c r="C9" s="185" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: 18.8% OM minus 560bps tariffs Also: FY2025 10-K: Operating margin 19.9% (one hit)</t>
         </is>
@@ -10950,7 +10982,7 @@
           <t>Add back 134.5M tariff refund in FY26 only.</t>
         </is>
       </c>
-      <c r="C10" s="185" t="inlineStr">
+      <c r="C10" s="167" t="inlineStr">
         <is>
           <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
         </is>
@@ -11110,7 +11142,7 @@
           <t>4.5% of sales from FY25 D&amp;A over revenue.</t>
         </is>
       </c>
-      <c r="C15" s="185" t="inlineStr">
+      <c r="C15" s="167" t="inlineStr">
         <is>
           <t>LULU CF statement (10-K)</t>
         </is>
@@ -11178,7 +11210,7 @@
           <t>5.5% model rate; FY26 7% capex guide fades down.</t>
         </is>
       </c>
-      <c r="C17" s="185" t="inlineStr">
+      <c r="C17" s="167" t="inlineStr">
         <is>
           <t>LULU 10-K: 2026 capex guide $725–745M Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
         </is>
@@ -11246,7 +11278,7 @@
           <t>NWC schedule nets to 13.2% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C19" s="188" t="inlineStr">
+      <c r="C19" s="128" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: working-capital components</t>
         </is>
@@ -11269,7 +11301,7 @@
           <t>6.3 days DSO held flat vs FY25 actual.</t>
         </is>
       </c>
-      <c r="C20" s="185" t="inlineStr">
+      <c r="C20" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
@@ -11309,7 +11341,7 @@
           <t>AR 1.7% of sales from FY25 balance sheet.</t>
         </is>
       </c>
-      <c r="C21" s="185" t="inlineStr">
+      <c r="C21" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts receivable, net</t>
         </is>
@@ -11349,7 +11381,7 @@
           <t>128.8 day DIO anchor; minus 1 day per year.</t>
         </is>
       </c>
-      <c r="C22" s="185" t="inlineStr">
+      <c r="C22" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories &amp; COGS Also: LULU FY2025 10-K: inventory &amp; markdown outlook</t>
         </is>
@@ -11389,7 +11421,7 @@
           <t>Inventory dollar balance driven by DIO times COGS.</t>
         </is>
       </c>
-      <c r="C23" s="185" t="inlineStr">
+      <c r="C23" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Inventories</t>
         </is>
@@ -11429,7 +11461,7 @@
           <t>25.1 days DPO held flat vs FY25 actual.</t>
         </is>
       </c>
-      <c r="C24" s="185" t="inlineStr">
+      <c r="C24" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
         </is>
@@ -11469,7 +11501,7 @@
           <t>AP 3.0% of sales from FY25 payables balance.</t>
         </is>
       </c>
-      <c r="C25" s="185" t="inlineStr">
+      <c r="C25" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accounts payable</t>
         </is>
@@ -11509,7 +11541,7 @@
           <t>5.1% of revenue from FY25 other current assets.</t>
         </is>
       </c>
-      <c r="C26" s="185" t="inlineStr">
+      <c r="C26" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
@@ -11549,7 +11581,7 @@
           <t>5.1% of revenue from FY25 other current assets.</t>
         </is>
       </c>
-      <c r="C27" s="185" t="inlineStr">
+      <c r="C27" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: other current assets (residual)</t>
         </is>
@@ -11589,7 +11621,7 @@
           <t>6.0% of revenue from FY25 accrued liabilities balance.</t>
         </is>
       </c>
-      <c r="C28" s="185" t="inlineStr">
+      <c r="C28" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
@@ -11629,7 +11661,7 @@
           <t>6.0% of revenue from FY25 accrued liabilities balance.</t>
         </is>
       </c>
-      <c r="C29" s="185" t="inlineStr">
+      <c r="C29" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
@@ -11669,7 +11701,7 @@
           <t>Operating assets sum to 22.1% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C30" s="185" t="inlineStr">
+      <c r="C30" s="167" t="inlineStr">
         <is>
           <t>Scenarios tab: AR + inventory + prepaids</t>
         </is>
@@ -11707,7 +11739,7 @@
           <t>Operating liabilities sum to 9.0% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C31" s="185" t="inlineStr">
+      <c r="C31" s="167" t="inlineStr">
         <is>
           <t>Scenarios tab: AP + accrued liabilities</t>
         </is>
@@ -11745,7 +11777,7 @@
           <t>Net working capital equals 13.2% of FY25 sales.</t>
         </is>
       </c>
-      <c r="C32" s="185" t="inlineStr">
+      <c r="C32" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: working-capital components</t>
         </is>
@@ -11785,7 +11817,7 @@
           <t>Year-over-year dollar change in net working capital schedule.</t>
         </is>
       </c>
-      <c r="C33" s="185" t="inlineStr">
+      <c r="C33" s="167" t="inlineStr">
         <is>
           <t>Scenarios tab: NWC roll-forward (driver schedule)</t>
         </is>
@@ -12008,7 +12040,7 @@
           <t>2.25% terminal g anchored to FRED GDPC1 macro series.</t>
         </is>
       </c>
-      <c r="C43" s="185" t="inlineStr">
+      <c r="C43" s="167" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -12138,7 +12170,7 @@
         </is>
       </c>
       <c r="B50" s="176" t="n"/>
-      <c r="C50" s="185" t="inlineStr">
+      <c r="C50" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -12163,7 +12195,7 @@
           <t>Subtract ASC 842 operating lease liabilities as debt.</t>
         </is>
       </c>
-      <c r="C51" s="185" t="inlineStr">
+      <c r="C51" s="167" t="inlineStr">
         <is>
           <t>LULU FY2025 10-K: operating lease liabilities</t>
         </is>
@@ -12228,7 +12260,7 @@
         </is>
       </c>
       <c r="B55" s="176" t="n"/>
-      <c r="C55" s="185" t="inlineStr">
+      <c r="C55" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -12267,7 +12299,7 @@
         </is>
       </c>
       <c r="B57" s="176" t="n"/>
-      <c r="C57" s="185" t="inlineStr">
+      <c r="C57" s="167" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -12805,7 +12837,7 @@
           <t>Gordon terminal value divided by FY30 EBITDA multiple.</t>
         </is>
       </c>
-      <c r="C82" s="185" t="inlineStr">
+      <c r="C82" s="167" t="inlineStr">
         <is>
           <t>DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
         </is>
@@ -12951,8 +12983,8 @@
         <f>D45</f>
         <v/>
       </c>
-      <c r="C90" s="188">
-        <f>D83</f>
+      <c r="C90" s="126">
+        <f>E83</f>
         <v/>
       </c>
       <c r="D90" s="176">
@@ -12975,8 +13007,8 @@
         <f>D46</f>
         <v/>
       </c>
-      <c r="C91" s="188">
-        <f>D82</f>
+      <c r="C91" s="126">
+        <f>E82</f>
         <v/>
       </c>
       <c r="D91" s="176">
@@ -13017,8 +13049,8 @@
         <f>D56</f>
         <v/>
       </c>
-      <c r="C93" s="188">
-        <f>D86</f>
+      <c r="C93" s="126">
+        <f>E86</f>
         <v/>
       </c>
       <c r="D93" s="176">
@@ -13100,7 +13132,7 @@
           <t>Sensitivity grid; terminal g spans 1.5% to 3.0%.</t>
         </is>
       </c>
-      <c r="C98" s="185" t="inlineStr">
+      <c r="C98" s="167" t="inlineStr">
         <is>
           <t>FRED: Real GDP (GDPC1)</t>
         </is>
@@ -13127,7 +13159,7 @@
         <v>0.095</v>
       </c>
       <c r="B99" s="176" t="n"/>
-      <c r="C99" s="185" t="inlineStr">
+      <c r="C99" s="167" t="inlineStr">
         <is>
           <t>Damodaran: Historical Implied ERP</t>
         </is>
@@ -13381,7 +13413,7 @@
         </is>
       </c>
       <c r="B4" s="176" t="n"/>
-      <c r="C4" s="185" t="inlineStr">
+      <c r="C4" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -13420,7 +13452,7 @@
         </is>
       </c>
       <c r="B6" s="176" t="n"/>
-      <c r="C6" s="188" t="inlineStr">
+      <c r="C6" s="128" t="inlineStr">
         <is>
           <t>↳ DCF base case</t>
         </is>
@@ -13442,7 +13474,7 @@
         </is>
       </c>
       <c r="B7" s="176" t="n"/>
-      <c r="C7" s="185" t="inlineStr">
+      <c r="C7" s="167" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
@@ -13463,7 +13495,7 @@
         </is>
       </c>
       <c r="B8" s="176" t="n"/>
-      <c r="C8" s="185" t="inlineStr">
+      <c r="C8" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -13484,7 +13516,7 @@
         </is>
       </c>
       <c r="B9" s="176" t="n"/>
-      <c r="C9" s="185" t="inlineStr">
+      <c r="C9" s="167" t="inlineStr">
         <is>
           <t>10-K</t>
         </is>
@@ -13505,7 +13537,7 @@
         </is>
       </c>
       <c r="B10" s="176" t="n"/>
-      <c r="C10" s="185" t="inlineStr">
+      <c r="C10" s="167" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -13641,7 +13673,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="C18" s="188" t="inlineStr">
+      <c r="C18" s="126" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -13676,7 +13708,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C19" s="185" t="inlineStr">
+      <c r="C19" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13706,7 +13738,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C20" s="185" t="inlineStr">
+      <c r="C20" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13736,7 +13768,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C21" s="185" t="inlineStr">
+      <c r="C21" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13766,7 +13798,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C22" s="185" t="inlineStr">
+      <c r="C22" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13796,7 +13828,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C23" s="185" t="inlineStr">
+      <c r="C23" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13826,7 +13858,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C24" s="185" t="inlineStr">
+      <c r="C24" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13856,7 +13888,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C25" s="185" t="inlineStr">
+      <c r="C25" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13886,7 +13918,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C26" s="185" t="inlineStr">
+      <c r="C26" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13916,7 +13948,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C27" s="185" t="inlineStr">
+      <c r="C27" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13946,7 +13978,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C28" s="185" t="inlineStr">
+      <c r="C28" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -13976,7 +14008,7 @@
           <t>PitchBook comp</t>
         </is>
       </c>
-      <c r="C29" s="185" t="inlineStr">
+      <c r="C29" s="168" t="inlineStr">
         <is>
           <t>PitchBook Comps Set 04-Sep-2026</t>
         </is>
@@ -14043,7 +14075,7 @@
           <t>Reuters: about $10 billion Moelis ask for Color.</t>
         </is>
       </c>
-      <c r="C33" s="185" t="inlineStr">
+      <c r="C33" s="167" t="inlineStr">
         <is>
           <t>Reuters: Alo parent $10bn Moelis ask Also: Reuters: Alo 2023 process; no deal</t>
         </is>
@@ -14068,7 +14100,7 @@
           <t>Forbes estimates Color Image parent sales nearly $2.</t>
         </is>
       </c>
-      <c r="C34" s="185" t="inlineStr">
+      <c r="C34" s="167" t="inlineStr">
         <is>
           <t>Forbes: Color Image nearly $2bn sales</t>
         </is>
@@ -14093,7 +14125,7 @@
           <t>5.0x = 10 / 2. Implied EV/Sales on.</t>
         </is>
       </c>
-      <c r="C35" s="185" t="inlineStr">
+      <c r="C35" s="167" t="inlineStr">
         <is>
           <t>Comps: Alo ask / parent sales</t>
         </is>
@@ -14119,7 +14151,7 @@
           <t>Alo Yoga excluded from comp set; no reliable EBITDA on pages.</t>
         </is>
       </c>
-      <c r="C36" s="185" t="inlineStr">
+      <c r="C36" s="168" t="inlineStr">
         <is>
           <t>None — no EBITDA source</t>
         </is>
@@ -14172,7 +14204,7 @@
           <t>Core comp average</t>
         </is>
       </c>
-      <c r="C39" s="188" t="inlineStr">
+      <c r="C39" s="126" t="inlineStr">
         <is>
           <t>Derived: Excel AVERAGE of the seven core prints</t>
         </is>
@@ -14198,7 +14230,7 @@
           <t>Wider comp average</t>
         </is>
       </c>
-      <c r="C40" s="188" t="inlineStr">
+      <c r="C40" s="126" t="inlineStr">
         <is>
           <t>Derived: Excel AVERAGE of every positive-EBITDA row</t>
         </is>
@@ -14430,7 +14462,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="C56" s="188" t="inlineStr">
+      <c r="C56" s="126" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -14470,7 +14502,7 @@
 Hi 8.0x DECK high-end cap.</t>
         </is>
       </c>
-      <c r="C57" s="185" t="inlineStr">
+      <c r="C57" s="167" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU EV/EBITDA Hi: StockAnalysis: DECK EV/EBITDA</t>
         </is>
@@ -14503,7 +14535,7 @@
           <t>Gordon TV / FY30 EBITDA exit.</t>
         </is>
       </c>
-      <c r="C58" s="185" t="inlineStr">
+      <c r="C58" s="167" t="inlineStr">
         <is>
           <t>DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
         </is>
@@ -14533,7 +14565,7 @@
 Hi 18x FY26E EPS recovery.</t>
         </is>
       </c>
-      <c r="C59" s="185" t="inlineStr">
+      <c r="C59" s="167" t="inlineStr">
         <is>
           <t>Lo: StockAnalysis: LULU Forward P/E Hi: StockAnalysis: NKE Forward P/E</t>
         </is>
@@ -14594,7 +14626,7 @@
         </is>
       </c>
       <c r="B62" s="176" t="n"/>
-      <c r="C62" s="185" t="inlineStr">
+      <c r="C62" s="167" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
@@ -14665,6 +14697,23 @@
           <t>scratch — dont touch</t>
         </is>
       </c>
+      <c r="B1" s="176" t="n"/>
+      <c r="C1" s="176" t="n"/>
+      <c r="D1" s="176" t="n"/>
+      <c r="E1" s="176" t="n"/>
+      <c r="F1" s="176" t="n"/>
+      <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="176" t="n"/>
+      <c r="B2" s="176" t="n"/>
+      <c r="C2" s="176" t="n"/>
+      <c r="D2" s="176" t="n"/>
+      <c r="E2" s="176" t="n"/>
+      <c r="F2" s="176" t="n"/>
+      <c r="G2" s="176" t="n"/>
+      <c r="H2" s="176" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="211" t="inlineStr">
@@ -14672,6 +14721,13 @@
           <t>10-K dump (FY25 MD&amp;A)</t>
         </is>
       </c>
+      <c r="B3" s="176" t="n"/>
+      <c r="C3" s="176" t="n"/>
+      <c r="D3" s="176" t="n"/>
+      <c r="E3" s="176" t="n"/>
+      <c r="F3" s="176" t="n"/>
+      <c r="G3" s="176" t="n"/>
+      <c r="H3" s="176" t="n"/>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="212" t="inlineStr">
@@ -14679,25 +14735,74 @@
           <t>MD&amp;A — FY2025: Net revenue increased 7% to $11.1 billion. Comparable sales increased 1% on a constant dollar basis. Americas comparable sales decreased 3%; China Mainland increased 20%; Rest of World increased 9%. Gross profit as a percent of net revenue was 59.2% compared to 58.3% last year. We ended the year with 811 company-operated stores globally. Looking ahead, we expect net revenue to decrease 5% to 7% in Q2 FY2026 vs prior year...</t>
         </is>
       </c>
+      <c r="B4" s="176" t="n"/>
+      <c r="C4" s="176" t="n"/>
+      <c r="D4" s="176" t="n"/>
+      <c r="E4" s="176" t="n"/>
+      <c r="F4" s="176" t="n"/>
+      <c r="G4" s="176" t="n"/>
+      <c r="H4" s="176" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="176" t="n"/>
+      <c r="B5" s="176" t="n"/>
+      <c r="C5" s="176" t="n"/>
+      <c r="D5" s="176" t="n"/>
+      <c r="E5" s="176" t="n"/>
+      <c r="F5" s="176" t="n"/>
+      <c r="G5" s="176" t="n"/>
+      <c r="H5" s="176" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="176" t="n"/>
+      <c r="B6" s="176" t="n"/>
+      <c r="C6" s="176" t="n"/>
+      <c r="D6" s="176" t="n"/>
+      <c r="E6" s="176" t="n"/>
+      <c r="F6" s="176" t="n"/>
+      <c r="G6" s="176" t="n"/>
+      <c r="H6" s="176" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="176" t="n"/>
+      <c r="B7" s="176" t="n"/>
+      <c r="C7" s="176" t="n"/>
+      <c r="D7" s="176" t="n"/>
+      <c r="E7" s="176" t="n"/>
+      <c r="F7" s="176" t="n"/>
+      <c r="G7" s="176" t="n"/>
+      <c r="H7" s="176" t="n"/>
     </row>
     <row r="8">
+      <c r="A8" s="176" t="n"/>
+      <c r="B8" s="176" t="n"/>
+      <c r="C8" s="176" t="n"/>
       <c r="D8" s="211" t="inlineStr">
         <is>
           <t>EPS paste from release</t>
         </is>
       </c>
+      <c r="E8" s="176" t="n"/>
+      <c r="F8" s="176" t="n"/>
+      <c r="G8" s="176" t="n"/>
+      <c r="H8" s="176" t="n"/>
     </row>
     <row r="9">
+      <c r="A9" s="176" t="n"/>
+      <c r="B9" s="176" t="n"/>
+      <c r="C9" s="176" t="n"/>
       <c r="D9" s="213" t="inlineStr">
         <is>
           <t>Q2 FY25</t>
         </is>
       </c>
+      <c r="E9" s="176" t="n"/>
       <c r="F9" s="213" t="inlineStr">
         <is>
           <t>2.92</t>
         </is>
       </c>
+      <c r="G9" s="176" t="n"/>
       <c r="H9" s="213" t="inlineStr">
         <is>
           <t>$</t>
@@ -14705,29 +14810,39 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" s="176" t="n"/>
+      <c r="B10" s="176" t="n"/>
+      <c r="C10" s="176" t="n"/>
       <c r="D10" s="213" t="inlineStr">
         <is>
           <t>Q3 FY25</t>
         </is>
       </c>
+      <c r="E10" s="176" t="n"/>
       <c r="F10" s="213" t="inlineStr">
         <is>
           <t>2.87</t>
         </is>
       </c>
+      <c r="G10" s="176" t="n"/>
       <c r="H10" s="213" t="inlineStr"/>
     </row>
     <row r="11">
+      <c r="A11" s="176" t="n"/>
+      <c r="B11" s="176" t="n"/>
+      <c r="C11" s="176" t="n"/>
       <c r="D11" s="213" t="inlineStr">
         <is>
           <t>Q4 FY25</t>
         </is>
       </c>
+      <c r="E11" s="176" t="n"/>
       <c r="F11" s="213" t="inlineStr">
         <is>
           <t>5.99</t>
         </is>
       </c>
+      <c r="G11" s="176" t="n"/>
       <c r="H11" s="213" t="inlineStr">
         <is>
           <t xml:space="preserve">  </t>
@@ -14735,16 +14850,21 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" s="176" t="n"/>
+      <c r="B12" s="176" t="n"/>
+      <c r="C12" s="176" t="n"/>
       <c r="D12" s="213" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
+      <c r="E12" s="176" t="n"/>
       <c r="F12" s="213" t="inlineStr">
         <is>
           <t>14.64</t>
         </is>
       </c>
+      <c r="G12" s="176" t="n"/>
       <c r="H12" s="213" t="inlineStr">
         <is>
           <t xml:space="preserve"> diluted</t>
@@ -14752,21 +14872,66 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" s="176" t="n"/>
+      <c r="B13" s="176" t="n"/>
+      <c r="C13" s="176" t="n"/>
       <c r="D13" s="213" t="inlineStr">
         <is>
           <t>FY26 guide</t>
         </is>
       </c>
+      <c r="E13" s="176" t="n"/>
       <c r="F13" s="213" t="inlineStr">
         <is>
           <t>~$14.50</t>
         </is>
       </c>
+      <c r="G13" s="176" t="n"/>
       <c r="H13" s="213" t="inlineStr">
         <is>
           <t>??? check slide 8</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="176" t="n"/>
+      <c r="B14" s="176" t="n"/>
+      <c r="C14" s="176" t="n"/>
+      <c r="D14" s="176" t="n"/>
+      <c r="E14" s="176" t="n"/>
+      <c r="F14" s="176" t="n"/>
+      <c r="G14" s="176" t="n"/>
+      <c r="H14" s="176" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="176" t="n"/>
+      <c r="B15" s="176" t="n"/>
+      <c r="C15" s="176" t="n"/>
+      <c r="D15" s="176" t="n"/>
+      <c r="E15" s="176" t="n"/>
+      <c r="F15" s="176" t="n"/>
+      <c r="G15" s="176" t="n"/>
+      <c r="H15" s="176" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="176" t="n"/>
+      <c r="B16" s="176" t="n"/>
+      <c r="C16" s="176" t="n"/>
+      <c r="D16" s="176" t="n"/>
+      <c r="E16" s="176" t="n"/>
+      <c r="F16" s="176" t="n"/>
+      <c r="G16" s="176" t="n"/>
+      <c r="H16" s="176" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="176" t="n"/>
+      <c r="B17" s="176" t="n"/>
+      <c r="C17" s="176" t="n"/>
+      <c r="D17" s="176" t="n"/>
+      <c r="E17" s="176" t="n"/>
+      <c r="F17" s="176" t="n"/>
+      <c r="G17" s="176" t="n"/>
+      <c r="H17" s="176" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="211" t="inlineStr">
@@ -14774,6 +14939,13 @@
           <t>wacc sanity</t>
         </is>
       </c>
+      <c r="B18" s="176" t="n"/>
+      <c r="C18" s="176" t="n"/>
+      <c r="D18" s="176" t="n"/>
+      <c r="E18" s="176" t="n"/>
+      <c r="F18" s="176" t="n"/>
+      <c r="G18" s="176" t="n"/>
+      <c r="H18" s="176" t="n"/>
     </row>
     <row r="19" ht="14" customHeight="1">
       <c r="A19" s="213" t="inlineStr">
@@ -14781,16 +14953,21 @@
           <t>rf</t>
         </is>
       </c>
+      <c r="B19" s="176" t="n"/>
       <c r="C19" s="213" t="inlineStr">
         <is>
           <t>4.8%</t>
         </is>
       </c>
+      <c r="D19" s="176" t="n"/>
       <c r="E19" s="213" t="inlineStr">
         <is>
           <t>FRED DGS10 9/9/26</t>
         </is>
       </c>
+      <c r="F19" s="176" t="n"/>
+      <c r="G19" s="176" t="n"/>
+      <c r="H19" s="176" t="n"/>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" s="213" t="inlineStr">
@@ -14798,16 +14975,21 @@
           <t>ERP</t>
         </is>
       </c>
+      <c r="B20" s="176" t="n"/>
       <c r="C20" s="213" t="inlineStr">
         <is>
           <t>5.5%</t>
         </is>
       </c>
+      <c r="D20" s="176" t="n"/>
       <c r="E20" s="213" t="inlineStr">
         <is>
           <t>Damodaran Jan-26 + 177bps</t>
         </is>
       </c>
+      <c r="F20" s="176" t="n"/>
+      <c r="G20" s="176" t="n"/>
+      <c r="H20" s="176" t="n"/>
     </row>
     <row r="21" ht="14" customHeight="1">
       <c r="A21" s="213" t="inlineStr">
@@ -14815,16 +14997,21 @@
           <t>beta</t>
         </is>
       </c>
+      <c r="B21" s="176" t="n"/>
       <c r="C21" s="213" t="inlineStr">
         <is>
           <t>1.35</t>
         </is>
       </c>
+      <c r="D21" s="176" t="n"/>
       <c r="E21" s="213" t="inlineStr">
         <is>
           <t>Yahoo 5Y mo — relever w/ lease D/E</t>
         </is>
       </c>
+      <c r="F21" s="176" t="n"/>
+      <c r="G21" s="176" t="n"/>
+      <c r="H21" s="176" t="n"/>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="213" t="inlineStr">
@@ -14832,21 +15019,25 @@
           <t>WACC?</t>
         </is>
       </c>
+      <c r="B22" s="176" t="n"/>
       <c r="C22" s="213" t="inlineStr">
         <is>
           <t>8.1%</t>
         </is>
       </c>
+      <c r="D22" s="176" t="n"/>
       <c r="E22" s="213" t="inlineStr">
         <is>
           <t>back of envelope — tie to WACC tab</t>
         </is>
       </c>
+      <c r="F22" s="176" t="n"/>
       <c r="G22" s="214" t="inlineStr">
         <is>
           <t>todo: fix capex fade note on Scenarios (typo: 'fades donw')</t>
         </is>
       </c>
+      <c r="H22" s="176" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -14,7 +14,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scratch" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1670,16 +1669,9 @@
         <t>Line item — FY25 10-K. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
+    <comment ref="C6" authorId="0" shapeId="0">
       <text>
         <t>Net revenue FY25 10-K. Source: https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
-      </text>
-    </comment>
-    <comment ref="B6" authorId="0" shapeId="0">
-      <text>
-        <t>Minus 6.1% FY26 revenue per company guidance midpoint.
-Source: LULU Q2 FY2026 earnings release Also: StockAnalysis: LULU 3Y revenue forecast
-https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
       </text>
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
@@ -1720,217 +1712,222 @@
     </comment>
     <comment ref="B15" authorId="0" shapeId="0">
       <text>
+        <t>FY25 D&amp;A from 10-K cash flow statement (Depreciation and amortization).</t>
+      </text>
+    </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
         <t>4.5% of sales from FY25 D&amp;A over revenue.
 Source: LULU CF statement (10-K)
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B17" authorId="0" shapeId="0">
+    <comment ref="B18" authorId="0" shapeId="0">
       <text>
         <t>5.5% model rate; FY26 7% capex guide fades down.
 Source: LULU 10-K: 2026 capex guide $725–745M Also: Q2 FY2026 outlook: $10.350B–$10.500B sales
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B19" authorId="0" shapeId="0">
+    <comment ref="B20" authorId="0" shapeId="0">
       <text>
         <t>NWC schedule nets to 13.2% of FY25 sales.
 Source: LULU FY2025 10-K: working-capital components
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B20" authorId="0" shapeId="0">
+    <comment ref="B21" authorId="0" shapeId="0">
       <text>
         <t>6.3 days DSO held flat vs FY25 actual.
 Source: LULU FY2025 10-K: Accounts receivable, net
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B21" authorId="0" shapeId="0">
+    <comment ref="B22" authorId="0" shapeId="0">
       <text>
         <t>Implied ~1.7% of revenue (not a direct %.
 Source: LULU FY2025 10-K: Accounts receivable, net
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B22" authorId="0" shapeId="0">
+    <comment ref="B23" authorId="0" shapeId="0">
       <text>
         <t>128.8 day DIO anchor; minus 1 day per year.
 Source: LULU FY2025 10-K: Inventories &amp; COGS Also: LULU FY2025 10-K: inventory &amp; markdown outlook
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B23" authorId="0" shapeId="0">
+    <comment ref="B24" authorId="0" shapeId="0">
       <text>
         <t>Not % of revenue; $ balance (not a.
 Source: LULU FY2025 10-K: Inventories
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B24" authorId="0" shapeId="0">
+    <comment ref="B25" authorId="0" shapeId="0">
       <text>
         <t>25.1 days DPO held flat vs FY25 actual.
 Source: LULU FY2025 10-K: Accounts payable &amp; COGS
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B25" authorId="0" shapeId="0">
+    <comment ref="B26" authorId="0" shapeId="0">
       <text>
         <t>Implied ~3.0% of revenue (not a direct %.
 Source: LULU FY2025 10-K: Accounts payable
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B26" authorId="0" shapeId="0">
+    <comment ref="B27" authorId="0" shapeId="0">
       <text>
         <t>5.1% of revenue (flat). FY25 other current assets.
 Source: LULU FY2025 10-K: other current assets (residual)
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B27" authorId="0" shapeId="0">
+    <comment ref="B28" authorId="0" shapeId="0">
       <text>
         <t>5.1% of revenue (flat). FY25 other current assets.
 Source: LULU FY2025 10-K: other current assets (residual)
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B28" authorId="0" shapeId="0">
+    <comment ref="B29" authorId="0" shapeId="0">
       <text>
         <t>6.0% of revenue (flat). FY25 accrued liabilities ÷.
 Source: LULU FY2025 10-K: Accrued liabilities and other
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B29" authorId="0" shapeId="0">
+    <comment ref="B30" authorId="0" shapeId="0">
       <text>
         <t>6.0% of revenue (flat). FY25 accrued liabilities ÷.
 Source: LULU FY2025 10-K: Accrued liabilities and other
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B30" authorId="0" shapeId="0">
+    <comment ref="B31" authorId="0" shapeId="0">
       <text>
         <t>Operating assets sum to 22.1% of FY25 sales.
 Source: Scenarios tab: AR + inventory + prepaids</t>
       </text>
     </comment>
-    <comment ref="B31" authorId="0" shapeId="0">
+    <comment ref="B32" authorId="0" shapeId="0">
       <text>
         <t>Operating liabilities sum to 9.0% of FY25 sales.
 Source: Scenarios tab: AP + accrued liabilities</t>
       </text>
     </comment>
-    <comment ref="B32" authorId="0" shapeId="0">
+    <comment ref="B33" authorId="0" shapeId="0">
       <text>
         <t>Not one %; net ≈13.2% of FY25 sales.
 Source: LULU FY2025 10-K: working-capital components
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B33" authorId="0" shapeId="0">
+    <comment ref="B34" authorId="0" shapeId="0">
       <text>
         <t>Year-over-year dollar change in net working capital schedule.
 Source: Scenarios tab: NWC roll-forward (driver schedule)</t>
       </text>
     </comment>
-    <comment ref="B43" authorId="0" shapeId="0">
+    <comment ref="B44" authorId="0" shapeId="0">
       <text>
         <t>2.25% terminal g sits next to FRED GDPC1.
 Source: FRED: Real GDP (GDPC1)
 https://fred.stlouisfed.org/series/GDPC1</t>
       </text>
     </comment>
-    <comment ref="B50" authorId="0" shapeId="0">
+    <comment ref="B51" authorId="0" shapeId="0">
       <text>
         <t>Source: 10-K
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B51" authorId="0" shapeId="0">
+    <comment ref="B52" authorId="0" shapeId="0">
       <text>
         <t>Subtract ASC 842 operating lease liabilities as debt.
 Source: LULU FY2025 10-K: operating lease liabilities
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B55" authorId="0" shapeId="0">
+    <comment ref="B56" authorId="0" shapeId="0">
       <text>
         <t>Source: 10-K
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
-    <comment ref="B57" authorId="0" shapeId="0">
+    <comment ref="B58" authorId="0" shapeId="0">
       <text>
         <t>Source: NASDAQ
 https://www.nasdaq.com/market-activity/stocks/lulu</t>
       </text>
     </comment>
-    <comment ref="B82" authorId="0" shapeId="0">
+    <comment ref="B83" authorId="0" shapeId="0">
       <text>
         <t>Selected exit is Gordon TV / FY30 EBITDA..
 Source: DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
       </text>
     </comment>
-    <comment ref="B89" authorId="0" shapeId="0">
+    <comment ref="B90" authorId="0" shapeId="0">
       <text>
         <t>Gordon Growth
 Source: Exit Multiple</t>
       </text>
     </comment>
-    <comment ref="B90" authorId="0" shapeId="0">
+    <comment ref="B91" authorId="0" shapeId="0">
       <text>
         <t>=E45
 Source: =E83</t>
       </text>
     </comment>
-    <comment ref="B91" authorId="0" shapeId="0">
+    <comment ref="B92" authorId="0" shapeId="0">
       <text>
         <t>=E46
 Source: =E82</t>
       </text>
     </comment>
-    <comment ref="B93" authorId="0" shapeId="0">
+    <comment ref="B94" authorId="0" shapeId="0">
       <text>
         <t>=E56
 Source: =E86</t>
       </text>
     </comment>
-    <comment ref="B94" authorId="0" shapeId="0">
+    <comment ref="B95" authorId="0" shapeId="0">
       <text>
         <t>=IF(ABS(D91)&lt;=1.5,"PASS","REVIEW")
 Source: =TEXT(D91,"0.0")&amp;"x spread vs Gordon-implied exit"</t>
       </text>
     </comment>
-    <comment ref="B98" authorId="0" shapeId="0">
+    <comment ref="B99" authorId="0" shapeId="0">
       <text>
         <t>Sensitivity grid; terminal g spans 1.5% to 3.0%.
 Source: FRED: Real GDP (GDPC1)
 https://fred.stlouisfed.org/series/GDPC1</t>
       </text>
     </comment>
-    <comment ref="B99" authorId="0" shapeId="0">
+    <comment ref="B100" authorId="0" shapeId="0">
       <text>
         <t>Source: Damodaran: Historical Implied ERP
 https://www.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html</t>
       </text>
     </comment>
-    <comment ref="C100" authorId="0" shapeId="0">
+    <comment ref="C101" authorId="0" shapeId="0">
       <text>
         <t>WACC sensitivity −100 bps vs base.</t>
       </text>
     </comment>
-    <comment ref="C101" authorId="0" shapeId="0">
+    <comment ref="C102" authorId="0" shapeId="0">
       <text>
         <t>WACC sensitivity −50 bps vs base.</t>
       </text>
     </comment>
-    <comment ref="C102" authorId="0" shapeId="0">
+    <comment ref="C103" authorId="0" shapeId="0">
       <text>
         <t>WACC sensitivity +50 bps vs base.</t>
       </text>
     </comment>
-    <comment ref="C103" authorId="0" shapeId="0">
+    <comment ref="C104" authorId="0" shapeId="0">
       <text>
         <t>WACC sensitivity +100 bps vs base.</t>
       </text>
@@ -2730,7 +2727,7 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Yahoo Total Debt (mrq)</t>
+          <t>Total Debt</t>
         </is>
       </c>
       <c r="B17" s="187" t="n">
@@ -2740,7 +2737,7 @@
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Yahoo Market Cap (same page as beta L)</t>
+          <t>Market Capitalization</t>
         </is>
       </c>
       <c r="B18" s="187" t="n">
@@ -2750,7 +2747,7 @@
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>D/E for unlever (Yahoo debt mrq / Yahoo market cap)</t>
+          <t>Target Debt-to-Equity</t>
         </is>
       </c>
       <c r="B19" s="28">
@@ -3204,13 +3201,13 @@
       </c>
       <c r="B15" s="176" t="n"/>
       <c r="C15" s="193" t="n">
-        <v>6.267883648875038</v>
+        <v>6.3</v>
       </c>
       <c r="D15" s="193" t="n">
-        <v>6.267883648875038</v>
+        <v>6.3</v>
       </c>
       <c r="E15" s="193" t="n">
-        <v>6.267883648875038</v>
+        <v>6.3</v>
       </c>
       <c r="F15" s="176" t="n"/>
       <c r="G15" s="176" t="n"/>
@@ -3223,13 +3220,13 @@
       </c>
       <c r="B16" s="176" t="n"/>
       <c r="C16" s="193" t="n">
-        <v>128.8324100108167</v>
+        <v>128.8</v>
       </c>
       <c r="D16" s="193" t="n">
-        <v>128.8324100108167</v>
+        <v>128.8</v>
       </c>
       <c r="E16" s="193" t="n">
-        <v>128.8324100108167</v>
+        <v>128.8</v>
       </c>
       <c r="F16" s="176" t="n"/>
       <c r="G16" s="176" t="n"/>
@@ -3261,13 +3258,13 @@
       </c>
       <c r="B18" s="176" t="n"/>
       <c r="C18" s="193" t="n">
-        <v>25.10521290169407</v>
+        <v>25.1</v>
       </c>
       <c r="D18" s="193" t="n">
-        <v>25.10521290169407</v>
+        <v>25.1</v>
       </c>
       <c r="E18" s="193" t="n">
-        <v>25.10521290169407</v>
+        <v>25.1</v>
       </c>
       <c r="F18" s="176" t="n"/>
       <c r="G18" s="176" t="n"/>
@@ -3280,13 +3277,13 @@
       </c>
       <c r="B19" s="176" t="n"/>
       <c r="C19" s="32" t="n">
-        <v>0.05080692810692991</v>
+        <v>0.051</v>
       </c>
       <c r="D19" s="32" t="n">
-        <v>0.05080692810692991</v>
+        <v>0.051</v>
       </c>
       <c r="E19" s="32" t="n">
-        <v>0.05080692810692991</v>
+        <v>0.051</v>
       </c>
       <c r="F19" s="176" t="n"/>
       <c r="G19" s="176" t="n"/>
@@ -3299,13 +3296,13 @@
       </c>
       <c r="B20" s="176" t="n"/>
       <c r="C20" s="32" t="n">
-        <v>0.05971412101669879</v>
+        <v>0.06</v>
       </c>
       <c r="D20" s="32" t="n">
-        <v>0.05971412101669879</v>
+        <v>0.06</v>
       </c>
       <c r="E20" s="32" t="n">
-        <v>0.05971412101669879</v>
+        <v>0.06</v>
       </c>
       <c r="F20" s="176" t="n"/>
       <c r="G20" s="176" t="n"/>
@@ -10361,7 +10358,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -10444,60 +10441,59 @@
       <c r="G4" s="176" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
-        <is>
-          <t>Net revenue</t>
-        </is>
-      </c>
-      <c r="B5" s="187" t="n">
-        <v>11102600</v>
-      </c>
-      <c r="C5" s="75">
-        <f>B5*(1+Scenarios!$D$4)</f>
-        <v/>
-      </c>
-      <c r="D5" s="75">
-        <f>C5*(1+Scenarios!$D$5)</f>
-        <v/>
-      </c>
-      <c r="E5" s="75">
-        <f>D5*(1+Scenarios!$D$5)</f>
-        <v/>
-      </c>
-      <c r="F5" s="75">
-        <f>E5*(1+Scenarios!$D$5)</f>
-        <v/>
-      </c>
-      <c r="G5" s="75">
-        <f>F5*(1+Scenarios!$D$5)</f>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Revenue Growth %</t>
+        </is>
+      </c>
+      <c r="C5">
+        <f>Scenarios!$D$4</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>Scenarios!$D$5</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>Scenarios!$D$5</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>Scenarios!$D$5</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>Scenarios!$D$5</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
         <is>
-          <t>Revenue growth %</t>
-        </is>
-      </c>
-      <c r="B6" s="176" t="n"/>
-      <c r="C6" s="32">
-        <f>C5/B5-1</f>
-        <v/>
-      </c>
-      <c r="D6" s="32">
-        <f>D5/C5-1</f>
-        <v/>
-      </c>
-      <c r="E6" s="32">
-        <f>E5/D5-1</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>F5/E5-1</f>
-        <v/>
-      </c>
-      <c r="G6" s="32">
-        <f>G5/F5-1</f>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="B6" s="187" t="n">
+        <v>11102600</v>
+      </c>
+      <c r="C6" s="75">
+        <f>B6*(1+C5)</f>
+        <v/>
+      </c>
+      <c r="D6" s="75">
+        <f>C6*(1+D5)</f>
+        <v/>
+      </c>
+      <c r="E6" s="75">
+        <f>D6*(1+E5)</f>
+        <v/>
+      </c>
+      <c r="F6" s="75">
+        <f>E6*(1+F5)</f>
+        <v/>
+      </c>
+      <c r="G6" s="75">
+        <f>F6*(1+G5)</f>
         <v/>
       </c>
     </row>
@@ -10541,23 +10537,23 @@
         <v>4818468</v>
       </c>
       <c r="C8" s="75">
-        <f>C5*(1-C7)</f>
+        <f>C6*(1-C7)</f>
         <v/>
       </c>
       <c r="D8" s="75">
-        <f>D5*(1-D7)</f>
+        <f>D6*(1-D7)</f>
         <v/>
       </c>
       <c r="E8" s="75">
-        <f>E5*(1-E7)</f>
+        <f>E6*(1-E7)</f>
         <v/>
       </c>
       <c r="F8" s="75">
-        <f>F5*(1-F7)</f>
+        <f>F6*(1-F7)</f>
         <v/>
       </c>
       <c r="G8" s="75">
-        <f>G5*(1-G7)</f>
+        <f>G6*(1-G7)</f>
         <v/>
       </c>
     </row>
@@ -10569,23 +10565,23 @@
       </c>
       <c r="B9" s="176" t="n"/>
       <c r="C9" s="32">
-        <f>Scenarios!$D$6+(Scenarios!$D$8-Scenarios!$D$6)*0/4</f>
+        <f>Scenarios!$D$6</f>
         <v/>
       </c>
       <c r="D9" s="32">
-        <f>Scenarios!$D$6+(Scenarios!$D$8-Scenarios!$D$6)*1/4</f>
+        <f>C9+(Scenarios!$D$8-Scenarios!$D$6)/4</f>
         <v/>
       </c>
       <c r="E9" s="32">
-        <f>Scenarios!$D$6+(Scenarios!$D$8-Scenarios!$D$6)*2/4</f>
+        <f>D9+(Scenarios!$D$8-Scenarios!$D$6)/4</f>
         <v/>
       </c>
       <c r="F9" s="32">
-        <f>Scenarios!$D$6+(Scenarios!$D$8-Scenarios!$D$6)*3/4</f>
+        <f>E9+(Scenarios!$D$8-Scenarios!$D$6)/4</f>
         <v/>
       </c>
       <c r="G9" s="32">
-        <f>Scenarios!$D$6+(Scenarios!$D$8-Scenarios!$D$6)*4/4</f>
+        <f>F9+(Scenarios!$D$8-Scenarios!$D$6)/4</f>
         <v/>
       </c>
     </row>
@@ -10599,7 +10595,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="75">
-        <f>Scenarios!$B$7</f>
+        <f>Scenarios!$D$7</f>
         <v/>
       </c>
       <c r="D10" s="75" t="n">
@@ -10625,23 +10621,23 @@
         <v>2210615</v>
       </c>
       <c r="C11" s="130">
-        <f>C5*C9</f>
+        <f>C6*C9+C10</f>
         <v/>
       </c>
       <c r="D11" s="130">
-        <f>D5*D9</f>
+        <f>D6*D9</f>
         <v/>
       </c>
       <c r="E11" s="130">
-        <f>E5*E9</f>
+        <f>E6*E9</f>
         <v/>
       </c>
       <c r="F11" s="130">
-        <f>F5*F9</f>
+        <f>F6*F9</f>
         <v/>
       </c>
       <c r="G11" s="130">
-        <f>G5*G9</f>
+        <f>G6*G9</f>
         <v/>
       </c>
     </row>
@@ -10655,23 +10651,23 @@
         <v>0.1991078666258354</v>
       </c>
       <c r="C12" s="32">
-        <f>C11/C5</f>
+        <f>C11/C6</f>
         <v/>
       </c>
       <c r="D12" s="32">
-        <f>D11/D5</f>
+        <f>D11/D6</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>E11/E5</f>
+        <f>E11/E6</f>
         <v/>
       </c>
       <c r="F12" s="32">
-        <f>F11/F5</f>
+        <f>F11/F6</f>
         <v/>
       </c>
       <c r="G12" s="32">
-        <f>G11/G5</f>
+        <f>G11/G6</f>
         <v/>
       </c>
     </row>
@@ -10732,675 +10728,672 @@
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t>D&amp;A % of revenue</t>
-        </is>
-      </c>
-      <c r="B15" s="176" t="n"/>
-      <c r="C15" s="32">
-        <f>C5*Scenarios!$D$12</f>
-        <v/>
-      </c>
-      <c r="D15" s="32">
-        <f>D5*Scenarios!$D$12</f>
-        <v/>
-      </c>
-      <c r="E15" s="32">
-        <f>E5*Scenarios!$D$12</f>
-        <v/>
-      </c>
-      <c r="F15" s="32">
-        <f>F5*Scenarios!$D$12</f>
-        <v/>
-      </c>
-      <c r="G15" s="32">
-        <f>G5*Scenarios!$D$12</f>
-        <v/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FY25 D&amp;A ($000)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>496228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>Plus: D&amp;A</t>
+          <t>D&amp;A % of revenue</t>
         </is>
       </c>
       <c r="B16" s="176" t="n"/>
-      <c r="C16" s="75">
-        <f>Scenarios!D55</f>
-        <v/>
-      </c>
-      <c r="D16" s="75">
-        <f>Scenarios!D56</f>
-        <v/>
-      </c>
-      <c r="E16" s="75">
-        <f>Scenarios!D57</f>
-        <v/>
-      </c>
-      <c r="F16" s="75">
-        <f>Scenarios!D58</f>
-        <v/>
-      </c>
-      <c r="G16" s="75">
-        <f>Scenarios!D59</f>
+      <c r="C16" s="32">
+        <f>Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="D16" s="32">
+        <f>Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="F16" s="32">
+        <f>Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>Scenarios!$D$12</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Capex % of revenue</t>
+          <t>Plus: D&amp;A</t>
         </is>
       </c>
       <c r="B17" s="176" t="n"/>
-      <c r="C17" s="32">
-        <f>-C5*Scenarios!$D$13</f>
-        <v/>
-      </c>
-      <c r="D17" s="32">
-        <f>-D5*Scenarios!$D$13</f>
-        <v/>
-      </c>
-      <c r="E17" s="32">
-        <f>-E5*Scenarios!$D$13</f>
-        <v/>
-      </c>
-      <c r="F17" s="32">
-        <f>-F5*Scenarios!$D$13</f>
-        <v/>
-      </c>
-      <c r="G17" s="32">
-        <f>-G5*Scenarios!$D$13</f>
+      <c r="C17" s="75">
+        <f>C6*Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="D17" s="75">
+        <f>D6*Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="E17" s="75">
+        <f>E6*Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="F17" s="75">
+        <f>F6*Scenarios!$D$12</f>
+        <v/>
+      </c>
+      <c r="G17" s="75">
+        <f>G6*Scenarios!$D$12</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
         <is>
+          <t>Capex % of revenue</t>
+        </is>
+      </c>
+      <c r="B18" s="176" t="n"/>
+      <c r="C18" s="32">
+        <f>-C6*Scenarios!$D$13</f>
+        <v/>
+      </c>
+      <c r="D18" s="32">
+        <f>-D6*Scenarios!$D$13</f>
+        <v/>
+      </c>
+      <c r="E18" s="32">
+        <f>-E6*Scenarios!$D$13</f>
+        <v/>
+      </c>
+      <c r="F18" s="32">
+        <f>-F6*Scenarios!$D$13</f>
+        <v/>
+      </c>
+      <c r="G18" s="32">
+        <f>-G6*Scenarios!$D$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
           <t>Less: Capex</t>
         </is>
       </c>
-      <c r="B18" s="176" t="n"/>
-      <c r="C18" s="75">
+      <c r="B19" s="176" t="n"/>
+      <c r="C19" s="75">
         <f>-Scenarios!D60</f>
         <v/>
       </c>
-      <c r="D18" s="75">
+      <c r="D19" s="75">
         <f>-Scenarios!D61</f>
         <v/>
       </c>
-      <c r="E18" s="75">
+      <c r="E19" s="75">
         <f>-Scenarios!D62</f>
         <v/>
       </c>
-      <c r="F18" s="75">
+      <c r="F19" s="75">
         <f>-Scenarios!D63</f>
         <v/>
       </c>
-      <c r="G18" s="75">
+      <c r="G19" s="75">
         <f>-Scenarios!D64</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="68" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="68" t="inlineStr">
         <is>
           <t>Working capital</t>
         </is>
       </c>
-      <c r="B19" s="176" t="n"/>
-      <c r="C19" s="176" t="n"/>
-      <c r="D19" s="176" t="n"/>
-      <c r="E19" s="176" t="n"/>
-      <c r="F19" s="176" t="n"/>
-      <c r="G19" s="176" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>DSO (days)</t>
-        </is>
-      </c>
-      <c r="B20" s="193" t="n">
-        <v>6.267883648875038</v>
-      </c>
-      <c r="C20" s="28">
-        <f>Scenarios!D65</f>
-        <v/>
-      </c>
-      <c r="D20" s="28">
-        <f>Scenarios!D66</f>
-        <v/>
-      </c>
-      <c r="E20" s="28">
-        <f>Scenarios!D67</f>
-        <v/>
-      </c>
-      <c r="F20" s="28">
-        <f>Scenarios!D68</f>
-        <v/>
-      </c>
-      <c r="G20" s="28">
-        <f>Scenarios!D69</f>
-        <v/>
-      </c>
+      <c r="B20" s="176" t="n"/>
+      <c r="C20" s="176" t="n"/>
+      <c r="D20" s="176" t="n"/>
+      <c r="E20" s="176" t="n"/>
+      <c r="F20" s="176" t="n"/>
+      <c r="G20" s="176" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Accounts receivable, net</t>
-        </is>
-      </c>
-      <c r="B21" s="187" t="n">
-        <v>190657</v>
-      </c>
-      <c r="C21" s="75">
-        <f>Scenarios!D70</f>
-        <v/>
-      </c>
-      <c r="D21" s="75">
-        <f>Scenarios!D71</f>
-        <v/>
-      </c>
-      <c r="E21" s="75">
-        <f>Scenarios!D72</f>
-        <v/>
-      </c>
-      <c r="F21" s="75">
-        <f>Scenarios!D73</f>
-        <v/>
-      </c>
-      <c r="G21" s="75">
-        <f>Scenarios!D74</f>
+          <t>DSO (days)</t>
+        </is>
+      </c>
+      <c r="B21" s="193" t="n">
+        <v>6.267883648875038</v>
+      </c>
+      <c r="C21" s="28">
+        <f>Scenarios!D65</f>
+        <v/>
+      </c>
+      <c r="D21" s="28">
+        <f>Scenarios!D66</f>
+        <v/>
+      </c>
+      <c r="E21" s="28">
+        <f>Scenarios!D67</f>
+        <v/>
+      </c>
+      <c r="F21" s="28">
+        <f>Scenarios!D68</f>
+        <v/>
+      </c>
+      <c r="G21" s="28">
+        <f>Scenarios!D69</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>DIO (days)</t>
-        </is>
-      </c>
-      <c r="B22" s="193" t="n">
-        <v>128.8324100108167</v>
-      </c>
-      <c r="C22" s="28">
-        <f>Scenarios!D75</f>
-        <v/>
-      </c>
-      <c r="D22" s="28">
-        <f>Scenarios!D76</f>
-        <v/>
-      </c>
-      <c r="E22" s="28">
-        <f>Scenarios!D77</f>
-        <v/>
-      </c>
-      <c r="F22" s="28">
-        <f>Scenarios!D78</f>
-        <v/>
-      </c>
-      <c r="G22" s="28">
-        <f>Scenarios!D79</f>
+          <t>Accounts receivable, net</t>
+        </is>
+      </c>
+      <c r="B22" s="187" t="n">
+        <v>190657</v>
+      </c>
+      <c r="C22" s="75">
+        <f>Scenarios!D70</f>
+        <v/>
+      </c>
+      <c r="D22" s="75">
+        <f>Scenarios!D71</f>
+        <v/>
+      </c>
+      <c r="E22" s="75">
+        <f>Scenarios!D72</f>
+        <v/>
+      </c>
+      <c r="F22" s="75">
+        <f>Scenarios!D73</f>
+        <v/>
+      </c>
+      <c r="G22" s="75">
+        <f>Scenarios!D74</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Inventories</t>
-        </is>
-      </c>
-      <c r="B23" s="187" t="n">
-        <v>1700753</v>
-      </c>
-      <c r="C23" s="75">
-        <f>Scenarios!D80</f>
-        <v/>
-      </c>
-      <c r="D23" s="75">
-        <f>Scenarios!D81</f>
-        <v/>
-      </c>
-      <c r="E23" s="75">
-        <f>Scenarios!D82</f>
-        <v/>
-      </c>
-      <c r="F23" s="75">
-        <f>Scenarios!D83</f>
-        <v/>
-      </c>
-      <c r="G23" s="75">
-        <f>Scenarios!D84</f>
+          <t>DIO (days)</t>
+        </is>
+      </c>
+      <c r="B23" s="193" t="n">
+        <v>128.8324100108167</v>
+      </c>
+      <c r="C23" s="28">
+        <f>Scenarios!D75</f>
+        <v/>
+      </c>
+      <c r="D23" s="28">
+        <f>Scenarios!D76</f>
+        <v/>
+      </c>
+      <c r="E23" s="28">
+        <f>Scenarios!D77</f>
+        <v/>
+      </c>
+      <c r="F23" s="28">
+        <f>Scenarios!D78</f>
+        <v/>
+      </c>
+      <c r="G23" s="28">
+        <f>Scenarios!D79</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>DPO (days)</t>
-        </is>
-      </c>
-      <c r="B24" s="193" t="n">
-        <v>25.10521290169407</v>
-      </c>
-      <c r="C24" s="28">
-        <f>Scenarios!D85</f>
-        <v/>
-      </c>
-      <c r="D24" s="28">
-        <f>Scenarios!D86</f>
-        <v/>
-      </c>
-      <c r="E24" s="28">
-        <f>Scenarios!D87</f>
-        <v/>
-      </c>
-      <c r="F24" s="28">
-        <f>Scenarios!D88</f>
-        <v/>
-      </c>
-      <c r="G24" s="28">
-        <f>Scenarios!D89</f>
+          <t>Inventories</t>
+        </is>
+      </c>
+      <c r="B24" s="187" t="n">
+        <v>1700753</v>
+      </c>
+      <c r="C24" s="75">
+        <f>Scenarios!D80</f>
+        <v/>
+      </c>
+      <c r="D24" s="75">
+        <f>Scenarios!D81</f>
+        <v/>
+      </c>
+      <c r="E24" s="75">
+        <f>Scenarios!D82</f>
+        <v/>
+      </c>
+      <c r="F24" s="75">
+        <f>Scenarios!D83</f>
+        <v/>
+      </c>
+      <c r="G24" s="75">
+        <f>Scenarios!D84</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Accounts payable</t>
-        </is>
-      </c>
-      <c r="B25" s="187" t="n">
-        <v>331421</v>
-      </c>
-      <c r="C25" s="75">
-        <f>Scenarios!D90</f>
-        <v/>
-      </c>
-      <c r="D25" s="75">
-        <f>Scenarios!D91</f>
-        <v/>
-      </c>
-      <c r="E25" s="75">
-        <f>Scenarios!D92</f>
-        <v/>
-      </c>
-      <c r="F25" s="75">
-        <f>Scenarios!D93</f>
-        <v/>
-      </c>
-      <c r="G25" s="75">
-        <f>Scenarios!D94</f>
+          <t>DPO (days)</t>
+        </is>
+      </c>
+      <c r="B25" s="193" t="n">
+        <v>25.10521290169407</v>
+      </c>
+      <c r="C25" s="28">
+        <f>Scenarios!D85</f>
+        <v/>
+      </c>
+      <c r="D25" s="28">
+        <f>Scenarios!D86</f>
+        <v/>
+      </c>
+      <c r="E25" s="28">
+        <f>Scenarios!D87</f>
+        <v/>
+      </c>
+      <c r="F25" s="28">
+        <f>Scenarios!D88</f>
+        <v/>
+      </c>
+      <c r="G25" s="28">
+        <f>Scenarios!D89</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Prepaid expenses (% of revenue)</t>
-        </is>
-      </c>
-      <c r="B26" s="32" t="n">
-        <v>0.05080692810692991</v>
-      </c>
-      <c r="C26" s="32">
-        <f>Scenarios!$B$19</f>
-        <v/>
-      </c>
-      <c r="D26" s="32">
-        <f>Scenarios!$B$19</f>
-        <v/>
-      </c>
-      <c r="E26" s="32">
-        <f>Scenarios!$B$19</f>
-        <v/>
-      </c>
-      <c r="F26" s="32">
-        <f>Scenarios!$B$19</f>
-        <v/>
-      </c>
-      <c r="G26" s="32">
-        <f>Scenarios!$B$19</f>
+          <t>Accounts payable</t>
+        </is>
+      </c>
+      <c r="B26" s="187" t="n">
+        <v>331421</v>
+      </c>
+      <c r="C26" s="75">
+        <f>Scenarios!D90</f>
+        <v/>
+      </c>
+      <c r="D26" s="75">
+        <f>Scenarios!D91</f>
+        <v/>
+      </c>
+      <c r="E26" s="75">
+        <f>Scenarios!D92</f>
+        <v/>
+      </c>
+      <c r="F26" s="75">
+        <f>Scenarios!D93</f>
+        <v/>
+      </c>
+      <c r="G26" s="75">
+        <f>Scenarios!D94</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Prepaid expenses (other current assets)</t>
-        </is>
-      </c>
-      <c r="B27" s="187" t="n">
-        <v>564089</v>
-      </c>
-      <c r="C27" s="75">
-        <f>Scenarios!D95</f>
-        <v/>
-      </c>
-      <c r="D27" s="75">
-        <f>Scenarios!D96</f>
-        <v/>
-      </c>
-      <c r="E27" s="75">
-        <f>Scenarios!D97</f>
-        <v/>
-      </c>
-      <c r="F27" s="75">
-        <f>Scenarios!D98</f>
-        <v/>
-      </c>
-      <c r="G27" s="75">
-        <f>Scenarios!D99</f>
+          <t>Prepaid expenses (% of revenue)</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="n">
+        <v>0.05080692810692991</v>
+      </c>
+      <c r="C27" s="32">
+        <f>Scenarios!$B$19</f>
+        <v/>
+      </c>
+      <c r="D27" s="32">
+        <f>Scenarios!$B$19</f>
+        <v/>
+      </c>
+      <c r="E27" s="32">
+        <f>Scenarios!$B$19</f>
+        <v/>
+      </c>
+      <c r="F27" s="32">
+        <f>Scenarios!$B$19</f>
+        <v/>
+      </c>
+      <c r="G27" s="32">
+        <f>Scenarios!$B$19</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Accrued liabilities (% of revenue)</t>
-        </is>
-      </c>
-      <c r="B28" s="32" t="n">
-        <v>0.05971412101669879</v>
-      </c>
-      <c r="C28" s="32">
-        <f>Scenarios!$B$20</f>
-        <v/>
-      </c>
-      <c r="D28" s="32">
-        <f>Scenarios!$B$20</f>
-        <v/>
-      </c>
-      <c r="E28" s="32">
-        <f>Scenarios!$B$20</f>
-        <v/>
-      </c>
-      <c r="F28" s="32">
-        <f>Scenarios!$B$20</f>
-        <v/>
-      </c>
-      <c r="G28" s="32">
-        <f>Scenarios!$B$20</f>
+          <t>Prepaid expenses (other current assets)</t>
+        </is>
+      </c>
+      <c r="B28" s="187" t="n">
+        <v>564089</v>
+      </c>
+      <c r="C28" s="75">
+        <f>Scenarios!D95</f>
+        <v/>
+      </c>
+      <c r="D28" s="75">
+        <f>Scenarios!D96</f>
+        <v/>
+      </c>
+      <c r="E28" s="75">
+        <f>Scenarios!D97</f>
+        <v/>
+      </c>
+      <c r="F28" s="75">
+        <f>Scenarios!D98</f>
+        <v/>
+      </c>
+      <c r="G28" s="75">
+        <f>Scenarios!D99</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Accrued liabilities and other</t>
-        </is>
-      </c>
-      <c r="B29" s="187" t="n">
-        <v>662982</v>
-      </c>
-      <c r="C29" s="75">
-        <f>Scenarios!D100</f>
-        <v/>
-      </c>
-      <c r="D29" s="75">
-        <f>Scenarios!D101</f>
-        <v/>
-      </c>
-      <c r="E29" s="75">
-        <f>Scenarios!D102</f>
-        <v/>
-      </c>
-      <c r="F29" s="75">
-        <f>Scenarios!D103</f>
-        <v/>
-      </c>
-      <c r="G29" s="75">
-        <f>Scenarios!D104</f>
+          <t>Accrued liabilities (% of revenue)</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="n">
+        <v>0.05971412101669879</v>
+      </c>
+      <c r="C29" s="32">
+        <f>Scenarios!$B$20</f>
+        <v/>
+      </c>
+      <c r="D29" s="32">
+        <f>Scenarios!$B$20</f>
+        <v/>
+      </c>
+      <c r="E29" s="32">
+        <f>Scenarios!$B$20</f>
+        <v/>
+      </c>
+      <c r="F29" s="32">
+        <f>Scenarios!$B$20</f>
+        <v/>
+      </c>
+      <c r="G29" s="32">
+        <f>Scenarios!$B$20</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Current operating assets (AR + inv + prepaids)</t>
-        </is>
-      </c>
-      <c r="B30" s="176" t="n"/>
+          <t>Accrued liabilities and other</t>
+        </is>
+      </c>
+      <c r="B30" s="187" t="n">
+        <v>662982</v>
+      </c>
       <c r="C30" s="75">
-        <f>Scenarios!D105</f>
+        <f>Scenarios!D100</f>
         <v/>
       </c>
       <c r="D30" s="75">
-        <f>Scenarios!D106</f>
+        <f>Scenarios!D101</f>
         <v/>
       </c>
       <c r="E30" s="75">
-        <f>Scenarios!D107</f>
+        <f>Scenarios!D102</f>
         <v/>
       </c>
       <c r="F30" s="75">
-        <f>Scenarios!D108</f>
+        <f>Scenarios!D103</f>
         <v/>
       </c>
       <c r="G30" s="75">
-        <f>Scenarios!D109</f>
+        <f>Scenarios!D104</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>Current operating liabilities (AP + accruals)</t>
+          <t>Current operating assets (AR + inv + prepaids)</t>
         </is>
       </c>
       <c r="B31" s="176" t="n"/>
       <c r="C31" s="75">
+        <f>Scenarios!D105</f>
+        <v/>
+      </c>
+      <c r="D31" s="75">
+        <f>Scenarios!D106</f>
+        <v/>
+      </c>
+      <c r="E31" s="75">
+        <f>Scenarios!D107</f>
+        <v/>
+      </c>
+      <c r="F31" s="75">
+        <f>Scenarios!D108</f>
+        <v/>
+      </c>
+      <c r="G31" s="75">
+        <f>Scenarios!D109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Current operating liabilities (AP + accruals)</t>
+        </is>
+      </c>
+      <c r="B32" s="176" t="n"/>
+      <c r="C32" s="75">
         <f>Scenarios!D110</f>
         <v/>
       </c>
-      <c r="D31" s="75">
+      <c r="D32" s="75">
         <f>Scenarios!D111</f>
         <v/>
       </c>
-      <c r="E31" s="75">
+      <c r="E32" s="75">
         <f>Scenarios!D112</f>
         <v/>
       </c>
-      <c r="F31" s="75">
+      <c r="F32" s="75">
         <f>Scenarios!D113</f>
         <v/>
       </c>
-      <c r="G31" s="75">
+      <c r="G32" s="75">
         <f>Scenarios!D114</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="68" t="inlineStr">
-        <is>
-          <t>Net working capital</t>
-        </is>
-      </c>
-      <c r="B32" s="197" t="n">
-        <v>1461096</v>
-      </c>
-      <c r="C32" s="130">
-        <f>Scenarios!D115</f>
-        <v/>
-      </c>
-      <c r="D32" s="130">
-        <f>Scenarios!D116</f>
-        <v/>
-      </c>
-      <c r="E32" s="130">
-        <f>Scenarios!D117</f>
-        <v/>
-      </c>
-      <c r="F32" s="130">
-        <f>Scenarios!D118</f>
-        <v/>
-      </c>
-      <c r="G32" s="130">
-        <f>Scenarios!D119</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="68" t="inlineStr">
         <is>
+          <t>Net working capital</t>
+        </is>
+      </c>
+      <c r="B33" s="197" t="n">
+        <v>1461096</v>
+      </c>
+      <c r="C33" s="130">
+        <f>Scenarios!D115</f>
+        <v/>
+      </c>
+      <c r="D33" s="130">
+        <f>Scenarios!D116</f>
+        <v/>
+      </c>
+      <c r="E33" s="130">
+        <f>Scenarios!D117</f>
+        <v/>
+      </c>
+      <c r="F33" s="130">
+        <f>Scenarios!D118</f>
+        <v/>
+      </c>
+      <c r="G33" s="130">
+        <f>Scenarios!D119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="68" t="inlineStr">
+        <is>
           <t>Delta NWC (prior yr - current yr)</t>
         </is>
       </c>
-      <c r="B33" s="176" t="n"/>
-      <c r="C33" s="130">
+      <c r="B34" s="176" t="n"/>
+      <c r="C34" s="130">
         <f>Scenarios!D120</f>
         <v/>
       </c>
-      <c r="D33" s="130">
+      <c r="D34" s="130">
         <f>Scenarios!D121</f>
         <v/>
       </c>
-      <c r="E33" s="130">
+      <c r="E34" s="130">
         <f>Scenarios!D122</f>
         <v/>
       </c>
-      <c r="F33" s="130">
+      <c r="F34" s="130">
         <f>Scenarios!D123</f>
         <v/>
       </c>
-      <c r="G33" s="130">
+      <c r="G34" s="130">
         <f>Scenarios!D124</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="26" t="n"/>
-      <c r="B34" s="176" t="n"/>
-      <c r="C34" s="176" t="n"/>
-      <c r="D34" s="176" t="n"/>
-      <c r="E34" s="176" t="n"/>
-      <c r="F34" s="176" t="n"/>
-      <c r="G34" s="176" t="n"/>
-    </row>
     <row r="35">
-      <c r="A35" s="68" t="inlineStr">
+      <c r="A35" s="26" t="n"/>
+      <c r="B35" s="176" t="n"/>
+      <c r="C35" s="176" t="n"/>
+      <c r="D35" s="176" t="n"/>
+      <c r="E35" s="176" t="n"/>
+      <c r="F35" s="176" t="n"/>
+      <c r="G35" s="176" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="68" t="inlineStr">
         <is>
           <t>Unlevered free cash flow</t>
         </is>
       </c>
-      <c r="B35" s="176" t="n"/>
-      <c r="C35" s="200">
+      <c r="B36" s="176" t="n"/>
+      <c r="C36" s="200">
         <f>Scenarios!D125</f>
         <v/>
       </c>
-      <c r="D35" s="200">
+      <c r="D36" s="200">
         <f>Scenarios!D126</f>
         <v/>
       </c>
-      <c r="E35" s="200">
+      <c r="E36" s="200">
         <f>Scenarios!D127</f>
         <v/>
       </c>
-      <c r="F35" s="200">
+      <c r="F36" s="200">
         <f>Scenarios!D128</f>
         <v/>
       </c>
-      <c r="G35" s="200">
+      <c r="G36" s="200">
         <f>Scenarios!D129</f>
         <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>Discount period (years)</t>
-        </is>
-      </c>
-      <c r="B36" s="176" t="n"/>
-      <c r="C36" s="90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D36" s="90" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="90" t="n">
-        <v>3</v>
-      </c>
-      <c r="F36" s="90" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" s="90" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
+          <t>Discount period (years)</t>
+        </is>
+      </c>
+      <c r="B37" s="176" t="n"/>
+      <c r="C37" s="90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="90" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
           <t>Discount factor @ WACC</t>
         </is>
       </c>
-      <c r="B37" s="176" t="n"/>
-      <c r="C37" s="91">
+      <c r="B38" s="176" t="n"/>
+      <c r="C38" s="91">
         <f>1/(1+Scenarios!$B$9)^C36</f>
         <v/>
       </c>
-      <c r="D37" s="91">
+      <c r="D38" s="91">
         <f>1/(1+Scenarios!$B$9)^D36</f>
         <v/>
       </c>
-      <c r="E37" s="91">
+      <c r="E38" s="91">
         <f>1/(1+Scenarios!$B$9)^E36</f>
         <v/>
       </c>
-      <c r="F37" s="91">
+      <c r="F38" s="91">
         <f>1/(1+Scenarios!$B$9)^F36</f>
         <v/>
       </c>
-      <c r="G37" s="91">
+      <c r="G38" s="91">
         <f>1/(1+Scenarios!$B$9)^G36</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="68" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="68" t="inlineStr">
         <is>
           <t>PV of unlevered FCF</t>
         </is>
       </c>
-      <c r="B38" s="176" t="n"/>
-      <c r="C38" s="130">
+      <c r="B39" s="176" t="n"/>
+      <c r="C39" s="130">
         <f>C35*C37</f>
         <v/>
       </c>
-      <c r="D38" s="130">
+      <c r="D39" s="130">
         <f>D35*D37</f>
         <v/>
       </c>
-      <c r="E38" s="130">
+      <c r="E39" s="130">
         <f>E35*E37</f>
         <v/>
       </c>
-      <c r="F38" s="130">
+      <c r="F39" s="130">
         <f>F35*F37</f>
         <v/>
       </c>
-      <c r="G38" s="130">
+      <c r="G39" s="130">
         <f>G35*G37</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="176" t="n"/>
-      <c r="B39" s="176" t="n"/>
-      <c r="C39" s="176" t="n"/>
-      <c r="D39" s="176" t="n"/>
-      <c r="E39" s="176" t="n"/>
-      <c r="F39" s="176" t="n"/>
-      <c r="G39" s="176" t="n"/>
-    </row>
     <row r="40">
-      <c r="A40" s="61" t="inlineStr">
-        <is>
-          <t>Scenarios tie-out</t>
-        </is>
-      </c>
+      <c r="A40" s="176" t="n"/>
       <c r="B40" s="176" t="n"/>
       <c r="C40" s="176" t="n"/>
       <c r="D40" s="176" t="n"/>
@@ -11409,9 +11402,9 @@
       <c r="G40" s="176" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="201" t="inlineStr">
-        <is>
-          <t>VALUATION - GORDON GROWTH (PERPETUITY) METHOD</t>
+      <c r="A41" s="61" t="inlineStr">
+        <is>
+          <t>Scenarios tie-out</t>
         </is>
       </c>
       <c r="B41" s="176" t="n"/>
@@ -11422,15 +11415,12 @@
       <c r="G41" s="176" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="68" t="inlineStr">
-        <is>
-          <t>Sum of PV of explicit FCF (FY26-FY30)</t>
-        </is>
-      </c>
-      <c r="B42" s="75">
-        <f>SUM(C38:G38)</f>
-        <v/>
-      </c>
+      <c r="A42" s="201" t="inlineStr">
+        <is>
+          <t>VALUATION - GORDON GROWTH (PERPETUITY) METHOD</t>
+        </is>
+      </c>
+      <c r="B42" s="176" t="n"/>
       <c r="C42" s="176" t="n"/>
       <c r="D42" s="176" t="n"/>
       <c r="E42" s="176" t="n"/>
@@ -11438,13 +11428,13 @@
       <c r="G42" s="176" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t>Terminal growth rate (g)</t>
-        </is>
-      </c>
-      <c r="B43" s="32">
-        <f>Scenarios!$B$10</f>
+      <c r="A43" s="68" t="inlineStr">
+        <is>
+          <t>Sum of PV of explicit FCF (FY26-FY30)</t>
+        </is>
+      </c>
+      <c r="B43" s="75">
+        <f>SUM(C38:G38)</f>
         <v/>
       </c>
       <c r="C43" s="176" t="n"/>
@@ -11454,13 +11444,13 @@
       <c r="G43" s="176" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="68" t="inlineStr">
-        <is>
-          <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
-        </is>
-      </c>
-      <c r="B44" s="130">
-        <f>G11+G16</f>
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Terminal growth rate (g)</t>
+        </is>
+      </c>
+      <c r="B44" s="32">
+        <f>Scenarios!$B$10</f>
         <v/>
       </c>
       <c r="C44" s="176" t="n"/>
@@ -11470,13 +11460,13 @@
       <c r="G44" s="176" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
-        <is>
-          <t>Terminal value = FCF5x(1+g)/(WACC-g)</t>
-        </is>
-      </c>
-      <c r="B45" s="75">
-        <f>G35*(1+Scenarios!$B$10)/(Scenarios!$B$9-Scenarios!$B$10)</f>
+      <c r="A45" s="68" t="inlineStr">
+        <is>
+          <t>Terminal EBITDA (FY2030E EBIT + D&amp;A)</t>
+        </is>
+      </c>
+      <c r="B45" s="130">
+        <f>G11+G16</f>
         <v/>
       </c>
       <c r="C45" s="176" t="n"/>
@@ -11488,11 +11478,11 @@
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Implied exit EV/EBITDA = Gordon TV / FY30 EBITDA</t>
-        </is>
-      </c>
-      <c r="B46" s="94">
-        <f>B45/B44</f>
+          <t>Terminal value = FCF5x(1+g)/(WACC-g)</t>
+        </is>
+      </c>
+      <c r="B46" s="75">
+        <f>G35*(1+Scenarios!$B$10)/(Scenarios!$B$9-Scenarios!$B$10)</f>
         <v/>
       </c>
       <c r="C46" s="176" t="n"/>
@@ -11504,11 +11494,11 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>(UFCF30 / EBITDA30) x (1+g) / (WACC-g)</t>
+          <t>Implied exit EV/EBITDA = Gordon TV / FY30 EBITDA</t>
         </is>
       </c>
       <c r="B47" s="94">
-        <f>G35/B44*(1+Scenarios!$B$10)/(Scenarios!$B$9-Scenarios!$B$10)</f>
+        <f>B45/B44</f>
         <v/>
       </c>
       <c r="C47" s="176" t="n"/>
@@ -11518,13 +11508,13 @@
       <c r="G47" s="176" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="68" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B48" s="75">
-        <f>B45/(1+Scenarios!$B$9)^G36</f>
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>(UFCF30 / EBITDA30) x (1+g) / (WACC-g)</t>
+        </is>
+      </c>
+      <c r="B48" s="94">
+        <f>G35/B44*(1+Scenarios!$B$10)/(Scenarios!$B$9-Scenarios!$B$10)</f>
         <v/>
       </c>
       <c r="C48" s="176" t="n"/>
@@ -11536,11 +11526,11 @@
     <row r="49">
       <c r="A49" s="68" t="inlineStr">
         <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
-      <c r="B49" s="130">
-        <f>B42+B48</f>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B49" s="75">
+        <f>B45/(1+Scenarios!$B$9)^G36</f>
         <v/>
       </c>
       <c r="C49" s="176" t="n"/>
@@ -11550,13 +11540,14 @@
       <c r="G49" s="176" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>Plus: cash &amp; equivalents (FY2025)</t>
-        </is>
-      </c>
-      <c r="B50" s="187" t="n">
-        <v>1807202</v>
+      <c r="A50" s="68" t="inlineStr">
+        <is>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="B50" s="130">
+        <f>B42+B48</f>
+        <v/>
       </c>
       <c r="C50" s="176" t="n"/>
       <c r="D50" s="176" t="n"/>
@@ -11567,11 +11558,11 @@
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Less: total debt &amp; operating leases</t>
+          <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
       <c r="B51" s="187" t="n">
-        <v>-1798441</v>
+        <v>1807202</v>
       </c>
       <c r="C51" s="176" t="n"/>
       <c r="D51" s="176" t="n"/>
@@ -11580,8 +11571,14 @@
       <c r="G51" s="176" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="n"/>
-      <c r="B52" s="176" t="n"/>
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Less: total debt &amp; operating leases</t>
+        </is>
+      </c>
+      <c r="B52" s="187" t="n">
+        <v>-1798441</v>
+      </c>
       <c r="C52" s="176" t="n"/>
       <c r="D52" s="176" t="n"/>
       <c r="E52" s="176" t="n"/>
@@ -11589,11 +11586,7 @@
       <c r="G52" s="176" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="26" t="inlineStr">
-        <is>
-          <t>Enterprise value bridge</t>
-        </is>
-      </c>
+      <c r="A53" s="26" t="n"/>
       <c r="B53" s="176" t="n"/>
       <c r="C53" s="176" t="n"/>
       <c r="D53" s="176" t="n"/>
@@ -11602,15 +11595,12 @@
       <c r="G53" s="176" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="68" t="inlineStr">
-        <is>
-          <t>Equity value</t>
-        </is>
-      </c>
-      <c r="B54" s="130">
-        <f>B49+B50+B51</f>
-        <v/>
-      </c>
+      <c r="A54" s="26" t="inlineStr">
+        <is>
+          <t>Enterprise value bridge</t>
+        </is>
+      </c>
+      <c r="B54" s="176" t="n"/>
       <c r="C54" s="176" t="n"/>
       <c r="D54" s="176" t="n"/>
       <c r="E54" s="176" t="n"/>
@@ -11618,13 +11608,14 @@
       <c r="G54" s="176" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>Shares outstanding (000)</t>
-        </is>
-      </c>
-      <c r="B55" s="187" t="n">
-        <v>111380</v>
+      <c r="A55" s="68" t="inlineStr">
+        <is>
+          <t>Equity value</t>
+        </is>
+      </c>
+      <c r="B55" s="130">
+        <f>B49+B50+B51</f>
+        <v/>
       </c>
       <c r="C55" s="176" t="n"/>
       <c r="D55" s="176" t="n"/>
@@ -11633,14 +11624,13 @@
       <c r="G55" s="176" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="68" t="inlineStr">
-        <is>
-          <t>Implied value per share</t>
-        </is>
-      </c>
-      <c r="B56" s="139">
-        <f>B54/B55</f>
-        <v/>
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>Shares outstanding (000)</t>
+        </is>
+      </c>
+      <c r="B56" s="187" t="n">
+        <v>111380</v>
       </c>
       <c r="C56" s="176" t="n"/>
       <c r="D56" s="176" t="n"/>
@@ -11649,13 +11639,14 @@
       <c r="G56" s="176" t="n"/>
     </row>
     <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>Current share price</t>
-        </is>
-      </c>
-      <c r="B57" s="186" t="n">
-        <v>100</v>
+      <c r="A57" s="68" t="inlineStr">
+        <is>
+          <t>Implied value per share</t>
+        </is>
+      </c>
+      <c r="B57" s="139">
+        <f>B54/B55</f>
+        <v/>
       </c>
       <c r="C57" s="176" t="n"/>
       <c r="D57" s="176" t="n"/>
@@ -11664,14 +11655,13 @@
       <c r="G57" s="176" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="68" t="inlineStr">
-        <is>
-          <t>Implied upside / (downside)</t>
-        </is>
-      </c>
-      <c r="B58" s="32">
-        <f>B56/B57-1</f>
-        <v/>
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>Current share price</t>
+        </is>
+      </c>
+      <c r="B58" s="186" t="n">
+        <v>100</v>
       </c>
       <c r="C58" s="176" t="n"/>
       <c r="D58" s="176" t="n"/>
@@ -11680,13 +11670,13 @@
       <c r="G58" s="176" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>% of EV from terminal value</t>
+      <c r="A59" s="68" t="inlineStr">
+        <is>
+          <t>Implied upside / (downside)</t>
         </is>
       </c>
       <c r="B59" s="32">
-        <f>B48/B49</f>
+        <f>B56/B57-1</f>
         <v/>
       </c>
       <c r="C59" s="176" t="n"/>
@@ -11696,8 +11686,15 @@
       <c r="G59" s="176" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="176" t="n"/>
-      <c r="B60" s="176" t="n"/>
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>% of EV from terminal value</t>
+        </is>
+      </c>
+      <c r="B60" s="32">
+        <f>B48/B49</f>
+        <v/>
+      </c>
       <c r="C60" s="176" t="n"/>
       <c r="D60" s="176" t="n"/>
       <c r="E60" s="176" t="n"/>
@@ -11714,12 +11711,8 @@
       <c r="G61" s="176" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="201" t="inlineStr">
-        <is>
-          <t>SHARE REPURCHASE &amp; EPS ACCRETION SCHEDULE</t>
-        </is>
-      </c>
-      <c r="B62" s="184" t="n"/>
+      <c r="A62" s="176" t="n"/>
+      <c r="B62" s="176" t="n"/>
       <c r="C62" s="176" t="n"/>
       <c r="D62" s="176" t="n"/>
       <c r="E62" s="176" t="n"/>
@@ -11727,8 +11720,12 @@
       <c r="G62" s="176" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="26" t="n"/>
-      <c r="B63" s="176" t="n"/>
+      <c r="A63" s="201" t="inlineStr">
+        <is>
+          <t>SHARE REPURCHASE &amp; EPS ACCRETION SCHEDULE</t>
+        </is>
+      </c>
+      <c r="B63" s="184" t="n"/>
       <c r="C63" s="176" t="n"/>
       <c r="D63" s="176" t="n"/>
       <c r="E63" s="176" t="n"/>
@@ -11736,7 +11733,7 @@
       <c r="G63" s="176" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="176" t="n"/>
+      <c r="A64" s="26" t="n"/>
       <c r="B64" s="176" t="n"/>
       <c r="C64" s="176" t="n"/>
       <c r="D64" s="176" t="n"/>
@@ -11745,373 +11742,369 @@
       <c r="G64" s="176" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t>Annual repurchase budget ($000) - base case</t>
-        </is>
-      </c>
-      <c r="B65" s="187" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C65" s="75">
-        <f>$B$65</f>
-        <v/>
-      </c>
-      <c r="D65" s="75">
-        <f>$B$65</f>
-        <v/>
-      </c>
-      <c r="E65" s="75">
-        <f>$B$65</f>
-        <v/>
-      </c>
-      <c r="F65" s="75">
-        <f>$B$65</f>
-        <v/>
-      </c>
-      <c r="G65" s="75">
-        <f>$B$65</f>
-        <v/>
-      </c>
+      <c r="A65" s="176" t="n"/>
+      <c r="B65" s="176" t="n"/>
+      <c r="C65" s="176" t="n"/>
+      <c r="D65" s="176" t="n"/>
+      <c r="E65" s="176" t="n"/>
+      <c r="F65" s="176" t="n"/>
+      <c r="G65" s="176" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
+          <t>Annual repurchase budget ($000) - base case</t>
+        </is>
+      </c>
+      <c r="B66" s="187" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C66" s="75">
+        <f>$B$65</f>
+        <v/>
+      </c>
+      <c r="D66" s="75">
+        <f>$B$65</f>
+        <v/>
+      </c>
+      <c r="E66" s="75">
+        <f>$B$65</f>
+        <v/>
+      </c>
+      <c r="F66" s="75">
+        <f>$B$65</f>
+        <v/>
+      </c>
+      <c r="G66" s="75">
+        <f>$B$65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="inlineStr">
+        <is>
           <t>Cost of equity - share-price growth rate</t>
         </is>
       </c>
-      <c r="B66" s="32" t="n">
+      <c r="B67" s="32" t="n">
         <v>0.105</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C67" s="32">
         <f>$B$66</f>
         <v/>
       </c>
-      <c r="D66" s="32">
+      <c r="D67" s="32">
         <f>$B$66</f>
         <v/>
       </c>
-      <c r="E66" s="32">
+      <c r="E67" s="32">
         <f>$B$66</f>
         <v/>
       </c>
-      <c r="F66" s="32">
+      <c r="F67" s="32">
         <f>$B$66</f>
         <v/>
       </c>
-      <c r="G66" s="32">
+      <c r="G67" s="32">
         <f>$B$66</f>
         <v/>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="176" t="n"/>
-      <c r="B67" s="176" t="n"/>
-      <c r="C67" s="176" t="n"/>
-      <c r="D67" s="176" t="n"/>
-      <c r="E67" s="176" t="n"/>
-      <c r="F67" s="176" t="n"/>
-      <c r="G67" s="176" t="n"/>
-    </row>
     <row r="68">
-      <c r="A68" s="16" t="inlineStr">
-        <is>
-          <t>Unlevered free cash flow (from DCF above)</t>
-        </is>
-      </c>
+      <c r="A68" s="176" t="n"/>
       <c r="B68" s="176" t="n"/>
-      <c r="C68" s="75">
-        <f>C35</f>
-        <v/>
-      </c>
-      <c r="D68" s="75">
-        <f>D35</f>
-        <v/>
-      </c>
-      <c r="E68" s="75">
-        <f>E35</f>
-        <v/>
-      </c>
-      <c r="F68" s="75">
-        <f>F35</f>
-        <v/>
-      </c>
-      <c r="G68" s="75">
-        <f>G35</f>
-        <v/>
-      </c>
+      <c r="C68" s="176" t="n"/>
+      <c r="D68" s="176" t="n"/>
+      <c r="E68" s="176" t="n"/>
+      <c r="F68" s="176" t="n"/>
+      <c r="G68" s="176" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>Repurchase cash deployed (= fixed budget)</t>
-        </is>
-      </c>
-      <c r="B69" s="75" t="n">
-        <v>0</v>
-      </c>
+          <t>Unlevered free cash flow (from DCF above)</t>
+        </is>
+      </c>
+      <c r="B69" s="176" t="n"/>
       <c r="C69" s="75">
-        <f>C65</f>
+        <f>C35</f>
         <v/>
       </c>
       <c r="D69" s="75">
-        <f>D65</f>
+        <f>D35</f>
         <v/>
       </c>
       <c r="E69" s="75">
-        <f>E65</f>
+        <f>E35</f>
         <v/>
       </c>
       <c r="F69" s="75">
-        <f>F65</f>
+        <f>F35</f>
         <v/>
       </c>
       <c r="G69" s="75">
-        <f>G65</f>
+        <f>G35</f>
         <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
+          <t>Repurchase cash deployed (= fixed budget)</t>
+        </is>
+      </c>
+      <c r="B70" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="75">
+        <f>C65</f>
+        <v/>
+      </c>
+      <c r="D70" s="75">
+        <f>D65</f>
+        <v/>
+      </c>
+      <c r="E70" s="75">
+        <f>E65</f>
+        <v/>
+      </c>
+      <c r="F70" s="75">
+        <f>F65</f>
+        <v/>
+      </c>
+      <c r="G70" s="75">
+        <f>G65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
           <t>Repurchase as % of UFCF (derived)</t>
         </is>
       </c>
-      <c r="B70" s="176" t="n"/>
-      <c r="C70" s="32">
+      <c r="B71" s="176" t="n"/>
+      <c r="C71" s="32">
         <f>C69/C68</f>
         <v/>
       </c>
-      <c r="D70" s="32">
+      <c r="D71" s="32">
         <f>D69/D68</f>
         <v/>
       </c>
-      <c r="E70" s="32">
+      <c r="E71" s="32">
         <f>E69/E68</f>
         <v/>
       </c>
-      <c r="F70" s="32">
+      <c r="F71" s="32">
         <f>F69/F68</f>
         <v/>
       </c>
-      <c r="G70" s="32">
+      <c r="G71" s="32">
         <f>G69/G68</f>
         <v/>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="176" t="n"/>
-      <c r="B71" s="176" t="n"/>
-      <c r="C71" s="176" t="n"/>
-      <c r="D71" s="176" t="n"/>
-      <c r="E71" s="176" t="n"/>
-      <c r="F71" s="176" t="n"/>
-      <c r="G71" s="176" t="n"/>
-    </row>
     <row r="72">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>Projected share price ($)</t>
-        </is>
-      </c>
-      <c r="B72" s="186" t="n">
-        <v>100</v>
-      </c>
-      <c r="C72" s="99">
-        <f>B72*(1+$B$66)</f>
-        <v/>
-      </c>
-      <c r="D72" s="99">
-        <f>C72*(1+$B$66)</f>
-        <v/>
-      </c>
-      <c r="E72" s="99">
-        <f>D72*(1+$B$66)</f>
-        <v/>
-      </c>
-      <c r="F72" s="99">
-        <f>E72*(1+$B$66)</f>
-        <v/>
-      </c>
-      <c r="G72" s="99">
-        <f>F72*(1+$B$66)</f>
-        <v/>
-      </c>
+      <c r="A72" s="176" t="n"/>
+      <c r="B72" s="176" t="n"/>
+      <c r="C72" s="176" t="n"/>
+      <c r="D72" s="176" t="n"/>
+      <c r="E72" s="176" t="n"/>
+      <c r="F72" s="176" t="n"/>
+      <c r="G72" s="176" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>Shares retired (000)</t>
-        </is>
-      </c>
-      <c r="B73" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="C73" s="75">
-        <f>C69/C72</f>
-        <v/>
-      </c>
-      <c r="D73" s="75">
-        <f>D69/D72</f>
-        <v/>
-      </c>
-      <c r="E73" s="75">
-        <f>E69/E72</f>
-        <v/>
-      </c>
-      <c r="F73" s="75">
-        <f>F69/F72</f>
-        <v/>
-      </c>
-      <c r="G73" s="75">
-        <f>G69/G72</f>
+          <t>Projected share price ($)</t>
+        </is>
+      </c>
+      <c r="B73" s="186" t="n">
+        <v>100</v>
+      </c>
+      <c r="C73" s="99">
+        <f>B72*(1+$B$66)</f>
+        <v/>
+      </c>
+      <c r="D73" s="99">
+        <f>C72*(1+$B$66)</f>
+        <v/>
+      </c>
+      <c r="E73" s="99">
+        <f>D72*(1+$B$66)</f>
+        <v/>
+      </c>
+      <c r="F73" s="99">
+        <f>E72*(1+$B$66)</f>
+        <v/>
+      </c>
+      <c r="G73" s="99">
+        <f>F72*(1+$B$66)</f>
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
         <is>
+          <t>Shares retired (000)</t>
+        </is>
+      </c>
+      <c r="B74" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="75">
+        <f>C69/C72</f>
+        <v/>
+      </c>
+      <c r="D74" s="75">
+        <f>D69/D72</f>
+        <v/>
+      </c>
+      <c r="E74" s="75">
+        <f>E69/E72</f>
+        <v/>
+      </c>
+      <c r="F74" s="75">
+        <f>F69/F72</f>
+        <v/>
+      </c>
+      <c r="G74" s="75">
+        <f>G69/G72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="inlineStr">
+        <is>
           <t>Beginning shares (000)</t>
         </is>
       </c>
-      <c r="B74" s="187" t="n">
+      <c r="B75" s="187" t="n">
         <v>111380</v>
       </c>
-      <c r="C74" s="75">
+      <c r="C75" s="75">
         <f>$B$74</f>
         <v/>
       </c>
-      <c r="D74" s="75">
+      <c r="D75" s="75">
         <f>C75</f>
         <v/>
       </c>
-      <c r="E74" s="75">
+      <c r="E75" s="75">
         <f>D75</f>
         <v/>
       </c>
-      <c r="F74" s="75">
+      <c r="F75" s="75">
         <f>E75</f>
         <v/>
       </c>
-      <c r="G74" s="75">
+      <c r="G75" s="75">
         <f>F75</f>
         <v/>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="68" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="68" t="inlineStr">
         <is>
           <t>Ending shares (000)</t>
         </is>
       </c>
-      <c r="B75" s="197" t="n">
+      <c r="B76" s="197" t="n">
         <v>111380</v>
       </c>
-      <c r="C75" s="130">
+      <c r="C76" s="130">
         <f>C74-C73</f>
         <v/>
       </c>
-      <c r="D75" s="130">
+      <c r="D76" s="130">
         <f>D74-D73</f>
         <v/>
       </c>
-      <c r="E75" s="130">
+      <c r="E76" s="130">
         <f>E74-E73</f>
         <v/>
       </c>
-      <c r="F75" s="130">
+      <c r="F76" s="130">
         <f>F74-F73</f>
         <v/>
       </c>
-      <c r="G75" s="130">
+      <c r="G76" s="130">
         <f>G74-G73</f>
         <v/>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="176" t="n"/>
-      <c r="B76" s="176" t="n"/>
-      <c r="C76" s="176" t="n"/>
-      <c r="D76" s="176" t="n"/>
-      <c r="E76" s="176" t="n"/>
-      <c r="F76" s="176" t="n"/>
-      <c r="G76" s="176" t="n"/>
-    </row>
     <row r="77">
-      <c r="A77" s="16" t="inlineStr">
+      <c r="A77" s="176" t="n"/>
+      <c r="B77" s="176" t="n"/>
+      <c r="C77" s="176" t="n"/>
+      <c r="D77" s="176" t="n"/>
+      <c r="E77" s="176" t="n"/>
+      <c r="F77" s="176" t="n"/>
+      <c r="G77" s="176" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
         <is>
           <t>Projected net income ($000)</t>
         </is>
       </c>
-      <c r="B77" s="187" t="n">
+      <c r="B78" s="187" t="n">
         <v>1579183</v>
       </c>
-      <c r="C77" s="75">
+      <c r="C78" s="75">
         <f>('NOPAT Bridge'!C36-'NOPAT Bridge'!C23)*(1-'NOPAT Bridge'!C$39)</f>
         <v/>
       </c>
-      <c r="D77" s="75">
+      <c r="D78" s="75">
         <f>('NOPAT Bridge'!D36-'NOPAT Bridge'!D23)*(1-'NOPAT Bridge'!D$39)</f>
         <v/>
       </c>
-      <c r="E77" s="75">
+      <c r="E78" s="75">
         <f>('NOPAT Bridge'!E36-'NOPAT Bridge'!E23)*(1-'NOPAT Bridge'!E$39)</f>
         <v/>
       </c>
-      <c r="F77" s="75">
+      <c r="F78" s="75">
         <f>('NOPAT Bridge'!F36-'NOPAT Bridge'!F23)*(1-'NOPAT Bridge'!F$39)</f>
         <v/>
       </c>
-      <c r="G77" s="75">
+      <c r="G78" s="75">
         <f>('NOPAT Bridge'!G36-'NOPAT Bridge'!G23)*(1-'NOPAT Bridge'!G$39)</f>
         <v/>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="68" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="68" t="inlineStr">
         <is>
           <t>Accretive EPS ($/share) = Net income / ending shares</t>
         </is>
       </c>
-      <c r="B78" s="202" t="n">
+      <c r="B79" s="202" t="n">
         <v>14.1783354282636</v>
       </c>
-      <c r="C78" s="150">
+      <c r="C79" s="150">
         <f>C77/C75</f>
         <v/>
       </c>
-      <c r="D78" s="150">
+      <c r="D79" s="150">
         <f>D77/D75</f>
         <v/>
       </c>
-      <c r="E78" s="150">
+      <c r="E79" s="150">
         <f>E77/E75</f>
         <v/>
       </c>
-      <c r="F78" s="150">
+      <c r="F79" s="150">
         <f>F77/F75</f>
         <v/>
       </c>
-      <c r="G78" s="150">
+      <c r="G79" s="150">
         <f>G77/G75</f>
         <v/>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="176" t="n"/>
-      <c r="B79" s="176" t="n"/>
-      <c r="C79" s="176" t="n"/>
-      <c r="D79" s="176" t="n"/>
-      <c r="E79" s="176" t="n"/>
-      <c r="F79" s="176" t="n"/>
-      <c r="G79" s="176" t="n"/>
-    </row>
     <row r="80">
-      <c r="A80" s="201" t="inlineStr">
-        <is>
-          <t>CROSS-CHECK - EXIT MULTIPLE METHOD</t>
-        </is>
-      </c>
+      <c r="A80" s="176" t="n"/>
       <c r="B80" s="176" t="n"/>
       <c r="C80" s="176" t="n"/>
       <c r="D80" s="176" t="n"/>
@@ -12120,7 +12113,11 @@
       <c r="G80" s="176" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="61" t="n"/>
+      <c r="A81" s="201" t="inlineStr">
+        <is>
+          <t>CROSS-CHECK - EXIT MULTIPLE METHOD</t>
+        </is>
+      </c>
       <c r="B81" s="176" t="n"/>
       <c r="C81" s="176" t="n"/>
       <c r="D81" s="176" t="n"/>
@@ -12129,15 +12126,8 @@
       <c r="G81" s="176" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
-      <c r="A82" s="16" t="inlineStr">
-        <is>
-          <t>Selected exit EV/EBITDA (Gordon implied)</t>
-        </is>
-      </c>
-      <c r="B82" s="94">
-        <f>B46</f>
-        <v/>
-      </c>
+      <c r="A82" s="61" t="n"/>
+      <c r="B82" s="176" t="n"/>
       <c r="C82" s="176" t="n"/>
       <c r="D82" s="176" t="n"/>
       <c r="E82" s="176" t="n"/>
@@ -12147,11 +12137,11 @@
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>Terminal value = Terminal EBITDA x exit multiple</t>
-        </is>
-      </c>
-      <c r="B83" s="75">
-        <f>B44*B82</f>
+          <t>Selected exit EV/EBITDA (Gordon implied)</t>
+        </is>
+      </c>
+      <c r="B83" s="94">
+        <f>B46</f>
         <v/>
       </c>
       <c r="C83" s="176" t="n"/>
@@ -12163,11 +12153,11 @@
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>PV of terminal value</t>
+          <t>Terminal value = Terminal EBITDA x exit multiple</t>
         </is>
       </c>
       <c r="B84" s="75">
-        <f>B83/(1+Scenarios!$B$9)^G36</f>
+        <f>B44*B82</f>
         <v/>
       </c>
       <c r="C84" s="176" t="n"/>
@@ -12177,13 +12167,13 @@
       <c r="G84" s="176" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="68" t="inlineStr">
-        <is>
-          <t>Enterprise value (exit method)</t>
-        </is>
-      </c>
-      <c r="B85" s="130">
-        <f>B42+B84</f>
+      <c r="A85" s="16" t="inlineStr">
+        <is>
+          <t>PV of terminal value</t>
+        </is>
+      </c>
+      <c r="B85" s="75">
+        <f>B83/(1+Scenarios!$B$9)^G36</f>
         <v/>
       </c>
       <c r="C85" s="176" t="n"/>
@@ -12195,11 +12185,11 @@
     <row r="86">
       <c r="A86" s="68" t="inlineStr">
         <is>
-          <t>Implied value per share (exit method)</t>
-        </is>
-      </c>
-      <c r="B86" s="99">
-        <f>(B85+B50+B51)/B55</f>
+          <t>Enterprise value (exit method)</t>
+        </is>
+      </c>
+      <c r="B86" s="130">
+        <f>B42+B84</f>
         <v/>
       </c>
       <c r="C86" s="176" t="n"/>
@@ -12209,8 +12199,15 @@
       <c r="G86" s="176" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="176" t="n"/>
-      <c r="B87" s="176" t="n"/>
+      <c r="A87" s="68" t="inlineStr">
+        <is>
+          <t>Implied value per share (exit method)</t>
+        </is>
+      </c>
+      <c r="B87" s="99">
+        <f>(B85+B50+B51)/B55</f>
+        <v/>
+      </c>
       <c r="C87" s="176" t="n"/>
       <c r="D87" s="176" t="n"/>
       <c r="E87" s="176" t="n"/>
@@ -12218,11 +12215,7 @@
       <c r="G87" s="176" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="201" t="inlineStr">
-        <is>
-          <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
-        </is>
-      </c>
+      <c r="A88" s="176" t="n"/>
       <c r="B88" s="176" t="n"/>
       <c r="C88" s="176" t="n"/>
       <c r="D88" s="176" t="n"/>
@@ -12231,12 +12224,12 @@
       <c r="G88" s="176" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="103" t="inlineStr"/>
-      <c r="B89" s="176" t="inlineStr">
-        <is>
-          <t>Variance</t>
-        </is>
-      </c>
+      <c r="A89" s="201" t="inlineStr">
+        <is>
+          <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
+        </is>
+      </c>
+      <c r="B89" s="176" t="n"/>
       <c r="C89" s="176" t="n"/>
       <c r="D89" s="176" t="n"/>
       <c r="E89" s="176" t="n"/>
@@ -12244,14 +12237,11 @@
       <c r="G89" s="176" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="68" t="inlineStr">
-        <is>
-          <t>Terminal value ($)</t>
-        </is>
-      </c>
-      <c r="B90" s="176">
-        <f>B90-C90</f>
-        <v/>
+      <c r="A90" s="103" t="inlineStr"/>
+      <c r="B90" s="176" t="inlineStr">
+        <is>
+          <t>Variance</t>
+        </is>
       </c>
       <c r="C90" s="176" t="n"/>
       <c r="D90" s="176" t="n"/>
@@ -12262,11 +12252,11 @@
     <row r="91">
       <c r="A91" s="68" t="inlineStr">
         <is>
-          <t>Exit EV/EBITDA (implied vs selected)</t>
+          <t>Terminal value ($)</t>
         </is>
       </c>
       <c r="B91" s="176">
-        <f>B91-C91</f>
+        <f>B90-C90</f>
         <v/>
       </c>
       <c r="C91" s="176" t="n"/>
@@ -12276,13 +12266,13 @@
       <c r="G91" s="176" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="inlineStr">
-        <is>
-          <t>Terminal value variance (%)</t>
+      <c r="A92" s="68" t="inlineStr">
+        <is>
+          <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
       <c r="B92" s="176">
-        <f>(B90-C90)/B90</f>
+        <f>B91-C91</f>
         <v/>
       </c>
       <c r="C92" s="176" t="n"/>
@@ -12292,13 +12282,13 @@
       <c r="G92" s="176" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="68" t="inlineStr">
-        <is>
-          <t>Implied share price</t>
+      <c r="A93" s="16" t="inlineStr">
+        <is>
+          <t>Terminal value variance (%)</t>
         </is>
       </c>
       <c r="B93" s="176">
-        <f>B93-C93</f>
+        <f>(B90-C90)/B90</f>
         <v/>
       </c>
       <c r="C93" s="176" t="n"/>
@@ -12308,11 +12298,14 @@
       <c r="G93" s="176" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="68" t="n"/>
-      <c r="B94" s="176" t="inlineStr">
-        <is>
-          <t>Selected exit is the Gordon identity, so spread should be 0</t>
-        </is>
+      <c r="A94" s="68" t="inlineStr">
+        <is>
+          <t>Implied share price</t>
+        </is>
+      </c>
+      <c r="B94" s="176">
+        <f>B93-C93</f>
+        <v/>
       </c>
       <c r="C94" s="176" t="n"/>
       <c r="D94" s="176" t="n"/>
@@ -12321,8 +12314,12 @@
       <c r="G94" s="176" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="176" t="n"/>
-      <c r="B95" s="176" t="n"/>
+      <c r="A95" s="68" t="n"/>
+      <c r="B95" s="176" t="inlineStr">
+        <is>
+          <t>Selected exit is the Gordon identity, so spread should be 0</t>
+        </is>
+      </c>
       <c r="C95" s="176" t="n"/>
       <c r="D95" s="176" t="n"/>
       <c r="E95" s="176" t="n"/>
@@ -12339,172 +12336,180 @@
       <c r="G96" s="176" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="201" t="inlineStr">
-        <is>
-          <t>SENSITIVITY - IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
-        </is>
-      </c>
-      <c r="B97" s="184" t="n"/>
-      <c r="C97" s="184" t="n"/>
-      <c r="D97" s="184" t="n"/>
-      <c r="E97" s="184" t="n"/>
+      <c r="A97" s="176" t="n"/>
+      <c r="B97" s="176" t="n"/>
+      <c r="C97" s="176" t="n"/>
+      <c r="D97" s="176" t="n"/>
+      <c r="E97" s="176" t="n"/>
       <c r="F97" s="176" t="n"/>
       <c r="G97" s="176" t="n"/>
     </row>
     <row r="98" ht="28" customHeight="1">
-      <c r="A98" s="203" t="inlineStr">
+      <c r="A98" s="201" t="inlineStr">
+        <is>
+          <t>SENSITIVITY - IMPLIED SHARE PRICE (WACC vs terminal growth)</t>
+        </is>
+      </c>
+      <c r="B98" s="184" t="n"/>
+      <c r="C98" s="184" t="n"/>
+      <c r="D98" s="184" t="n"/>
+      <c r="E98" s="184" t="n"/>
+      <c r="F98" s="176" t="n"/>
+      <c r="G98" s="176" t="n"/>
+    </row>
+    <row r="99" ht="28" customHeight="1">
+      <c r="A99" s="203" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B98" s="176" t="n"/>
-      <c r="C98" s="204" t="n">
+      <c r="B99" s="176" t="n"/>
+      <c r="C99" s="204" t="n">
         <v>0.015</v>
       </c>
-      <c r="D98" s="204" t="n">
+      <c r="D99" s="204" t="n">
         <v>0.02</v>
       </c>
-      <c r="E98" s="204" t="n">
+      <c r="E99" s="204" t="n">
         <v>0.0225</v>
       </c>
-      <c r="F98" s="204" t="n">
+      <c r="F99" s="204" t="n">
         <v>0.025</v>
       </c>
-      <c r="G98" s="204" t="n">
+      <c r="G99" s="204" t="n">
         <v>0.03</v>
-      </c>
-    </row>
-    <row r="99" ht="28" customHeight="1">
-      <c r="A99" s="205" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="B99" s="176" t="n"/>
-      <c r="C99" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.015)/(0.095-0.015))/(1+0.095)^5+B50+B51)/B55</f>
-        <v/>
-      </c>
-      <c r="D99" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.02)/(0.095-0.02))/(1+0.095)^5+B50+B51)/B55</f>
-        <v/>
-      </c>
-      <c r="E99" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+B50+B51)/B55</f>
-        <v/>
-      </c>
-      <c r="F99" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.025)/(0.095-0.025))/(1+0.095)^5+B50+B51)/B55</f>
-        <v/>
-      </c>
-      <c r="G99" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.03)/(0.095-0.03))/(1+0.095)^5+B50+B51)/B55</f>
-        <v/>
       </c>
     </row>
     <row r="100" ht="28" customHeight="1">
       <c r="A100" s="205" t="n">
-        <v>0.1</v>
+        <v>0.095</v>
       </c>
       <c r="B100" s="176" t="n"/>
       <c r="C100" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.015)/(0.1-0.015))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C35:G35)+(G35*(1+0.015)/(0.095-0.015))/(1+0.095)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="D100" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.02)/(0.1-0.02))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C35:G35)+(G35*(1+0.02)/(0.095-0.02))/(1+0.095)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="E100" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C35:G35)+(G35*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="F100" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.025)/(0.1-0.025))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C35:G35)+(G35*(1+0.025)/(0.095-0.025))/(1+0.095)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="G100" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.03)/(0.1-0.03))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C35:G35)+(G35*(1+0.03)/(0.095-0.03))/(1+0.095)^5+B50+B51)/B55</f>
         <v/>
       </c>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="205" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="B101" s="176" t="n"/>
       <c r="C101" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.015)/(0.105-0.015))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C35:G35)+(G35*(1+0.015)/(0.1-0.015))/(1+0.1)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="D101" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.02)/(0.105-0.02))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C35:G35)+(G35*(1+0.02)/(0.1-0.02))/(1+0.1)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="E101" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C35:G35)+(G35*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="F101" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.025)/(0.105-0.025))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C35:G35)+(G35*(1+0.025)/(0.1-0.025))/(1+0.1)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="G101" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.03)/(0.105-0.03))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C35:G35)+(G35*(1+0.03)/(0.1-0.03))/(1+0.1)^5+B50+B51)/B55</f>
         <v/>
       </c>
     </row>
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="205" t="n">
-        <v>0.11</v>
+        <v>0.105</v>
       </c>
       <c r="B102" s="176" t="n"/>
       <c r="C102" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.015)/(0.11-0.015))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C35:G35)+(G35*(1+0.015)/(0.105-0.015))/(1+0.105)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="D102" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.02)/(0.11-0.02))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C35:G35)+(G35*(1+0.02)/(0.105-0.02))/(1+0.105)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="E102" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C35:G35)+(G35*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="F102" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.025)/(0.11-0.025))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C35:G35)+(G35*(1+0.025)/(0.105-0.025))/(1+0.105)^5+B50+B51)/B55</f>
         <v/>
       </c>
       <c r="G102" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.03)/(0.11-0.03))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C35:G35)+(G35*(1+0.03)/(0.105-0.03))/(1+0.105)^5+B50+B51)/B55</f>
         <v/>
       </c>
     </row>
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="205" t="n">
-        <v>0.115</v>
+        <v>0.11</v>
       </c>
       <c r="B103" s="176" t="n"/>
       <c r="C103" s="121">
+        <f>(NPV(0.11,C35:G35)+(G35*(1+0.015)/(0.11-0.015))/(1+0.11)^5+B50+B51)/B55</f>
+        <v/>
+      </c>
+      <c r="D103" s="121">
+        <f>(NPV(0.11,C35:G35)+(G35*(1+0.02)/(0.11-0.02))/(1+0.11)^5+B50+B51)/B55</f>
+        <v/>
+      </c>
+      <c r="E103" s="121">
+        <f>(NPV(0.11,C35:G35)+(G35*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+B50+B51)/B55</f>
+        <v/>
+      </c>
+      <c r="F103" s="121">
+        <f>(NPV(0.11,C35:G35)+(G35*(1+0.025)/(0.11-0.025))/(1+0.11)^5+B50+B51)/B55</f>
+        <v/>
+      </c>
+      <c r="G103" s="121">
+        <f>(NPV(0.11,C35:G35)+(G35*(1+0.03)/(0.11-0.03))/(1+0.11)^5+B50+B51)/B55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" ht="28" customHeight="1">
+      <c r="A104" s="205" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="B104" s="176" t="n"/>
+      <c r="C104" s="121">
         <f>(NPV(0.115,C35:G35)+(G35*(1+0.015)/(0.115-0.015))/(1+0.115)^5+B50+B51)/B55</f>
         <v/>
       </c>
-      <c r="D103" s="121">
+      <c r="D104" s="121">
         <f>(NPV(0.115,C35:G35)+(G35*(1+0.02)/(0.115-0.02))/(1+0.115)^5+B50+B51)/B55</f>
         <v/>
       </c>
-      <c r="E103" s="121">
+      <c r="E104" s="121">
         <f>(NPV(0.115,C35:G35)+(G35*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+B50+B51)/B55</f>
         <v/>
       </c>
-      <c r="F103" s="121">
+      <c r="F104" s="121">
         <f>(NPV(0.115,C35:G35)+(G35*(1+0.025)/(0.115-0.025))/(1+0.115)^5+B50+B51)/B55</f>
         <v/>
       </c>
-      <c r="G103" s="121">
+      <c r="G104" s="121">
         <f>(NPV(0.115,C35:G35)+(G35*(1+0.03)/(0.115-0.03))/(1+0.115)^5+B50+B51)/B55</f>
         <v/>
       </c>
     </row>
-    <row r="104" ht="28" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -12589,7 +12594,7 @@
         </is>
       </c>
       <c r="B5" s="75">
-        <f>DCF!B11+496228</f>
+        <f>DCF!B11+DCF!B15</f>
         <v/>
       </c>
       <c r="C5" s="176" t="n"/>
@@ -13474,376 +13479,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="3" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="210" t="inlineStr">
-        <is>
-          <t>scratch — dont touch</t>
-        </is>
-      </c>
-      <c r="B1" s="176" t="n"/>
-      <c r="C1" s="176" t="n"/>
-      <c r="D1" s="176" t="n"/>
-      <c r="E1" s="176" t="n"/>
-      <c r="F1" s="176" t="n"/>
-      <c r="G1" s="176" t="n"/>
-      <c r="H1" s="176" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="176" t="n"/>
-      <c r="B2" s="176" t="n"/>
-      <c r="C2" s="176" t="n"/>
-      <c r="D2" s="176" t="n"/>
-      <c r="E2" s="176" t="n"/>
-      <c r="F2" s="176" t="n"/>
-      <c r="G2" s="176" t="n"/>
-      <c r="H2" s="176" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="211" t="inlineStr">
-        <is>
-          <t>10-K dump (FY25 MD&amp;A)</t>
-        </is>
-      </c>
-      <c r="B3" s="176" t="n"/>
-      <c r="C3" s="176" t="n"/>
-      <c r="D3" s="176" t="n"/>
-      <c r="E3" s="176" t="n"/>
-      <c r="F3" s="176" t="n"/>
-      <c r="G3" s="176" t="n"/>
-      <c r="H3" s="176" t="n"/>
-    </row>
-    <row r="4" ht="72" customHeight="1">
-      <c r="A4" s="212" t="inlineStr">
-        <is>
-          <t>MD&amp;A — FY2025: Net revenue increased 7% to $11.1 billion. Comparable sales increased 1% on a constant dollar basis. Americas comparable sales decreased 3%; China Mainland increased 20%; Rest of World increased 9%. Gross profit as a percent of net revenue was 59.2% compared to 58.3% last year. We ended the year with 811 company-operated stores globally. Looking ahead, we expect net revenue to decrease 5% to 7% in Q2 FY2026 vs prior year...</t>
-        </is>
-      </c>
-      <c r="B4" s="176" t="n"/>
-      <c r="C4" s="176" t="n"/>
-      <c r="D4" s="176" t="n"/>
-      <c r="E4" s="176" t="n"/>
-      <c r="F4" s="176" t="n"/>
-      <c r="G4" s="176" t="n"/>
-      <c r="H4" s="176" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="176" t="n"/>
-      <c r="B5" s="176" t="n"/>
-      <c r="C5" s="176" t="n"/>
-      <c r="D5" s="176" t="n"/>
-      <c r="E5" s="176" t="n"/>
-      <c r="F5" s="176" t="n"/>
-      <c r="G5" s="176" t="n"/>
-      <c r="H5" s="176" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="176" t="n"/>
-      <c r="B6" s="176" t="n"/>
-      <c r="C6" s="176" t="n"/>
-      <c r="D6" s="176" t="n"/>
-      <c r="E6" s="176" t="n"/>
-      <c r="F6" s="176" t="n"/>
-      <c r="G6" s="176" t="n"/>
-      <c r="H6" s="176" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="176" t="n"/>
-      <c r="B7" s="176" t="n"/>
-      <c r="C7" s="176" t="n"/>
-      <c r="D7" s="176" t="n"/>
-      <c r="E7" s="176" t="n"/>
-      <c r="F7" s="176" t="n"/>
-      <c r="G7" s="176" t="n"/>
-      <c r="H7" s="176" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="176" t="n"/>
-      <c r="B8" s="176" t="n"/>
-      <c r="C8" s="176" t="n"/>
-      <c r="D8" s="211" t="inlineStr">
-        <is>
-          <t>EPS paste from release</t>
-        </is>
-      </c>
-      <c r="E8" s="176" t="n"/>
-      <c r="F8" s="176" t="n"/>
-      <c r="G8" s="176" t="n"/>
-      <c r="H8" s="176" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="176" t="n"/>
-      <c r="B9" s="176" t="n"/>
-      <c r="C9" s="176" t="n"/>
-      <c r="D9" s="213" t="inlineStr">
-        <is>
-          <t>Q2 FY25</t>
-        </is>
-      </c>
-      <c r="E9" s="176" t="n"/>
-      <c r="F9" s="213" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="G9" s="176" t="n"/>
-      <c r="H9" s="213" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="176" t="n"/>
-      <c r="B10" s="176" t="n"/>
-      <c r="C10" s="176" t="n"/>
-      <c r="D10" s="213" t="inlineStr">
-        <is>
-          <t>Q3 FY25</t>
-        </is>
-      </c>
-      <c r="E10" s="176" t="n"/>
-      <c r="F10" s="213" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="G10" s="176" t="n"/>
-      <c r="H10" s="213" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="176" t="n"/>
-      <c r="B11" s="176" t="n"/>
-      <c r="C11" s="176" t="n"/>
-      <c r="D11" s="213" t="inlineStr">
-        <is>
-          <t>Q4 FY25</t>
-        </is>
-      </c>
-      <c r="E11" s="176" t="n"/>
-      <c r="F11" s="213" t="inlineStr">
-        <is>
-          <t>5.99</t>
-        </is>
-      </c>
-      <c r="G11" s="176" t="n"/>
-      <c r="H11" s="213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  </t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="176" t="n"/>
-      <c r="B12" s="176" t="n"/>
-      <c r="C12" s="176" t="n"/>
-      <c r="D12" s="213" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="E12" s="176" t="n"/>
-      <c r="F12" s="213" t="inlineStr">
-        <is>
-          <t>14.64</t>
-        </is>
-      </c>
-      <c r="G12" s="176" t="n"/>
-      <c r="H12" s="213" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> diluted</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="176" t="n"/>
-      <c r="B13" s="176" t="n"/>
-      <c r="C13" s="176" t="n"/>
-      <c r="D13" s="213" t="inlineStr">
-        <is>
-          <t>FY26 guide</t>
-        </is>
-      </c>
-      <c r="E13" s="176" t="n"/>
-      <c r="F13" s="213" t="inlineStr">
-        <is>
-          <t>~$14.50</t>
-        </is>
-      </c>
-      <c r="G13" s="176" t="n"/>
-      <c r="H13" s="213" t="inlineStr">
-        <is>
-          <t>??? check slide 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="176" t="n"/>
-      <c r="B14" s="176" t="n"/>
-      <c r="C14" s="176" t="n"/>
-      <c r="D14" s="176" t="n"/>
-      <c r="E14" s="176" t="n"/>
-      <c r="F14" s="176" t="n"/>
-      <c r="G14" s="176" t="n"/>
-      <c r="H14" s="176" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="176" t="n"/>
-      <c r="B15" s="176" t="n"/>
-      <c r="C15" s="176" t="n"/>
-      <c r="D15" s="176" t="n"/>
-      <c r="E15" s="176" t="n"/>
-      <c r="F15" s="176" t="n"/>
-      <c r="G15" s="176" t="n"/>
-      <c r="H15" s="176" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="176" t="n"/>
-      <c r="B16" s="176" t="n"/>
-      <c r="C16" s="176" t="n"/>
-      <c r="D16" s="176" t="n"/>
-      <c r="E16" s="176" t="n"/>
-      <c r="F16" s="176" t="n"/>
-      <c r="G16" s="176" t="n"/>
-      <c r="H16" s="176" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="176" t="n"/>
-      <c r="B17" s="176" t="n"/>
-      <c r="C17" s="176" t="n"/>
-      <c r="D17" s="176" t="n"/>
-      <c r="E17" s="176" t="n"/>
-      <c r="F17" s="176" t="n"/>
-      <c r="G17" s="176" t="n"/>
-      <c r="H17" s="176" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="211" t="inlineStr">
-        <is>
-          <t>wacc sanity</t>
-        </is>
-      </c>
-      <c r="B18" s="176" t="n"/>
-      <c r="C18" s="176" t="n"/>
-      <c r="D18" s="176" t="n"/>
-      <c r="E18" s="176" t="n"/>
-      <c r="F18" s="176" t="n"/>
-      <c r="G18" s="176" t="n"/>
-      <c r="H18" s="176" t="n"/>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="213" t="inlineStr">
-        <is>
-          <t>rf</t>
-        </is>
-      </c>
-      <c r="B19" s="176" t="n"/>
-      <c r="C19" s="213" t="inlineStr">
-        <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="D19" s="176" t="n"/>
-      <c r="E19" s="213" t="inlineStr">
-        <is>
-          <t>FRED DGS10 9/9/26</t>
-        </is>
-      </c>
-      <c r="F19" s="176" t="n"/>
-      <c r="G19" s="176" t="n"/>
-      <c r="H19" s="176" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="213" t="inlineStr">
-        <is>
-          <t>ERP</t>
-        </is>
-      </c>
-      <c r="B20" s="176" t="n"/>
-      <c r="C20" s="213" t="inlineStr">
-        <is>
-          <t>5.5%</t>
-        </is>
-      </c>
-      <c r="D20" s="176" t="n"/>
-      <c r="E20" s="213" t="inlineStr">
-        <is>
-          <t>Damodaran Jan-26 + 177bps</t>
-        </is>
-      </c>
-      <c r="F20" s="176" t="n"/>
-      <c r="G20" s="176" t="n"/>
-      <c r="H20" s="176" t="n"/>
-    </row>
-    <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="213" t="inlineStr">
-        <is>
-          <t>beta</t>
-        </is>
-      </c>
-      <c r="B21" s="176" t="n"/>
-      <c r="C21" s="213" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="D21" s="176" t="n"/>
-      <c r="E21" s="213" t="inlineStr">
-        <is>
-          <t>Yahoo 5Y mo — relever w/ lease D/E</t>
-        </is>
-      </c>
-      <c r="F21" s="176" t="n"/>
-      <c r="G21" s="176" t="n"/>
-      <c r="H21" s="176" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="213" t="inlineStr">
-        <is>
-          <t>WACC?</t>
-        </is>
-      </c>
-      <c r="B22" s="176" t="n"/>
-      <c r="C22" s="213" t="inlineStr">
-        <is>
-          <t>8.1%</t>
-        </is>
-      </c>
-      <c r="D22" s="176" t="n"/>
-      <c r="E22" s="213" t="inlineStr">
-        <is>
-          <t>back of envelope — tie to WACC tab</t>
-        </is>
-      </c>
-      <c r="F22" s="176" t="n"/>
-      <c r="G22" s="214" t="inlineStr">
-        <is>
-          <t>todo: fix capex fade note on Scenarios (typo: 'fades donw')</t>
-        </is>
-      </c>
-      <c r="H22" s="176" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -11052,23 +11052,23 @@
         <v>0.05080692810692991</v>
       </c>
       <c r="C27" s="32">
-        <f>Scenarios!$B$19</f>
+        <f>Scenarios!$D$19</f>
         <v/>
       </c>
       <c r="D27" s="32">
-        <f>Scenarios!$B$19</f>
+        <f>Scenarios!$D$19</f>
         <v/>
       </c>
       <c r="E27" s="32">
-        <f>Scenarios!$B$19</f>
+        <f>Scenarios!$D$19</f>
         <v/>
       </c>
       <c r="F27" s="32">
-        <f>Scenarios!$B$19</f>
+        <f>Scenarios!$D$19</f>
         <v/>
       </c>
       <c r="G27" s="32">
-        <f>Scenarios!$B$19</f>
+        <f>Scenarios!$D$19</f>
         <v/>
       </c>
     </row>
@@ -11112,23 +11112,23 @@
         <v>0.05971412101669879</v>
       </c>
       <c r="C29" s="32">
-        <f>Scenarios!$B$20</f>
+        <f>Scenarios!$D$20</f>
         <v/>
       </c>
       <c r="D29" s="32">
-        <f>Scenarios!$B$20</f>
+        <f>Scenarios!$D$20</f>
         <v/>
       </c>
       <c r="E29" s="32">
-        <f>Scenarios!$B$20</f>
+        <f>Scenarios!$D$20</f>
         <v/>
       </c>
       <c r="F29" s="32">
-        <f>Scenarios!$B$20</f>
+        <f>Scenarios!$D$20</f>
         <v/>
       </c>
       <c r="G29" s="32">
-        <f>Scenarios!$B$20</f>
+        <f>Scenarios!$D$20</f>
         <v/>
       </c>
     </row>
@@ -11344,23 +11344,23 @@
       </c>
       <c r="B38" s="176" t="n"/>
       <c r="C38" s="91">
-        <f>1/(1+Scenarios!$B$9)^C36</f>
+        <f>1/(1+Scenarios!$D$9)^C37</f>
         <v/>
       </c>
       <c r="D38" s="91">
-        <f>1/(1+Scenarios!$B$9)^D36</f>
+        <f>1/(1+Scenarios!$D$9)^D37</f>
         <v/>
       </c>
       <c r="E38" s="91">
-        <f>1/(1+Scenarios!$B$9)^E36</f>
+        <f>1/(1+Scenarios!$D$9)^E37</f>
         <v/>
       </c>
       <c r="F38" s="91">
-        <f>1/(1+Scenarios!$B$9)^F36</f>
+        <f>1/(1+Scenarios!$D$9)^F37</f>
         <v/>
       </c>
       <c r="G38" s="91">
-        <f>1/(1+Scenarios!$B$9)^G36</f>
+        <f>1/(1+Scenarios!$D$9)^G37</f>
         <v/>
       </c>
     </row>
@@ -11372,23 +11372,23 @@
       </c>
       <c r="B39" s="176" t="n"/>
       <c r="C39" s="130">
-        <f>C35*C37</f>
+        <f>C36*C38</f>
         <v/>
       </c>
       <c r="D39" s="130">
-        <f>D35*D37</f>
+        <f>D36*D38</f>
         <v/>
       </c>
       <c r="E39" s="130">
-        <f>E35*E37</f>
+        <f>E36*E38</f>
         <v/>
       </c>
       <c r="F39" s="130">
-        <f>F35*F37</f>
+        <f>F36*F38</f>
         <v/>
       </c>
       <c r="G39" s="130">
-        <f>G35*G37</f>
+        <f>G36*G38</f>
         <v/>
       </c>
     </row>
@@ -11434,7 +11434,7 @@
         </is>
       </c>
       <c r="B43" s="75">
-        <f>SUM(C38:G38)</f>
+        <f>SUM(C39:G39)</f>
         <v/>
       </c>
       <c r="C43" s="176" t="n"/>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="B44" s="32">
-        <f>Scenarios!$B$10</f>
+        <f>Scenarios!$D$10</f>
         <v/>
       </c>
       <c r="C44" s="176" t="n"/>
@@ -11466,7 +11466,7 @@
         </is>
       </c>
       <c r="B45" s="130">
-        <f>G11+G16</f>
+        <f>G11+G17</f>
         <v/>
       </c>
       <c r="C45" s="176" t="n"/>
@@ -11482,7 +11482,7 @@
         </is>
       </c>
       <c r="B46" s="75">
-        <f>G35*(1+Scenarios!$B$10)/(Scenarios!$B$9-Scenarios!$B$10)</f>
+        <f>G36*(1+Scenarios!$D$10)/(Scenarios!$D$9-Scenarios!$D$10)</f>
         <v/>
       </c>
       <c r="C46" s="176" t="n"/>
@@ -11498,7 +11498,7 @@
         </is>
       </c>
       <c r="B47" s="94">
-        <f>B45/B44</f>
+        <f>B46/B45</f>
         <v/>
       </c>
       <c r="C47" s="176" t="n"/>
@@ -11514,7 +11514,7 @@
         </is>
       </c>
       <c r="B48" s="94">
-        <f>G35/B44*(1+Scenarios!$B$10)/(Scenarios!$B$9-Scenarios!$B$10)</f>
+        <f>G36/B45*(1+Scenarios!$D$10)/(Scenarios!$D$9-Scenarios!$D$10)</f>
         <v/>
       </c>
       <c r="C48" s="176" t="n"/>
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="B49" s="75">
-        <f>B45/(1+Scenarios!$B$9)^G36</f>
+        <f>B46/(1+Scenarios!$D$9)^G37</f>
         <v/>
       </c>
       <c r="C49" s="176" t="n"/>
@@ -11546,7 +11546,7 @@
         </is>
       </c>
       <c r="B50" s="130">
-        <f>B42+B48</f>
+        <f>B43+B49</f>
         <v/>
       </c>
       <c r="C50" s="176" t="n"/>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="B55" s="130">
-        <f>B49+B50+B51</f>
+        <f>B50+B51+B52</f>
         <v/>
       </c>
       <c r="C55" s="176" t="n"/>
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="B57" s="139">
-        <f>B54/B55</f>
+        <f>B55/B56</f>
         <v/>
       </c>
       <c r="C57" s="176" t="n"/>
@@ -11676,7 +11676,7 @@
         </is>
       </c>
       <c r="B59" s="32">
-        <f>B56/B57-1</f>
+        <f>B57/B58-1</f>
         <v/>
       </c>
       <c r="C59" s="176" t="n"/>
@@ -11692,7 +11692,7 @@
         </is>
       </c>
       <c r="B60" s="32">
-        <f>B48/B49</f>
+        <f>B49/B50</f>
         <v/>
       </c>
       <c r="C60" s="176" t="n"/>
@@ -12141,7 +12141,7 @@
         </is>
       </c>
       <c r="B83" s="94">
-        <f>B46</f>
+        <f>B47</f>
         <v/>
       </c>
       <c r="C83" s="176" t="n"/>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="B84" s="75">
-        <f>B44*B82</f>
+        <f>B45*B82</f>
         <v/>
       </c>
       <c r="C84" s="176" t="n"/>
@@ -12173,7 +12173,7 @@
         </is>
       </c>
       <c r="B85" s="75">
-        <f>B83/(1+Scenarios!$B$9)^G36</f>
+        <f>B83/(1+Scenarios!$D$9)^G37</f>
         <v/>
       </c>
       <c r="C85" s="176" t="n"/>
@@ -12189,7 +12189,7 @@
         </is>
       </c>
       <c r="B86" s="130">
-        <f>B42+B84</f>
+        <f>B43+B85</f>
         <v/>
       </c>
       <c r="C86" s="176" t="n"/>
@@ -12205,7 +12205,7 @@
         </is>
       </c>
       <c r="B87" s="99">
-        <f>(B85+B50+B51)/B55</f>
+        <f>(B85+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="C87" s="176" t="n"/>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -3375,15 +3375,15 @@
       </c>
       <c r="B25" s="176" t="n"/>
       <c r="C25" s="75">
-        <f>DCF!$B$5*(1+C4)</f>
+        <f>DCF!$B$6*(1+C4)</f>
         <v/>
       </c>
       <c r="D25" s="75">
-        <f>DCF!$B$5*(1+D4)</f>
+        <f>DCF!$B$6*(1+D4)</f>
         <v/>
       </c>
       <c r="E25" s="75">
-        <f>DCF!$B$5*(1+E4)</f>
+        <f>DCF!$B$6*(1+E4)</f>
         <v/>
       </c>
       <c r="F25" s="176" t="n"/>
@@ -6445,15 +6445,15 @@
       </c>
       <c r="B168" s="176" t="n"/>
       <c r="C168" s="75">
-        <f>8456743*C25/DCF!$B$5</f>
+        <f>8456743*C25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D168" s="75">
-        <f>8456743*D25/DCF!$B$5</f>
+        <f>8456743*D25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E168" s="75">
-        <f>8456743*E25/DCF!$B$5</f>
+        <f>8456743*E25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F168" s="176" t="n"/>
@@ -6467,15 +6467,15 @@
       </c>
       <c r="B169" s="176" t="n"/>
       <c r="C169" s="75">
-        <f>8456743*C26/DCF!$B$5</f>
+        <f>8456743*C26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D169" s="75">
-        <f>8456743*D26/DCF!$B$5</f>
+        <f>8456743*D26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E169" s="75">
-        <f>8456743*E26/DCF!$B$5</f>
+        <f>8456743*E26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F169" s="176" t="n"/>
@@ -6489,15 +6489,15 @@
       </c>
       <c r="B170" s="176" t="n"/>
       <c r="C170" s="75">
-        <f>8456743*C27/DCF!$B$5</f>
+        <f>8456743*C27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D170" s="75">
-        <f>8456743*D27/DCF!$B$5</f>
+        <f>8456743*D27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E170" s="75">
-        <f>8456743*E27/DCF!$B$5</f>
+        <f>8456743*E27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F170" s="176" t="n"/>
@@ -6511,15 +6511,15 @@
       </c>
       <c r="B171" s="176" t="n"/>
       <c r="C171" s="75">
-        <f>8456743*C28/DCF!$B$5</f>
+        <f>8456743*C28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D171" s="75">
-        <f>8456743*D28/DCF!$B$5</f>
+        <f>8456743*D28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E171" s="75">
-        <f>8456743*E28/DCF!$B$5</f>
+        <f>8456743*E28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F171" s="176" t="n"/>
@@ -6533,15 +6533,15 @@
       </c>
       <c r="B172" s="176" t="n"/>
       <c r="C172" s="75">
-        <f>8456743*C29/DCF!$B$5</f>
+        <f>8456743*C29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D172" s="75">
-        <f>8456743*D29/DCF!$B$5</f>
+        <f>8456743*D29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E172" s="75">
-        <f>8456743*E29/DCF!$B$5</f>
+        <f>8456743*E29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F172" s="176" t="n"/>
@@ -6555,15 +6555,15 @@
       </c>
       <c r="B173" s="176" t="n"/>
       <c r="C173" s="75">
-        <f>3494903*C25/DCF!$B$5</f>
+        <f>3494903*C25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D173" s="75">
-        <f>3494903*D25/DCF!$B$5</f>
+        <f>3494903*D25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E173" s="75">
-        <f>3494903*E25/DCF!$B$5</f>
+        <f>3494903*E25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F173" s="176" t="n"/>
@@ -6577,15 +6577,15 @@
       </c>
       <c r="B174" s="176" t="n"/>
       <c r="C174" s="75">
-        <f>3494903*C26/DCF!$B$5</f>
+        <f>3494903*C26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D174" s="75">
-        <f>3494903*D26/DCF!$B$5</f>
+        <f>3494903*D26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E174" s="75">
-        <f>3494903*E26/DCF!$B$5</f>
+        <f>3494903*E26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F174" s="176" t="n"/>
@@ -6599,15 +6599,15 @@
       </c>
       <c r="B175" s="176" t="n"/>
       <c r="C175" s="75">
-        <f>3494903*C27/DCF!$B$5</f>
+        <f>3494903*C27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D175" s="75">
-        <f>3494903*D27/DCF!$B$5</f>
+        <f>3494903*D27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E175" s="75">
-        <f>3494903*E27/DCF!$B$5</f>
+        <f>3494903*E27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F175" s="176" t="n"/>
@@ -6621,15 +6621,15 @@
       </c>
       <c r="B176" s="176" t="n"/>
       <c r="C176" s="75">
-        <f>3494903*C28/DCF!$B$5</f>
+        <f>3494903*C28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D176" s="75">
-        <f>3494903*D28/DCF!$B$5</f>
+        <f>3494903*D28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E176" s="75">
-        <f>3494903*E28/DCF!$B$5</f>
+        <f>3494903*E28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F176" s="176" t="n"/>
@@ -6643,15 +6643,15 @@
       </c>
       <c r="B177" s="176" t="n"/>
       <c r="C177" s="75">
-        <f>3494903*C29/DCF!$B$5</f>
+        <f>3494903*C29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D177" s="75">
-        <f>3494903*D29/DCF!$B$5</f>
+        <f>3494903*D29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E177" s="75">
-        <f>3494903*E29/DCF!$B$5</f>
+        <f>3494903*E29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F177" s="176" t="n"/>
@@ -6665,15 +6665,15 @@
       </c>
       <c r="B178" s="176" t="n"/>
       <c r="C178" s="75">
-        <f>4961840*C25/DCF!$B$5</f>
+        <f>4961840*C25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D178" s="75">
-        <f>4961840*D25/DCF!$B$5</f>
+        <f>4961840*D25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E178" s="75">
-        <f>4961840*E25/DCF!$B$5</f>
+        <f>4961840*E25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F178" s="176" t="n"/>
@@ -6687,15 +6687,15 @@
       </c>
       <c r="B179" s="176" t="n"/>
       <c r="C179" s="75">
-        <f>4961840*C26/DCF!$B$5</f>
+        <f>4961840*C26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D179" s="75">
-        <f>4961840*D26/DCF!$B$5</f>
+        <f>4961840*D26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E179" s="75">
-        <f>4961840*E26/DCF!$B$5</f>
+        <f>4961840*E26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F179" s="176" t="n"/>
@@ -6709,15 +6709,15 @@
       </c>
       <c r="B180" s="176" t="n"/>
       <c r="C180" s="75">
-        <f>4961840*C27/DCF!$B$5</f>
+        <f>4961840*C27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D180" s="75">
-        <f>4961840*D27/DCF!$B$5</f>
+        <f>4961840*D27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E180" s="75">
-        <f>4961840*E27/DCF!$B$5</f>
+        <f>4961840*E27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F180" s="176" t="n"/>
@@ -6731,15 +6731,15 @@
       </c>
       <c r="B181" s="176" t="n"/>
       <c r="C181" s="75">
-        <f>4961840*C28/DCF!$B$5</f>
+        <f>4961840*C28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D181" s="75">
-        <f>4961840*D28/DCF!$B$5</f>
+        <f>4961840*D28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E181" s="75">
-        <f>4961840*E28/DCF!$B$5</f>
+        <f>4961840*E28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F181" s="176" t="n"/>
@@ -6753,15 +6753,15 @@
       </c>
       <c r="B182" s="176" t="n"/>
       <c r="C182" s="75">
-        <f>4961840*C29/DCF!$B$5</f>
+        <f>4961840*C29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D182" s="75">
-        <f>4961840*D29/DCF!$B$5</f>
+        <f>4961840*D29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E182" s="75">
-        <f>4961840*E29/DCF!$B$5</f>
+        <f>4961840*E29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F182" s="176" t="n"/>
@@ -9599,23 +9599,23 @@
         <v/>
       </c>
       <c r="C20" s="75">
-        <f>Scenarios!D25/DCF!$B$5*62203*$B$7</f>
+        <f>Scenarios!D25/DCF!$B$6*62203*$B$7</f>
         <v/>
       </c>
       <c r="D20" s="75">
-        <f>Scenarios!D26/DCF!$B$5*62203*$B$7</f>
+        <f>Scenarios!D26/DCF!$B$6*62203*$B$7</f>
         <v/>
       </c>
       <c r="E20" s="75">
-        <f>Scenarios!D27/DCF!$B$5*62203*$B$7</f>
+        <f>Scenarios!D27/DCF!$B$6*62203*$B$7</f>
         <v/>
       </c>
       <c r="F20" s="75">
-        <f>Scenarios!D28/DCF!$B$5*62203*$B$7</f>
+        <f>Scenarios!D28/DCF!$B$6*62203*$B$7</f>
         <v/>
       </c>
       <c r="G20" s="75">
-        <f>Scenarios!D29/DCF!$B$5*62203*$B$7</f>
+        <f>Scenarios!D29/DCF!$B$6*62203*$B$7</f>
         <v/>
       </c>
     </row>
@@ -9670,23 +9670,23 @@
         <v>1028</v>
       </c>
       <c r="C23" s="75">
-        <f>1028*(Scenarios!D25/DCF!$B$5)</f>
+        <f>1028*(Scenarios!D25/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="D23" s="75">
-        <f>1028*(Scenarios!D26/DCF!$B$5)</f>
+        <f>1028*(Scenarios!D26/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="E23" s="75">
-        <f>1028*(Scenarios!D27/DCF!$B$5)</f>
+        <f>1028*(Scenarios!D27/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="F23" s="75">
-        <f>1028*(Scenarios!D28/DCF!$B$5)</f>
+        <f>1028*(Scenarios!D28/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="G23" s="75">
-        <f>1028*(Scenarios!D29/DCF!$B$5)</f>
+        <f>1028*(Scenarios!D29/DCF!$B$6)</f>
         <v/>
       </c>
     </row>
@@ -10801,23 +10801,23 @@
       </c>
       <c r="B18" s="176" t="n"/>
       <c r="C18" s="32">
-        <f>-C6*Scenarios!$D$13</f>
+        <f>Scenarios!$D$13</f>
         <v/>
       </c>
       <c r="D18" s="32">
-        <f>-D6*Scenarios!$D$13</f>
+        <f>Scenarios!$D$13</f>
         <v/>
       </c>
       <c r="E18" s="32">
-        <f>-E6*Scenarios!$D$13</f>
+        <f>Scenarios!$D$13</f>
         <v/>
       </c>
       <c r="F18" s="32">
-        <f>-F6*Scenarios!$D$13</f>
+        <f>Scenarios!$D$13</f>
         <v/>
       </c>
       <c r="G18" s="32">
-        <f>-G6*Scenarios!$D$13</f>
+        <f>Scenarios!$D$13</f>
         <v/>
       </c>
     </row>
@@ -11843,7 +11843,7 @@
         <v/>
       </c>
       <c r="G69" s="75">
-        <f>G35</f>
+        <f>G36</f>
         <v/>
       </c>
     </row>
@@ -12127,7 +12127,10 @@
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="61" t="n"/>
-      <c r="B82" s="176" t="n"/>
+      <c r="B82" s="176">
+        <f>B47</f>
+        <v/>
+      </c>
       <c r="C82" s="176" t="n"/>
       <c r="D82" s="176" t="n"/>
       <c r="E82" s="176" t="n"/>
@@ -12386,23 +12389,23 @@
       </c>
       <c r="B100" s="176" t="n"/>
       <c r="C100" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.015)/(0.095-0.015))/(1+0.095)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C36:G36)+(G36*(1+0.015)/(0.095-0.015))/(1+0.095)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D100" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.02)/(0.095-0.02))/(1+0.095)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C36:G36)+(G36*(1+0.02)/(0.095-0.02))/(1+0.095)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E100" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C36:G36)+(G36*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F100" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.025)/(0.095-0.025))/(1+0.095)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C36:G36)+(G36*(1+0.025)/(0.095-0.025))/(1+0.095)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G100" s="121">
-        <f>(NPV(0.095,C35:G35)+(G35*(1+0.03)/(0.095-0.03))/(1+0.095)^5+B50+B51)/B55</f>
+        <f>(NPV(0.095,C36:G36)+(G36*(1+0.03)/(0.095-0.03))/(1+0.095)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>
@@ -12412,23 +12415,23 @@
       </c>
       <c r="B101" s="176" t="n"/>
       <c r="C101" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.015)/(0.1-0.015))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C36:G36)+(G36*(1+0.015)/(0.1-0.015))/(1+0.1)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D101" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.02)/(0.1-0.02))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C36:G36)+(G36*(1+0.02)/(0.1-0.02))/(1+0.1)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E101" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C36:G36)+(G36*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F101" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.025)/(0.1-0.025))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C36:G36)+(G36*(1+0.025)/(0.1-0.025))/(1+0.1)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G101" s="121">
-        <f>(NPV(0.1,C35:G35)+(G35*(1+0.03)/(0.1-0.03))/(1+0.1)^5+B50+B51)/B55</f>
+        <f>(NPV(0.1,C36:G36)+(G36*(1+0.03)/(0.1-0.03))/(1+0.1)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>
@@ -12438,23 +12441,23 @@
       </c>
       <c r="B102" s="176" t="n"/>
       <c r="C102" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.015)/(0.105-0.015))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C36:G36)+(G36*(1+0.015)/(0.105-0.015))/(1+0.105)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D102" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.02)/(0.105-0.02))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C36:G36)+(G36*(1+0.02)/(0.105-0.02))/(1+0.105)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E102" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C36:G36)+(G36*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F102" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.025)/(0.105-0.025))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C36:G36)+(G36*(1+0.025)/(0.105-0.025))/(1+0.105)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G102" s="121">
-        <f>(NPV(0.105,C35:G35)+(G35*(1+0.03)/(0.105-0.03))/(1+0.105)^5+B50+B51)/B55</f>
+        <f>(NPV(0.105,C36:G36)+(G36*(1+0.03)/(0.105-0.03))/(1+0.105)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>
@@ -12464,23 +12467,23 @@
       </c>
       <c r="B103" s="176" t="n"/>
       <c r="C103" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.015)/(0.11-0.015))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.11,C36:G36)+(G36*(1+0.015)/(0.11-0.015))/(1+0.11)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D103" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.02)/(0.11-0.02))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.11,C36:G36)+(G36*(1+0.02)/(0.11-0.02))/(1+0.11)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E103" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.11,C36:G36)+(G36*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F103" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.025)/(0.11-0.025))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.11,C36:G36)+(G36*(1+0.025)/(0.11-0.025))/(1+0.11)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G103" s="121">
-        <f>(NPV(0.11,C35:G35)+(G35*(1+0.03)/(0.11-0.03))/(1+0.11)^5+B50+B51)/B55</f>
+        <f>(NPV(0.11,C36:G36)+(G36*(1+0.03)/(0.11-0.03))/(1+0.11)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>
@@ -12490,23 +12493,23 @@
       </c>
       <c r="B104" s="176" t="n"/>
       <c r="C104" s="121">
-        <f>(NPV(0.115,C35:G35)+(G35*(1+0.015)/(0.115-0.015))/(1+0.115)^5+B50+B51)/B55</f>
+        <f>(NPV(0.115,C36:G36)+(G36*(1+0.015)/(0.115-0.015))/(1+0.115)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D104" s="121">
-        <f>(NPV(0.115,C35:G35)+(G35*(1+0.02)/(0.115-0.02))/(1+0.115)^5+B50+B51)/B55</f>
+        <f>(NPV(0.115,C36:G36)+(G36*(1+0.02)/(0.115-0.02))/(1+0.115)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E104" s="121">
-        <f>(NPV(0.115,C35:G35)+(G35*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+B50+B51)/B55</f>
+        <f>(NPV(0.115,C36:G36)+(G36*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F104" s="121">
-        <f>(NPV(0.115,C35:G35)+(G35*(1+0.025)/(0.115-0.025))/(1+0.115)^5+B50+B51)/B55</f>
+        <f>(NPV(0.115,C36:G36)+(G36*(1+0.025)/(0.115-0.025))/(1+0.115)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G104" s="121">
-        <f>(NPV(0.115,C35:G35)+(G35*(1+0.03)/(0.115-0.03))/(1+0.115)^5+B50+B51)/B55</f>
+        <f>(NPV(0.115,C36:G36)+(G36*(1+0.03)/(0.115-0.03))/(1+0.115)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>
@@ -12610,7 +12613,7 @@
         </is>
       </c>
       <c r="B6" s="75">
-        <f>DCF!B44</f>
+        <f>DCF!B45</f>
         <v/>
       </c>
       <c r="C6" s="176" t="n"/>
@@ -13199,7 +13202,7 @@
         </is>
       </c>
       <c r="B44" s="94">
-        <f>DCF!B46</f>
+        <f>DCF!B47</f>
         <v/>
       </c>
       <c r="C44" s="176" t="n"/>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -3375,15 +3375,15 @@
       </c>
       <c r="B25" s="176" t="n"/>
       <c r="C25" s="75">
-        <f>DCF!$B$6*(1+C4)</f>
+        <f>11102600*(1+C4)</f>
         <v/>
       </c>
       <c r="D25" s="75">
-        <f>DCF!$B$6*(1+D4)</f>
+        <f>11102600*(1+D4)</f>
         <v/>
       </c>
       <c r="E25" s="75">
-        <f>DCF!$B$6*(1+E4)</f>
+        <f>11102600*(1+E4)</f>
         <v/>
       </c>
       <c r="F25" s="176" t="n"/>
@@ -6445,15 +6445,15 @@
       </c>
       <c r="B168" s="176" t="n"/>
       <c r="C168" s="75">
-        <f>8456743*C25/DCF!$B$6</f>
+        <f>8456743*C25/11102600</f>
         <v/>
       </c>
       <c r="D168" s="75">
-        <f>8456743*D25/DCF!$B$6</f>
+        <f>8456743*D25/11102600</f>
         <v/>
       </c>
       <c r="E168" s="75">
-        <f>8456743*E25/DCF!$B$6</f>
+        <f>8456743*E25/11102600</f>
         <v/>
       </c>
       <c r="F168" s="176" t="n"/>
@@ -6467,15 +6467,15 @@
       </c>
       <c r="B169" s="176" t="n"/>
       <c r="C169" s="75">
-        <f>8456743*C26/DCF!$B$6</f>
+        <f>8456743*C26/11102600</f>
         <v/>
       </c>
       <c r="D169" s="75">
-        <f>8456743*D26/DCF!$B$6</f>
+        <f>8456743*D26/11102600</f>
         <v/>
       </c>
       <c r="E169" s="75">
-        <f>8456743*E26/DCF!$B$6</f>
+        <f>8456743*E26/11102600</f>
         <v/>
       </c>
       <c r="F169" s="176" t="n"/>
@@ -6489,15 +6489,15 @@
       </c>
       <c r="B170" s="176" t="n"/>
       <c r="C170" s="75">
-        <f>8456743*C27/DCF!$B$6</f>
+        <f>8456743*C27/11102600</f>
         <v/>
       </c>
       <c r="D170" s="75">
-        <f>8456743*D27/DCF!$B$6</f>
+        <f>8456743*D27/11102600</f>
         <v/>
       </c>
       <c r="E170" s="75">
-        <f>8456743*E27/DCF!$B$6</f>
+        <f>8456743*E27/11102600</f>
         <v/>
       </c>
       <c r="F170" s="176" t="n"/>
@@ -6511,15 +6511,15 @@
       </c>
       <c r="B171" s="176" t="n"/>
       <c r="C171" s="75">
-        <f>8456743*C28/DCF!$B$6</f>
+        <f>8456743*C28/11102600</f>
         <v/>
       </c>
       <c r="D171" s="75">
-        <f>8456743*D28/DCF!$B$6</f>
+        <f>8456743*D28/11102600</f>
         <v/>
       </c>
       <c r="E171" s="75">
-        <f>8456743*E28/DCF!$B$6</f>
+        <f>8456743*E28/11102600</f>
         <v/>
       </c>
       <c r="F171" s="176" t="n"/>
@@ -6533,15 +6533,15 @@
       </c>
       <c r="B172" s="176" t="n"/>
       <c r="C172" s="75">
-        <f>8456743*C29/DCF!$B$6</f>
+        <f>8456743*C29/11102600</f>
         <v/>
       </c>
       <c r="D172" s="75">
-        <f>8456743*D29/DCF!$B$6</f>
+        <f>8456743*D29/11102600</f>
         <v/>
       </c>
       <c r="E172" s="75">
-        <f>8456743*E29/DCF!$B$6</f>
+        <f>8456743*E29/11102600</f>
         <v/>
       </c>
       <c r="F172" s="176" t="n"/>
@@ -6555,15 +6555,15 @@
       </c>
       <c r="B173" s="176" t="n"/>
       <c r="C173" s="75">
-        <f>3494903*C25/DCF!$B$6</f>
+        <f>3494903*C25/11102600</f>
         <v/>
       </c>
       <c r="D173" s="75">
-        <f>3494903*D25/DCF!$B$6</f>
+        <f>3494903*D25/11102600</f>
         <v/>
       </c>
       <c r="E173" s="75">
-        <f>3494903*E25/DCF!$B$6</f>
+        <f>3494903*E25/11102600</f>
         <v/>
       </c>
       <c r="F173" s="176" t="n"/>
@@ -6577,15 +6577,15 @@
       </c>
       <c r="B174" s="176" t="n"/>
       <c r="C174" s="75">
-        <f>3494903*C26/DCF!$B$6</f>
+        <f>3494903*C26/11102600</f>
         <v/>
       </c>
       <c r="D174" s="75">
-        <f>3494903*D26/DCF!$B$6</f>
+        <f>3494903*D26/11102600</f>
         <v/>
       </c>
       <c r="E174" s="75">
-        <f>3494903*E26/DCF!$B$6</f>
+        <f>3494903*E26/11102600</f>
         <v/>
       </c>
       <c r="F174" s="176" t="n"/>
@@ -6599,15 +6599,15 @@
       </c>
       <c r="B175" s="176" t="n"/>
       <c r="C175" s="75">
-        <f>3494903*C27/DCF!$B$6</f>
+        <f>3494903*C27/11102600</f>
         <v/>
       </c>
       <c r="D175" s="75">
-        <f>3494903*D27/DCF!$B$6</f>
+        <f>3494903*D27/11102600</f>
         <v/>
       </c>
       <c r="E175" s="75">
-        <f>3494903*E27/DCF!$B$6</f>
+        <f>3494903*E27/11102600</f>
         <v/>
       </c>
       <c r="F175" s="176" t="n"/>
@@ -6621,15 +6621,15 @@
       </c>
       <c r="B176" s="176" t="n"/>
       <c r="C176" s="75">
-        <f>3494903*C28/DCF!$B$6</f>
+        <f>3494903*C28/11102600</f>
         <v/>
       </c>
       <c r="D176" s="75">
-        <f>3494903*D28/DCF!$B$6</f>
+        <f>3494903*D28/11102600</f>
         <v/>
       </c>
       <c r="E176" s="75">
-        <f>3494903*E28/DCF!$B$6</f>
+        <f>3494903*E28/11102600</f>
         <v/>
       </c>
       <c r="F176" s="176" t="n"/>
@@ -6643,15 +6643,15 @@
       </c>
       <c r="B177" s="176" t="n"/>
       <c r="C177" s="75">
-        <f>3494903*C29/DCF!$B$6</f>
+        <f>3494903*C29/11102600</f>
         <v/>
       </c>
       <c r="D177" s="75">
-        <f>3494903*D29/DCF!$B$6</f>
+        <f>3494903*D29/11102600</f>
         <v/>
       </c>
       <c r="E177" s="75">
-        <f>3494903*E29/DCF!$B$6</f>
+        <f>3494903*E29/11102600</f>
         <v/>
       </c>
       <c r="F177" s="176" t="n"/>
@@ -6665,15 +6665,15 @@
       </c>
       <c r="B178" s="176" t="n"/>
       <c r="C178" s="75">
-        <f>4961840*C25/DCF!$B$6</f>
+        <f>4961840*C25/11102600</f>
         <v/>
       </c>
       <c r="D178" s="75">
-        <f>4961840*D25/DCF!$B$6</f>
+        <f>4961840*D25/11102600</f>
         <v/>
       </c>
       <c r="E178" s="75">
-        <f>4961840*E25/DCF!$B$6</f>
+        <f>4961840*E25/11102600</f>
         <v/>
       </c>
       <c r="F178" s="176" t="n"/>
@@ -6687,15 +6687,15 @@
       </c>
       <c r="B179" s="176" t="n"/>
       <c r="C179" s="75">
-        <f>4961840*C26/DCF!$B$6</f>
+        <f>4961840*C26/11102600</f>
         <v/>
       </c>
       <c r="D179" s="75">
-        <f>4961840*D26/DCF!$B$6</f>
+        <f>4961840*D26/11102600</f>
         <v/>
       </c>
       <c r="E179" s="75">
-        <f>4961840*E26/DCF!$B$6</f>
+        <f>4961840*E26/11102600</f>
         <v/>
       </c>
       <c r="F179" s="176" t="n"/>
@@ -6709,15 +6709,15 @@
       </c>
       <c r="B180" s="176" t="n"/>
       <c r="C180" s="75">
-        <f>4961840*C27/DCF!$B$6</f>
+        <f>4961840*C27/11102600</f>
         <v/>
       </c>
       <c r="D180" s="75">
-        <f>4961840*D27/DCF!$B$6</f>
+        <f>4961840*D27/11102600</f>
         <v/>
       </c>
       <c r="E180" s="75">
-        <f>4961840*E27/DCF!$B$6</f>
+        <f>4961840*E27/11102600</f>
         <v/>
       </c>
       <c r="F180" s="176" t="n"/>
@@ -6731,15 +6731,15 @@
       </c>
       <c r="B181" s="176" t="n"/>
       <c r="C181" s="75">
-        <f>4961840*C28/DCF!$B$6</f>
+        <f>4961840*C28/11102600</f>
         <v/>
       </c>
       <c r="D181" s="75">
-        <f>4961840*D28/DCF!$B$6</f>
+        <f>4961840*D28/11102600</f>
         <v/>
       </c>
       <c r="E181" s="75">
-        <f>4961840*E28/DCF!$B$6</f>
+        <f>4961840*E28/11102600</f>
         <v/>
       </c>
       <c r="F181" s="176" t="n"/>
@@ -6753,15 +6753,15 @@
       </c>
       <c r="B182" s="176" t="n"/>
       <c r="C182" s="75">
-        <f>4961840*C29/DCF!$B$6</f>
+        <f>4961840*C29/11102600</f>
         <v/>
       </c>
       <c r="D182" s="75">
-        <f>4961840*D29/DCF!$B$6</f>
+        <f>4961840*D29/11102600</f>
         <v/>
       </c>
       <c r="E182" s="75">
-        <f>4961840*E29/DCF!$B$6</f>
+        <f>4961840*E29/11102600</f>
         <v/>
       </c>
       <c r="F182" s="176" t="n"/>
@@ -9599,23 +9599,23 @@
         <v/>
       </c>
       <c r="C20" s="75">
-        <f>Scenarios!D25/DCF!$B$6*62203*$B$7</f>
+        <f>Scenarios!D25/11102600*62203*$B$7</f>
         <v/>
       </c>
       <c r="D20" s="75">
-        <f>Scenarios!D26/DCF!$B$6*62203*$B$7</f>
+        <f>Scenarios!D26/11102600*62203*$B$7</f>
         <v/>
       </c>
       <c r="E20" s="75">
-        <f>Scenarios!D27/DCF!$B$6*62203*$B$7</f>
+        <f>Scenarios!D27/11102600*62203*$B$7</f>
         <v/>
       </c>
       <c r="F20" s="75">
-        <f>Scenarios!D28/DCF!$B$6*62203*$B$7</f>
+        <f>Scenarios!D28/11102600*62203*$B$7</f>
         <v/>
       </c>
       <c r="G20" s="75">
-        <f>Scenarios!D29/DCF!$B$6*62203*$B$7</f>
+        <f>Scenarios!D29/11102600*62203*$B$7</f>
         <v/>
       </c>
     </row>
@@ -9670,23 +9670,23 @@
         <v>1028</v>
       </c>
       <c r="C23" s="75">
-        <f>1028*(Scenarios!D25/DCF!$B$6)</f>
+        <f>1028*(Scenarios!D25/11102600)</f>
         <v/>
       </c>
       <c r="D23" s="75">
-        <f>1028*(Scenarios!D26/DCF!$B$6)</f>
+        <f>1028*(Scenarios!D26/11102600)</f>
         <v/>
       </c>
       <c r="E23" s="75">
-        <f>1028*(Scenarios!D27/DCF!$B$6)</f>
+        <f>1028*(Scenarios!D27/11102600)</f>
         <v/>
       </c>
       <c r="F23" s="75">
-        <f>1028*(Scenarios!D28/DCF!$B$6)</f>
+        <f>1028*(Scenarios!D28/11102600)</f>
         <v/>
       </c>
       <c r="G23" s="75">
-        <f>1028*(Scenarios!D29/DCF!$B$6)</f>
+        <f>1028*(Scenarios!D29/11102600)</f>
         <v/>
       </c>
     </row>
@@ -9791,23 +9791,23 @@
         <v>5049744</v>
       </c>
       <c r="C28" s="75">
-        <f>'Revenue Drivers'!F31</f>
+        <f>'Revenue Drivers'!C31</f>
         <v/>
       </c>
       <c r="D28" s="75">
-        <f>'Revenue Drivers'!G31</f>
+        <f>'Revenue Drivers'!D31</f>
         <v/>
       </c>
       <c r="E28" s="75">
-        <f>'Revenue Drivers'!H31</f>
+        <f>'Revenue Drivers'!E31</f>
         <v/>
       </c>
       <c r="F28" s="75">
-        <f>'Revenue Drivers'!I31</f>
+        <f>'Revenue Drivers'!C31</f>
         <v/>
       </c>
       <c r="G28" s="75">
-        <f>'Revenue Drivers'!J31</f>
+        <f>'Revenue Drivers'!D31</f>
         <v/>
       </c>
     </row>
@@ -9821,23 +9821,23 @@
         <v>4918697</v>
       </c>
       <c r="C29" s="75">
-        <f>'Revenue Drivers'!F41</f>
+        <f>'Revenue Drivers'!C41</f>
         <v/>
       </c>
       <c r="D29" s="75">
-        <f>'Revenue Drivers'!G41</f>
+        <f>'Revenue Drivers'!D41</f>
         <v/>
       </c>
       <c r="E29" s="75">
-        <f>'Revenue Drivers'!H41</f>
+        <f>'Revenue Drivers'!E41</f>
         <v/>
       </c>
       <c r="F29" s="75">
-        <f>'Revenue Drivers'!I41</f>
+        <f>'Revenue Drivers'!C41</f>
         <v/>
       </c>
       <c r="G29" s="75">
-        <f>'Revenue Drivers'!J41</f>
+        <f>'Revenue Drivers'!D41</f>
         <v/>
       </c>
     </row>
@@ -9851,23 +9851,23 @@
         <v>1134159</v>
       </c>
       <c r="C30" s="75">
-        <f>'Revenue Drivers'!F45</f>
+        <f>'Revenue Drivers'!C45</f>
         <v/>
       </c>
       <c r="D30" s="75">
-        <f>'Revenue Drivers'!G45</f>
+        <f>'Revenue Drivers'!D45</f>
         <v/>
       </c>
       <c r="E30" s="75">
-        <f>'Revenue Drivers'!H45</f>
+        <f>'Revenue Drivers'!E45</f>
         <v/>
       </c>
       <c r="F30" s="75">
-        <f>'Revenue Drivers'!I45</f>
+        <f>'Revenue Drivers'!C45</f>
         <v/>
       </c>
       <c r="G30" s="75">
-        <f>'Revenue Drivers'!J45</f>
+        <f>'Revenue Drivers'!D45</f>
         <v/>
       </c>
     </row>
@@ -10477,23 +10477,23 @@
         <v>11102600</v>
       </c>
       <c r="C6" s="75">
-        <f>B6*(1+C5)</f>
+        <f>Scenarios!D25</f>
         <v/>
       </c>
       <c r="D6" s="75">
-        <f>C6*(1+D5)</f>
+        <f>Scenarios!D26</f>
         <v/>
       </c>
       <c r="E6" s="75">
-        <f>D6*(1+E5)</f>
+        <f>Scenarios!D27</f>
         <v/>
       </c>
       <c r="F6" s="75">
-        <f>E6*(1+F5)</f>
+        <f>Scenarios!D28</f>
         <v/>
       </c>
       <c r="G6" s="75">
-        <f>F6*(1+G5)</f>
+        <f>Scenarios!D29</f>
         <v/>
       </c>
     </row>
@@ -10537,23 +10537,23 @@
         <v>4818468</v>
       </c>
       <c r="C8" s="75">
-        <f>C6*(1-C7)</f>
+        <f>Scenarios!D35</f>
         <v/>
       </c>
       <c r="D8" s="75">
-        <f>D6*(1-D7)</f>
+        <f>Scenarios!D36</f>
         <v/>
       </c>
       <c r="E8" s="75">
-        <f>E6*(1-E7)</f>
+        <f>Scenarios!D37</f>
         <v/>
       </c>
       <c r="F8" s="75">
-        <f>F6*(1-F7)</f>
+        <f>Scenarios!D38</f>
         <v/>
       </c>
       <c r="G8" s="75">
-        <f>G6*(1-G7)</f>
+        <f>Scenarios!D39</f>
         <v/>
       </c>
     </row>
@@ -10565,23 +10565,23 @@
       </c>
       <c r="B9" s="176" t="n"/>
       <c r="C9" s="32">
-        <f>Scenarios!$D$6</f>
+        <f>Scenarios!D40</f>
         <v/>
       </c>
       <c r="D9" s="32">
-        <f>C9+(Scenarios!$D$8-Scenarios!$D$6)/4</f>
+        <f>Scenarios!D41</f>
         <v/>
       </c>
       <c r="E9" s="32">
-        <f>D9+(Scenarios!$D$8-Scenarios!$D$6)/4</f>
+        <f>Scenarios!D42</f>
         <v/>
       </c>
       <c r="F9" s="32">
-        <f>E9+(Scenarios!$D$8-Scenarios!$D$6)/4</f>
+        <f>Scenarios!D43</f>
         <v/>
       </c>
       <c r="G9" s="32">
-        <f>F9+(Scenarios!$D$8-Scenarios!$D$6)/4</f>
+        <f>Scenarios!D44</f>
         <v/>
       </c>
     </row>
@@ -10621,23 +10621,23 @@
         <v>2210615</v>
       </c>
       <c r="C11" s="130">
-        <f>C6*C9+C10</f>
+        <f>Scenarios!D45</f>
         <v/>
       </c>
       <c r="D11" s="130">
-        <f>D6*D9</f>
+        <f>Scenarios!D46</f>
         <v/>
       </c>
       <c r="E11" s="130">
-        <f>E6*E9</f>
+        <f>Scenarios!D47</f>
         <v/>
       </c>
       <c r="F11" s="130">
-        <f>F6*F9</f>
+        <f>Scenarios!D48</f>
         <v/>
       </c>
       <c r="G11" s="130">
-        <f>G6*G9</f>
+        <f>Scenarios!D49</f>
         <v/>
       </c>
     </row>
@@ -10707,23 +10707,23 @@
       </c>
       <c r="B14" s="176" t="n"/>
       <c r="C14" s="130">
-        <f>'NOPAT Bridge'!C41</f>
+        <f>Scenarios!D50</f>
         <v/>
       </c>
       <c r="D14" s="130">
-        <f>'NOPAT Bridge'!D41</f>
+        <f>Scenarios!D51</f>
         <v/>
       </c>
       <c r="E14" s="130">
-        <f>'NOPAT Bridge'!E41</f>
+        <f>Scenarios!D52</f>
         <v/>
       </c>
       <c r="F14" s="130">
-        <f>'NOPAT Bridge'!F41</f>
+        <f>Scenarios!D53</f>
         <v/>
       </c>
       <c r="G14" s="130">
-        <f>'NOPAT Bridge'!G41</f>
+        <f>Scenarios!D54</f>
         <v/>
       </c>
     </row>
@@ -10773,23 +10773,23 @@
       </c>
       <c r="B17" s="176" t="n"/>
       <c r="C17" s="75">
-        <f>C6*Scenarios!$D$12</f>
+        <f>Scenarios!D55</f>
         <v/>
       </c>
       <c r="D17" s="75">
-        <f>D6*Scenarios!$D$12</f>
+        <f>Scenarios!D56</f>
         <v/>
       </c>
       <c r="E17" s="75">
-        <f>E6*Scenarios!$D$12</f>
+        <f>Scenarios!D57</f>
         <v/>
       </c>
       <c r="F17" s="75">
-        <f>F6*Scenarios!$D$12</f>
+        <f>Scenarios!D58</f>
         <v/>
       </c>
       <c r="G17" s="75">
-        <f>G6*Scenarios!$D$12</f>
+        <f>Scenarios!D59</f>
         <v/>
       </c>
     </row>
@@ -10829,23 +10829,23 @@
       </c>
       <c r="B19" s="176" t="n"/>
       <c r="C19" s="75">
-        <f>-Scenarios!D60</f>
+        <f>Scenarios!D60</f>
         <v/>
       </c>
       <c r="D19" s="75">
-        <f>-Scenarios!D61</f>
+        <f>Scenarios!D61</f>
         <v/>
       </c>
       <c r="E19" s="75">
-        <f>-Scenarios!D62</f>
+        <f>Scenarios!D62</f>
         <v/>
       </c>
       <c r="F19" s="75">
-        <f>-Scenarios!D63</f>
+        <f>Scenarios!D63</f>
         <v/>
       </c>
       <c r="G19" s="75">
-        <f>-Scenarios!D64</f>
+        <f>Scenarios!D64</f>
         <v/>
       </c>
     </row>
@@ -11344,23 +11344,23 @@
       </c>
       <c r="B38" s="176" t="n"/>
       <c r="C38" s="91">
-        <f>1/(1+Scenarios!$D$9)^C37</f>
+        <f>1/(1+WACC!B36)^C37</f>
         <v/>
       </c>
       <c r="D38" s="91">
-        <f>1/(1+Scenarios!$D$9)^D37</f>
+        <f>1/(1+WACC!B36)^D37</f>
         <v/>
       </c>
       <c r="E38" s="91">
-        <f>1/(1+Scenarios!$D$9)^E37</f>
+        <f>1/(1+WACC!B36)^E37</f>
         <v/>
       </c>
       <c r="F38" s="91">
-        <f>1/(1+Scenarios!$D$9)^F37</f>
+        <f>1/(1+WACC!B36)^F37</f>
         <v/>
       </c>
       <c r="G38" s="91">
-        <f>1/(1+Scenarios!$D$9)^G37</f>
+        <f>1/(1+WACC!B36)^G37</f>
         <v/>
       </c>
     </row>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="B44" s="32">
-        <f>Scenarios!$D$10</f>
+        <f>Scenarios!D10</f>
         <v/>
       </c>
       <c r="C44" s="176" t="n"/>
@@ -11482,7 +11482,7 @@
         </is>
       </c>
       <c r="B46" s="75">
-        <f>G36*(1+Scenarios!$D$10)/(Scenarios!$D$9-Scenarios!$D$10)</f>
+        <f>G36*(1+Scenarios!D10)/(WACC!B36-Scenarios!D10)</f>
         <v/>
       </c>
       <c r="C46" s="176" t="n"/>
@@ -11514,7 +11514,7 @@
         </is>
       </c>
       <c r="B48" s="94">
-        <f>G36/B45*(1+Scenarios!$D$10)/(Scenarios!$D$9-Scenarios!$D$10)</f>
+        <f>G36/B45*(1+Scenarios!D10)/(WACC!B36-Scenarios!D10)</f>
         <v/>
       </c>
       <c r="C48" s="176" t="n"/>
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="B49" s="75">
-        <f>B46/(1+Scenarios!$D$9)^G37</f>
+        <f>B46/(1+WACC!B36)^G37</f>
         <v/>
       </c>
       <c r="C49" s="176" t="n"/>
@@ -11760,23 +11760,23 @@
         <v>500000</v>
       </c>
       <c r="C66" s="75">
-        <f>$B$65</f>
+        <f>$B$66</f>
         <v/>
       </c>
       <c r="D66" s="75">
-        <f>$B$65</f>
+        <f>$B$66</f>
         <v/>
       </c>
       <c r="E66" s="75">
-        <f>$B$65</f>
+        <f>$B$66</f>
         <v/>
       </c>
       <c r="F66" s="75">
-        <f>$B$65</f>
+        <f>$B$66</f>
         <v/>
       </c>
       <c r="G66" s="75">
-        <f>$B$65</f>
+        <f>$B$66</f>
         <v/>
       </c>
     </row>
@@ -11790,23 +11790,23 @@
         <v>0.105</v>
       </c>
       <c r="C67" s="32">
-        <f>$B$66</f>
+        <f>$B$67</f>
         <v/>
       </c>
       <c r="D67" s="32">
-        <f>$B$66</f>
+        <f>$B$67</f>
         <v/>
       </c>
       <c r="E67" s="32">
-        <f>$B$66</f>
+        <f>$B$67</f>
         <v/>
       </c>
       <c r="F67" s="32">
-        <f>$B$66</f>
+        <f>$B$67</f>
         <v/>
       </c>
       <c r="G67" s="32">
-        <f>$B$66</f>
+        <f>$B$67</f>
         <v/>
       </c>
     </row>
@@ -11827,19 +11827,19 @@
       </c>
       <c r="B69" s="176" t="n"/>
       <c r="C69" s="75">
-        <f>C35</f>
+        <f>C36</f>
         <v/>
       </c>
       <c r="D69" s="75">
-        <f>D35</f>
+        <f>D36</f>
         <v/>
       </c>
       <c r="E69" s="75">
-        <f>E35</f>
+        <f>E36</f>
         <v/>
       </c>
       <c r="F69" s="75">
-        <f>F35</f>
+        <f>F36</f>
         <v/>
       </c>
       <c r="G69" s="75">
@@ -11857,23 +11857,23 @@
         <v>0</v>
       </c>
       <c r="C70" s="75">
-        <f>C65</f>
+        <f>C66</f>
         <v/>
       </c>
       <c r="D70" s="75">
-        <f>D65</f>
+        <f>D66</f>
         <v/>
       </c>
       <c r="E70" s="75">
-        <f>E65</f>
+        <f>E66</f>
         <v/>
       </c>
       <c r="F70" s="75">
-        <f>F65</f>
+        <f>F66</f>
         <v/>
       </c>
       <c r="G70" s="75">
-        <f>G65</f>
+        <f>G66</f>
         <v/>
       </c>
     </row>
@@ -11885,23 +11885,23 @@
       </c>
       <c r="B71" s="176" t="n"/>
       <c r="C71" s="32">
-        <f>C69/C68</f>
+        <f>C70/C69</f>
         <v/>
       </c>
       <c r="D71" s="32">
-        <f>D69/D68</f>
+        <f>D70/D69</f>
         <v/>
       </c>
       <c r="E71" s="32">
-        <f>E69/E68</f>
+        <f>E70/E69</f>
         <v/>
       </c>
       <c r="F71" s="32">
-        <f>F69/F68</f>
+        <f>F70/F69</f>
         <v/>
       </c>
       <c r="G71" s="32">
-        <f>G69/G68</f>
+        <f>G70/G69</f>
         <v/>
       </c>
     </row>
@@ -11924,23 +11924,23 @@
         <v>100</v>
       </c>
       <c r="C73" s="99">
-        <f>B72*(1+$B$66)</f>
+        <f>B73*(1+$B$67)</f>
         <v/>
       </c>
       <c r="D73" s="99">
-        <f>C72*(1+$B$66)</f>
+        <f>B73*(1+$B$67)</f>
         <v/>
       </c>
       <c r="E73" s="99">
-        <f>D72*(1+$B$66)</f>
+        <f>D73*(1+$B$67)</f>
         <v/>
       </c>
       <c r="F73" s="99">
-        <f>E72*(1+$B$66)</f>
+        <f>E73*(1+$B$67)</f>
         <v/>
       </c>
       <c r="G73" s="99">
-        <f>F72*(1+$B$66)</f>
+        <f>F73*(1+$B$67)</f>
         <v/>
       </c>
     </row>
@@ -11954,23 +11954,23 @@
         <v>0</v>
       </c>
       <c r="C74" s="75">
-        <f>C69/C72</f>
+        <f>C70/C73</f>
         <v/>
       </c>
       <c r="D74" s="75">
-        <f>D69/D72</f>
+        <f>D70/D73</f>
         <v/>
       </c>
       <c r="E74" s="75">
-        <f>E69/E72</f>
+        <f>E70/E73</f>
         <v/>
       </c>
       <c r="F74" s="75">
-        <f>F69/F72</f>
+        <f>F70/F73</f>
         <v/>
       </c>
       <c r="G74" s="75">
-        <f>G69/G72</f>
+        <f>G70/G73</f>
         <v/>
       </c>
     </row>
@@ -11984,23 +11984,23 @@
         <v>111380</v>
       </c>
       <c r="C75" s="75">
-        <f>$B$74</f>
+        <f>$B$75</f>
         <v/>
       </c>
       <c r="D75" s="75">
-        <f>C75</f>
+        <f>C76</f>
         <v/>
       </c>
       <c r="E75" s="75">
-        <f>D75</f>
+        <f>D76</f>
         <v/>
       </c>
       <c r="F75" s="75">
-        <f>E75</f>
+        <f>E76</f>
         <v/>
       </c>
       <c r="G75" s="75">
-        <f>F75</f>
+        <f>F76</f>
         <v/>
       </c>
     </row>
@@ -12014,23 +12014,23 @@
         <v>111380</v>
       </c>
       <c r="C76" s="130">
-        <f>C74-C73</f>
+        <f>C75-C74</f>
         <v/>
       </c>
       <c r="D76" s="130">
-        <f>D74-D73</f>
+        <f>D75-D74</f>
         <v/>
       </c>
       <c r="E76" s="130">
-        <f>E74-E73</f>
+        <f>E75-E74</f>
         <v/>
       </c>
       <c r="F76" s="130">
-        <f>F74-F73</f>
+        <f>F75-F74</f>
         <v/>
       </c>
       <c r="G76" s="130">
-        <f>G74-G73</f>
+        <f>G75-G74</f>
         <v/>
       </c>
     </row>
@@ -12083,23 +12083,23 @@
         <v>14.1783354282636</v>
       </c>
       <c r="C79" s="150">
-        <f>C77/C75</f>
+        <f>C78/C76</f>
         <v/>
       </c>
       <c r="D79" s="150">
-        <f>D77/D75</f>
+        <f>D78/D76</f>
         <v/>
       </c>
       <c r="E79" s="150">
-        <f>E77/E75</f>
+        <f>E78/E76</f>
         <v/>
       </c>
       <c r="F79" s="150">
-        <f>F77/F75</f>
+        <f>F78/F76</f>
         <v/>
       </c>
       <c r="G79" s="150">
-        <f>G77/G75</f>
+        <f>G78/G76</f>
         <v/>
       </c>
     </row>
@@ -12176,7 +12176,7 @@
         </is>
       </c>
       <c r="B85" s="75">
-        <f>B83/(1+Scenarios!$D$9)^G37</f>
+        <f>B83/(1+WACC!B36)^G37</f>
         <v/>
       </c>
       <c r="C85" s="176" t="n"/>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -1164,43 +1164,32 @@
   <commentList>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
-        <t>4.8% risk-free = FRED DGS10 on 2026-09-03 (4.77%).
-Source: FRED: 10Y Treasury (DGS10)
-https://fred.stlouisfed.org/series/DGS10</t>
+        <t>FRED DGS10 anchor (4.8%).</t>
       </text>
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>6.0% ERP is a conservative overlay vs Damodaran.
-Source: Damodaran: Historical Implied ERP
-https://www.stern.nyu.edu/~adamodar/New_Home_Page/datafile/histimpl.html</t>
+        <t>Damodaran US ERP (Jan-26).</t>
       </text>
     </comment>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
-        <t>30% cash tax matches FY2026 guidance (“approximately 30%”)..
-Source: Q2 FY2026 outlook: tax rate ≈ 30%
-https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
+        <t>FY26 mgmt guidance (~30%).</t>
       </text>
     </comment>
     <comment ref="B8" authorId="0" shapeId="0">
       <text>
-        <t>$100 share price ≈ NASDAQ Last Sale after.
-Source: NASDAQ LULU last sale (current price)
-https://www.nasdaq.com/market-activity/stocks/lulu</t>
+        <t>NASDAQ last sale (~$100).</t>
       </text>
     </comment>
     <comment ref="B9" authorId="0" shapeId="0">
       <text>
-        <t>111,380k class A shares outstanding at FY25 year-end.
-Source: LULU FY2025 10-K: shares outstanding
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 10-K share count.</t>
       </text>
     </comment>
     <comment ref="B10" authorId="0" shapeId="0">
       <text>
-        <t>Market equity = share price × shares outstanding..
-Source: WACC tab: price × shares</t>
+        <t>Price × shares outstanding.</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0" shapeId="0">
@@ -1222,6 +1211,11 @@
         <t>Source: Lease + funded debt (above)</t>
       </text>
     </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>Yahoo βL (5Y monthly).</t>
+      </text>
+    </comment>
     <comment ref="B17" authorId="0" shapeId="0">
       <text>
         <t>Yahoo Total Debt (mrq) = $2.14B on the.
@@ -1245,15 +1239,12 @@
     </comment>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>Yahoo Total Debt/Equity (mrq) = 44.69% is book.
-Source: Yahoo Finance: Total Debt/Equity (mrq)
-https://finance.yahoo.com/quote/LULU/key-statistics/</t>
+        <t>Yahoo book D/E reference.</t>
       </text>
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
-        <t>Hamada unlever beta using Yahoo market D/E and tax rate.
-Source: WACC tab: Hamada unlever (Yahoo market D/E)</t>
+        <t>Hamada unlever (Yahoo D/E).</t>
       </text>
     </comment>
     <comment ref="B22" authorId="0" shapeId="0">
@@ -1280,11 +1271,14 @@
         <t>Source: CAPM: rf + β × ERP</t>
       </text>
     </comment>
+    <comment ref="B29" authorId="0" shapeId="0">
+      <text>
+        <t>Lease-equivalent borrowing cost.</t>
+      </text>
+    </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>Lease-equivalent kd
-Source: LULU FY2025 10-K: lease liabilities &amp; no funded debt
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Lease-equivalent borrowing cost.</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
@@ -1299,15 +1293,12 @@
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>Equity weight = market cap ÷ (market cap.
-Source: WACC tab: capital structure</t>
+        <t>Mkt cap / total capital.</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>Debt weight = lease liabilities ÷ (market cap.
-Source: LULU FY2025 10-K: operating lease liabilities
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Lease debt / total capital.</t>
       </text>
     </comment>
     <comment ref="B36" authorId="0" shapeId="0">
@@ -1327,23 +1318,17 @@
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
-        <t>Q2 FY26 rev guide
-Source: LULU Q2 FY2026 earnings release
-https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
+        <t>Q2 FY26 mgmt guidance midpoint.</t>
       </text>
     </comment>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
-        <t>2.3% FY27–30 growth matches StockAnalysis Revenue Growth Forecast.
-Source: StockAnalysis: LULU 3Y revenue forecast
-https://stockanalysis.com/stocks/lulu/statistics/</t>
+        <t>Q2 FY26 mgmt guidance midpoint.</t>
       </text>
     </comment>
     <comment ref="B6" authorId="0" shapeId="0">
       <text>
-        <t>Q2 FY26 run-rate OM
-Source: Q2 FY2026 release: 18.8% OM minus 560bps tariffs
-https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
+        <t>Q2 FY26 run-rate OM (ex-tariff).</t>
       </text>
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
@@ -1355,50 +1340,37 @@
     </comment>
     <comment ref="B8" authorId="0" shapeId="0">
       <text>
-        <t>Partial OM recovery
-Source: FY2025 10-K: Operating margin 19.9% (one hit)
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Partial recovery vs FY25 OM.</t>
       </text>
     </comment>
     <comment ref="B9" authorId="0" shapeId="0">
       <text>
-        <t>Links to WACC tab
-Source: WACC tab: CAPM build</t>
+        <t>Lease-adjusted CAPM (WACC tab).</t>
       </text>
     </comment>
     <comment ref="B10" authorId="0" shapeId="0">
       <text>
-        <t>FRED GDPC1 ~2.1%
-Source: FRED: Real GDP (GDPC1)
-https://fred.stlouisfed.org/series/GDPC1</t>
+        <t>FRED GDPC1 anchor (~2.1%).</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0" shapeId="0">
       <text>
-        <t>Q2 FY26 guide ~30%
-Source: Q2 FY2026 outlook: tax rate ≈ 30%
-https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
+        <t>FY26 mgmt guidance (~30%).</t>
       </text>
     </comment>
     <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>FY25 D&amp;A / sales
-Source: LULU CF statement (10-K)
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 D&amp;A run-rate vs sales.</t>
       </text>
     </comment>
     <comment ref="B13" authorId="0" shapeId="0">
       <text>
-        <t>5.5% model rate; FY26 7% capex guide fades down.
-Source: LULU 10-K: 2026 capex guide $725–745M Also: Q2 FY2026 outlook: $10.350B–$10.500B sales
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>5.5% model rate; FY26 7% capex guide fades down.</t>
       </text>
     </comment>
     <comment ref="B14" authorId="0" shapeId="0">
       <text>
-        <t>Flat vs FY25
-Source: LULU FY2025 10-K: Gross profit &amp; COGS
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Held flat vs FY25 actuals.</t>
       </text>
     </comment>
     <comment ref="B15" authorId="0" shapeId="0">
@@ -1408,11 +1380,14 @@
 https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
       </text>
     </comment>
+    <comment ref="B16" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 anchor minus 1 day/yr.</t>
+      </text>
+    </comment>
     <comment ref="B17" authorId="0" shapeId="0">
       <text>
-        <t>−1 day / yr
-Source: LULU FY2025 10-K: inventory &amp; markdown outlook
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Minus 1 day per forecast yr.</t>
       </text>
     </comment>
     <comment ref="B18" authorId="0" shapeId="0">
@@ -1424,16 +1399,57 @@
     </comment>
     <comment ref="B19" authorId="0" shapeId="0">
       <text>
-        <t>FY25 prepaids % rev
-Source: LULU FY2025 10-K: other current assets (residual)
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 OCA % of revenue.</t>
       </text>
     </comment>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>FY25 accrued % rev
-Source: LULU FY2025 10-K: Accrued liabilities and other
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>FY25 accrued % of revenue.</t>
+      </text>
+    </comment>
+    <comment ref="B100" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 accrued % of revenue.</t>
+      </text>
+    </comment>
+    <comment ref="B101" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 accrued % of revenue.</t>
+      </text>
+    </comment>
+    <comment ref="B102" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 accrued % of revenue.</t>
+      </text>
+    </comment>
+    <comment ref="B103" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 accrued % of revenue.</t>
+      </text>
+    </comment>
+    <comment ref="B104" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 accrued % of revenue.</t>
+      </text>
+    </comment>
+    <comment ref="B194" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 10-K total assets.</t>
+      </text>
+    </comment>
+    <comment ref="B195" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 10-K total liabilities.</t>
+      </text>
+    </comment>
+    <comment ref="B196" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 10-K total equity.</t>
+      </text>
+    </comment>
+    <comment ref="B197" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 10-K diluted share count.</t>
       </text>
     </comment>
   </commentList>
@@ -1448,174 +1464,142 @@
   <commentList>
     <comment ref="B9" authorId="0" shapeId="0">
       <text>
-        <t>Not % of consolidated revenue; EBIT as %.
-Source: FY2025 10-K: company-operated stores net revenue
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Store EBIT % of store rev.</t>
       </text>
     </comment>
     <comment ref="B10" authorId="0" shapeId="0">
       <text>
-        <t>Not % of consolidated revenue; EBIT as %.
-Source: FY2025 10-K: e-commerce net revenue
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>E-comm EBIT % of e-comm rev.</t>
       </text>
     </comment>
     <comment ref="B11" authorId="0" shapeId="0">
       <text>
-        <t>Not % of consolidated revenue; EBIT as %.
-Source: FY2025 10-K: other channels (residual)
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Other EBIT % of other rev.</t>
       </text>
     </comment>
     <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>30% statutory marginal rate. t_operating transitions here over.
-Source: Q2 FY2026 outlook: tax rate ≈ 30%
-https://corporate.lululemon.com/newsroom/press-releases/2026/09-03-2026-210528733</t>
+        <t>Statutory marginal rate (30%).</t>
       </text>
     </comment>
     <comment ref="B13" authorId="0" shapeId="0">
       <text>
-        <t>Not % of revenue; amortization period (years) if.
-Source: NOPAT Bridge: capitalization convention</t>
+        <t>R&amp;D capitalization period (yrs).</t>
       </text>
     </comment>
     <comment ref="B16" authorId="0" shapeId="0">
       <text>
-        <t>FY25: reported operating income from 10-K. Forecast: Scenarios.
-Source: LULU FY2025 10-K: Income from operations
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>10-K EBIT / Scenarios forecast.</t>
       </text>
     </comment>
     <comment ref="B17" authorId="0" shapeId="0">
       <text>
-        <t>Add back intangible amortization / impairments. FY25 =.
-Source: LULU FY2025 10-K: amortization of intangible assets
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Run-rate intangible amort add-back.</t>
       </text>
     </comment>
     <comment ref="B18" authorId="0" shapeId="0">
       <text>
-        <t>Add back restructuring (severance, store closures). LULU FY25:.
-Source: LULU FY2025 10-K: restructuring charges
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Non-recurring restructuring add-back.</t>
       </text>
     </comment>
     <comment ref="B19" authorId="0" shapeId="0">
       <text>
-        <t>Strip one-off legal / M&amp;A advisory fees. LULU.
-Source: LULU FY2025 10-K: SG&amp;A one-offs
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>One-off legal / M&amp;A strip.</t>
       </text>
     </comment>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>Not % of revenue; SBC add-back flag. Set.
-Source: LULU CF statement (10-K): stock-based compensation
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>SBC add-back (if flag = 1).</t>
       </text>
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
-        <t>Reported EBIT plus all listed non-recurring add-backs above.
-Source: NOPAT Bridge tab: Phase 1 subtotal</t>
+        <t>Reported EBIT plus non-recurring add-backs (10-K).</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="0" shapeId="0">
+      <text>
+        <t>Lease interest and R&amp;D capitalization adjustments.</t>
       </text>
     </comment>
     <comment ref="B23" authorId="0" shapeId="0">
       <text>
-        <t>Not % of revenue; implied lease interest ($1,028k.
-Source: LULU FY2025 10-K: interest on lease liabilities (supplemental)
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Lease interest reclass (memo).</t>
       </text>
     </comment>
     <comment ref="B24" authorId="0" shapeId="0">
       <text>
-        <t>Capitalize multi-year software/R&amp;D. LULU: immaterial separate R&amp;D line;.
-Source: LULU FY2025 10-K: R&amp;D / software expense
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>R&amp;D cap immaterial this yr.</t>
       </text>
     </comment>
     <comment ref="B25" authorId="0" shapeId="0">
       <text>
-        <t>Amortization of prior capitalized intangibles. LULU: flows through.
-Source: LULU FY2025 10-K: intangible amortization
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Prior capitalized intangible amort.</t>
       </text>
     </comment>
     <comment ref="B26" authorId="0" shapeId="0">
       <text>
-        <t>Reported EBIT plus lease interest and R&amp;D adjustments.
-Source: NOPAT Bridge tab: Phase 2 subtotal</t>
+        <t>Lease interest and R&amp;D capitalization adjustments.</t>
       </text>
     </comment>
     <comment ref="B28" authorId="0" shapeId="0">
       <text>
-        <t>Not % of revenue; store-channel revenue from Revenue.
-Source: Revenue Drivers tab: store-channel revenue</t>
+        <t>Store rev from Revenue Drivers.</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>Not % of revenue; e-commerce revenue from Revenue.
-Source: Revenue Drivers tab: e-commerce revenue</t>
+        <t>E-comm rev from Revenue Drivers.</t>
       </text>
     </comment>
     <comment ref="B30" authorId="0" shapeId="0">
       <text>
-        <t>Not % of revenue; wholesale/license/outlet revenue from Revenue.
-Source: Revenue Drivers tab: other channels revenue</t>
+        <t>Other rev from Revenue Drivers.</t>
       </text>
     </comment>
     <comment ref="B31" authorId="0" shapeId="0">
       <text>
-        <t>Not % of consolidated revenue; store EBIT ÷.
-Source: FY2025 10-K: company-operated stores net revenue
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Store EBIT ÷ store rev only.</t>
       </text>
     </comment>
     <comment ref="B32" authorId="0" shapeId="0">
       <text>
-        <t>Not % of consolidated revenue; e-commerce EBIT ÷.
-Source: FY2025 10-K: e-commerce net revenue
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>E-comm EBIT ÷ e-comm rev only.</t>
       </text>
     </comment>
     <comment ref="B33" authorId="0" shapeId="0">
       <text>
-        <t>Not % of consolidated revenue; other-channel EBIT ÷.
-Source: FY2025 10-K: other channels (residual)
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Other EBIT % of other rev.</t>
       </text>
     </comment>
     <comment ref="B34" authorId="0" shapeId="0">
       <text>
-        <t>Sum of store, e-comm, and other channel EBIT lines.
-Source: NOPAT Bridge tab: sector EBIT subtotal</t>
+        <t>Sum of sector EBIT ().</t>
       </text>
     </comment>
     <comment ref="B35" authorId="0" shapeId="0">
       <text>
-        <t>Channel-mix EBIT output line before tax normalization step.
-Source: NOPAT Bridge tab: Phase 3 subtotal</t>
+        <t>Channel-mix EBIT output ().</t>
       </text>
     </comment>
     <comment ref="B36" authorId="0" shapeId="0">
       <text>
-        <t>FY25: Phases 1–2 walk-through (SBC not added back;.
-Source: Scenarios tab: base-case EBIT (forecast)</t>
+        <t>FY25 walk-through Phases 1–2.</t>
       </text>
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>Operating effective tax rate: (tax + interest shield).
-Source: LULU FY2025 10-K: income tax &amp; interest expense
-https://www.sec.gov/Archives/edgar/data/1397187/000139718726000020/lulu-20260201.htm</t>
+        <t>Operating ETR with interest shield.</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>Normalized EBIT × t_operating.
-Source: NOPAT Bridge tab: unlevered tax expense</t>
+        <t>Normalized EBIT × t_operating.</t>
+      </text>
+    </comment>
+    <comment ref="B41" authorId="0" shapeId="0">
+      <text>
+        <t>EBIT_norm × (1 − t_operating).</t>
       </text>
     </comment>
     <comment ref="B45" authorId="0" shapeId="0">
@@ -1979,74 +1963,62 @@
     </comment>
     <comment ref="B18" authorId="0" shapeId="0">
       <text>
-        <t>Justification
-Source: Source</t>
+        <t>Source: Source</t>
       </text>
     </comment>
     <comment ref="B19" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B21" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B22" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B23" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B24" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B25" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B26" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B27" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B28" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B29" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook Comps Set 04-Sep-2026. Multiple = daily EV.
-Source: PitchBook Comps Set 04-Sep-2026</t>
+        <t>PitchBook EV/TTM EBITDA comp.</t>
       </text>
     </comment>
     <comment ref="B33" authorId="0" shapeId="0">
@@ -2077,40 +2049,34 @@
     </comment>
     <comment ref="B39" authorId="0" shapeId="0">
       <text>
-        <t>PitchBook core set, UAA out. Current tape —.
-Source: Derived: Excel AVERAGE of the seven core prints</t>
+        <t>PitchBook core set ex-UAA.</t>
       </text>
     </comment>
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
-        <t>Wider PitchBook tape. WSM/MOV/LZB are adjacent retail, not.
-Source: Derived: Excel AVERAGE of every positive-EBITDA row</t>
+        <t>Wider tape incl. adjacent retail.</t>
       </text>
     </comment>
     <comment ref="B56" authorId="0" shapeId="0">
       <text>
-        <t>Justification
-Source: Source</t>
+        <t>Source: Source</t>
       </text>
     </comment>
     <comment ref="B57" authorId="0" shapeId="0">
       <text>
-        <t>Lo: 5.0x on FY2030E EBITDA ≈ LULU current.
-Source: Lo: StockAnalysis: LULU EV/EBITDA Hi: StockAnalysis: DECK EV/EBITDA
-https://stockanalysis.com/stocks/lulu/statistics/</t>
+        <t>Lo 5.0x FY30E EBITDA trough.
+Hi 8.0x DECK high-end cap.</t>
       </text>
     </comment>
     <comment ref="B58" authorId="0" shapeId="0">
       <text>
-        <t>Selected exit is Gordon TV / FY30 EBITDA..
-Source: DCF: Gordon implied exit (TV / FY30 EBITDA)</t>
+        <t>Gordon TV / FY30 EBITDA exit.</t>
       </text>
     </comment>
     <comment ref="B59" authorId="0" shapeId="0">
       <text>
-        <t>Lo: 10x P/E low on FY2026E EPS; trough.
-Source: Lo: StockAnalysis: LULU Forward P/E Hi: StockAnalysis: NKE Forward P/E
-https://stockanalysis.com/stocks/lulu/statistics/</t>
+        <t>Lo 10x FY26E EPS trough.
+Hi 18x FY26E EPS recovery.</t>
       </text>
     </comment>
     <comment ref="B62" authorId="0" shapeId="0">
@@ -2923,7 +2889,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3146,8 +3112,9 @@
       <c r="C12" s="32" t="n">
         <v>0.045</v>
       </c>
-      <c r="D12" s="32" t="n">
-        <v>0.045</v>
+      <c r="D12" s="32">
+        <f>DCF!B15/DCF!$B$6</f>
+        <v/>
       </c>
       <c r="E12" s="32" t="n">
         <v>0.045</v>
@@ -3184,8 +3151,9 @@
       <c r="C14" s="32" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="D14" s="32" t="n">
-        <v>0.5659999999999999</v>
+      <c r="D14" s="32">
+        <f>(DCF!B6-DCF!B8)/DCF!B6</f>
+        <v/>
       </c>
       <c r="E14" s="32" t="n">
         <v>0.575</v>
@@ -3375,15 +3343,15 @@
       </c>
       <c r="B25" s="176" t="n"/>
       <c r="C25" s="75">
-        <f>11102600*(1+C4)</f>
+        <f>DCF!$B$6*(1+C4)</f>
         <v/>
       </c>
       <c r="D25" s="75">
-        <f>11102600*(1+D4)</f>
+        <f>DCF!$B$6*(1+D4)</f>
         <v/>
       </c>
       <c r="E25" s="75">
-        <f>11102600*(1+E4)</f>
+        <f>DCF!$B$6*(1+E4)</f>
         <v/>
       </c>
       <c r="F25" s="176" t="n"/>
@@ -5782,7 +5750,7 @@
     <row r="137">
       <c r="A137" s="127" t="inlineStr">
         <is>
-          <t>Pitch deck bridge (IS / CFS / BS)</t>
+          <t>Financial statement bridge (IS / CFS / BS)</t>
         </is>
       </c>
       <c r="B137" s="176" t="n"/>
@@ -6445,15 +6413,15 @@
       </c>
       <c r="B168" s="176" t="n"/>
       <c r="C168" s="75">
-        <f>8456743*C25/11102600</f>
+        <f>$B$194*C25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D168" s="75">
-        <f>8456743*D25/11102600</f>
+        <f>$B$194*D25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E168" s="75">
-        <f>8456743*E25/11102600</f>
+        <f>$B$194*E25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F168" s="176" t="n"/>
@@ -6467,15 +6435,15 @@
       </c>
       <c r="B169" s="176" t="n"/>
       <c r="C169" s="75">
-        <f>8456743*C26/11102600</f>
+        <f>$B$194*C26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D169" s="75">
-        <f>8456743*D26/11102600</f>
+        <f>$B$194*D26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E169" s="75">
-        <f>8456743*E26/11102600</f>
+        <f>$B$194*E26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F169" s="176" t="n"/>
@@ -6489,15 +6457,15 @@
       </c>
       <c r="B170" s="176" t="n"/>
       <c r="C170" s="75">
-        <f>8456743*C27/11102600</f>
+        <f>$B$194*C27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D170" s="75">
-        <f>8456743*D27/11102600</f>
+        <f>$B$194*D27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E170" s="75">
-        <f>8456743*E27/11102600</f>
+        <f>$B$194*E27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F170" s="176" t="n"/>
@@ -6511,15 +6479,15 @@
       </c>
       <c r="B171" s="176" t="n"/>
       <c r="C171" s="75">
-        <f>8456743*C28/11102600</f>
+        <f>$B$194*C28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D171" s="75">
-        <f>8456743*D28/11102600</f>
+        <f>$B$194*D28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E171" s="75">
-        <f>8456743*E28/11102600</f>
+        <f>$B$194*E28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F171" s="176" t="n"/>
@@ -6533,15 +6501,15 @@
       </c>
       <c r="B172" s="176" t="n"/>
       <c r="C172" s="75">
-        <f>8456743*C29/11102600</f>
+        <f>$B$194*C29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D172" s="75">
-        <f>8456743*D29/11102600</f>
+        <f>$B$194*D29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E172" s="75">
-        <f>8456743*E29/11102600</f>
+        <f>$B$194*E29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F172" s="176" t="n"/>
@@ -6555,15 +6523,15 @@
       </c>
       <c r="B173" s="176" t="n"/>
       <c r="C173" s="75">
-        <f>3494903*C25/11102600</f>
+        <f>$B$195*C25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D173" s="75">
-        <f>3494903*D25/11102600</f>
+        <f>$B$195*D25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E173" s="75">
-        <f>3494903*E25/11102600</f>
+        <f>$B$195*E25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F173" s="176" t="n"/>
@@ -6577,15 +6545,15 @@
       </c>
       <c r="B174" s="176" t="n"/>
       <c r="C174" s="75">
-        <f>3494903*C26/11102600</f>
+        <f>$B$195*C26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D174" s="75">
-        <f>3494903*D26/11102600</f>
+        <f>$B$195*D26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E174" s="75">
-        <f>3494903*E26/11102600</f>
+        <f>$B$195*E26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F174" s="176" t="n"/>
@@ -6599,15 +6567,15 @@
       </c>
       <c r="B175" s="176" t="n"/>
       <c r="C175" s="75">
-        <f>3494903*C27/11102600</f>
+        <f>$B$195*C27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D175" s="75">
-        <f>3494903*D27/11102600</f>
+        <f>$B$195*D27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E175" s="75">
-        <f>3494903*E27/11102600</f>
+        <f>$B$195*E27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F175" s="176" t="n"/>
@@ -6621,15 +6589,15 @@
       </c>
       <c r="B176" s="176" t="n"/>
       <c r="C176" s="75">
-        <f>3494903*C28/11102600</f>
+        <f>$B$195*C28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D176" s="75">
-        <f>3494903*D28/11102600</f>
+        <f>$B$195*D28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E176" s="75">
-        <f>3494903*E28/11102600</f>
+        <f>$B$195*E28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F176" s="176" t="n"/>
@@ -6643,15 +6611,15 @@
       </c>
       <c r="B177" s="176" t="n"/>
       <c r="C177" s="75">
-        <f>3494903*C29/11102600</f>
+        <f>$B$195*C29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D177" s="75">
-        <f>3494903*D29/11102600</f>
+        <f>$B$195*D29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E177" s="75">
-        <f>3494903*E29/11102600</f>
+        <f>$B$195*E29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F177" s="176" t="n"/>
@@ -6665,15 +6633,15 @@
       </c>
       <c r="B178" s="176" t="n"/>
       <c r="C178" s="75">
-        <f>4961840*C25/11102600</f>
+        <f>$B$196*C25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D178" s="75">
-        <f>4961840*D25/11102600</f>
+        <f>$B$196*D25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E178" s="75">
-        <f>4961840*E25/11102600</f>
+        <f>$B$196*E25/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F178" s="176" t="n"/>
@@ -6687,15 +6655,15 @@
       </c>
       <c r="B179" s="176" t="n"/>
       <c r="C179" s="75">
-        <f>4961840*C26/11102600</f>
+        <f>$B$196*C26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D179" s="75">
-        <f>4961840*D26/11102600</f>
+        <f>$B$196*D26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E179" s="75">
-        <f>4961840*E26/11102600</f>
+        <f>$B$196*E26/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F179" s="176" t="n"/>
@@ -6709,15 +6677,15 @@
       </c>
       <c r="B180" s="176" t="n"/>
       <c r="C180" s="75">
-        <f>4961840*C27/11102600</f>
+        <f>$B$196*C27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D180" s="75">
-        <f>4961840*D27/11102600</f>
+        <f>$B$196*D27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E180" s="75">
-        <f>4961840*E27/11102600</f>
+        <f>$B$196*E27/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F180" s="176" t="n"/>
@@ -6731,15 +6699,15 @@
       </c>
       <c r="B181" s="176" t="n"/>
       <c r="C181" s="75">
-        <f>4961840*C28/11102600</f>
+        <f>$B$196*C28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D181" s="75">
-        <f>4961840*D28/11102600</f>
+        <f>$B$196*D28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E181" s="75">
-        <f>4961840*E28/11102600</f>
+        <f>$B$196*E28/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F181" s="176" t="n"/>
@@ -6753,15 +6721,15 @@
       </c>
       <c r="B182" s="176" t="n"/>
       <c r="C182" s="75">
-        <f>4961840*C29/11102600</f>
+        <f>$B$196*C29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="D182" s="75">
-        <f>4961840*D29/11102600</f>
+        <f>$B$196*D29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="E182" s="75">
-        <f>4961840*E29/11102600</f>
+        <f>$B$196*E29/DCF!$B$6</f>
         <v/>
       </c>
       <c r="F182" s="176" t="n"/>
@@ -6775,15 +6743,15 @@
       </c>
       <c r="B183" s="176" t="n"/>
       <c r="C183" s="75">
-        <f>119068-C21/100</f>
+        <f>$B$197-C21/DCF!C$73</f>
         <v/>
       </c>
       <c r="D183" s="75">
-        <f>119068-D21/100</f>
+        <f>$B$197-D21/DCF!C$73</f>
         <v/>
       </c>
       <c r="E183" s="75">
-        <f>119068-ROUND(E22*E153,0)/100</f>
+        <f>Scenarios!D197-ROUND(E22*E153,0)/100</f>
         <v/>
       </c>
       <c r="F183" s="176" t="n"/>
@@ -6797,11 +6765,11 @@
       </c>
       <c r="B184" s="176" t="n"/>
       <c r="C184" s="75">
-        <f>C183-C21/108</f>
+        <f>C183-C21/DCF!D$73</f>
         <v/>
       </c>
       <c r="D184" s="75">
-        <f>D183-D21/108</f>
+        <f>D183-D21/DCF!D$73</f>
         <v/>
       </c>
       <c r="E184" s="75">
@@ -6819,11 +6787,11 @@
       </c>
       <c r="B185" s="176" t="n"/>
       <c r="C185" s="75">
-        <f>C184-C21/115</f>
+        <f>C184-C21/DCF!E$73</f>
         <v/>
       </c>
       <c r="D185" s="75">
-        <f>D184-D21/115</f>
+        <f>D184-D21/DCF!E$73</f>
         <v/>
       </c>
       <c r="E185" s="75">
@@ -6841,11 +6809,11 @@
       </c>
       <c r="B186" s="176" t="n"/>
       <c r="C186" s="75">
-        <f>C185-C21/122</f>
+        <f>C185-C21/DCF!F$73</f>
         <v/>
       </c>
       <c r="D186" s="75">
-        <f>D185-D21/122</f>
+        <f>D185-D21/DCF!F$73</f>
         <v/>
       </c>
       <c r="E186" s="75">
@@ -6863,11 +6831,11 @@
       </c>
       <c r="B187" s="176" t="n"/>
       <c r="C187" s="75">
-        <f>C186-C21/130</f>
+        <f>C186-C21/DCF!G$73</f>
         <v/>
       </c>
       <c r="D187" s="75">
-        <f>D186-D21/130</f>
+        <f>D186-D21/DCF!G$73</f>
         <v/>
       </c>
       <c r="E187" s="75">
@@ -6995,6 +6963,46 @@
       <c r="E193" s="176" t="n"/>
       <c r="F193" s="176" t="n"/>
       <c r="G193" s="176" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>FY25 total assets ($000)</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>8456743</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>FY25 total liabilities ($000)</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>3494903</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>FY25 total equity ($000)</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>4961840</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>FY25 diluted shares (000)</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>119068</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7008,7 +7016,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -8053,23 +8061,23 @@
         <v>5049744</v>
       </c>
       <c r="C29" s="75">
-        <f>B28*0.71*(1+C25)+B28*0.16*(1+C26)+B28*0.13*(1+C27)</f>
+        <f>B28*$B$71*(1+C25)+B28*$B$72*(1+C26)+B28*$B$73*(1+C27)</f>
         <v/>
       </c>
       <c r="D29" s="75">
-        <f>C28*0.71*(1+D25)+C28*0.16*(1+D26)+C28*0.13*(1+D27)</f>
+        <f>C28*$B$71*(1+D25)+C28*$B$72*(1+D26)+C28*$B$73*(1+D27)</f>
         <v/>
       </c>
       <c r="E29" s="75">
-        <f>D28*0.71*(1+E25)+D28*0.16*(1+E26)+D28*0.13*(1+E27)</f>
+        <f>D28*$B$71*(1+E25)+D28*$B$72*(1+E26)+D28*$B$73*(1+E27)</f>
         <v/>
       </c>
       <c r="F29" s="75">
-        <f>E28*0.71*(1+F25)+E28*0.16*(1+F26)+E28*0.13*(1+F27)</f>
+        <f>E28*$B$71*(1+F25)+E28*$B$72*(1+F26)+E28*$B$73*(1+F27)</f>
         <v/>
       </c>
       <c r="G29" s="75">
-        <f>F28*0.71*(1+G25)+F28*0.16*(1+G26)+F28*0.13*(1+G27)</f>
+        <f>F28*$B$71*(1+G25)+F28*$B$72*(1+G26)+F28*$B$73*(1+G27)</f>
         <v/>
       </c>
       <c r="H29" s="176" t="n"/>
@@ -9136,6 +9144,36 @@
       <c r="H59" s="176" t="n"/>
       <c r="I59" s="176" t="n"/>
       <c r="J59" s="176" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Americas comp mix %</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>China comp mix %</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>RoW comp mix %</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.13</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9594,28 +9632,27 @@
           <t>+ Stock-based compensation (add-back only if flag = 1)</t>
         </is>
       </c>
-      <c r="B20" s="75">
-        <f>62203*$B$7</f>
-        <v/>
+      <c r="B20" s="75" t="n">
+        <v>62203</v>
       </c>
       <c r="C20" s="75">
-        <f>Scenarios!D25/11102600*62203*$B$7</f>
+        <f>Scenarios!C25/DCF!$B$6*$B$20*$B$7</f>
         <v/>
       </c>
       <c r="D20" s="75">
-        <f>Scenarios!D26/11102600*62203*$B$7</f>
+        <f>Scenarios!D25/DCF!$B$6*$B$20*$B$7</f>
         <v/>
       </c>
       <c r="E20" s="75">
-        <f>Scenarios!D27/11102600*62203*$B$7</f>
+        <f>Scenarios!E25/DCF!$B$6*$B$20*$B$7</f>
         <v/>
       </c>
       <c r="F20" s="75">
-        <f>Scenarios!D28/11102600*62203*$B$7</f>
+        <f>Scenarios!F25/DCF!$B$6*$B$20*$B$7</f>
         <v/>
       </c>
       <c r="G20" s="75">
-        <f>Scenarios!D29/11102600*62203*$B$7</f>
+        <f>Scenarios!G25/DCF!$B$6*$B$20*$B$7</f>
         <v/>
       </c>
     </row>
@@ -9627,23 +9664,23 @@
       </c>
       <c r="B21" s="176" t="n"/>
       <c r="C21" s="130">
-        <f>C16+C17+C18+C19+C20</f>
+        <f>SUM(C16:C20)</f>
         <v/>
       </c>
       <c r="D21" s="130">
-        <f>D16+D17+D18+D19+D20</f>
+        <f>SUM(D16:D20)</f>
         <v/>
       </c>
       <c r="E21" s="130">
-        <f>E16+E17+E18+E19+E20</f>
+        <f>SUM(E16:E20)</f>
         <v/>
       </c>
       <c r="F21" s="130">
-        <f>F16+F17+F18+F19+F20</f>
+        <f>SUM(F16:F20)</f>
         <v/>
       </c>
       <c r="G21" s="130">
-        <f>G16+G17+G18+G19+G20</f>
+        <f>SUM(G16:G20)</f>
         <v/>
       </c>
     </row>
@@ -9670,23 +9707,23 @@
         <v>1028</v>
       </c>
       <c r="C23" s="75">
-        <f>1028*(Scenarios!D25/11102600)</f>
+        <f>$B$23*(Scenarios!C25/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="D23" s="75">
-        <f>1028*(Scenarios!D26/11102600)</f>
+        <f>$B$23*(Scenarios!D25/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="E23" s="75">
-        <f>1028*(Scenarios!D27/11102600)</f>
+        <f>$B$23*(Scenarios!E25/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="F23" s="75">
-        <f>1028*(Scenarios!D28/11102600)</f>
+        <f>$B$23*(Scenarios!F25/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="G23" s="75">
-        <f>1028*(Scenarios!D29/11102600)</f>
+        <f>$B$23*(Scenarios!G25/DCF!$B$6)</f>
         <v/>
       </c>
     </row>
@@ -9803,11 +9840,11 @@
         <v/>
       </c>
       <c r="F28" s="75">
-        <f>'Revenue Drivers'!C31</f>
+        <f>'Revenue Drivers'!F31</f>
         <v/>
       </c>
       <c r="G28" s="75">
-        <f>'Revenue Drivers'!D31</f>
+        <f>'Revenue Drivers'!G31</f>
         <v/>
       </c>
     </row>
@@ -9833,11 +9870,11 @@
         <v/>
       </c>
       <c r="F29" s="75">
-        <f>'Revenue Drivers'!C41</f>
+        <f>'Revenue Drivers'!F41</f>
         <v/>
       </c>
       <c r="G29" s="75">
-        <f>'Revenue Drivers'!D41</f>
+        <f>'Revenue Drivers'!G41</f>
         <v/>
       </c>
     </row>
@@ -9863,11 +9900,11 @@
         <v/>
       </c>
       <c r="F30" s="75">
-        <f>'Revenue Drivers'!C45</f>
+        <f>'Revenue Drivers'!F45</f>
         <v/>
       </c>
       <c r="G30" s="75">
-        <f>'Revenue Drivers'!D45</f>
+        <f>'Revenue Drivers'!G45</f>
         <v/>
       </c>
     </row>
@@ -10101,23 +10138,23 @@
         <v>0.2946847649213503</v>
       </c>
       <c r="C39" s="32">
-        <f>0.29468476492135026+(C$12-0.29468476492135026)*1/5</f>
+        <f>$B$39+(C$12-$B$39)*1/5</f>
         <v/>
       </c>
       <c r="D39" s="32">
-        <f>0.29468476492135026+(D$12-0.29468476492135026)*2/5</f>
+        <f>$B$39+(D$12-$B$39)*2/5</f>
         <v/>
       </c>
       <c r="E39" s="32">
-        <f>0.29468476492135026+(E$12-0.29468476492135026)*3/5</f>
+        <f>$B$39+(E$12-$B$39)*3/5</f>
         <v/>
       </c>
       <c r="F39" s="32">
-        <f>0.29468476492135026+(F$12-0.29468476492135026)*4/5</f>
+        <f>$B$39+(F$12-$B$39)*4/5</f>
         <v/>
       </c>
       <c r="G39" s="32">
-        <f>0.29468476492135026+(G$12-0.29468476492135026)*5/5</f>
+        <f>$B$39+(G$12-$B$39)*5/5</f>
         <v/>
       </c>
     </row>
@@ -11478,7 +11515,7 @@
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Terminal value = FCF5x(1+g)/(WACC-g)</t>
+          <t>Terminal value (Gordon growth)</t>
         </is>
       </c>
       <c r="B46" s="75">
@@ -11760,23 +11797,23 @@
         <v>500000</v>
       </c>
       <c r="C66" s="75">
-        <f>$B$66</f>
+        <f>B66</f>
         <v/>
       </c>
       <c r="D66" s="75">
-        <f>$B$66</f>
+        <f>B66</f>
         <v/>
       </c>
       <c r="E66" s="75">
-        <f>$B$66</f>
+        <f>B66</f>
         <v/>
       </c>
       <c r="F66" s="75">
-        <f>$B$66</f>
+        <f>B66</f>
         <v/>
       </c>
       <c r="G66" s="75">
-        <f>$B$66</f>
+        <f>B66</f>
         <v/>
       </c>
     </row>
@@ -11790,23 +11827,23 @@
         <v>0.105</v>
       </c>
       <c r="C67" s="32">
-        <f>$B$67</f>
+        <f>B67</f>
         <v/>
       </c>
       <c r="D67" s="32">
-        <f>$B$67</f>
+        <f>B67</f>
         <v/>
       </c>
       <c r="E67" s="32">
-        <f>$B$67</f>
+        <f>B67</f>
         <v/>
       </c>
       <c r="F67" s="32">
-        <f>$B$67</f>
+        <f>B67</f>
         <v/>
       </c>
       <c r="G67" s="32">
-        <f>$B$67</f>
+        <f>B67</f>
         <v/>
       </c>
     </row>
@@ -11924,23 +11961,23 @@
         <v>100</v>
       </c>
       <c r="C73" s="99">
-        <f>B73*(1+$B$67)</f>
+        <f>B73*(1+B67)</f>
         <v/>
       </c>
       <c r="D73" s="99">
-        <f>B73*(1+$B$67)</f>
+        <f>B73*(1+B67)</f>
         <v/>
       </c>
       <c r="E73" s="99">
-        <f>D73*(1+$B$67)</f>
+        <f>D73*(1+B67)</f>
         <v/>
       </c>
       <c r="F73" s="99">
-        <f>E73*(1+$B$67)</f>
+        <f>E73*(1+B67)</f>
         <v/>
       </c>
       <c r="G73" s="99">
-        <f>F73*(1+$B$67)</f>
+        <f>F73*(1+B67)</f>
         <v/>
       </c>
     </row>
@@ -11984,7 +12021,7 @@
         <v>111380</v>
       </c>
       <c r="C75" s="75">
-        <f>$B$75</f>
+        <f>B75</f>
         <v/>
       </c>
       <c r="D75" s="75">
@@ -12389,23 +12426,23 @@
       </c>
       <c r="B100" s="176" t="n"/>
       <c r="C100" s="121">
-        <f>(NPV(0.095,C36:G36)+(G36*(1+0.015)/(0.095-0.015))/(1+0.095)^5+B51+B52)/B56</f>
+        <f>(NPV($A100,C36:G36)+(G36*(1+C$99)/($A100-C$99))/(1+$A100)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D100" s="121">
-        <f>(NPV(0.095,C36:G36)+(G36*(1+0.02)/(0.095-0.02))/(1+0.095)^5+B51+B52)/B56</f>
+        <f>(NPV($A100,C36:G36)+(G36*(1+D$99)/($A100-D$99))/(1+$A100)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E100" s="121">
-        <f>(NPV(0.095,C36:G36)+(G36*(1+0.0225)/(0.095-0.0225))/(1+0.095)^5+B51+B52)/B56</f>
+        <f>(NPV($A100,C36:G36)+(G36*(1+E$99)/($A100-E$99))/(1+$A100)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F100" s="121">
-        <f>(NPV(0.095,C36:G36)+(G36*(1+0.025)/(0.095-0.025))/(1+0.095)^5+B51+B52)/B56</f>
+        <f>(NPV($A100,C36:G36)+(G36*(1+F$99)/($A100-F$99))/(1+$A100)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G100" s="121">
-        <f>(NPV(0.095,C36:G36)+(G36*(1+0.03)/(0.095-0.03))/(1+0.095)^5+B51+B52)/B56</f>
+        <f>(NPV($A100,C36:G36)+(G36*(1+G$99)/($A100-G$99))/(1+$A100)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>
@@ -12415,23 +12452,23 @@
       </c>
       <c r="B101" s="176" t="n"/>
       <c r="C101" s="121">
-        <f>(NPV(0.1,C36:G36)+(G36*(1+0.015)/(0.1-0.015))/(1+0.1)^5+B51+B52)/B56</f>
+        <f>(NPV($A101,C36:G36)+(G36*(1+C$99)/($A101-C$99))/(1+$A101)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D101" s="121">
-        <f>(NPV(0.1,C36:G36)+(G36*(1+0.02)/(0.1-0.02))/(1+0.1)^5+B51+B52)/B56</f>
+        <f>(NPV($A101,C36:G36)+(G36*(1+D$99)/($A101-D$99))/(1+$A101)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E101" s="121">
-        <f>(NPV(0.1,C36:G36)+(G36*(1+0.0225)/(0.1-0.0225))/(1+0.1)^5+B51+B52)/B56</f>
+        <f>(NPV($A101,C36:G36)+(G36*(1+E$99)/($A101-E$99))/(1+$A101)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F101" s="121">
-        <f>(NPV(0.1,C36:G36)+(G36*(1+0.025)/(0.1-0.025))/(1+0.1)^5+B51+B52)/B56</f>
+        <f>(NPV($A101,C36:G36)+(G36*(1+F$99)/($A101-F$99))/(1+$A101)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G101" s="121">
-        <f>(NPV(0.1,C36:G36)+(G36*(1+0.03)/(0.1-0.03))/(1+0.1)^5+B51+B52)/B56</f>
+        <f>(NPV($A101,C36:G36)+(G36*(1+G$99)/($A101-G$99))/(1+$A101)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>
@@ -12441,23 +12478,23 @@
       </c>
       <c r="B102" s="176" t="n"/>
       <c r="C102" s="121">
-        <f>(NPV(0.105,C36:G36)+(G36*(1+0.015)/(0.105-0.015))/(1+0.105)^5+B51+B52)/B56</f>
+        <f>(NPV($A102,C36:G36)+(G36*(1+C$99)/($A102-C$99))/(1+$A102)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D102" s="121">
-        <f>(NPV(0.105,C36:G36)+(G36*(1+0.02)/(0.105-0.02))/(1+0.105)^5+B51+B52)/B56</f>
+        <f>(NPV($A102,C36:G36)+(G36*(1+D$99)/($A102-D$99))/(1+$A102)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E102" s="121">
-        <f>(NPV(0.105,C36:G36)+(G36*(1+0.0225)/(0.105-0.0225))/(1+0.105)^5+B51+B52)/B56</f>
+        <f>(NPV($A102,C36:G36)+(G36*(1+E$99)/($A102-E$99))/(1+$A102)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F102" s="121">
-        <f>(NPV(0.105,C36:G36)+(G36*(1+0.025)/(0.105-0.025))/(1+0.105)^5+B51+B52)/B56</f>
+        <f>(NPV($A102,C36:G36)+(G36*(1+F$99)/($A102-F$99))/(1+$A102)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G102" s="121">
-        <f>(NPV(0.105,C36:G36)+(G36*(1+0.03)/(0.105-0.03))/(1+0.105)^5+B51+B52)/B56</f>
+        <f>(NPV($A102,C36:G36)+(G36*(1+G$99)/($A102-G$99))/(1+$A102)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>
@@ -12467,23 +12504,23 @@
       </c>
       <c r="B103" s="176" t="n"/>
       <c r="C103" s="121">
-        <f>(NPV(0.11,C36:G36)+(G36*(1+0.015)/(0.11-0.015))/(1+0.11)^5+B51+B52)/B56</f>
+        <f>(NPV($A103,C36:G36)+(G36*(1+C$99)/($A103-C$99))/(1+$A103)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D103" s="121">
-        <f>(NPV(0.11,C36:G36)+(G36*(1+0.02)/(0.11-0.02))/(1+0.11)^5+B51+B52)/B56</f>
+        <f>(NPV($A103,C36:G36)+(G36*(1+D$99)/($A103-D$99))/(1+$A103)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E103" s="121">
-        <f>(NPV(0.11,C36:G36)+(G36*(1+0.0225)/(0.11-0.0225))/(1+0.11)^5+B51+B52)/B56</f>
+        <f>(NPV($A103,C36:G36)+(G36*(1+E$99)/($A103-E$99))/(1+$A103)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F103" s="121">
-        <f>(NPV(0.11,C36:G36)+(G36*(1+0.025)/(0.11-0.025))/(1+0.11)^5+B51+B52)/B56</f>
+        <f>(NPV($A103,C36:G36)+(G36*(1+F$99)/($A103-F$99))/(1+$A103)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G103" s="121">
-        <f>(NPV(0.11,C36:G36)+(G36*(1+0.03)/(0.11-0.03))/(1+0.11)^5+B51+B52)/B56</f>
+        <f>(NPV($A103,C36:G36)+(G36*(1+G$99)/($A103-G$99))/(1+$A103)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>
@@ -12493,23 +12530,23 @@
       </c>
       <c r="B104" s="176" t="n"/>
       <c r="C104" s="121">
-        <f>(NPV(0.115,C36:G36)+(G36*(1+0.015)/(0.115-0.015))/(1+0.115)^5+B51+B52)/B56</f>
+        <f>(NPV($A104,C36:G36)+(G36*(1+C$99)/($A104-C$99))/(1+$A104)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="D104" s="121">
-        <f>(NPV(0.115,C36:G36)+(G36*(1+0.02)/(0.115-0.02))/(1+0.115)^5+B51+B52)/B56</f>
+        <f>(NPV($A104,C36:G36)+(G36*(1+D$99)/($A104-D$99))/(1+$A104)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="E104" s="121">
-        <f>(NPV(0.115,C36:G36)+(G36*(1+0.0225)/(0.115-0.0225))/(1+0.115)^5+B51+B52)/B56</f>
+        <f>(NPV($A104,C36:G36)+(G36*(1+E$99)/($A104-E$99))/(1+$A104)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="F104" s="121">
-        <f>(NPV(0.115,C36:G36)+(G36*(1+0.025)/(0.115-0.025))/(1+0.115)^5+B51+B52)/B56</f>
+        <f>(NPV($A104,C36:G36)+(G36*(1+F$99)/($A104-F$99))/(1+$A104)^5+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="G104" s="121">
-        <f>(NPV(0.115,C36:G36)+(G36*(1+0.03)/(0.115-0.03))/(1+0.115)^5+B51+B52)/B56</f>
+        <f>(NPV($A104,C36:G36)+(G36*(1+G$99)/($A104-G$99))/(1+$A104)^5+B51+B52)/B56</f>
         <v/>
       </c>
     </row>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -12245,7 +12245,7 @@
         </is>
       </c>
       <c r="B87" s="99">
-        <f>(B85+B51+B52)/B56</f>
+        <f>(B86+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="C87" s="176" t="n"/>
@@ -12280,11 +12280,19 @@
       <c r="A90" s="103" t="inlineStr"/>
       <c r="B90" s="176" t="inlineStr">
         <is>
+          <t>Gordon Growth</t>
+        </is>
+      </c>
+      <c r="C90" s="176" t="inlineStr">
+        <is>
+          <t>Exit Multiple</t>
+        </is>
+      </c>
+      <c r="D90" s="176" t="inlineStr">
+        <is>
           <t>Variance</t>
         </is>
       </c>
-      <c r="C90" s="176" t="n"/>
-      <c r="D90" s="176" t="n"/>
       <c r="E90" s="176" t="n"/>
       <c r="F90" s="176" t="n"/>
       <c r="G90" s="176" t="n"/>
@@ -12296,11 +12304,17 @@
         </is>
       </c>
       <c r="B91" s="176">
-        <f>B90-C90</f>
-        <v/>
-      </c>
-      <c r="C91" s="176" t="n"/>
-      <c r="D91" s="176" t="n"/>
+        <f>D46</f>
+        <v/>
+      </c>
+      <c r="C91" s="176">
+        <f>D83</f>
+        <v/>
+      </c>
+      <c r="D91" s="176">
+        <f>B91-C91</f>
+        <v/>
+      </c>
       <c r="E91" s="176" t="n"/>
       <c r="F91" s="176" t="n"/>
       <c r="G91" s="176" t="n"/>
@@ -12312,11 +12326,17 @@
         </is>
       </c>
       <c r="B92" s="176">
-        <f>B91-C91</f>
-        <v/>
-      </c>
-      <c r="C92" s="176" t="n"/>
-      <c r="D92" s="176" t="n"/>
+        <f>D47</f>
+        <v/>
+      </c>
+      <c r="C92" s="176">
+        <f>D82</f>
+        <v/>
+      </c>
+      <c r="D92" s="176">
+        <f>B92-C92</f>
+        <v/>
+      </c>
       <c r="E92" s="176" t="n"/>
       <c r="F92" s="176" t="n"/>
       <c r="G92" s="176" t="n"/>
@@ -12327,12 +12347,12 @@
           <t>Terminal value variance (%)</t>
         </is>
       </c>
-      <c r="B93" s="176">
-        <f>(B90-C90)/B90</f>
-        <v/>
-      </c>
+      <c r="B93" s="176" t="n"/>
       <c r="C93" s="176" t="n"/>
-      <c r="D93" s="176" t="n"/>
+      <c r="D93" s="176">
+        <f>(B91-C91)/B91</f>
+        <v/>
+      </c>
       <c r="E93" s="176" t="n"/>
       <c r="F93" s="176" t="n"/>
       <c r="G93" s="176" t="n"/>
@@ -12344,24 +12364,40 @@
         </is>
       </c>
       <c r="B94" s="176">
-        <f>B93-C93</f>
-        <v/>
-      </c>
-      <c r="C94" s="176" t="n"/>
-      <c r="D94" s="176" t="n"/>
+        <f>D57</f>
+        <v/>
+      </c>
+      <c r="C94" s="176">
+        <f>D87</f>
+        <v/>
+      </c>
+      <c r="D94" s="176">
+        <f>B94-C94</f>
+        <v/>
+      </c>
       <c r="E94" s="176" t="n"/>
       <c r="F94" s="176" t="n"/>
       <c r="G94" s="176" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="68" t="n"/>
-      <c r="B95" s="176" t="inlineStr">
+      <c r="A95" s="68" t="inlineStr">
+        <is>
+          <t>Sanity check: multiples within ±1.5 turns?</t>
+        </is>
+      </c>
+      <c r="B95" s="176">
+        <f>IF(ABS(D92)&lt;=1.5,"PASS","REVIEW")</f>
+        <v/>
+      </c>
+      <c r="C95" s="176">
+        <f>TEXT(D92,"0.0")&amp;"x spread vs Gordon-implied exit"</f>
+        <v/>
+      </c>
+      <c r="D95" s="176" t="inlineStr">
         <is>
           <t>Selected exit is the Gordon identity, so spread should be 0</t>
         </is>
       </c>
-      <c r="C95" s="176" t="n"/>
-      <c r="D95" s="176" t="n"/>
       <c r="E95" s="176" t="n"/>
       <c r="F95" s="176" t="n"/>
       <c r="G95" s="176" t="n"/>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -510,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="223">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1080,6 +1080,16 @@
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="70" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2580,7 +2590,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="B4" s="32" t="n">
+      <c r="B4" s="75" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -2612,7 +2622,7 @@
           <t>Share price ($)</t>
         </is>
       </c>
-      <c r="B8" s="186" t="n">
+      <c r="B8" s="99" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2643,7 +2653,7 @@
           <t>Capitalized Operating Leases</t>
         </is>
       </c>
-      <c r="B11" s="187" t="n">
+      <c r="B11" s="75" t="n">
         <v>1798441</v>
       </c>
     </row>
@@ -2696,7 +2706,7 @@
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="B17" s="187" t="n">
+      <c r="B17" s="75" t="n">
         <v>2140000</v>
       </c>
     </row>
@@ -2706,7 +2716,7 @@
           <t>Market Capitalization</t>
         </is>
       </c>
-      <c r="B18" s="187" t="n">
+      <c r="B18" s="75" t="n">
         <v>11140000</v>
       </c>
     </row>
@@ -2716,7 +2726,7 @@
           <t>Target Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="75">
         <f>B17/B18</f>
         <v/>
       </c>
@@ -2792,7 +2802,7 @@
           <t>Cost of Equity</t>
         </is>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="130">
         <f>B3+B24*B4</f>
         <v/>
       </c>
@@ -3013,13 +3023,13 @@
         </is>
       </c>
       <c r="B7" s="176" t="n"/>
-      <c r="C7" s="187" t="n">
+      <c r="C7" s="75" t="n">
         <v>134500</v>
       </c>
-      <c r="D7" s="187" t="n">
+      <c r="D7" s="75" t="n">
         <v>134500</v>
       </c>
-      <c r="E7" s="187" t="n">
+      <c r="E7" s="75" t="n">
         <v>134500</v>
       </c>
       <c r="F7" s="176" t="n"/>
@@ -3263,13 +3273,13 @@
         </is>
       </c>
       <c r="B20" s="176" t="n"/>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="75" t="n">
         <v>0.06</v>
       </c>
-      <c r="D20" s="32" t="n">
+      <c r="D20" s="75" t="n">
         <v>0.06</v>
       </c>
-      <c r="E20" s="32" t="n">
+      <c r="E20" s="75" t="n">
         <v>0.06</v>
       </c>
       <c r="F20" s="176" t="n"/>
@@ -3282,10 +3292,10 @@
         </is>
       </c>
       <c r="B21" s="176" t="n"/>
-      <c r="C21" s="187" t="n">
+      <c r="C21" s="75" t="n">
         <v>500000</v>
       </c>
-      <c r="D21" s="187" t="n">
+      <c r="D21" s="75" t="n">
         <v>500000</v>
       </c>
       <c r="E21" s="75" t="n">
@@ -4222,15 +4232,15 @@
         </is>
       </c>
       <c r="B65" s="176" t="n"/>
-      <c r="C65" s="28">
+      <c r="C65" s="193">
         <f>C15</f>
         <v/>
       </c>
-      <c r="D65" s="28">
+      <c r="D65" s="193">
         <f>D15</f>
         <v/>
       </c>
-      <c r="E65" s="28">
+      <c r="E65" s="193">
         <f>E15</f>
         <v/>
       </c>
@@ -4244,15 +4254,15 @@
         </is>
       </c>
       <c r="B66" s="176" t="n"/>
-      <c r="C66" s="28">
+      <c r="C66" s="193">
         <f>C15</f>
         <v/>
       </c>
-      <c r="D66" s="28">
+      <c r="D66" s="193">
         <f>D15</f>
         <v/>
       </c>
-      <c r="E66" s="28">
+      <c r="E66" s="193">
         <f>E15</f>
         <v/>
       </c>
@@ -4266,15 +4276,15 @@
         </is>
       </c>
       <c r="B67" s="176" t="n"/>
-      <c r="C67" s="28">
+      <c r="C67" s="193">
         <f>C15</f>
         <v/>
       </c>
-      <c r="D67" s="28">
+      <c r="D67" s="193">
         <f>D15</f>
         <v/>
       </c>
-      <c r="E67" s="28">
+      <c r="E67" s="193">
         <f>E15</f>
         <v/>
       </c>
@@ -4288,15 +4298,15 @@
         </is>
       </c>
       <c r="B68" s="176" t="n"/>
-      <c r="C68" s="28">
+      <c r="C68" s="193">
         <f>C15</f>
         <v/>
       </c>
-      <c r="D68" s="28">
+      <c r="D68" s="193">
         <f>D15</f>
         <v/>
       </c>
-      <c r="E68" s="28">
+      <c r="E68" s="193">
         <f>E15</f>
         <v/>
       </c>
@@ -4310,15 +4320,15 @@
         </is>
       </c>
       <c r="B69" s="176" t="n"/>
-      <c r="C69" s="28">
+      <c r="C69" s="193">
         <f>C15</f>
         <v/>
       </c>
-      <c r="D69" s="28">
+      <c r="D69" s="193">
         <f>D15</f>
         <v/>
       </c>
-      <c r="E69" s="28">
+      <c r="E69" s="193">
         <f>E15</f>
         <v/>
       </c>
@@ -4442,15 +4452,15 @@
         </is>
       </c>
       <c r="B75" s="176" t="n"/>
-      <c r="C75" s="28">
+      <c r="C75" s="193">
         <f>C16-C17*1</f>
         <v/>
       </c>
-      <c r="D75" s="28">
+      <c r="D75" s="193">
         <f>D16-D17*1</f>
         <v/>
       </c>
-      <c r="E75" s="28">
+      <c r="E75" s="193">
         <f>E16-E17*1</f>
         <v/>
       </c>
@@ -4464,15 +4474,15 @@
         </is>
       </c>
       <c r="B76" s="176" t="n"/>
-      <c r="C76" s="28">
+      <c r="C76" s="193">
         <f>C16-C17*2</f>
         <v/>
       </c>
-      <c r="D76" s="28">
+      <c r="D76" s="193">
         <f>D16-D17*2</f>
         <v/>
       </c>
-      <c r="E76" s="28">
+      <c r="E76" s="193">
         <f>E16-E17*2</f>
         <v/>
       </c>
@@ -4486,15 +4496,15 @@
         </is>
       </c>
       <c r="B77" s="176" t="n"/>
-      <c r="C77" s="28">
+      <c r="C77" s="193">
         <f>C16-C17*3</f>
         <v/>
       </c>
-      <c r="D77" s="28">
+      <c r="D77" s="193">
         <f>D16-D17*3</f>
         <v/>
       </c>
-      <c r="E77" s="28">
+      <c r="E77" s="193">
         <f>E16-E17*3</f>
         <v/>
       </c>
@@ -4508,15 +4518,15 @@
         </is>
       </c>
       <c r="B78" s="176" t="n"/>
-      <c r="C78" s="28">
+      <c r="C78" s="193">
         <f>C16-C17*4</f>
         <v/>
       </c>
-      <c r="D78" s="28">
+      <c r="D78" s="193">
         <f>D16-D17*4</f>
         <v/>
       </c>
-      <c r="E78" s="28">
+      <c r="E78" s="193">
         <f>E16-E17*4</f>
         <v/>
       </c>
@@ -4530,15 +4540,15 @@
         </is>
       </c>
       <c r="B79" s="176" t="n"/>
-      <c r="C79" s="28">
+      <c r="C79" s="193">
         <f>C16-C17*5</f>
         <v/>
       </c>
-      <c r="D79" s="28">
+      <c r="D79" s="193">
         <f>D16-D17*5</f>
         <v/>
       </c>
-      <c r="E79" s="28">
+      <c r="E79" s="193">
         <f>E16-E17*5</f>
         <v/>
       </c>
@@ -4662,15 +4672,15 @@
         </is>
       </c>
       <c r="B85" s="176" t="n"/>
-      <c r="C85" s="28">
+      <c r="C85" s="193">
         <f>C18</f>
         <v/>
       </c>
-      <c r="D85" s="28">
+      <c r="D85" s="193">
         <f>D18</f>
         <v/>
       </c>
-      <c r="E85" s="28">
+      <c r="E85" s="193">
         <f>E18</f>
         <v/>
       </c>
@@ -4684,15 +4694,15 @@
         </is>
       </c>
       <c r="B86" s="176" t="n"/>
-      <c r="C86" s="28">
+      <c r="C86" s="193">
         <f>C18</f>
         <v/>
       </c>
-      <c r="D86" s="28">
+      <c r="D86" s="193">
         <f>D18</f>
         <v/>
       </c>
-      <c r="E86" s="28">
+      <c r="E86" s="193">
         <f>E18</f>
         <v/>
       </c>
@@ -4706,15 +4716,15 @@
         </is>
       </c>
       <c r="B87" s="176" t="n"/>
-      <c r="C87" s="28">
+      <c r="C87" s="193">
         <f>C18</f>
         <v/>
       </c>
-      <c r="D87" s="28">
+      <c r="D87" s="193">
         <f>D18</f>
         <v/>
       </c>
-      <c r="E87" s="28">
+      <c r="E87" s="193">
         <f>E18</f>
         <v/>
       </c>
@@ -4728,15 +4738,15 @@
         </is>
       </c>
       <c r="B88" s="176" t="n"/>
-      <c r="C88" s="28">
+      <c r="C88" s="193">
         <f>C18</f>
         <v/>
       </c>
-      <c r="D88" s="28">
+      <c r="D88" s="193">
         <f>D18</f>
         <v/>
       </c>
-      <c r="E88" s="28">
+      <c r="E88" s="193">
         <f>E18</f>
         <v/>
       </c>
@@ -4750,15 +4760,15 @@
         </is>
       </c>
       <c r="B89" s="176" t="n"/>
-      <c r="C89" s="28">
+      <c r="C89" s="193">
         <f>C18</f>
         <v/>
       </c>
-      <c r="D89" s="28">
+      <c r="D89" s="193">
         <f>D18</f>
         <v/>
       </c>
-      <c r="E89" s="28">
+      <c r="E89" s="193">
         <f>E18</f>
         <v/>
       </c>
@@ -5661,15 +5671,15 @@
         </is>
       </c>
       <c r="B131" s="176" t="n"/>
-      <c r="C131" s="130">
+      <c r="C131" s="31">
         <f>NPV(C9,C125,C126,C127,C128,C129)+(C129*(1+C10)/(C9-C10))/(1+C9)^5</f>
         <v/>
       </c>
-      <c r="D131" s="130">
+      <c r="D131" s="31">
         <f>NPV(D9,D125,D126,D127,D128,D129)+(D129*(1+D10)/(D9-D10))/(1+D9)^5</f>
         <v/>
       </c>
-      <c r="E131" s="130">
+      <c r="E131" s="31">
         <f>NPV(E9,E125,E126,E127,E128,E129)+(E129*(1+E10)/(E9-E10))/(1+E9)^5</f>
         <v/>
       </c>
@@ -6742,15 +6752,15 @@
         </is>
       </c>
       <c r="B183" s="176" t="n"/>
-      <c r="C183" s="75">
+      <c r="C183" s="187">
         <f>$B$197-C21/DCF!C$73</f>
         <v/>
       </c>
-      <c r="D183" s="75">
+      <c r="D183" s="187">
         <f>$B$197-D21/DCF!C$73</f>
         <v/>
       </c>
-      <c r="E183" s="75">
+      <c r="E183" s="187">
         <f>Scenarios!D197-ROUND(E22*E153,0)/100</f>
         <v/>
       </c>
@@ -6764,15 +6774,15 @@
         </is>
       </c>
       <c r="B184" s="176" t="n"/>
-      <c r="C184" s="75">
+      <c r="C184" s="187">
         <f>C183-C21/DCF!D$73</f>
         <v/>
       </c>
-      <c r="D184" s="75">
+      <c r="D184" s="187">
         <f>D183-D21/DCF!D$73</f>
         <v/>
       </c>
-      <c r="E184" s="75">
+      <c r="E184" s="187">
         <f>E183-ROUND(E22*E154,0)/108</f>
         <v/>
       </c>
@@ -6786,15 +6796,15 @@
         </is>
       </c>
       <c r="B185" s="176" t="n"/>
-      <c r="C185" s="75">
+      <c r="C185" s="187">
         <f>C184-C21/DCF!E$73</f>
         <v/>
       </c>
-      <c r="D185" s="75">
+      <c r="D185" s="187">
         <f>D184-D21/DCF!E$73</f>
         <v/>
       </c>
-      <c r="E185" s="75">
+      <c r="E185" s="187">
         <f>E184-ROUND(E22*E155,0)/115</f>
         <v/>
       </c>
@@ -6808,15 +6818,15 @@
         </is>
       </c>
       <c r="B186" s="176" t="n"/>
-      <c r="C186" s="75">
+      <c r="C186" s="187">
         <f>C185-C21/DCF!F$73</f>
         <v/>
       </c>
-      <c r="D186" s="75">
+      <c r="D186" s="187">
         <f>D185-D21/DCF!F$73</f>
         <v/>
       </c>
-      <c r="E186" s="75">
+      <c r="E186" s="187">
         <f>E185-ROUND(E22*E156,0)/122</f>
         <v/>
       </c>
@@ -6830,15 +6840,15 @@
         </is>
       </c>
       <c r="B187" s="176" t="n"/>
-      <c r="C187" s="75">
+      <c r="C187" s="187">
         <f>C186-C21/DCF!G$73</f>
         <v/>
       </c>
-      <c r="D187" s="75">
+      <c r="D187" s="187">
         <f>D186-D21/DCF!G$73</f>
         <v/>
       </c>
-      <c r="E187" s="75">
+      <c r="E187" s="187">
         <f>E186-ROUND(E22*E157,0)/130</f>
         <v/>
       </c>
@@ -6970,7 +6980,7 @@
           <t>FY25 total assets ($000)</t>
         </is>
       </c>
-      <c r="B194" t="n">
+      <c r="B194" s="215" t="n">
         <v>8456743</v>
       </c>
     </row>
@@ -6980,7 +6990,7 @@
           <t>FY25 total liabilities ($000)</t>
         </is>
       </c>
-      <c r="B195" t="n">
+      <c r="B195" s="215" t="n">
         <v>3494903</v>
       </c>
     </row>
@@ -6990,7 +7000,7 @@
           <t>FY25 total equity ($000)</t>
         </is>
       </c>
-      <c r="B196" t="n">
+      <c r="B196" s="215" t="n">
         <v>4961840</v>
       </c>
     </row>
@@ -7000,7 +7010,7 @@
           <t>FY25 diluted shares (000)</t>
         </is>
       </c>
-      <c r="B197" t="n">
+      <c r="B197" s="216" t="n">
         <v>119068</v>
       </c>
     </row>
@@ -8012,7 +8022,7 @@
           <t>Prior-year store channel revenue ($000)</t>
         </is>
       </c>
-      <c r="B28" s="187" t="n">
+      <c r="B28" s="75" t="n">
         <v>5049744</v>
       </c>
       <c r="C28" s="75">
@@ -8057,7 +8067,7 @@
           <t>Comparable store revenue ($000)</t>
         </is>
       </c>
-      <c r="B29" s="187" t="n">
+      <c r="B29" s="75" t="n">
         <v>5049744</v>
       </c>
       <c r="C29" s="75">
@@ -8139,7 +8149,7 @@
           <t>Store channel revenue ($000)</t>
         </is>
       </c>
-      <c r="B31" s="187" t="n">
+      <c r="B31" s="75" t="n">
         <v>5049744</v>
       </c>
       <c r="C31" s="75">
@@ -8484,7 +8494,7 @@
           <t>E-commerce revenue ($000)</t>
         </is>
       </c>
-      <c r="B41" s="187" t="n">
+      <c r="B41" s="75" t="n">
         <v>4918697</v>
       </c>
       <c r="C41" s="75">
@@ -8605,7 +8615,7 @@
           <t>Other channels (wholesale / license / outlets) ($000)</t>
         </is>
       </c>
-      <c r="B45" s="187" t="n">
+      <c r="B45" s="75" t="n">
         <v>1134159</v>
       </c>
       <c r="C45" s="75">
@@ -8650,7 +8660,7 @@
           <t>Americas net revenue ($000)</t>
         </is>
       </c>
-      <c r="B46" s="187" t="n">
+      <c r="B46" s="75" t="n">
         <v>7847044</v>
       </c>
       <c r="C46" s="75">
@@ -8695,7 +8705,7 @@
           <t>China Mainland net revenue ($000)</t>
         </is>
       </c>
-      <c r="B47" s="187" t="n">
+      <c r="B47" s="75" t="n">
         <v>1754799</v>
       </c>
       <c r="C47" s="75">
@@ -8740,7 +8750,7 @@
           <t>Rest of World net revenue ($000)</t>
         </is>
       </c>
-      <c r="B48" s="187" t="n">
+      <c r="B48" s="75" t="n">
         <v>1500757</v>
       </c>
       <c r="C48" s="75">
@@ -8785,22 +8795,22 @@
           <t>Women's % of revenue</t>
         </is>
       </c>
-      <c r="B49" s="32" t="n">
+      <c r="B49" s="75" t="n">
         <v>0.63</v>
       </c>
-      <c r="C49" s="32" t="n">
+      <c r="C49" s="75" t="n">
         <v>0.62</v>
       </c>
-      <c r="D49" s="32" t="n">
+      <c r="D49" s="75" t="n">
         <v>0.615</v>
       </c>
-      <c r="E49" s="32" t="n">
+      <c r="E49" s="75" t="n">
         <v>0.61</v>
       </c>
-      <c r="F49" s="32" t="n">
+      <c r="F49" s="75" t="n">
         <v>0.605</v>
       </c>
-      <c r="G49" s="32" t="n">
+      <c r="G49" s="75" t="n">
         <v>0.6</v>
       </c>
       <c r="H49" s="176" t="n"/>
@@ -8821,22 +8831,22 @@
           <t>Men's % of revenue</t>
         </is>
       </c>
-      <c r="B50" s="32" t="n">
+      <c r="B50" s="75" t="n">
         <v>0.24</v>
       </c>
-      <c r="C50" s="32" t="n">
+      <c r="C50" s="75" t="n">
         <v>0.25</v>
       </c>
-      <c r="D50" s="32" t="n">
+      <c r="D50" s="75" t="n">
         <v>0.255</v>
       </c>
-      <c r="E50" s="32" t="n">
+      <c r="E50" s="75" t="n">
         <v>0.26</v>
       </c>
-      <c r="F50" s="32" t="n">
+      <c r="F50" s="75" t="n">
         <v>0.265</v>
       </c>
-      <c r="G50" s="32" t="n">
+      <c r="G50" s="75" t="n">
         <v>0.27</v>
       </c>
       <c r="H50" s="176" t="n"/>
@@ -8857,22 +8867,22 @@
           <t>Accessories &amp; other % of revenue</t>
         </is>
       </c>
-      <c r="B51" s="32" t="n">
+      <c r="B51" s="75" t="n">
         <v>0.13</v>
       </c>
-      <c r="C51" s="32" t="n">
+      <c r="C51" s="75" t="n">
         <v>0.13</v>
       </c>
-      <c r="D51" s="32" t="n">
+      <c r="D51" s="75" t="n">
         <v>0.13</v>
       </c>
-      <c r="E51" s="32" t="n">
+      <c r="E51" s="75" t="n">
         <v>0.13</v>
       </c>
-      <c r="F51" s="32" t="n">
+      <c r="F51" s="75" t="n">
         <v>0.13</v>
       </c>
-      <c r="G51" s="32" t="n">
+      <c r="G51" s="75" t="n">
         <v>0.13</v>
       </c>
       <c r="H51" s="176" t="n"/>
@@ -8973,7 +8983,7 @@
           <t>Bottom-up total revenue ($000)</t>
         </is>
       </c>
-      <c r="B55" s="187" t="n">
+      <c r="B55" s="75" t="n">
         <v>11102600</v>
       </c>
       <c r="C55" s="75">
@@ -9014,7 +9024,7 @@
           <t>Scenarios base-case revenue ($000)</t>
         </is>
       </c>
-      <c r="B56" s="187" t="n">
+      <c r="B56" s="75" t="n">
         <v>11102600</v>
       </c>
       <c r="C56" s="75">
@@ -9151,7 +9161,7 @@
           <t>Americas comp mix %</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B71" s="217" t="n">
         <v>0.71</v>
       </c>
     </row>
@@ -9161,7 +9171,7 @@
           <t>China comp mix %</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B72" s="217" t="n">
         <v>0.16</v>
       </c>
     </row>
@@ -9171,7 +9181,7 @@
           <t>RoW comp mix %</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B73" s="217" t="n">
         <v>0.13</v>
       </c>
     </row>
@@ -9346,22 +9356,22 @@
           <t>SBC add-back flag (0 = expensed)</t>
         </is>
       </c>
-      <c r="B7" s="90" t="n">
+      <c r="B7" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="90" t="n">
+      <c r="C7" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="90" t="n">
+      <c r="D7" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="90" t="n">
+      <c r="E7" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="90" t="n">
+      <c r="F7" s="75" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="90" t="n">
+      <c r="G7" s="75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9527,7 +9537,7 @@
           <t>Reported operating income (EBIT)</t>
         </is>
       </c>
-      <c r="B16" s="187" t="n">
+      <c r="B16" s="75" t="n">
         <v>2210615</v>
       </c>
       <c r="C16" s="75">
@@ -9557,7 +9567,7 @@
           <t>+ Impairment / intangible amortization (add-back)</t>
         </is>
       </c>
-      <c r="B17" s="187" t="n">
+      <c r="B17" s="75" t="n">
         <v>6961</v>
       </c>
       <c r="C17" s="75" t="n">
@@ -9703,7 +9713,7 @@
           <t>+ Implied lease interest expense (reclass from rent)</t>
         </is>
       </c>
-      <c r="B23" s="187" t="n">
+      <c r="B23" s="75" t="n">
         <v>1028</v>
       </c>
       <c r="C23" s="75">
@@ -9758,7 +9768,7 @@
           <t>Amortization of prior capitalized intangibles</t>
         </is>
       </c>
-      <c r="B25" s="187" t="n">
+      <c r="B25" s="75" t="n">
         <v>6961</v>
       </c>
       <c r="C25" s="75" t="n">
@@ -9824,7 +9834,7 @@
           <t>Store-channel revenue</t>
         </is>
       </c>
-      <c r="B28" s="187" t="n">
+      <c r="B28" s="75" t="n">
         <v>5049744</v>
       </c>
       <c r="C28" s="75">
@@ -9854,7 +9864,7 @@
           <t>E-commerce revenue</t>
         </is>
       </c>
-      <c r="B29" s="187" t="n">
+      <c r="B29" s="75" t="n">
         <v>4918697</v>
       </c>
       <c r="C29" s="75">
@@ -9884,7 +9894,7 @@
           <t>Other channels revenue</t>
         </is>
       </c>
-      <c r="B30" s="187" t="n">
+      <c r="B30" s="75" t="n">
         <v>1134159</v>
       </c>
       <c r="C30" s="75">
@@ -9914,26 +9924,26 @@
           <t>Store-channel EBIT (= Rev x store margin)</t>
         </is>
       </c>
-      <c r="B31" s="75" t="n">
+      <c r="B31" s="32" t="n">
         <v>939252.384</v>
       </c>
-      <c r="C31" s="75">
+      <c r="C31" s="32">
         <f>C28*B$9</f>
         <v/>
       </c>
-      <c r="D31" s="75">
+      <c r="D31" s="32">
         <f>D28*B$9</f>
         <v/>
       </c>
-      <c r="E31" s="75">
+      <c r="E31" s="32">
         <f>E28*B$9</f>
         <v/>
       </c>
-      <c r="F31" s="75">
+      <c r="F31" s="32">
         <f>F28*B$9</f>
         <v/>
       </c>
-      <c r="G31" s="75">
+      <c r="G31" s="32">
         <f>G28*B$9</f>
         <v/>
       </c>
@@ -9944,26 +9954,26 @@
           <t>E-commerce EBIT (= Rev x e-comm margin)</t>
         </is>
       </c>
-      <c r="B32" s="75" t="n">
+      <c r="B32" s="32" t="n">
         <v>1160812.492</v>
       </c>
-      <c r="C32" s="75">
+      <c r="C32" s="32">
         <f>C29*B$10</f>
         <v/>
       </c>
-      <c r="D32" s="75">
+      <c r="D32" s="32">
         <f>D29*B$10</f>
         <v/>
       </c>
-      <c r="E32" s="75">
+      <c r="E32" s="32">
         <f>E29*B$10</f>
         <v/>
       </c>
-      <c r="F32" s="75">
+      <c r="F32" s="32">
         <f>F29*B$10</f>
         <v/>
       </c>
-      <c r="G32" s="75">
+      <c r="G32" s="32">
         <f>G29*B$10</f>
         <v/>
       </c>
@@ -9974,26 +9984,26 @@
           <t>Other-channels EBIT (= Rev x other margin)</t>
         </is>
       </c>
-      <c r="B33" s="75" t="n">
+      <c r="B33" s="32" t="n">
         <v>103208.469</v>
       </c>
-      <c r="C33" s="75">
+      <c r="C33" s="32">
         <f>C30*B$11</f>
         <v/>
       </c>
-      <c r="D33" s="75">
+      <c r="D33" s="32">
         <f>D30*B$11</f>
         <v/>
       </c>
-      <c r="E33" s="75">
+      <c r="E33" s="32">
         <f>E30*B$11</f>
         <v/>
       </c>
-      <c r="F33" s="75">
+      <c r="F33" s="32">
         <f>F30*B$11</f>
         <v/>
       </c>
-      <c r="G33" s="75">
+      <c r="G33" s="32">
         <f>G30*B$11</f>
         <v/>
       </c>
@@ -10032,26 +10042,26 @@
           <t>EBIT after channel mix</t>
         </is>
       </c>
-      <c r="B35" s="197" t="n">
+      <c r="B35" s="31" t="n">
         <v>2203273.345</v>
       </c>
-      <c r="C35" s="130">
+      <c r="C35" s="31">
         <f>C34</f>
         <v/>
       </c>
-      <c r="D35" s="130">
+      <c r="D35" s="31">
         <f>D34</f>
         <v/>
       </c>
-      <c r="E35" s="130">
+      <c r="E35" s="31">
         <f>E34</f>
         <v/>
       </c>
-      <c r="F35" s="130">
+      <c r="F35" s="31">
         <f>F34</f>
         <v/>
       </c>
-      <c r="G35" s="130">
+      <c r="G35" s="31">
         <f>G34</f>
         <v/>
       </c>
@@ -10062,27 +10072,27 @@
           <t>Normalized EBIT (tax base for NOPAT)</t>
         </is>
       </c>
-      <c r="B36" s="130">
+      <c r="B36" s="31">
         <f>B21+B23+B24-B25</f>
         <v/>
       </c>
-      <c r="C36" s="130">
+      <c r="C36" s="31">
         <f>Scenarios!D45</f>
         <v/>
       </c>
-      <c r="D36" s="130">
+      <c r="D36" s="31">
         <f>Scenarios!D46</f>
         <v/>
       </c>
-      <c r="E36" s="130">
+      <c r="E36" s="31">
         <f>Scenarios!D47</f>
         <v/>
       </c>
-      <c r="F36" s="130">
+      <c r="F36" s="31">
         <f>Scenarios!D48</f>
         <v/>
       </c>
-      <c r="G36" s="130">
+      <c r="G36" s="31">
         <f>Scenarios!D49</f>
         <v/>
       </c>
@@ -10165,23 +10175,23 @@
         </is>
       </c>
       <c r="B40" s="176" t="n"/>
-      <c r="C40" s="75">
+      <c r="C40" s="32">
         <f>C36*C39</f>
         <v/>
       </c>
-      <c r="D40" s="75">
+      <c r="D40" s="32">
         <f>D36*D39</f>
         <v/>
       </c>
-      <c r="E40" s="75">
+      <c r="E40" s="32">
         <f>E36*E39</f>
         <v/>
       </c>
-      <c r="F40" s="75">
+      <c r="F40" s="32">
         <f>F36*F39</f>
         <v/>
       </c>
-      <c r="G40" s="75">
+      <c r="G40" s="32">
         <f>G36*G39</f>
         <v/>
       </c>
@@ -10483,23 +10493,23 @@
           <t>Revenue Growth %</t>
         </is>
       </c>
-      <c r="C5">
+      <c r="C5" s="217">
         <f>Scenarios!$D$4</f>
         <v/>
       </c>
-      <c r="D5">
+      <c r="D5" s="217">
         <f>Scenarios!$D$5</f>
         <v/>
       </c>
-      <c r="E5">
+      <c r="E5" s="217">
         <f>Scenarios!$D$5</f>
         <v/>
       </c>
-      <c r="F5">
+      <c r="F5" s="217">
         <f>Scenarios!$D$5</f>
         <v/>
       </c>
-      <c r="G5">
+      <c r="G5" s="217">
         <f>Scenarios!$D$5</f>
         <v/>
       </c>
@@ -10510,7 +10520,7 @@
           <t>Net revenue</t>
         </is>
       </c>
-      <c r="B6" s="187" t="n">
+      <c r="B6" s="75" t="n">
         <v>11102600</v>
       </c>
       <c r="C6" s="75">
@@ -10570,7 +10580,7 @@
           <t>COGS</t>
         </is>
       </c>
-      <c r="B8" s="187" t="n">
+      <c r="B8" s="75" t="n">
         <v>4818468</v>
       </c>
       <c r="C8" s="75">
@@ -10654,7 +10664,7 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B11" s="197" t="n">
+      <c r="B11" s="130" t="n">
         <v>2210615</v>
       </c>
       <c r="C11" s="130">
@@ -10715,23 +10725,23 @@
         </is>
       </c>
       <c r="B13" s="176" t="n"/>
-      <c r="C13" s="75">
+      <c r="C13" s="32">
         <f>-'NOPAT Bridge'!C40</f>
         <v/>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="32">
         <f>-'NOPAT Bridge'!D40</f>
         <v/>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="32">
         <f>-'NOPAT Bridge'!E40</f>
         <v/>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="32">
         <f>-'NOPAT Bridge'!F40</f>
         <v/>
       </c>
-      <c r="G13" s="75">
+      <c r="G13" s="32">
         <f>-'NOPAT Bridge'!G40</f>
         <v/>
       </c>
@@ -10770,7 +10780,7 @@
           <t>FY25 D&amp;A ($000)</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="215" t="n">
         <v>496228</v>
       </c>
     </row>
@@ -10908,23 +10918,23 @@
       <c r="B21" s="193" t="n">
         <v>6.267883648875038</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="193">
         <f>Scenarios!D65</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="193">
         <f>Scenarios!D66</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="193">
         <f>Scenarios!D67</f>
         <v/>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="193">
         <f>Scenarios!D68</f>
         <v/>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="193">
         <f>Scenarios!D69</f>
         <v/>
       </c>
@@ -10968,23 +10978,23 @@
       <c r="B23" s="193" t="n">
         <v>128.8324100108167</v>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="193">
         <f>Scenarios!D75</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="193">
         <f>Scenarios!D76</f>
         <v/>
       </c>
-      <c r="E23" s="28">
+      <c r="E23" s="193">
         <f>Scenarios!D77</f>
         <v/>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="193">
         <f>Scenarios!D78</f>
         <v/>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="193">
         <f>Scenarios!D79</f>
         <v/>
       </c>
@@ -11028,23 +11038,23 @@
       <c r="B25" s="193" t="n">
         <v>25.10521290169407</v>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="193">
         <f>Scenarios!D85</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="193">
         <f>Scenarios!D86</f>
         <v/>
       </c>
-      <c r="E25" s="28">
+      <c r="E25" s="193">
         <f>Scenarios!D87</f>
         <v/>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="193">
         <f>Scenarios!D88</f>
         <v/>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="193">
         <f>Scenarios!D89</f>
         <v/>
       </c>
@@ -11055,7 +11065,7 @@
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="B26" s="187" t="n">
+      <c r="B26" s="75" t="n">
         <v>331421</v>
       </c>
       <c r="C26" s="75">
@@ -11115,7 +11125,7 @@
           <t>Prepaid expenses (other current assets)</t>
         </is>
       </c>
-      <c r="B28" s="187" t="n">
+      <c r="B28" s="75" t="n">
         <v>564089</v>
       </c>
       <c r="C28" s="75">
@@ -11145,26 +11155,26 @@
           <t>Accrued liabilities (% of revenue)</t>
         </is>
       </c>
-      <c r="B29" s="32" t="n">
+      <c r="B29" s="75" t="n">
         <v>0.05971412101669879</v>
       </c>
-      <c r="C29" s="32">
+      <c r="C29" s="75">
         <f>Scenarios!$D$20</f>
         <v/>
       </c>
-      <c r="D29" s="32">
+      <c r="D29" s="75">
         <f>Scenarios!$D$20</f>
         <v/>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="75">
         <f>Scenarios!$D$20</f>
         <v/>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="75">
         <f>Scenarios!$D$20</f>
         <v/>
       </c>
-      <c r="G29" s="32">
+      <c r="G29" s="75">
         <f>Scenarios!$D$20</f>
         <v/>
       </c>
@@ -11175,7 +11185,7 @@
           <t>Accrued liabilities and other</t>
         </is>
       </c>
-      <c r="B30" s="187" t="n">
+      <c r="B30" s="75" t="n">
         <v>662982</v>
       </c>
       <c r="C30" s="75">
@@ -11261,7 +11271,7 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B33" s="197" t="n">
+      <c r="B33" s="130" t="n">
         <v>1461096</v>
       </c>
       <c r="C33" s="130">
@@ -11518,7 +11528,7 @@
           <t>Terminal value (Gordon growth)</t>
         </is>
       </c>
-      <c r="B46" s="75">
+      <c r="B46" s="32">
         <f>G36*(1+Scenarios!D10)/(WACC!B36-Scenarios!D10)</f>
         <v/>
       </c>
@@ -11550,7 +11560,7 @@
           <t>(UFCF30 / EBITDA30) x (1+g) / (WACC-g)</t>
         </is>
       </c>
-      <c r="B48" s="94">
+      <c r="B48" s="32">
         <f>G36/B45*(1+Scenarios!D10)/(WACC!B36-Scenarios!D10)</f>
         <v/>
       </c>
@@ -11582,7 +11592,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B50" s="130">
+      <c r="B50" s="31">
         <f>B43+B49</f>
         <v/>
       </c>
@@ -11598,7 +11608,7 @@
           <t>Plus: cash &amp; equivalents (FY2025)</t>
         </is>
       </c>
-      <c r="B51" s="187" t="n">
+      <c r="B51" s="75" t="n">
         <v>1807202</v>
       </c>
       <c r="C51" s="176" t="n"/>
@@ -11613,7 +11623,7 @@
           <t>Less: total debt &amp; operating leases</t>
         </is>
       </c>
-      <c r="B52" s="187" t="n">
+      <c r="B52" s="75" t="n">
         <v>-1798441</v>
       </c>
       <c r="C52" s="176" t="n"/>
@@ -11697,7 +11707,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="B58" s="186" t="n">
+      <c r="B58" s="99" t="n">
         <v>100</v>
       </c>
       <c r="C58" s="176" t="n"/>
@@ -11728,7 +11738,7 @@
           <t>% of EV from terminal value</t>
         </is>
       </c>
-      <c r="B60" s="32">
+      <c r="B60" s="75">
         <f>B49/B50</f>
         <v/>
       </c>
@@ -11793,7 +11803,7 @@
           <t>Annual repurchase budget ($000) - base case</t>
         </is>
       </c>
-      <c r="B66" s="187" t="n">
+      <c r="B66" s="75" t="n">
         <v>500000</v>
       </c>
       <c r="C66" s="75">
@@ -11921,23 +11931,23 @@
         </is>
       </c>
       <c r="B71" s="176" t="n"/>
-      <c r="C71" s="32">
+      <c r="C71" s="75">
         <f>C70/C69</f>
         <v/>
       </c>
-      <c r="D71" s="32">
+      <c r="D71" s="75">
         <f>D70/D69</f>
         <v/>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="75">
         <f>E70/E69</f>
         <v/>
       </c>
-      <c r="F71" s="32">
+      <c r="F71" s="75">
         <f>F70/F69</f>
         <v/>
       </c>
-      <c r="G71" s="32">
+      <c r="G71" s="75">
         <f>G70/G69</f>
         <v/>
       </c>
@@ -11957,7 +11967,7 @@
           <t>Projected share price ($)</t>
         </is>
       </c>
-      <c r="B73" s="186" t="n">
+      <c r="B73" s="99" t="n">
         <v>100</v>
       </c>
       <c r="C73" s="99">
@@ -11987,26 +11997,26 @@
           <t>Shares retired (000)</t>
         </is>
       </c>
-      <c r="B74" s="75" t="n">
+      <c r="B74" s="187" t="n">
         <v>0</v>
       </c>
-      <c r="C74" s="75">
+      <c r="C74" s="187">
         <f>C70/C73</f>
         <v/>
       </c>
-      <c r="D74" s="75">
+      <c r="D74" s="187">
         <f>D70/D73</f>
         <v/>
       </c>
-      <c r="E74" s="75">
+      <c r="E74" s="187">
         <f>E70/E73</f>
         <v/>
       </c>
-      <c r="F74" s="75">
+      <c r="F74" s="187">
         <f>F70/F73</f>
         <v/>
       </c>
-      <c r="G74" s="75">
+      <c r="G74" s="187">
         <f>G70/G73</f>
         <v/>
       </c>
@@ -12020,23 +12030,23 @@
       <c r="B75" s="187" t="n">
         <v>111380</v>
       </c>
-      <c r="C75" s="75">
+      <c r="C75" s="187">
         <f>B75</f>
         <v/>
       </c>
-      <c r="D75" s="75">
+      <c r="D75" s="187">
         <f>C76</f>
         <v/>
       </c>
-      <c r="E75" s="75">
+      <c r="E75" s="187">
         <f>D76</f>
         <v/>
       </c>
-      <c r="F75" s="75">
+      <c r="F75" s="187">
         <f>E76</f>
         <v/>
       </c>
-      <c r="G75" s="75">
+      <c r="G75" s="187">
         <f>F76</f>
         <v/>
       </c>
@@ -12050,23 +12060,23 @@
       <c r="B76" s="197" t="n">
         <v>111380</v>
       </c>
-      <c r="C76" s="130">
+      <c r="C76" s="197">
         <f>C75-C74</f>
         <v/>
       </c>
-      <c r="D76" s="130">
+      <c r="D76" s="197">
         <f>D75-D74</f>
         <v/>
       </c>
-      <c r="E76" s="130">
+      <c r="E76" s="197">
         <f>E75-E74</f>
         <v/>
       </c>
-      <c r="F76" s="130">
+      <c r="F76" s="197">
         <f>F75-F74</f>
         <v/>
       </c>
-      <c r="G76" s="130">
+      <c r="G76" s="197">
         <f>G75-G74</f>
         <v/>
       </c>
@@ -12086,7 +12096,7 @@
           <t>Projected net income ($000)</t>
         </is>
       </c>
-      <c r="B78" s="187" t="n">
+      <c r="B78" s="75" t="n">
         <v>1579183</v>
       </c>
       <c r="C78" s="75">
@@ -12116,7 +12126,7 @@
           <t>Accretive EPS ($/share) = Net income / ending shares</t>
         </is>
       </c>
-      <c r="B79" s="202" t="n">
+      <c r="B79" s="150" t="n">
         <v>14.1783354282636</v>
       </c>
       <c r="C79" s="150">
@@ -12164,10 +12174,7 @@
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="61" t="n"/>
-      <c r="B82" s="176">
-        <f>B47</f>
-        <v/>
-      </c>
+      <c r="B82" s="176" t="n"/>
       <c r="C82" s="176" t="n"/>
       <c r="D82" s="176" t="n"/>
       <c r="E82" s="176" t="n"/>
@@ -12196,8 +12203,8 @@
           <t>Terminal value = Terminal EBITDA x exit multiple</t>
         </is>
       </c>
-      <c r="B84" s="75">
-        <f>B45*B82</f>
+      <c r="B84" s="94">
+        <f>B45*B83</f>
         <v/>
       </c>
       <c r="C84" s="176" t="n"/>
@@ -12228,7 +12235,7 @@
           <t>Enterprise value (exit method)</t>
         </is>
       </c>
-      <c r="B86" s="130">
+      <c r="B86" s="31">
         <f>B43+B85</f>
         <v/>
       </c>
@@ -12303,15 +12310,15 @@
           <t>Terminal value ($)</t>
         </is>
       </c>
-      <c r="B91" s="176">
-        <f>D46</f>
-        <v/>
-      </c>
-      <c r="C91" s="176">
-        <f>D83</f>
-        <v/>
-      </c>
-      <c r="D91" s="176">
+      <c r="B91" s="218">
+        <f>B46</f>
+        <v/>
+      </c>
+      <c r="C91" s="218">
+        <f>B84</f>
+        <v/>
+      </c>
+      <c r="D91" s="218">
         <f>B91-C91</f>
         <v/>
       </c>
@@ -12325,15 +12332,15 @@
           <t>Exit EV/EBITDA (implied vs selected)</t>
         </is>
       </c>
-      <c r="B92" s="176">
-        <f>D47</f>
-        <v/>
-      </c>
-      <c r="C92" s="176">
-        <f>D82</f>
-        <v/>
-      </c>
-      <c r="D92" s="176">
+      <c r="B92" s="219">
+        <f>B47</f>
+        <v/>
+      </c>
+      <c r="C92" s="219">
+        <f>B83</f>
+        <v/>
+      </c>
+      <c r="D92" s="219">
         <f>B92-C92</f>
         <v/>
       </c>
@@ -12349,7 +12356,7 @@
       </c>
       <c r="B93" s="176" t="n"/>
       <c r="C93" s="176" t="n"/>
-      <c r="D93" s="176">
+      <c r="D93" s="220">
         <f>(B91-C91)/B91</f>
         <v/>
       </c>
@@ -12363,15 +12370,15 @@
           <t>Implied share price</t>
         </is>
       </c>
-      <c r="B94" s="176">
-        <f>D57</f>
-        <v/>
-      </c>
-      <c r="C94" s="176">
-        <f>D87</f>
-        <v/>
-      </c>
-      <c r="D94" s="176">
+      <c r="B94" s="221">
+        <f>B57</f>
+        <v/>
+      </c>
+      <c r="C94" s="221">
+        <f>B87</f>
+        <v/>
+      </c>
+      <c r="D94" s="221">
         <f>B94-C94</f>
         <v/>
       </c>
@@ -12385,11 +12392,11 @@
           <t>Sanity check: multiples within ±1.5 turns?</t>
         </is>
       </c>
-      <c r="B95" s="176">
+      <c r="B95" s="218">
         <f>IF(ABS(D92)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C95" s="176">
+      <c r="C95" s="218">
         <f>TEXT(D92,"0.0")&amp;"x spread vs Gordon-implied exit"</f>
         <v/>
       </c>
@@ -12654,7 +12661,7 @@
           <t>FY2025A revenue</t>
         </is>
       </c>
-      <c r="B4" s="187" t="n">
+      <c r="B4" s="75" t="n">
         <v>11102600</v>
       </c>
       <c r="C4" s="176" t="n"/>
@@ -12716,7 +12723,7 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="B8" s="187" t="n">
+      <c r="B8" s="75" t="n">
         <v>1807202</v>
       </c>
       <c r="C8" s="176" t="n"/>
@@ -12746,7 +12753,7 @@
           <t>Current share price</t>
         </is>
       </c>
-      <c r="B10" s="186" t="n">
+      <c r="B10" s="99" t="n">
         <v>100</v>
       </c>
       <c r="C10" s="176" t="n"/>
@@ -13227,7 +13234,7 @@
           <t>All positive-EBITDA mean (ex-UAA; includes WSM / MOV / LZB)</t>
         </is>
       </c>
-      <c r="B40" s="115">
+      <c r="B40" s="222">
         <f>AVERAGE(B19,B21,B22,B23,B24,B25,B26,B27,B28,B29)</f>
         <v/>
       </c>
@@ -13440,17 +13447,17 @@
           <t>EV / EBITDA (FY2030E terminal)</t>
         </is>
       </c>
-      <c r="B57" s="115" t="n">
+      <c r="B57" s="222" t="n">
         <v>5</v>
       </c>
-      <c r="C57" s="115" t="n">
+      <c r="C57" s="222" t="n">
         <v>8</v>
       </c>
-      <c r="D57" s="121">
+      <c r="D57" s="222">
         <f>(B6*B57+B8)/B9</f>
         <v/>
       </c>
-      <c r="E57" s="121">
+      <c r="E57" s="222">
         <f>(B6*C57+B8)/B9</f>
         <v/>
       </c>
@@ -13463,12 +13470,12 @@
           <t>DCF exit method (Gordon-implied on FY2030E EBITDA)</t>
         </is>
       </c>
-      <c r="B58" s="115">
+      <c r="B58" s="222">
         <f>DCF!B82</f>
         <v/>
       </c>
       <c r="C58" s="176" t="n"/>
-      <c r="D58" s="121">
+      <c r="D58" s="222">
         <f>(B6*B58+B8)/B9</f>
         <v/>
       </c>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -510,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1090,6 +1090,7 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1855,6 +1856,11 @@
       <text>
         <t>Source: NASDAQ
 https://www.nasdaq.com/market-activity/stocks/lulu</t>
+      </text>
+    </comment>
+    <comment ref="B79" authorId="0" shapeId="0">
+      <text>
+        <t>FY25 reported diluted EPS (10-K).</t>
       </text>
     </comment>
     <comment ref="B83" authorId="0" shapeId="0">
@@ -2590,7 +2596,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="B4" s="75" t="n">
+      <c r="B4" s="32" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -2726,7 +2732,7 @@
           <t>Target Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B19" s="75">
+      <c r="B19" s="28">
         <f>B17/B18</f>
         <v/>
       </c>
@@ -2802,7 +2808,7 @@
           <t>Cost of Equity</t>
         </is>
       </c>
-      <c r="B27" s="130">
+      <c r="B27" s="31">
         <f>B3+B24*B4</f>
         <v/>
       </c>
@@ -2899,7 +2905,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3273,13 +3279,13 @@
         </is>
       </c>
       <c r="B20" s="176" t="n"/>
-      <c r="C20" s="75" t="n">
+      <c r="C20" s="32" t="n">
         <v>0.06</v>
       </c>
-      <c r="D20" s="75" t="n">
+      <c r="D20" s="32" t="n">
         <v>0.06</v>
       </c>
-      <c r="E20" s="75" t="n">
+      <c r="E20" s="32" t="n">
         <v>0.06</v>
       </c>
       <c r="F20" s="176" t="n"/>
@@ -3293,10 +3299,10 @@
       </c>
       <c r="B21" s="176" t="n"/>
       <c r="C21" s="75" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="D21" s="75" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="E21" s="75" t="n">
         <v>0</v>
@@ -6753,11 +6759,11 @@
       </c>
       <c r="B183" s="176" t="n"/>
       <c r="C183" s="187">
-        <f>$B$197-C21/DCF!C$73</f>
+        <f>$B$197-C21/$B$198</f>
         <v/>
       </c>
       <c r="D183" s="187">
-        <f>$B$197-D21/DCF!C$73</f>
+        <f>$B$197-D21/$B$198</f>
         <v/>
       </c>
       <c r="E183" s="187">
@@ -6775,11 +6781,11 @@
       </c>
       <c r="B184" s="176" t="n"/>
       <c r="C184" s="187">
-        <f>C183-C21/DCF!D$73</f>
+        <f>C183-C21/$B$199</f>
         <v/>
       </c>
       <c r="D184" s="187">
-        <f>D183-D21/DCF!D$73</f>
+        <f>D183-D21/$B$199</f>
         <v/>
       </c>
       <c r="E184" s="187">
@@ -6797,11 +6803,11 @@
       </c>
       <c r="B185" s="176" t="n"/>
       <c r="C185" s="187">
-        <f>C184-C21/DCF!E$73</f>
+        <f>C184-C21/$B$200</f>
         <v/>
       </c>
       <c r="D185" s="187">
-        <f>D184-D21/DCF!E$73</f>
+        <f>D184-D21/$B$200</f>
         <v/>
       </c>
       <c r="E185" s="187">
@@ -6819,11 +6825,11 @@
       </c>
       <c r="B186" s="176" t="n"/>
       <c r="C186" s="187">
-        <f>C185-C21/DCF!F$73</f>
+        <f>C185-C21/$B$201</f>
         <v/>
       </c>
       <c r="D186" s="187">
-        <f>D185-D21/DCF!F$73</f>
+        <f>D185-D21/$B$201</f>
         <v/>
       </c>
       <c r="E186" s="187">
@@ -6841,11 +6847,11 @@
       </c>
       <c r="B187" s="176" t="n"/>
       <c r="C187" s="187">
-        <f>C186-C21/DCF!G$73</f>
+        <f>C186-C21/$B$202</f>
         <v/>
       </c>
       <c r="D187" s="187">
-        <f>D186-D21/DCF!G$73</f>
+        <f>D186-D21/$B$202</f>
         <v/>
       </c>
       <c r="E187" s="187">
@@ -7012,6 +7018,56 @@
       </c>
       <c r="B197" s="216" t="n">
         <v>119068</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Repurchase avg price Y1 ($/sh)</t>
+        </is>
+      </c>
+      <c r="B198" s="215" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Repurchase avg price Y2 ($/sh)</t>
+        </is>
+      </c>
+      <c r="B199" s="215" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Repurchase avg price Y3 ($/sh)</t>
+        </is>
+      </c>
+      <c r="B200" s="215" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Repurchase avg price Y4 ($/sh)</t>
+        </is>
+      </c>
+      <c r="B201" s="215" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Repurchase avg price Y5 ($/sh)</t>
+        </is>
+      </c>
+      <c r="B202" s="215" t="n">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -9924,8 +9980,9 @@
           <t>Store-channel EBIT (= Rev x store margin)</t>
         </is>
       </c>
-      <c r="B31" s="32" t="n">
-        <v>939252.384</v>
+      <c r="B31" s="75">
+        <f>C31</f>
+        <v/>
       </c>
       <c r="C31" s="32">
         <f>C28*B$9</f>
@@ -9954,8 +10011,9 @@
           <t>E-commerce EBIT (= Rev x e-comm margin)</t>
         </is>
       </c>
-      <c r="B32" s="32" t="n">
-        <v>1160812.492</v>
+      <c r="B32" s="75">
+        <f>C32</f>
+        <v/>
       </c>
       <c r="C32" s="32">
         <f>C29*B$10</f>
@@ -9984,8 +10042,9 @@
           <t>Other-channels EBIT (= Rev x other margin)</t>
         </is>
       </c>
-      <c r="B33" s="32" t="n">
-        <v>103208.469</v>
+      <c r="B33" s="75">
+        <f>C33</f>
+        <v/>
       </c>
       <c r="C33" s="32">
         <f>C30*B$11</f>
@@ -10042,8 +10101,9 @@
           <t>EBIT after channel mix</t>
         </is>
       </c>
-      <c r="B35" s="31" t="n">
-        <v>2203273.345</v>
+      <c r="B35" s="130">
+        <f>C35</f>
+        <v/>
       </c>
       <c r="C35" s="31">
         <f>C34</f>
@@ -10145,7 +10205,7 @@
         </is>
       </c>
       <c r="B39" s="32" t="n">
-        <v>0.2946847649213503</v>
+        <v>0.295</v>
       </c>
       <c r="C39" s="32">
         <f>$B$39+(C$12-$B$39)*1/5</f>
@@ -10550,8 +10610,9 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
-        <v>0.566005440167168</v>
+      <c r="B7" s="32">
+        <f>(B6-B8)/B6</f>
+        <v/>
       </c>
       <c r="C7" s="32">
         <f>Scenarios!$D$14</f>
@@ -10694,8 +10755,9 @@
           <t>Reported EBIT margin % (incl. FY26 refund)</t>
         </is>
       </c>
-      <c r="B12" s="32" t="n">
-        <v>0.1991078666258354</v>
+      <c r="B12" s="32">
+        <f>B11/B6</f>
+        <v/>
       </c>
       <c r="C12" s="32">
         <f>C11/C6</f>
@@ -10915,8 +10977,9 @@
           <t>DSO (days)</t>
         </is>
       </c>
-      <c r="B21" s="193" t="n">
-        <v>6.267883648875038</v>
+      <c r="B21" s="193">
+        <f>Scenarios!$D$15</f>
+        <v/>
       </c>
       <c r="C21" s="193">
         <f>Scenarios!D65</f>
@@ -10975,8 +11038,9 @@
           <t>DIO (days)</t>
         </is>
       </c>
-      <c r="B23" s="193" t="n">
-        <v>128.8324100108167</v>
+      <c r="B23" s="193">
+        <f>Scenarios!$D$16</f>
+        <v/>
       </c>
       <c r="C23" s="193">
         <f>Scenarios!D75</f>
@@ -11035,8 +11099,9 @@
           <t>DPO (days)</t>
         </is>
       </c>
-      <c r="B25" s="193" t="n">
-        <v>25.10521290169407</v>
+      <c r="B25" s="193">
+        <f>Scenarios!$D$18</f>
+        <v/>
       </c>
       <c r="C25" s="193">
         <f>Scenarios!D85</f>
@@ -11095,8 +11160,9 @@
           <t>Prepaid expenses (% of revenue)</t>
         </is>
       </c>
-      <c r="B27" s="32" t="n">
-        <v>0.05080692810692991</v>
+      <c r="B27" s="32">
+        <f>Scenarios!$D$19</f>
+        <v/>
       </c>
       <c r="C27" s="32">
         <f>Scenarios!$D$19</f>
@@ -11155,8 +11221,9 @@
           <t>Accrued liabilities (% of revenue)</t>
         </is>
       </c>
-      <c r="B29" s="75" t="n">
-        <v>0.05971412101669879</v>
+      <c r="B29" s="32">
+        <f>Scenarios!$D$20</f>
+        <v/>
       </c>
       <c r="C29" s="75">
         <f>Scenarios!$D$20</f>
@@ -11803,27 +11870,28 @@
           <t>Annual repurchase budget ($000) - base case</t>
         </is>
       </c>
-      <c r="B66" s="75" t="n">
-        <v>500000</v>
+      <c r="B66" s="75">
+        <f>Scenarios!$D$21</f>
+        <v/>
       </c>
       <c r="C66" s="75">
-        <f>B66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
       <c r="D66" s="75">
-        <f>B66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
       <c r="E66" s="75">
-        <f>B66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
       <c r="F66" s="75">
-        <f>B66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
       <c r="G66" s="75">
-        <f>B66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
     </row>
@@ -11904,23 +11972,23 @@
         <v>0</v>
       </c>
       <c r="C70" s="75">
-        <f>C66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
       <c r="D70" s="75">
-        <f>D66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
       <c r="E70" s="75">
-        <f>E66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
       <c r="F70" s="75">
-        <f>F66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
       <c r="G70" s="75">
-        <f>G66</f>
+        <f>Scenarios!$D$21</f>
         <v/>
       </c>
     </row>
@@ -11971,23 +12039,23 @@
         <v>100</v>
       </c>
       <c r="C73" s="99">
-        <f>B73*(1+B67)</f>
+        <f>Scenarios!$B$198</f>
         <v/>
       </c>
       <c r="D73" s="99">
-        <f>B73*(1+B67)</f>
+        <f>Scenarios!$B$199</f>
         <v/>
       </c>
       <c r="E73" s="99">
-        <f>D73*(1+B67)</f>
+        <f>Scenarios!$B$200</f>
         <v/>
       </c>
       <c r="F73" s="99">
-        <f>E73*(1+B67)</f>
+        <f>Scenarios!$B$201</f>
         <v/>
       </c>
       <c r="G73" s="99">
-        <f>F73*(1+B67)</f>
+        <f>Scenarios!$B$202</f>
         <v/>
       </c>
     </row>
@@ -12031,7 +12099,7 @@
         <v>111380</v>
       </c>
       <c r="C75" s="187">
-        <f>B75</f>
+        <f>Scenarios!$D$197</f>
         <v/>
       </c>
       <c r="D75" s="187">
@@ -12061,23 +12129,23 @@
         <v>111380</v>
       </c>
       <c r="C76" s="197">
-        <f>C75-C74</f>
+        <f>Scenarios!$D$183</f>
         <v/>
       </c>
       <c r="D76" s="197">
-        <f>D75-D74</f>
+        <f>Scenarios!$D$184</f>
         <v/>
       </c>
       <c r="E76" s="197">
-        <f>E75-E74</f>
+        <f>Scenarios!$D$185</f>
         <v/>
       </c>
       <c r="F76" s="197">
-        <f>F75-F74</f>
+        <f>Scenarios!$D$186</f>
         <v/>
       </c>
       <c r="G76" s="197">
-        <f>G75-G74</f>
+        <f>Scenarios!$D$187</f>
         <v/>
       </c>
     </row>
@@ -12100,23 +12168,23 @@
         <v>1579183</v>
       </c>
       <c r="C78" s="75">
-        <f>('NOPAT Bridge'!C36-'NOPAT Bridge'!C23)*(1-'NOPAT Bridge'!C$39)</f>
+        <f>Scenarios!$D$143</f>
         <v/>
       </c>
       <c r="D78" s="75">
-        <f>('NOPAT Bridge'!D36-'NOPAT Bridge'!D23)*(1-'NOPAT Bridge'!D$39)</f>
+        <f>Scenarios!$D$144</f>
         <v/>
       </c>
       <c r="E78" s="75">
-        <f>('NOPAT Bridge'!E36-'NOPAT Bridge'!E23)*(1-'NOPAT Bridge'!E$39)</f>
+        <f>Scenarios!$D$145</f>
         <v/>
       </c>
       <c r="F78" s="75">
-        <f>('NOPAT Bridge'!F36-'NOPAT Bridge'!F23)*(1-'NOPAT Bridge'!F$39)</f>
+        <f>Scenarios!$D$146</f>
         <v/>
       </c>
       <c r="G78" s="75">
-        <f>('NOPAT Bridge'!G36-'NOPAT Bridge'!G23)*(1-'NOPAT Bridge'!G$39)</f>
+        <f>Scenarios!$D$147</f>
         <v/>
       </c>
     </row>
@@ -12127,26 +12195,26 @@
         </is>
       </c>
       <c r="B79" s="150" t="n">
-        <v>14.1783354282636</v>
+        <v>14.18</v>
       </c>
       <c r="C79" s="150">
-        <f>C78/C76</f>
+        <f>Scenarios!$D$188</f>
         <v/>
       </c>
       <c r="D79" s="150">
-        <f>D78/D76</f>
+        <f>Scenarios!$D$189</f>
         <v/>
       </c>
       <c r="E79" s="150">
-        <f>E78/E76</f>
+        <f>Scenarios!$D$190</f>
         <v/>
       </c>
       <c r="F79" s="150">
-        <f>F78/F76</f>
+        <f>Scenarios!$D$191</f>
         <v/>
       </c>
       <c r="G79" s="150">
-        <f>G78/G76</f>
+        <f>Scenarios!$D$192</f>
         <v/>
       </c>
     </row>
@@ -12174,7 +12242,10 @@
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="61" t="n"/>
-      <c r="B82" s="176" t="n"/>
+      <c r="B82" s="218">
+        <f>B47</f>
+        <v/>
+      </c>
       <c r="C82" s="176" t="n"/>
       <c r="D82" s="176" t="n"/>
       <c r="E82" s="176" t="n"/>
@@ -12204,7 +12275,7 @@
         </is>
       </c>
       <c r="B84" s="94">
-        <f>B45*B83</f>
+        <f>B45*B82</f>
         <v/>
       </c>
       <c r="C84" s="176" t="n"/>
@@ -12252,7 +12323,7 @@
         </is>
       </c>
       <c r="B87" s="99">
-        <f>(B86+B51+B52)/B56</f>
+        <f>(B85+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="C87" s="176" t="n"/>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="169" formatCode="0.0x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="71">
+  <fonts count="72">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -446,6 +446,10 @@
       <i val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -510,7 +514,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1091,6 +1095,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1639,8 +1645,7 @@
     </comment>
     <comment ref="B49" authorId="0" shapeId="0">
       <text>
-        <t>Normalized EBIT &amp; t_operating
-Source: NOPAT = EBIT × (1 − 30%) flat sc_tax.</t>
+        <t>EBIT_norm × (1 − t_operating).</t>
       </text>
     </comment>
     <comment ref="B50" authorId="0" shapeId="0">
@@ -1833,6 +1838,12 @@
 https://fred.stlouisfed.org/series/GDPC1</t>
       </text>
     </comment>
+    <comment ref="B46" authorId="0" shapeId="0">
+      <text>
+        <t>=E45
+Source: =E83</t>
+      </text>
+    </comment>
     <comment ref="B51" authorId="0" shapeId="0">
       <text>
         <t>Source: 10-K
@@ -1977,11 +1988,6 @@
 https://www.nasdaq.com/market-activity/stocks/lulu</t>
       </text>
     </comment>
-    <comment ref="B18" authorId="0" shapeId="0">
-      <text>
-        <t>Source: Source</t>
-      </text>
-    </comment>
     <comment ref="B19" authorId="0" shapeId="0">
       <text>
         <t>PitchBook EV/TTM EBITDA comp.</t>
@@ -2071,11 +2077,6 @@
     <comment ref="B40" authorId="0" shapeId="0">
       <text>
         <t>Wider tape incl. adjacent retail.</t>
-      </text>
-    </comment>
-    <comment ref="B56" authorId="0" shapeId="0">
-      <text>
-        <t>Source: Source</t>
       </text>
     </comment>
     <comment ref="B57" authorId="0" shapeId="0">
@@ -2554,7 +2555,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2571,6 +2572,7 @@
         </is>
       </c>
       <c r="B1" s="184" t="n"/>
+      <c r="C1" s="176" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="127" t="inlineStr">
@@ -2579,6 +2581,11 @@
         </is>
       </c>
       <c r="B2" s="176" t="n"/>
+      <c r="C2" s="224" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
@@ -2589,6 +2596,11 @@
       <c r="B3" s="32" t="n">
         <v>0.048</v>
       </c>
+      <c r="C3" s="188" t="inlineStr">
+        <is>
+          <t>FRED: 10Y Treasury (DGS10)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -2599,6 +2611,11 @@
       <c r="B4" s="32" t="n">
         <v>0.06</v>
       </c>
+      <c r="C4" s="188" t="inlineStr">
+        <is>
+          <t>Damodaran: Historical Implied ERP</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -2608,11 +2625,17 @@
       </c>
       <c r="B5" s="32" t="n">
         <v>0.3</v>
+      </c>
+      <c r="C5" s="188" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="176" t="n"/>
       <c r="B6" s="176" t="n"/>
+      <c r="C6" s="176" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="127" t="inlineStr">
@@ -2621,6 +2644,7 @@
         </is>
       </c>
       <c r="B7" s="176" t="n"/>
+      <c r="C7" s="176" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -2631,6 +2655,11 @@
       <c r="B8" s="99" t="n">
         <v>100</v>
       </c>
+      <c r="C8" s="188" t="inlineStr">
+        <is>
+          <t>NASDAQ LULU last sale (current price)</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -2641,6 +2670,11 @@
       <c r="B9" s="187" t="n">
         <v>111380</v>
       </c>
+      <c r="C9" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: shares outstanding</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="68" t="inlineStr">
@@ -2652,6 +2686,7 @@
         <f>B8*B9</f>
         <v/>
       </c>
+      <c r="C10" s="176" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
@@ -2662,6 +2697,7 @@
       <c r="B11" s="75" t="n">
         <v>1798441</v>
       </c>
+      <c r="C11" s="176" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -2672,6 +2708,7 @@
       <c r="B12" s="75" t="n">
         <v>0</v>
       </c>
+      <c r="C12" s="176" t="n"/>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="68" t="inlineStr">
@@ -2683,10 +2720,12 @@
         <f>B11+B12</f>
         <v/>
       </c>
+      <c r="C13" s="176" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="176" t="n"/>
       <c r="B14" s="176" t="n"/>
+      <c r="C14" s="176" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="127" t="inlineStr">
@@ -2695,6 +2734,7 @@
         </is>
       </c>
       <c r="B15" s="176" t="n"/>
+      <c r="C15" s="176" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -2705,6 +2745,11 @@
       <c r="B16" s="28" t="n">
         <v>0.86</v>
       </c>
+      <c r="C16" s="188" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: LULU Beta (5Y Monthly)</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -2715,6 +2760,7 @@
       <c r="B17" s="75" t="n">
         <v>2140000</v>
       </c>
+      <c r="C17" s="176" t="n"/>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
@@ -2725,6 +2771,7 @@
       <c r="B18" s="75" t="n">
         <v>11140000</v>
       </c>
+      <c r="C18" s="176" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -2736,6 +2783,7 @@
         <f>B17/B18</f>
         <v/>
       </c>
+      <c r="C19" s="176" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -2746,6 +2794,11 @@
       <c r="B20" s="28" t="n">
         <v>0.4469</v>
       </c>
+      <c r="C20" s="188" t="inlineStr">
+        <is>
+          <t>Yahoo Finance: Total Debt/Equity (mrq)</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -2757,6 +2810,7 @@
         <f>B16/(1+(1-B5)*B19)</f>
         <v/>
       </c>
+      <c r="C21" s="176" t="n"/>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -2768,6 +2822,7 @@
         <f>B13/B10</f>
         <v/>
       </c>
+      <c r="C22" s="176" t="n"/>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
@@ -2778,6 +2833,7 @@
       <c r="B23" s="28" t="n">
         <v>0.95</v>
       </c>
+      <c r="C23" s="176" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="68" t="inlineStr">
@@ -2789,10 +2845,12 @@
         <f>B21*(1+(1-B5)*B22)</f>
         <v/>
       </c>
+      <c r="C24" s="176" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="26" t="n"/>
       <c r="B25" s="176" t="n"/>
+      <c r="C25" s="176" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="127" t="inlineStr">
@@ -2801,6 +2859,7 @@
         </is>
       </c>
       <c r="B26" s="176" t="n"/>
+      <c r="C26" s="176" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="68" t="inlineStr">
@@ -2812,10 +2871,12 @@
         <f>B3+B24*B4</f>
         <v/>
       </c>
+      <c r="C27" s="176" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="176" t="n"/>
       <c r="B28" s="176" t="n"/>
+      <c r="C28" s="176" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="127" t="inlineStr">
@@ -2824,6 +2885,7 @@
         </is>
       </c>
       <c r="B29" s="176" t="n"/>
+      <c r="C29" s="176" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
@@ -2834,6 +2896,7 @@
       <c r="B30" s="32" t="n">
         <v>0.05</v>
       </c>
+      <c r="C30" s="176" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -2845,10 +2908,12 @@
         <f>B30*(1-B5)</f>
         <v/>
       </c>
+      <c r="C31" s="176" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="176" t="n"/>
       <c r="B32" s="176" t="n"/>
+      <c r="C32" s="176" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="127" t="inlineStr">
@@ -2857,6 +2922,7 @@
         </is>
       </c>
       <c r="B33" s="176" t="n"/>
+      <c r="C33" s="176" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
@@ -2868,6 +2934,7 @@
         <f>B10/(B10+B13)</f>
         <v/>
       </c>
+      <c r="C34" s="176" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="16" t="inlineStr">
@@ -2879,6 +2946,7 @@
         <f>B13/(B10+B13)</f>
         <v/>
       </c>
+      <c r="C35" s="176" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="68" t="inlineStr">
@@ -2890,10 +2958,20 @@
         <f>B34*B27+B35*B31</f>
         <v/>
       </c>
+      <c r="C36" s="176" t="n"/>
     </row>
     <row r="39" ht="28" customHeight="1"/>
     <row r="40" ht="28" customHeight="1"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -2933,7 +3011,11 @@
     </row>
     <row r="2">
       <c r="A2" s="176" t="n"/>
-      <c r="B2" s="176" t="n"/>
+      <c r="B2" s="224" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
       <c r="C2" s="189" t="inlineStr">
         <is>
           <t>Bear</t>
@@ -2971,7 +3053,11 @@
           <t>FY26 Rev Growth</t>
         </is>
       </c>
-      <c r="B4" s="176" t="n"/>
+      <c r="B4" s="188" t="inlineStr">
+        <is>
+          <t>LULU Q2 FY2026 earnings release</t>
+        </is>
+      </c>
       <c r="C4" s="32" t="n">
         <v>-0.09</v>
       </c>
@@ -2990,7 +3076,11 @@
           <t>FY27-30 Rev Growth</t>
         </is>
       </c>
-      <c r="B5" s="176" t="n"/>
+      <c r="B5" s="188" t="inlineStr">
+        <is>
+          <t>StockAnalysis: LULU 3Y revenue forecast</t>
+        </is>
+      </c>
       <c r="C5" s="32" t="n">
         <v>-0.01</v>
       </c>
@@ -3009,7 +3099,11 @@
           <t>Run-Rate EBIT Margin</t>
         </is>
       </c>
-      <c r="B6" s="176" t="n"/>
+      <c r="B6" s="188" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 release: run-rate operating margin</t>
+        </is>
+      </c>
       <c r="C6" s="32" t="n">
         <v>0.12</v>
       </c>
@@ -3028,7 +3122,11 @@
           <t>FY26 Tariff Refund</t>
         </is>
       </c>
-      <c r="B7" s="176" t="n"/>
+      <c r="B7" s="188" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 release: $134.5M IEEPA tariff refunds</t>
+        </is>
+      </c>
       <c r="C7" s="75" t="n">
         <v>134500</v>
       </c>
@@ -3047,7 +3145,11 @@
           <t>Terminal EBIT Margin</t>
         </is>
       </c>
-      <c r="B8" s="176" t="n"/>
+      <c r="B8" s="188" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: operating margin benchmark</t>
+        </is>
+      </c>
       <c r="C8" s="32" t="n">
         <v>0.12</v>
       </c>
@@ -3066,7 +3168,11 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="B9" s="176" t="n"/>
+      <c r="B9" s="188" t="inlineStr">
+        <is>
+          <t>WACC tab: CAPM build</t>
+        </is>
+      </c>
       <c r="C9" s="32" t="n">
         <v>0.11</v>
       </c>
@@ -3086,7 +3192,11 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="B10" s="176" t="n"/>
+      <c r="B10" s="188" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
       <c r="C10" s="32" t="n">
         <v>0.015</v>
       </c>
@@ -3105,7 +3215,11 @@
           <t>Cash tax rate</t>
         </is>
       </c>
-      <c r="B11" s="176" t="n"/>
+      <c r="B11" s="188" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
+        </is>
+      </c>
       <c r="C11" s="32" t="n">
         <v>0.32</v>
       </c>
@@ -3124,7 +3238,11 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B12" s="176" t="n"/>
+      <c r="B12" s="188" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K)</t>
+        </is>
+      </c>
       <c r="C12" s="32" t="n">
         <v>0.045</v>
       </c>
@@ -3144,7 +3262,11 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B13" s="176" t="n"/>
+      <c r="B13" s="188" t="inlineStr">
+        <is>
+          <t>LULU 10-K: 2026 capex guide $725–745M Also: Q2 FY2026 outlook: $10.350B–$10.500B sales</t>
+        </is>
+      </c>
       <c r="C13" s="32" t="n">
         <v>0.07000000000000001</v>
       </c>
@@ -3163,7 +3285,11 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B14" s="176" t="n"/>
+      <c r="B14" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Gross profit &amp; COGS</t>
+        </is>
+      </c>
       <c r="C14" s="32" t="n">
         <v>0.5600000000000001</v>
       </c>
@@ -3183,7 +3309,11 @@
           <t>DSO (days)</t>
         </is>
       </c>
-      <c r="B15" s="176" t="n"/>
+      <c r="B15" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accounts receivable, net</t>
+        </is>
+      </c>
       <c r="C15" s="193" t="n">
         <v>6.3</v>
       </c>
@@ -3202,7 +3332,11 @@
           <t>FY25 DIO anchor (days)</t>
         </is>
       </c>
-      <c r="B16" s="176" t="n"/>
+      <c r="B16" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Inventories &amp; COGS</t>
+        </is>
+      </c>
       <c r="C16" s="193" t="n">
         <v>128.8</v>
       </c>
@@ -3221,7 +3355,11 @@
           <t>DIO decline (days / forecast yr)</t>
         </is>
       </c>
-      <c r="B17" s="176" t="n"/>
+      <c r="B17" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: inventory &amp; markdown outlook</t>
+        </is>
+      </c>
       <c r="C17" s="193" t="n">
         <v>1</v>
       </c>
@@ -3240,7 +3378,11 @@
           <t>DPO (days)</t>
         </is>
       </c>
-      <c r="B18" s="176" t="n"/>
+      <c r="B18" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accounts payable &amp; COGS</t>
+        </is>
+      </c>
       <c r="C18" s="193" t="n">
         <v>25.1</v>
       </c>
@@ -3259,7 +3401,11 @@
           <t>Prepaid expenses (% of revenue)</t>
         </is>
       </c>
-      <c r="B19" s="176" t="n"/>
+      <c r="B19" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: other current assets (residual)</t>
+        </is>
+      </c>
       <c r="C19" s="32" t="n">
         <v>0.051</v>
       </c>
@@ -3278,7 +3424,11 @@
           <t>Accrued liabilities (% of revenue)</t>
         </is>
       </c>
-      <c r="B20" s="176" t="n"/>
+      <c r="B20" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accrued liabilities and other</t>
+        </is>
+      </c>
       <c r="C20" s="32" t="n">
         <v>0.06</v>
       </c>
@@ -3294,10 +3444,14 @@
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
         <is>
-          <t>Pitch CFF: fixed buyback ($k/yr) bear/base</t>
-        </is>
-      </c>
-      <c r="B21" s="176" t="n"/>
+          <t>Fixed buyback ($k/yr)</t>
+        </is>
+      </c>
+      <c r="B21" s="188" t="inlineStr">
+        <is>
+          <t>Pitch deck: $750M/yr buyback (bear/base)</t>
+        </is>
+      </c>
       <c r="C21" s="75" t="n">
         <v>750000</v>
       </c>
@@ -3313,10 +3467,14 @@
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>Pitch CFF: % of FCF to buybacks (bull)</t>
-        </is>
-      </c>
-      <c r="B22" s="176" t="n"/>
+          <t>% of FCF to buybacks (bull)</t>
+        </is>
+      </c>
+      <c r="B22" s="188" t="inlineStr">
+        <is>
+          <t>Pitch deck: 75% of FCF to buybacks (bull case)</t>
+        </is>
+      </c>
       <c r="C22" s="32" t="n">
         <v>0</v>
       </c>
@@ -5782,7 +5940,11 @@
           <t>Other income - year 1</t>
         </is>
       </c>
-      <c r="B138" s="176" t="n"/>
+      <c r="B138" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: other income</t>
+        </is>
+      </c>
       <c r="C138" s="187" t="n">
         <v>45000</v>
       </c>
@@ -5801,7 +5963,11 @@
           <t>Other income - year 2</t>
         </is>
       </c>
-      <c r="B139" s="176" t="n"/>
+      <c r="B139" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: other income</t>
+        </is>
+      </c>
       <c r="C139" s="187" t="n">
         <v>40000</v>
       </c>
@@ -5820,7 +5986,11 @@
           <t>Other income - year 3</t>
         </is>
       </c>
-      <c r="B140" s="176" t="n"/>
+      <c r="B140" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: other income</t>
+        </is>
+      </c>
       <c r="C140" s="187" t="n">
         <v>35000</v>
       </c>
@@ -5839,7 +6009,11 @@
           <t>Other income - year 4</t>
         </is>
       </c>
-      <c r="B141" s="176" t="n"/>
+      <c r="B141" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: other income</t>
+        </is>
+      </c>
       <c r="C141" s="187" t="n">
         <v>30000</v>
       </c>
@@ -5858,7 +6032,11 @@
           <t>Other income - year 5</t>
         </is>
       </c>
-      <c r="B142" s="176" t="n"/>
+      <c r="B142" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: other income</t>
+        </is>
+      </c>
       <c r="C142" s="187" t="n">
         <v>25000</v>
       </c>
@@ -6767,7 +6945,7 @@
         <v/>
       </c>
       <c r="E183" s="187">
-        <f>Scenarios!D197-ROUND(E22*E153,0)/100</f>
+        <f>$B$197-ROUND(E22*E153,0)/$B$198</f>
         <v/>
       </c>
       <c r="F183" s="176" t="n"/>
@@ -6789,7 +6967,7 @@
         <v/>
       </c>
       <c r="E184" s="187">
-        <f>E183-ROUND(E22*E154,0)/108</f>
+        <f>E183-ROUND(E22*E154,0)/$B$199</f>
         <v/>
       </c>
       <c r="F184" s="176" t="n"/>
@@ -6811,7 +6989,7 @@
         <v/>
       </c>
       <c r="E185" s="187">
-        <f>E184-ROUND(E22*E155,0)/115</f>
+        <f>E184-ROUND(E22*E155,0)/$B$200</f>
         <v/>
       </c>
       <c r="F185" s="176" t="n"/>
@@ -6833,7 +7011,7 @@
         <v/>
       </c>
       <c r="E186" s="187">
-        <f>E185-ROUND(E22*E156,0)/122</f>
+        <f>E185-ROUND(E22*E156,0)/$B$201</f>
         <v/>
       </c>
       <c r="F186" s="176" t="n"/>
@@ -6855,7 +7033,7 @@
         <v/>
       </c>
       <c r="E187" s="187">
-        <f>E186-ROUND(E22*E157,0)/130</f>
+        <f>E186-ROUND(E22*E157,0)/$B$202</f>
         <v/>
       </c>
       <c r="F187" s="176" t="n"/>
@@ -6972,7 +7150,11 @@
       <c r="G192" s="176" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="26" t="n"/>
+      <c r="A193" s="26" t="inlineStr">
+        <is>
+          <t>Assumptions (FY25 anchors &amp; repurchase prices)</t>
+        </is>
+      </c>
       <c r="B193" s="176" t="n"/>
       <c r="C193" s="176" t="n"/>
       <c r="D193" s="176" t="n"/>
@@ -6981,96 +7163,165 @@
       <c r="G193" s="176" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="176" t="inlineStr">
         <is>
           <t>FY25 total assets ($000)</t>
         </is>
       </c>
-      <c r="B194" s="215" t="n">
+      <c r="B194" s="218" t="n">
         <v>8456743</v>
       </c>
+      <c r="C194" s="176" t="n"/>
+      <c r="D194" s="176" t="n"/>
+      <c r="E194" s="176" t="n"/>
+      <c r="F194" s="176" t="n"/>
+      <c r="G194" s="176" t="n"/>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="176" t="inlineStr">
         <is>
           <t>FY25 total liabilities ($000)</t>
         </is>
       </c>
-      <c r="B195" s="215" t="n">
+      <c r="B195" s="218" t="n">
         <v>3494903</v>
       </c>
+      <c r="C195" s="176" t="n"/>
+      <c r="D195" s="176" t="n"/>
+      <c r="E195" s="176" t="n"/>
+      <c r="F195" s="176" t="n"/>
+      <c r="G195" s="176" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="176" t="inlineStr">
         <is>
           <t>FY25 total equity ($000)</t>
         </is>
       </c>
-      <c r="B196" s="215" t="n">
+      <c r="B196" s="218" t="n">
         <v>4961840</v>
       </c>
+      <c r="C196" s="176" t="n"/>
+      <c r="D196" s="176" t="n"/>
+      <c r="E196" s="176" t="n"/>
+      <c r="F196" s="176" t="n"/>
+      <c r="G196" s="176" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="176" t="inlineStr">
         <is>
           <t>FY25 diluted shares (000)</t>
         </is>
       </c>
-      <c r="B197" s="216" t="n">
+      <c r="B197" s="225" t="n">
         <v>119068</v>
       </c>
+      <c r="C197" s="176" t="n"/>
+      <c r="D197" s="176" t="n"/>
+      <c r="E197" s="176" t="n"/>
+      <c r="F197" s="176" t="n"/>
+      <c r="G197" s="176" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
+      <c r="A198" s="176" t="inlineStr">
         <is>
           <t>Repurchase avg price Y1 ($/sh)</t>
         </is>
       </c>
-      <c r="B198" s="215" t="n">
+      <c r="B198" s="218" t="n">
         <v>100</v>
       </c>
+      <c r="C198" s="176" t="n"/>
+      <c r="D198" s="176" t="n"/>
+      <c r="E198" s="176" t="n"/>
+      <c r="F198" s="176" t="n"/>
+      <c r="G198" s="176" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
+      <c r="A199" s="176" t="inlineStr">
         <is>
           <t>Repurchase avg price Y2 ($/sh)</t>
         </is>
       </c>
-      <c r="B199" s="215" t="n">
+      <c r="B199" s="218" t="n">
         <v>108</v>
       </c>
+      <c r="C199" s="176" t="n"/>
+      <c r="D199" s="176" t="n"/>
+      <c r="E199" s="176" t="n"/>
+      <c r="F199" s="176" t="n"/>
+      <c r="G199" s="176" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
+      <c r="A200" s="176" t="inlineStr">
         <is>
           <t>Repurchase avg price Y3 ($/sh)</t>
         </is>
       </c>
-      <c r="B200" s="215" t="n">
+      <c r="B200" s="218" t="n">
         <v>115</v>
       </c>
+      <c r="C200" s="176" t="n"/>
+      <c r="D200" s="176" t="n"/>
+      <c r="E200" s="176" t="n"/>
+      <c r="F200" s="176" t="n"/>
+      <c r="G200" s="176" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
+      <c r="A201" s="176" t="inlineStr">
         <is>
           <t>Repurchase avg price Y4 ($/sh)</t>
         </is>
       </c>
-      <c r="B201" s="215" t="n">
+      <c r="B201" s="218" t="n">
         <v>122</v>
       </c>
+      <c r="C201" s="176" t="n"/>
+      <c r="D201" s="176" t="n"/>
+      <c r="E201" s="176" t="n"/>
+      <c r="F201" s="176" t="n"/>
+      <c r="G201" s="176" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
+      <c r="A202" s="176" t="inlineStr">
         <is>
           <t>Repurchase avg price Y5 ($/sh)</t>
         </is>
       </c>
-      <c r="B202" s="215" t="n">
+      <c r="B202" s="218" t="n">
         <v>130</v>
       </c>
+      <c r="C202" s="176" t="n"/>
+      <c r="D202" s="176" t="n"/>
+      <c r="E202" s="176" t="n"/>
+      <c r="F202" s="176" t="n"/>
+      <c r="G202" s="176" t="n"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId5"/>
+    <hyperlink ref="B9" location="'WACC'!E41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B138" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B139" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B140" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B141" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B142" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -7102,7 +7353,7 @@
     <row r="1">
       <c r="A1" s="194" t="inlineStr">
         <is>
-          <t>BOTTOM-UP REVENUE DRIVER SCHEDULE (FY2026E-FY2030E)</t>
+          <t>Revenue drivers (FY26–30)</t>
         </is>
       </c>
       <c r="B1" s="184" t="n"/>
@@ -7201,7 +7452,7 @@
           <t>Notes</t>
         </is>
       </c>
-      <c r="J5" s="188" t="inlineStr">
+      <c r="J5" s="224" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -8968,7 +9219,7 @@
     <row r="53">
       <c r="A53" s="68" t="inlineStr">
         <is>
-          <t>V. CONSOLIDATED REVENUE &amp; RECONCILIATION</t>
+          <t>Consolidated revenue check</t>
         </is>
       </c>
       <c r="B53" s="176" t="n"/>
@@ -9036,7 +9287,7 @@
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="68" t="inlineStr">
         <is>
-          <t>Bottom-up total revenue ($000)</t>
+          <t>Total revenue ($000)</t>
         </is>
       </c>
       <c r="B55" s="75" t="n">
@@ -9118,7 +9369,7 @@
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="41" t="inlineStr">
         <is>
-          <t>Variance (bottom-up - scenarios) ($000)</t>
+          <t>Variance vs scenarios ($000)</t>
         </is>
       </c>
       <c r="B57" s="75">
@@ -9211,35 +9462,191 @@
       <c r="I59" s="176" t="n"/>
       <c r="J59" s="176" t="n"/>
     </row>
+    <row r="60">
+      <c r="A60" s="176" t="n"/>
+      <c r="B60" s="176" t="n"/>
+      <c r="C60" s="176" t="n"/>
+      <c r="D60" s="176" t="n"/>
+      <c r="E60" s="176" t="n"/>
+      <c r="F60" s="176" t="n"/>
+      <c r="G60" s="176" t="n"/>
+      <c r="H60" s="176" t="n"/>
+      <c r="I60" s="176" t="n"/>
+      <c r="J60" s="176" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="176" t="n"/>
+      <c r="B61" s="176" t="n"/>
+      <c r="C61" s="176" t="n"/>
+      <c r="D61" s="176" t="n"/>
+      <c r="E61" s="176" t="n"/>
+      <c r="F61" s="176" t="n"/>
+      <c r="G61" s="176" t="n"/>
+      <c r="H61" s="176" t="n"/>
+      <c r="I61" s="176" t="n"/>
+      <c r="J61" s="176" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="176" t="n"/>
+      <c r="B62" s="176" t="n"/>
+      <c r="C62" s="176" t="n"/>
+      <c r="D62" s="176" t="n"/>
+      <c r="E62" s="176" t="n"/>
+      <c r="F62" s="176" t="n"/>
+      <c r="G62" s="176" t="n"/>
+      <c r="H62" s="176" t="n"/>
+      <c r="I62" s="176" t="n"/>
+      <c r="J62" s="176" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="176" t="n"/>
+      <c r="B63" s="176" t="n"/>
+      <c r="C63" s="176" t="n"/>
+      <c r="D63" s="176" t="n"/>
+      <c r="E63" s="176" t="n"/>
+      <c r="F63" s="176" t="n"/>
+      <c r="G63" s="176" t="n"/>
+      <c r="H63" s="176" t="n"/>
+      <c r="I63" s="176" t="n"/>
+      <c r="J63" s="176" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="176" t="n"/>
+      <c r="B64" s="176" t="n"/>
+      <c r="C64" s="176" t="n"/>
+      <c r="D64" s="176" t="n"/>
+      <c r="E64" s="176" t="n"/>
+      <c r="F64" s="176" t="n"/>
+      <c r="G64" s="176" t="n"/>
+      <c r="H64" s="176" t="n"/>
+      <c r="I64" s="176" t="n"/>
+      <c r="J64" s="176" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="176" t="n"/>
+      <c r="B65" s="176" t="n"/>
+      <c r="C65" s="176" t="n"/>
+      <c r="D65" s="176" t="n"/>
+      <c r="E65" s="176" t="n"/>
+      <c r="F65" s="176" t="n"/>
+      <c r="G65" s="176" t="n"/>
+      <c r="H65" s="176" t="n"/>
+      <c r="I65" s="176" t="n"/>
+      <c r="J65" s="176" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="176" t="n"/>
+      <c r="B66" s="176" t="n"/>
+      <c r="C66" s="176" t="n"/>
+      <c r="D66" s="176" t="n"/>
+      <c r="E66" s="176" t="n"/>
+      <c r="F66" s="176" t="n"/>
+      <c r="G66" s="176" t="n"/>
+      <c r="H66" s="176" t="n"/>
+      <c r="I66" s="176" t="n"/>
+      <c r="J66" s="176" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="176" t="n"/>
+      <c r="B67" s="176" t="n"/>
+      <c r="C67" s="176" t="n"/>
+      <c r="D67" s="176" t="n"/>
+      <c r="E67" s="176" t="n"/>
+      <c r="F67" s="176" t="n"/>
+      <c r="G67" s="176" t="n"/>
+      <c r="H67" s="176" t="n"/>
+      <c r="I67" s="176" t="n"/>
+      <c r="J67" s="176" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="176" t="n"/>
+      <c r="B68" s="176" t="n"/>
+      <c r="C68" s="176" t="n"/>
+      <c r="D68" s="176" t="n"/>
+      <c r="E68" s="176" t="n"/>
+      <c r="F68" s="176" t="n"/>
+      <c r="G68" s="176" t="n"/>
+      <c r="H68" s="176" t="n"/>
+      <c r="I68" s="176" t="n"/>
+      <c r="J68" s="176" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="176" t="n"/>
+      <c r="B69" s="176" t="n"/>
+      <c r="C69" s="176" t="n"/>
+      <c r="D69" s="176" t="n"/>
+      <c r="E69" s="176" t="n"/>
+      <c r="F69" s="176" t="n"/>
+      <c r="G69" s="176" t="n"/>
+      <c r="H69" s="176" t="n"/>
+      <c r="I69" s="176" t="n"/>
+      <c r="J69" s="176" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="176" t="n"/>
+      <c r="B70" s="176" t="n"/>
+      <c r="C70" s="176" t="n"/>
+      <c r="D70" s="176" t="n"/>
+      <c r="E70" s="176" t="n"/>
+      <c r="F70" s="176" t="n"/>
+      <c r="G70" s="176" t="n"/>
+      <c r="H70" s="176" t="n"/>
+      <c r="I70" s="176" t="n"/>
+      <c r="J70" s="176" t="n"/>
+    </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="176" t="inlineStr">
         <is>
           <t>Americas comp mix %</t>
         </is>
       </c>
-      <c r="B71" s="217" t="n">
+      <c r="B71" s="220" t="n">
         <v>0.71</v>
       </c>
+      <c r="C71" s="176" t="n"/>
+      <c r="D71" s="176" t="n"/>
+      <c r="E71" s="176" t="n"/>
+      <c r="F71" s="176" t="n"/>
+      <c r="G71" s="176" t="n"/>
+      <c r="H71" s="176" t="n"/>
+      <c r="I71" s="176" t="n"/>
+      <c r="J71" s="176" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="176" t="inlineStr">
         <is>
           <t>China comp mix %</t>
         </is>
       </c>
-      <c r="B72" s="217" t="n">
+      <c r="B72" s="220" t="n">
         <v>0.16</v>
       </c>
+      <c r="C72" s="176" t="n"/>
+      <c r="D72" s="176" t="n"/>
+      <c r="E72" s="176" t="n"/>
+      <c r="F72" s="176" t="n"/>
+      <c r="G72" s="176" t="n"/>
+      <c r="H72" s="176" t="n"/>
+      <c r="I72" s="176" t="n"/>
+      <c r="J72" s="176" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="176" t="inlineStr">
         <is>
           <t>RoW comp mix %</t>
         </is>
       </c>
-      <c r="B73" s="217" t="n">
+      <c r="B73" s="220" t="n">
         <v>0.13</v>
       </c>
+      <c r="C73" s="176" t="n"/>
+      <c r="D73" s="176" t="n"/>
+      <c r="E73" s="176" t="n"/>
+      <c r="F73" s="176" t="n"/>
+      <c r="G73" s="176" t="n"/>
+      <c r="H73" s="176" t="n"/>
+      <c r="I73" s="176" t="n"/>
+      <c r="J73" s="176" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9301,7 +9708,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -9319,7 +9726,7 @@
     <row r="1">
       <c r="A1" s="183" t="inlineStr">
         <is>
-          <t>NOPAT RECONCILIATION (BASE CASE)</t>
+          <t>NOPAT bridge</t>
         </is>
       </c>
       <c r="B1" s="184" t="n"/>
@@ -9328,6 +9735,7 @@
       <c r="E1" s="184" t="n"/>
       <c r="F1" s="184" t="n"/>
       <c r="G1" s="184" t="n"/>
+      <c r="H1" s="176" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="176" t="n"/>
@@ -9359,6 +9767,11 @@
       <c r="G2" s="189" t="inlineStr">
         <is>
           <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="H2" s="224" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -9374,6 +9787,7 @@
       <c r="E3" s="176" t="n"/>
       <c r="F3" s="176" t="n"/>
       <c r="G3" s="176" t="n"/>
+      <c r="H3" s="176" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="26" t="n"/>
@@ -9383,6 +9797,7 @@
       <c r="E4" s="176" t="n"/>
       <c r="F4" s="176" t="n"/>
       <c r="G4" s="176" t="n"/>
+      <c r="H4" s="176" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="176" t="n"/>
@@ -9392,6 +9807,7 @@
       <c r="E5" s="176" t="n"/>
       <c r="F5" s="176" t="n"/>
       <c r="G5" s="176" t="n"/>
+      <c r="H5" s="176" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="68" t="inlineStr">
@@ -9405,6 +9821,7 @@
       <c r="E6" s="176" t="n"/>
       <c r="F6" s="176" t="n"/>
       <c r="G6" s="176" t="n"/>
+      <c r="H6" s="176" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
@@ -9429,6 +9846,11 @@
       </c>
       <c r="G7" s="75" t="n">
         <v>0</v>
+      </c>
+      <c r="H7" s="188" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K): stock-based compensation</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -9439,6 +9861,7 @@
       <c r="E8" s="176" t="n"/>
       <c r="F8" s="176" t="n"/>
       <c r="G8" s="176" t="n"/>
+      <c r="H8" s="176" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -9464,6 +9887,11 @@
       <c r="G9" s="32" t="n">
         <v>0.186</v>
       </c>
+      <c r="H9" s="188" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: company-operated stores net revenue</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -9489,6 +9917,11 @@
       <c r="G10" s="32" t="n">
         <v>0.236</v>
       </c>
+      <c r="H10" s="188" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: e-commerce net revenue</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
@@ -9514,6 +9947,11 @@
       <c r="G11" s="32" t="n">
         <v>0.091</v>
       </c>
+      <c r="H11" s="188" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: other channels (residual)</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
@@ -9539,6 +9977,11 @@
       <c r="G12" s="32" t="n">
         <v>0.3</v>
       </c>
+      <c r="H12" s="188" t="inlineStr">
+        <is>
+          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
@@ -9563,6 +10006,11 @@
       </c>
       <c r="G13" s="90" t="n">
         <v>4</v>
+      </c>
+      <c r="H13" s="188" t="inlineStr">
+        <is>
+          <t>NOPAT Bridge: capitalization convention</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -9573,6 +10021,7 @@
       <c r="E14" s="176" t="n"/>
       <c r="F14" s="176" t="n"/>
       <c r="G14" s="176" t="n"/>
+      <c r="H14" s="176" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="61" t="inlineStr">
@@ -9586,6 +10035,7 @@
       <c r="E15" s="176" t="n"/>
       <c r="F15" s="176" t="n"/>
       <c r="G15" s="176" t="n"/>
+      <c r="H15" s="176" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
@@ -9616,6 +10066,11 @@
         <f>Scenarios!D49</f>
         <v/>
       </c>
+      <c r="H16" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Income from operations</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -9641,6 +10096,11 @@
       <c r="G17" s="75" t="n">
         <v>0</v>
       </c>
+      <c r="H17" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: amortization of intangible assets</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
@@ -9666,6 +10126,11 @@
       <c r="G18" s="75" t="n">
         <v>0</v>
       </c>
+      <c r="H18" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: restructuring charges</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -9691,6 +10156,11 @@
       <c r="G19" s="75" t="n">
         <v>0</v>
       </c>
+      <c r="H19" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: SG&amp;A one-offs</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -9720,6 +10190,11 @@
       <c r="G20" s="75">
         <f>Scenarios!G25/DCF!$B$6*$B$20*$B$7</f>
         <v/>
+      </c>
+      <c r="H20" s="188" t="inlineStr">
+        <is>
+          <t>LULU CF statement (10-K): stock-based compensation</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
@@ -9749,6 +10224,7 @@
         <f>SUM(G16:G20)</f>
         <v/>
       </c>
+      <c r="H21" s="176" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="61" t="inlineStr">
@@ -9762,6 +10238,7 @@
       <c r="E22" s="176" t="n"/>
       <c r="F22" s="176" t="n"/>
       <c r="G22" s="176" t="n"/>
+      <c r="H22" s="176" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
@@ -9792,6 +10269,11 @@
         <f>$B$23*(Scenarios!G25/DCF!$B$6)</f>
         <v/>
       </c>
+      <c r="H23" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: interest on lease liabilities (supplemental)</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -9817,6 +10299,11 @@
       <c r="G24" s="75" t="n">
         <v>0</v>
       </c>
+      <c r="H24" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: R&amp;D / software expense</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -9841,6 +10328,11 @@
       </c>
       <c r="G25" s="75" t="n">
         <v>0</v>
+      </c>
+      <c r="H25" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: intangible amortization</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
@@ -9870,6 +10362,7 @@
         <f>G21+G23+G24-G25</f>
         <v/>
       </c>
+      <c r="H26" s="176" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="61" t="inlineStr">
@@ -9883,6 +10376,7 @@
       <c r="E27" s="176" t="n"/>
       <c r="F27" s="176" t="n"/>
       <c r="G27" s="176" t="n"/>
+      <c r="H27" s="176" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
@@ -9913,6 +10407,11 @@
         <f>'Revenue Drivers'!G31</f>
         <v/>
       </c>
+      <c r="H28" s="188" t="inlineStr">
+        <is>
+          <t>Revenue Drivers tab: store-channel revenue</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
@@ -9943,6 +10442,11 @@
         <f>'Revenue Drivers'!G41</f>
         <v/>
       </c>
+      <c r="H29" s="188" t="inlineStr">
+        <is>
+          <t>Revenue Drivers tab: e-commerce revenue</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
@@ -9973,6 +10477,11 @@
         <f>'Revenue Drivers'!G45</f>
         <v/>
       </c>
+      <c r="H30" s="188" t="inlineStr">
+        <is>
+          <t>Revenue Drivers tab: other channels revenue</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
@@ -10004,6 +10513,7 @@
         <f>G28*B$9</f>
         <v/>
       </c>
+      <c r="H31" s="176" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
@@ -10035,6 +10545,7 @@
         <f>G29*B$10</f>
         <v/>
       </c>
+      <c r="H32" s="176" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
@@ -10066,6 +10577,7 @@
         <f>G30*B$11</f>
         <v/>
       </c>
+      <c r="H33" s="176" t="n"/>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="68" t="inlineStr">
@@ -10094,6 +10606,7 @@
         <f>G31+G32+G33</f>
         <v/>
       </c>
+      <c r="H34" s="176" t="n"/>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="68" t="inlineStr">
@@ -10125,6 +10638,7 @@
         <f>G34</f>
         <v/>
       </c>
+      <c r="H35" s="176" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="68" t="inlineStr">
@@ -10156,6 +10670,7 @@
         <f>Scenarios!D49</f>
         <v/>
       </c>
+      <c r="H36" s="176" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -10184,6 +10699,7 @@
         <f>G36-Scenarios!D49</f>
         <v/>
       </c>
+      <c r="H37" s="176" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="61" t="inlineStr">
@@ -10197,6 +10713,7 @@
       <c r="E38" s="176" t="n"/>
       <c r="F38" s="176" t="n"/>
       <c r="G38" s="176" t="n"/>
+      <c r="H38" s="176" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="16" t="inlineStr">
@@ -10226,6 +10743,11 @@
       <c r="G39" s="32">
         <f>$B$39+(G$12-$B$39)*5/5</f>
         <v/>
+      </c>
+      <c r="H39" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: income tax &amp; interest expense</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
@@ -10255,6 +10777,7 @@
         <f>G36*G39</f>
         <v/>
       </c>
+      <c r="H40" s="176" t="n"/>
     </row>
     <row r="41" ht="28" customHeight="1">
       <c r="A41" s="68" t="inlineStr">
@@ -10283,6 +10806,7 @@
         <f>G36-G40</f>
         <v/>
       </c>
+      <c r="H41" s="176" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="176" t="n"/>
@@ -10292,11 +10816,12 @@
       <c r="E42" s="176" t="n"/>
       <c r="F42" s="176" t="n"/>
       <c r="G42" s="176" t="n"/>
+      <c r="H42" s="176" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>
-          <t>Reconciliation (execution steps)</t>
+          <t>Build checklist</t>
         </is>
       </c>
       <c r="B43" s="176" t="n"/>
@@ -10305,6 +10830,7 @@
       <c r="E43" s="176" t="n"/>
       <c r="F43" s="176" t="n"/>
       <c r="G43" s="176" t="n"/>
+      <c r="H43" s="176" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="176" t="n"/>
@@ -10318,11 +10844,12 @@
       <c r="E44" s="176" t="n"/>
       <c r="F44" s="176" t="n"/>
       <c r="G44" s="176" t="n"/>
+      <c r="H44" s="176" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="61" t="inlineStr">
         <is>
-          <t>1. Clean base</t>
+          <t>Reported EBIT adjustments</t>
         </is>
       </c>
       <c r="B45" s="176" t="n"/>
@@ -10335,11 +10862,12 @@
       <c r="E45" s="176" t="n"/>
       <c r="F45" s="176" t="n"/>
       <c r="G45" s="176" t="n"/>
+      <c r="H45" s="176" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="61" t="inlineStr">
         <is>
-          <t>2. Capitalize R&amp;D</t>
+          <t>R&amp;D capitalization</t>
         </is>
       </c>
       <c r="B46" s="176" t="n"/>
@@ -10352,11 +10880,12 @@
       <c r="E46" s="176" t="n"/>
       <c r="F46" s="176" t="n"/>
       <c r="G46" s="176" t="n"/>
+      <c r="H46" s="176" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="61" t="inlineStr">
         <is>
-          <t>3. Lease shift</t>
+          <t>Lease interest reclass</t>
         </is>
       </c>
       <c r="B47" s="176" t="n"/>
@@ -10369,11 +10898,12 @@
       <c r="E47" s="176" t="n"/>
       <c r="F47" s="176" t="n"/>
       <c r="G47" s="176" t="n"/>
+      <c r="H47" s="176" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="61" t="inlineStr">
         <is>
-          <t>4. Segment mix</t>
+          <t>Channel EBIT mix</t>
         </is>
       </c>
       <c r="B48" s="176" t="n"/>
@@ -10386,11 +10916,12 @@
       <c r="E48" s="176" t="n"/>
       <c r="F48" s="176" t="n"/>
       <c r="G48" s="176" t="n"/>
+      <c r="H48" s="176" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="61" t="inlineStr">
         <is>
-          <t>5. NOPAT bridge</t>
+          <t>Tax-normalized NOPAT</t>
         </is>
       </c>
       <c r="B49" s="176" t="n"/>
@@ -10403,11 +10934,12 @@
       <c r="E49" s="176" t="n"/>
       <c r="F49" s="176" t="n"/>
       <c r="G49" s="176" t="n"/>
+      <c r="H49" s="176" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="61" t="inlineStr">
         <is>
-          <t>6. Tariff refund (Scenarios)</t>
+          <t>FY26 tariff refund</t>
         </is>
       </c>
       <c r="B50" s="176" t="n"/>
@@ -10420,6 +10952,7 @@
       <c r="E50" s="176" t="n"/>
       <c r="F50" s="176" t="n"/>
       <c r="G50" s="176" t="n"/>
+      <c r="H50" s="176" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="26" t="n"/>
@@ -10429,6 +10962,7 @@
       <c r="E51" s="176" t="n"/>
       <c r="F51" s="176" t="n"/>
       <c r="G51" s="176" t="n"/>
+      <c r="H51" s="176" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="26" t="n"/>
@@ -10438,21 +10972,39 @@
       <c r="E52" s="176" t="n"/>
       <c r="F52" s="176" t="n"/>
       <c r="G52" s="176" t="n"/>
+      <c r="H52" s="176" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId21"/>
+    <hyperlink ref="H28" location="'Revenue Drivers'!B31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId22"/>
+    <hyperlink ref="H29" location="'Revenue Drivers'!B41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId23"/>
+    <hyperlink ref="H30" location="'Revenue Drivers'!B45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -10465,7 +11017,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -10495,6 +11047,7 @@
       <c r="E1" s="184" t="n"/>
       <c r="F1" s="184" t="n"/>
       <c r="G1" s="184" t="n"/>
+      <c r="H1" s="176" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="176" t="n"/>
@@ -10526,6 +11079,11 @@
       <c r="G2" s="189" t="inlineStr">
         <is>
           <t>FY2030E</t>
+        </is>
+      </c>
+      <c r="H2" s="224" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -10537,6 +11095,7 @@
       <c r="E3" s="176" t="n"/>
       <c r="F3" s="176" t="n"/>
       <c r="G3" s="176" t="n"/>
+      <c r="H3" s="176" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="199" t="n"/>
@@ -10546,33 +11105,36 @@
       <c r="E4" s="176" t="n"/>
       <c r="F4" s="176" t="n"/>
       <c r="G4" s="176" t="n"/>
+      <c r="H4" s="176" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="176" t="inlineStr">
         <is>
           <t>Revenue Growth %</t>
         </is>
       </c>
-      <c r="C5" s="217">
+      <c r="B5" s="176" t="n"/>
+      <c r="C5" s="220">
         <f>Scenarios!$D$4</f>
         <v/>
       </c>
-      <c r="D5" s="217">
+      <c r="D5" s="220">
         <f>Scenarios!$D$5</f>
         <v/>
       </c>
-      <c r="E5" s="217">
+      <c r="E5" s="220">
         <f>Scenarios!$D$5</f>
         <v/>
       </c>
-      <c r="F5" s="217">
+      <c r="F5" s="220">
         <f>Scenarios!$D$5</f>
         <v/>
       </c>
-      <c r="G5" s="217">
+      <c r="G5" s="220">
         <f>Scenarios!$D$5</f>
         <v/>
       </c>
+      <c r="H5" s="176" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -10603,6 +11165,7 @@
         <f>Scenarios!D29</f>
         <v/>
       </c>
+      <c r="H6" s="176" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
@@ -10634,6 +11197,7 @@
         <f>Scenarios!$D$14</f>
         <v/>
       </c>
+      <c r="H7" s="176" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="inlineStr">
@@ -10664,6 +11228,7 @@
         <f>Scenarios!D39</f>
         <v/>
       </c>
+      <c r="H8" s="176" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -10692,6 +11257,7 @@
         <f>Scenarios!D44</f>
         <v/>
       </c>
+      <c r="H9" s="176" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -10718,6 +11284,11 @@
       <c r="G10" s="75" t="n">
         <v>0</v>
       </c>
+      <c r="H10" s="188" t="inlineStr">
+        <is>
+          <t>No tariff refund post-FY26 (forecast years 2–5)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="68" t="inlineStr">
@@ -10748,6 +11319,7 @@
         <f>Scenarios!D49</f>
         <v/>
       </c>
+      <c r="H11" s="176" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="inlineStr">
@@ -10779,6 +11351,7 @@
         <f>G11/G6</f>
         <v/>
       </c>
+      <c r="H12" s="176" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
@@ -10807,6 +11380,7 @@
         <f>-'NOPAT Bridge'!G40</f>
         <v/>
       </c>
+      <c r="H13" s="176" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="68" t="inlineStr">
@@ -10835,16 +11409,23 @@
         <f>Scenarios!D54</f>
         <v/>
       </c>
+      <c r="H14" s="176" t="n"/>
     </row>
     <row r="15" ht="28" customHeight="1">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="176" t="inlineStr">
         <is>
           <t>FY25 D&amp;A ($000)</t>
         </is>
       </c>
-      <c r="B15" s="215" t="n">
+      <c r="B15" s="218" t="n">
         <v>496228</v>
       </c>
+      <c r="C15" s="176" t="n"/>
+      <c r="D15" s="176" t="n"/>
+      <c r="E15" s="176" t="n"/>
+      <c r="F15" s="176" t="n"/>
+      <c r="G15" s="176" t="n"/>
+      <c r="H15" s="176" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -10873,6 +11454,7 @@
         <f>Scenarios!$D$12</f>
         <v/>
       </c>
+      <c r="H16" s="176" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -10901,6 +11483,7 @@
         <f>Scenarios!D59</f>
         <v/>
       </c>
+      <c r="H17" s="176" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -10929,6 +11512,7 @@
         <f>Scenarios!$D$13</f>
         <v/>
       </c>
+      <c r="H18" s="176" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -10957,6 +11541,7 @@
         <f>Scenarios!D64</f>
         <v/>
       </c>
+      <c r="H19" s="176" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="68" t="inlineStr">
@@ -10970,6 +11555,7 @@
       <c r="E20" s="176" t="n"/>
       <c r="F20" s="176" t="n"/>
       <c r="G20" s="176" t="n"/>
+      <c r="H20" s="176" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -11001,6 +11587,7 @@
         <f>Scenarios!D69</f>
         <v/>
       </c>
+      <c r="H21" s="176" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -11031,6 +11618,11 @@
         <f>Scenarios!D74</f>
         <v/>
       </c>
+      <c r="H22" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accounts receivable, net</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
@@ -11062,6 +11654,7 @@
         <f>Scenarios!D79</f>
         <v/>
       </c>
+      <c r="H23" s="176" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -11092,6 +11685,11 @@
         <f>Scenarios!D84</f>
         <v/>
       </c>
+      <c r="H24" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Inventories</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -11123,6 +11721,7 @@
         <f>Scenarios!D89</f>
         <v/>
       </c>
+      <c r="H25" s="176" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -11153,6 +11752,11 @@
         <f>Scenarios!D94</f>
         <v/>
       </c>
+      <c r="H26" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accounts payable</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
@@ -11184,6 +11788,7 @@
         <f>Scenarios!$D$19</f>
         <v/>
       </c>
+      <c r="H27" s="176" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
@@ -11214,6 +11819,11 @@
         <f>Scenarios!D99</f>
         <v/>
       </c>
+      <c r="H28" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: other current assets (residual)</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
@@ -11245,6 +11855,7 @@
         <f>Scenarios!$D$20</f>
         <v/>
       </c>
+      <c r="H29" s="176" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
@@ -11274,6 +11885,11 @@
       <c r="G30" s="75">
         <f>Scenarios!D104</f>
         <v/>
+      </c>
+      <c r="H30" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: Accrued liabilities and other</t>
+        </is>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -11303,6 +11919,7 @@
         <f>Scenarios!D109</f>
         <v/>
       </c>
+      <c r="H31" s="176" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
@@ -11331,6 +11948,7 @@
         <f>Scenarios!D114</f>
         <v/>
       </c>
+      <c r="H32" s="176" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="68" t="inlineStr">
@@ -11360,6 +11978,11 @@
       <c r="G33" s="130">
         <f>Scenarios!D119</f>
         <v/>
+      </c>
+      <c r="H33" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: working-capital components</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -11389,6 +12012,7 @@
         <f>Scenarios!D124</f>
         <v/>
       </c>
+      <c r="H34" s="176" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="26" t="n"/>
@@ -11398,6 +12022,7 @@
       <c r="E35" s="176" t="n"/>
       <c r="F35" s="176" t="n"/>
       <c r="G35" s="176" t="n"/>
+      <c r="H35" s="176" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="68" t="inlineStr">
@@ -11426,6 +12051,7 @@
         <f>Scenarios!D129</f>
         <v/>
       </c>
+      <c r="H36" s="176" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -11449,6 +12075,11 @@
       <c r="G37" s="90" t="n">
         <v>5</v>
       </c>
+      <c r="H37" s="188" t="inlineStr">
+        <is>
+          <t>Mid-year discount convention (yrs 1–5)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -11477,6 +12108,7 @@
         <f>1/(1+WACC!B36)^G37</f>
         <v/>
       </c>
+      <c r="H38" s="176" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="68" t="inlineStr">
@@ -11505,6 +12137,7 @@
         <f>G36*G38</f>
         <v/>
       </c>
+      <c r="H39" s="176" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="176" t="n"/>
@@ -11514,6 +12147,7 @@
       <c r="E40" s="176" t="n"/>
       <c r="F40" s="176" t="n"/>
       <c r="G40" s="176" t="n"/>
+      <c r="H40" s="176" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="61" t="inlineStr">
@@ -11527,11 +12161,12 @@
       <c r="E41" s="176" t="n"/>
       <c r="F41" s="176" t="n"/>
       <c r="G41" s="176" t="n"/>
+      <c r="H41" s="176" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="201" t="inlineStr">
         <is>
-          <t>VALUATION - GORDON GROWTH (PERPETUITY) METHOD</t>
+          <t>Terminal value — Gordon growth</t>
         </is>
       </c>
       <c r="B42" s="176" t="n"/>
@@ -11540,6 +12175,7 @@
       <c r="E42" s="176" t="n"/>
       <c r="F42" s="176" t="n"/>
       <c r="G42" s="176" t="n"/>
+      <c r="H42" s="176" t="n"/>
     </row>
     <row r="43" ht="28" customHeight="1">
       <c r="A43" s="68" t="inlineStr">
@@ -11556,6 +12192,7 @@
       <c r="E43" s="176" t="n"/>
       <c r="F43" s="176" t="n"/>
       <c r="G43" s="176" t="n"/>
+      <c r="H43" s="176" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
@@ -11572,6 +12209,7 @@
       <c r="E44" s="176" t="n"/>
       <c r="F44" s="176" t="n"/>
       <c r="G44" s="176" t="n"/>
+      <c r="H44" s="176" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="68" t="inlineStr">
@@ -11588,11 +12226,12 @@
       <c r="E45" s="176" t="n"/>
       <c r="F45" s="176" t="n"/>
       <c r="G45" s="176" t="n"/>
+      <c r="H45" s="176" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Terminal value (Gordon growth)</t>
+          <t>Terminal value</t>
         </is>
       </c>
       <c r="B46" s="32">
@@ -11604,11 +12243,12 @@
       <c r="E46" s="176" t="n"/>
       <c r="F46" s="176" t="n"/>
       <c r="G46" s="176" t="n"/>
+      <c r="H46" s="176" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>Implied exit EV/EBITDA = Gordon TV / FY30 EBITDA</t>
+          <t>Implied exit EV/EBITDA</t>
         </is>
       </c>
       <c r="B47" s="94">
@@ -11620,6 +12260,7 @@
       <c r="E47" s="176" t="n"/>
       <c r="F47" s="176" t="n"/>
       <c r="G47" s="176" t="n"/>
+      <c r="H47" s="176" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -11636,6 +12277,7 @@
       <c r="E48" s="176" t="n"/>
       <c r="F48" s="176" t="n"/>
       <c r="G48" s="176" t="n"/>
+      <c r="H48" s="176" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="68" t="inlineStr">
@@ -11652,6 +12294,7 @@
       <c r="E49" s="176" t="n"/>
       <c r="F49" s="176" t="n"/>
       <c r="G49" s="176" t="n"/>
+      <c r="H49" s="176" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="68" t="inlineStr">
@@ -11668,6 +12311,7 @@
       <c r="E50" s="176" t="n"/>
       <c r="F50" s="176" t="n"/>
       <c r="G50" s="176" t="n"/>
+      <c r="H50" s="176" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
@@ -11683,6 +12327,11 @@
       <c r="E51" s="176" t="n"/>
       <c r="F51" s="176" t="n"/>
       <c r="G51" s="176" t="n"/>
+      <c r="H51" s="188" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -11698,6 +12347,11 @@
       <c r="E52" s="176" t="n"/>
       <c r="F52" s="176" t="n"/>
       <c r="G52" s="176" t="n"/>
+      <c r="H52" s="188" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: operating lease liabilities</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="26" t="n"/>
@@ -11707,6 +12361,7 @@
       <c r="E53" s="176" t="n"/>
       <c r="F53" s="176" t="n"/>
       <c r="G53" s="176" t="n"/>
+      <c r="H53" s="176" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="26" t="inlineStr">
@@ -11720,6 +12375,7 @@
       <c r="E54" s="176" t="n"/>
       <c r="F54" s="176" t="n"/>
       <c r="G54" s="176" t="n"/>
+      <c r="H54" s="176" t="n"/>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="68" t="inlineStr">
@@ -11736,6 +12392,7 @@
       <c r="E55" s="176" t="n"/>
       <c r="F55" s="176" t="n"/>
       <c r="G55" s="176" t="n"/>
+      <c r="H55" s="176" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -11751,6 +12408,11 @@
       <c r="E56" s="176" t="n"/>
       <c r="F56" s="176" t="n"/>
       <c r="G56" s="176" t="n"/>
+      <c r="H56" s="188" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="68" t="inlineStr">
@@ -11767,6 +12429,7 @@
       <c r="E57" s="176" t="n"/>
       <c r="F57" s="176" t="n"/>
       <c r="G57" s="176" t="n"/>
+      <c r="H57" s="176" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -11782,6 +12445,11 @@
       <c r="E58" s="176" t="n"/>
       <c r="F58" s="176" t="n"/>
       <c r="G58" s="176" t="n"/>
+      <c r="H58" s="188" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="68" t="inlineStr">
@@ -11798,11 +12466,12 @@
       <c r="E59" s="176" t="n"/>
       <c r="F59" s="176" t="n"/>
       <c r="G59" s="176" t="n"/>
+      <c r="H59" s="176" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>% of EV from terminal value</t>
+          <t>Terminal value % of EV</t>
         </is>
       </c>
       <c r="B60" s="75">
@@ -11814,6 +12483,7 @@
       <c r="E60" s="176" t="n"/>
       <c r="F60" s="176" t="n"/>
       <c r="G60" s="176" t="n"/>
+      <c r="H60" s="176" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="176" t="n"/>
@@ -11823,6 +12493,7 @@
       <c r="E61" s="176" t="n"/>
       <c r="F61" s="176" t="n"/>
       <c r="G61" s="176" t="n"/>
+      <c r="H61" s="176" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="176" t="n"/>
@@ -11832,6 +12503,7 @@
       <c r="E62" s="176" t="n"/>
       <c r="F62" s="176" t="n"/>
       <c r="G62" s="176" t="n"/>
+      <c r="H62" s="176" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="201" t="inlineStr">
@@ -11845,6 +12517,7 @@
       <c r="E63" s="176" t="n"/>
       <c r="F63" s="176" t="n"/>
       <c r="G63" s="176" t="n"/>
+      <c r="H63" s="176" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="26" t="n"/>
@@ -11854,6 +12527,7 @@
       <c r="E64" s="176" t="n"/>
       <c r="F64" s="176" t="n"/>
       <c r="G64" s="176" t="n"/>
+      <c r="H64" s="176" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="176" t="n"/>
@@ -11863,6 +12537,7 @@
       <c r="E65" s="176" t="n"/>
       <c r="F65" s="176" t="n"/>
       <c r="G65" s="176" t="n"/>
+      <c r="H65" s="176" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -11894,6 +12569,7 @@
         <f>Scenarios!$D$21</f>
         <v/>
       </c>
+      <c r="H66" s="176" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
@@ -11924,6 +12600,7 @@
         <f>B67</f>
         <v/>
       </c>
+      <c r="H67" s="176" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="176" t="n"/>
@@ -11933,6 +12610,7 @@
       <c r="E68" s="176" t="n"/>
       <c r="F68" s="176" t="n"/>
       <c r="G68" s="176" t="n"/>
+      <c r="H68" s="176" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
@@ -11961,6 +12639,7 @@
         <f>G36</f>
         <v/>
       </c>
+      <c r="H69" s="176" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
@@ -11991,6 +12670,7 @@
         <f>Scenarios!$D$21</f>
         <v/>
       </c>
+      <c r="H70" s="176" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
@@ -12019,6 +12699,7 @@
         <f>G70/G69</f>
         <v/>
       </c>
+      <c r="H71" s="176" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="176" t="n"/>
@@ -12028,6 +12709,7 @@
       <c r="E72" s="176" t="n"/>
       <c r="F72" s="176" t="n"/>
       <c r="G72" s="176" t="n"/>
+      <c r="H72" s="176" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
@@ -12058,6 +12740,7 @@
         <f>Scenarios!$B$202</f>
         <v/>
       </c>
+      <c r="H73" s="176" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
@@ -12088,6 +12771,7 @@
         <f>G70/G73</f>
         <v/>
       </c>
+      <c r="H74" s="176" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
@@ -12118,6 +12802,7 @@
         <f>F76</f>
         <v/>
       </c>
+      <c r="H75" s="176" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="68" t="inlineStr">
@@ -12148,6 +12833,7 @@
         <f>Scenarios!$D$187</f>
         <v/>
       </c>
+      <c r="H76" s="176" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="176" t="n"/>
@@ -12157,6 +12843,7 @@
       <c r="E77" s="176" t="n"/>
       <c r="F77" s="176" t="n"/>
       <c r="G77" s="176" t="n"/>
+      <c r="H77" s="176" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
@@ -12187,6 +12874,7 @@
         <f>Scenarios!$D$147</f>
         <v/>
       </c>
+      <c r="H78" s="176" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="68" t="inlineStr">
@@ -12217,6 +12905,7 @@
         <f>Scenarios!$D$192</f>
         <v/>
       </c>
+      <c r="H79" s="176" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="176" t="n"/>
@@ -12226,6 +12915,7 @@
       <c r="E80" s="176" t="n"/>
       <c r="F80" s="176" t="n"/>
       <c r="G80" s="176" t="n"/>
+      <c r="H80" s="176" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="201" t="inlineStr">
@@ -12239,23 +12929,22 @@
       <c r="E81" s="176" t="n"/>
       <c r="F81" s="176" t="n"/>
       <c r="G81" s="176" t="n"/>
+      <c r="H81" s="176" t="n"/>
     </row>
     <row r="82" ht="28" customHeight="1">
       <c r="A82" s="61" t="n"/>
-      <c r="B82" s="218">
-        <f>B47</f>
-        <v/>
-      </c>
+      <c r="B82" s="218" t="n"/>
       <c r="C82" s="176" t="n"/>
       <c r="D82" s="176" t="n"/>
       <c r="E82" s="176" t="n"/>
       <c r="F82" s="176" t="n"/>
       <c r="G82" s="176" t="n"/>
+      <c r="H82" s="176" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>Selected exit EV/EBITDA (Gordon implied)</t>
+          <t>Selected exit EV/EBITDA</t>
         </is>
       </c>
       <c r="B83" s="94">
@@ -12267,15 +12956,16 @@
       <c r="E83" s="176" t="n"/>
       <c r="F83" s="176" t="n"/>
       <c r="G83" s="176" t="n"/>
+      <c r="H83" s="176" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>Terminal value = Terminal EBITDA x exit multiple</t>
+          <t>Terminal value (exit multiple)</t>
         </is>
       </c>
       <c r="B84" s="94">
-        <f>B45*B82</f>
+        <f>B45*B83</f>
         <v/>
       </c>
       <c r="C84" s="176" t="n"/>
@@ -12283,6 +12973,7 @@
       <c r="E84" s="176" t="n"/>
       <c r="F84" s="176" t="n"/>
       <c r="G84" s="176" t="n"/>
+      <c r="H84" s="176" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
@@ -12299,6 +12990,7 @@
       <c r="E85" s="176" t="n"/>
       <c r="F85" s="176" t="n"/>
       <c r="G85" s="176" t="n"/>
+      <c r="H85" s="176" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="68" t="inlineStr">
@@ -12315,6 +13007,7 @@
       <c r="E86" s="176" t="n"/>
       <c r="F86" s="176" t="n"/>
       <c r="G86" s="176" t="n"/>
+      <c r="H86" s="176" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="68" t="inlineStr">
@@ -12323,7 +13016,7 @@
         </is>
       </c>
       <c r="B87" s="99">
-        <f>(B85+B51+B52)/B56</f>
+        <f>(B86+B51+B52)/B56</f>
         <v/>
       </c>
       <c r="C87" s="176" t="n"/>
@@ -12331,6 +13024,7 @@
       <c r="E87" s="176" t="n"/>
       <c r="F87" s="176" t="n"/>
       <c r="G87" s="176" t="n"/>
+      <c r="H87" s="176" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="176" t="n"/>
@@ -12340,11 +13034,12 @@
       <c r="E88" s="176" t="n"/>
       <c r="F88" s="176" t="n"/>
       <c r="G88" s="176" t="n"/>
+      <c r="H88" s="176" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="201" t="inlineStr">
         <is>
-          <t>TERMINAL VALUE RECONCILIATION (GORDON vs EXIT MULTIPLE)</t>
+          <t>Terminal value check</t>
         </is>
       </c>
       <c r="B89" s="176" t="n"/>
@@ -12353,6 +13048,7 @@
       <c r="E89" s="176" t="n"/>
       <c r="F89" s="176" t="n"/>
       <c r="G89" s="176" t="n"/>
+      <c r="H89" s="176" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="103" t="inlineStr"/>
@@ -12374,6 +13070,7 @@
       <c r="E90" s="176" t="n"/>
       <c r="F90" s="176" t="n"/>
       <c r="G90" s="176" t="n"/>
+      <c r="H90" s="176" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="68" t="inlineStr">
@@ -12396,6 +13093,7 @@
       <c r="E91" s="176" t="n"/>
       <c r="F91" s="176" t="n"/>
       <c r="G91" s="176" t="n"/>
+      <c r="H91" s="176" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="68" t="inlineStr">
@@ -12418,6 +13116,7 @@
       <c r="E92" s="176" t="n"/>
       <c r="F92" s="176" t="n"/>
       <c r="G92" s="176" t="n"/>
+      <c r="H92" s="176" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
@@ -12434,6 +13133,7 @@
       <c r="E93" s="176" t="n"/>
       <c r="F93" s="176" t="n"/>
       <c r="G93" s="176" t="n"/>
+      <c r="H93" s="176" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="68" t="inlineStr">
@@ -12456,18 +13156,19 @@
       <c r="E94" s="176" t="n"/>
       <c r="F94" s="176" t="n"/>
       <c r="G94" s="176" t="n"/>
+      <c r="H94" s="176" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="68" t="inlineStr">
         <is>
-          <t>Sanity check: multiples within ±1.5 turns?</t>
-        </is>
-      </c>
-      <c r="B95" s="218">
+          <t>Exit multiple check (±1.5x)</t>
+        </is>
+      </c>
+      <c r="B95" s="219">
         <f>IF(ABS(D92)&lt;=1.5,"PASS","REVIEW")</f>
         <v/>
       </c>
-      <c r="C95" s="218">
+      <c r="C95" s="219">
         <f>TEXT(D92,"0.0")&amp;"x spread vs Gordon-implied exit"</f>
         <v/>
       </c>
@@ -12479,6 +13180,11 @@
       <c r="E95" s="176" t="n"/>
       <c r="F95" s="176" t="n"/>
       <c r="G95" s="176" t="n"/>
+      <c r="H95" s="188" t="inlineStr">
+        <is>
+          <t>Model check: Gordon vs exit-multiple spread</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="176" t="n"/>
@@ -12488,6 +13194,7 @@
       <c r="E96" s="176" t="n"/>
       <c r="F96" s="176" t="n"/>
       <c r="G96" s="176" t="n"/>
+      <c r="H96" s="176" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="176" t="n"/>
@@ -12497,6 +13204,7 @@
       <c r="E97" s="176" t="n"/>
       <c r="F97" s="176" t="n"/>
       <c r="G97" s="176" t="n"/>
+      <c r="H97" s="176" t="n"/>
     </row>
     <row r="98" ht="28" customHeight="1">
       <c r="A98" s="201" t="inlineStr">
@@ -12510,6 +13218,7 @@
       <c r="E98" s="184" t="n"/>
       <c r="F98" s="176" t="n"/>
       <c r="G98" s="176" t="n"/>
+      <c r="H98" s="176" t="n"/>
     </row>
     <row r="99" ht="28" customHeight="1">
       <c r="A99" s="203" t="inlineStr">
@@ -12533,6 +13242,11 @@
       <c r="G99" s="204" t="n">
         <v>0.03</v>
       </c>
+      <c r="H99" s="188" t="inlineStr">
+        <is>
+          <t>FRED: Real GDP (GDPC1)</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="28" customHeight="1">
       <c r="A100" s="205" t="n">
@@ -12559,6 +13273,7 @@
         <f>(NPV($A100,C36:G36)+(G36*(1+G$99)/($A100-G$99))/(1+$A100)^5+B51+B52)/B56</f>
         <v/>
       </c>
+      <c r="H100" s="176" t="n"/>
     </row>
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="205" t="n">
@@ -12585,6 +13300,7 @@
         <f>(NPV($A101,C36:G36)+(G36*(1+G$99)/($A101-G$99))/(1+$A101)^5+B51+B52)/B56</f>
         <v/>
       </c>
+      <c r="H101" s="176" t="n"/>
     </row>
     <row r="102" ht="28" customHeight="1">
       <c r="A102" s="205" t="n">
@@ -12611,6 +13327,7 @@
         <f>(NPV($A102,C36:G36)+(G36*(1+G$99)/($A102-G$99))/(1+$A102)^5+B51+B52)/B56</f>
         <v/>
       </c>
+      <c r="H102" s="176" t="n"/>
     </row>
     <row r="103" ht="28" customHeight="1">
       <c r="A103" s="205" t="n">
@@ -12637,6 +13354,7 @@
         <f>(NPV($A103,C36:G36)+(G36*(1+G$99)/($A103-G$99))/(1+$A103)^5+B51+B52)/B56</f>
         <v/>
       </c>
+      <c r="H103" s="176" t="n"/>
     </row>
     <row r="104" ht="28" customHeight="1">
       <c r="A104" s="205" t="n">
@@ -12663,8 +13381,22 @@
         <f>(NPV($A104,C36:G36)+(G36*(1+G$99)/($A104-G$99))/(1+$A104)^5+B51+B52)/B56</f>
         <v/>
       </c>
+      <c r="H104" s="176" t="n"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -12676,7 +13408,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -12703,6 +13435,7 @@
       <c r="E1" s="184" t="n"/>
       <c r="F1" s="176" t="n"/>
       <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="176" t="n"/>
@@ -12712,6 +13445,11 @@
       <c r="E2" s="176" t="n"/>
       <c r="F2" s="176" t="n"/>
       <c r="G2" s="176" t="n"/>
+      <c r="H2" s="224" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="127" t="inlineStr">
@@ -12725,6 +13463,7 @@
       <c r="E3" s="176" t="n"/>
       <c r="F3" s="176" t="n"/>
       <c r="G3" s="176" t="n"/>
+      <c r="H3" s="176" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -12740,6 +13479,11 @@
       <c r="E4" s="176" t="n"/>
       <c r="F4" s="176" t="n"/>
       <c r="G4" s="176" t="n"/>
+      <c r="H4" s="188" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -12756,6 +13500,7 @@
       <c r="E5" s="176" t="n"/>
       <c r="F5" s="176" t="n"/>
       <c r="G5" s="176" t="n"/>
+      <c r="H5" s="176" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -12772,6 +13517,7 @@
       <c r="E6" s="176" t="n"/>
       <c r="F6" s="176" t="n"/>
       <c r="G6" s="176" t="n"/>
+      <c r="H6" s="176" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
@@ -12787,6 +13533,11 @@
       <c r="E7" s="176" t="n"/>
       <c r="F7" s="176" t="n"/>
       <c r="G7" s="176" t="n"/>
+      <c r="H7" s="188" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -12802,6 +13553,11 @@
       <c r="E8" s="176" t="n"/>
       <c r="F8" s="176" t="n"/>
       <c r="G8" s="176" t="n"/>
+      <c r="H8" s="188" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -12817,6 +13573,11 @@
       <c r="E9" s="176" t="n"/>
       <c r="F9" s="176" t="n"/>
       <c r="G9" s="176" t="n"/>
+      <c r="H9" s="188" t="inlineStr">
+        <is>
+          <t>10-K</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -12832,6 +13593,11 @@
       <c r="E10" s="176" t="n"/>
       <c r="F10" s="176" t="n"/>
       <c r="G10" s="176" t="n"/>
+      <c r="H10" s="188" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="107" t="inlineStr">
@@ -12848,6 +13614,7 @@
       <c r="E11" s="176" t="n"/>
       <c r="F11" s="176" t="n"/>
       <c r="G11" s="176" t="n"/>
+      <c r="H11" s="176" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="107" t="inlineStr">
@@ -12864,6 +13631,7 @@
       <c r="E12" s="176" t="n"/>
       <c r="F12" s="176" t="n"/>
       <c r="G12" s="176" t="n"/>
+      <c r="H12" s="176" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="176" t="n"/>
@@ -12873,6 +13641,7 @@
       <c r="E13" s="176" t="n"/>
       <c r="F13" s="176" t="n"/>
       <c r="G13" s="176" t="n"/>
+      <c r="H13" s="176" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="127" t="inlineStr">
@@ -12886,6 +13655,7 @@
       <c r="E14" s="176" t="n"/>
       <c r="F14" s="176" t="n"/>
       <c r="G14" s="176" t="n"/>
+      <c r="H14" s="176" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="107" t="inlineStr">
@@ -12899,6 +13669,7 @@
       <c r="E15" s="176" t="n"/>
       <c r="F15" s="176" t="n"/>
       <c r="G15" s="176" t="n"/>
+      <c r="H15" s="176" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="127" t="inlineStr">
@@ -12912,6 +13683,7 @@
       <c r="E16" s="176" t="n"/>
       <c r="F16" s="176" t="n"/>
       <c r="G16" s="176" t="n"/>
+      <c r="H16" s="176" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="26" t="n"/>
@@ -12921,6 +13693,7 @@
       <c r="E17" s="176" t="n"/>
       <c r="F17" s="176" t="n"/>
       <c r="G17" s="176" t="n"/>
+      <c r="H17" s="176" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="206" t="inlineStr">
@@ -12946,6 +13719,7 @@
           <t>EBITDA ($000)</t>
         </is>
       </c>
+      <c r="H18" s="176" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -12966,6 +13740,11 @@
       <c r="G19" s="207" t="n">
         <v>2548084</v>
       </c>
+      <c r="H19" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -12986,6 +13765,11 @@
       <c r="G20" s="207" t="n">
         <v>-23230</v>
       </c>
+      <c r="H20" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
@@ -13006,6 +13790,11 @@
       <c r="G21" s="207" t="n">
         <v>3857684</v>
       </c>
+      <c r="H21" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
@@ -13026,6 +13815,11 @@
       <c r="G22" s="207" t="n">
         <v>4647000</v>
       </c>
+      <c r="H22" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="28" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
@@ -13046,6 +13840,11 @@
       <c r="G23" s="207" t="n">
         <v>1329439</v>
       </c>
+      <c r="H23" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
@@ -13066,6 +13865,11 @@
       <c r="G24" s="207" t="n">
         <v>1768400</v>
       </c>
+      <c r="H24" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
@@ -13086,6 +13890,11 @@
       <c r="G25" s="207" t="n">
         <v>922278</v>
       </c>
+      <c r="H25" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
@@ -13106,6 +13915,11 @@
       <c r="G26" s="207" t="n">
         <v>62010</v>
       </c>
+      <c r="H26" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
@@ -13126,6 +13940,11 @@
       <c r="G27" s="207" t="n">
         <v>976700</v>
       </c>
+      <c r="H27" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
@@ -13146,6 +13965,11 @@
       <c r="G28" s="207" t="n">
         <v>235723</v>
       </c>
+      <c r="H28" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
@@ -13165,6 +13989,11 @@
       </c>
       <c r="G29" s="207" t="n">
         <v>407521</v>
+      </c>
+      <c r="H29" s="188" t="inlineStr">
+        <is>
+          <t>PitchBook Comps Set 04-Sep-2026</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -13175,6 +14004,7 @@
       <c r="E30" s="176" t="n"/>
       <c r="F30" s="176" t="n"/>
       <c r="G30" s="176" t="n"/>
+      <c r="H30" s="176" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="127" t="inlineStr">
@@ -13188,6 +14018,7 @@
       <c r="E31" s="176" t="n"/>
       <c r="F31" s="176" t="n"/>
       <c r="G31" s="176" t="n"/>
+      <c r="H31" s="176" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="26" t="n"/>
@@ -13197,6 +14028,7 @@
       <c r="E32" s="176" t="n"/>
       <c r="F32" s="176" t="n"/>
       <c r="G32" s="176" t="n"/>
+      <c r="H32" s="176" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="16" t="inlineStr">
@@ -13212,6 +14044,11 @@
       <c r="E33" s="176" t="n"/>
       <c r="F33" s="176" t="n"/>
       <c r="G33" s="176" t="n"/>
+      <c r="H33" s="188" t="inlineStr">
+        <is>
+          <t>Reuters: Alo parent $10bn Moelis ask Also: Reuters: Alo 2023 process; no deal</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
@@ -13227,6 +14064,11 @@
       <c r="E34" s="176" t="n"/>
       <c r="F34" s="176" t="n"/>
       <c r="G34" s="176" t="n"/>
+      <c r="H34" s="188" t="inlineStr">
+        <is>
+          <t>Forbes: Color Image nearly $2bn sales</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="68" t="inlineStr">
@@ -13243,6 +14085,7 @@
       <c r="E35" s="176" t="n"/>
       <c r="F35" s="176" t="n"/>
       <c r="G35" s="176" t="n"/>
+      <c r="H35" s="176" t="n"/>
     </row>
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="16" t="inlineStr">
@@ -13260,6 +14103,7 @@
       <c r="E36" s="176" t="n"/>
       <c r="F36" s="176" t="n"/>
       <c r="G36" s="176" t="n"/>
+      <c r="H36" s="176" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="176" t="n"/>
@@ -13269,6 +14113,7 @@
       <c r="E37" s="176" t="n"/>
       <c r="F37" s="176" t="n"/>
       <c r="G37" s="176" t="n"/>
+      <c r="H37" s="176" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="127" t="inlineStr">
@@ -13282,6 +14127,7 @@
       <c r="E38" s="176" t="n"/>
       <c r="F38" s="176" t="n"/>
       <c r="G38" s="176" t="n"/>
+      <c r="H38" s="176" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -13298,6 +14144,7 @@
       <c r="E39" s="176" t="n"/>
       <c r="F39" s="176" t="n"/>
       <c r="G39" s="176" t="n"/>
+      <c r="H39" s="176" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
@@ -13314,6 +14161,7 @@
       <c r="E40" s="176" t="n"/>
       <c r="F40" s="176" t="n"/>
       <c r="G40" s="176" t="n"/>
+      <c r="H40" s="176" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="107" t="n"/>
@@ -13323,6 +14171,7 @@
       <c r="E41" s="176" t="n"/>
       <c r="F41" s="176" t="n"/>
       <c r="G41" s="176" t="n"/>
+      <c r="H41" s="176" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="176" t="n"/>
@@ -13332,6 +14181,7 @@
       <c r="E42" s="176" t="n"/>
       <c r="F42" s="176" t="n"/>
       <c r="G42" s="176" t="n"/>
+      <c r="H42" s="176" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="127" t="inlineStr">
@@ -13345,11 +14195,12 @@
       <c r="E43" s="176" t="n"/>
       <c r="F43" s="176" t="n"/>
       <c r="G43" s="176" t="n"/>
+      <c r="H43" s="176" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>Gordon Growth implied exit EV/EBITDA</t>
+          <t>Gordon-implied exit EV/EBITDA</t>
         </is>
       </c>
       <c r="B44" s="94">
@@ -13361,6 +14212,7 @@
       <c r="E44" s="176" t="n"/>
       <c r="F44" s="176" t="n"/>
       <c r="G44" s="176" t="n"/>
+      <c r="H44" s="176" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="68" t="inlineStr">
@@ -13377,11 +14229,12 @@
       <c r="E45" s="176" t="n"/>
       <c r="F45" s="176" t="n"/>
       <c r="G45" s="176" t="n"/>
+      <c r="H45" s="176" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>Spread (selected - Gordon implied)</t>
+          <t>Spread vs Gordon-implied</t>
         </is>
       </c>
       <c r="B46" s="94">
@@ -13393,11 +14246,12 @@
       <c r="E46" s="176" t="n"/>
       <c r="F46" s="176" t="n"/>
       <c r="G46" s="176" t="n"/>
+      <c r="H46" s="176" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="68" t="inlineStr">
         <is>
-          <t>Selected exit multiple (Gordon growth)</t>
+          <t>Selected exit multiple</t>
         </is>
       </c>
       <c r="B47" s="176" t="n"/>
@@ -13406,6 +14260,7 @@
       <c r="E47" s="176" t="n"/>
       <c r="F47" s="176" t="n"/>
       <c r="G47" s="176" t="n"/>
+      <c r="H47" s="176" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="41" t="n"/>
@@ -13415,6 +14270,7 @@
       <c r="E48" s="176" t="n"/>
       <c r="F48" s="176" t="n"/>
       <c r="G48" s="176" t="n"/>
+      <c r="H48" s="176" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="41" t="n"/>
@@ -13424,6 +14280,7 @@
       <c r="E49" s="176" t="n"/>
       <c r="F49" s="176" t="n"/>
       <c r="G49" s="176" t="n"/>
+      <c r="H49" s="176" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="41" t="n"/>
@@ -13433,6 +14290,7 @@
       <c r="E50" s="176" t="n"/>
       <c r="F50" s="176" t="n"/>
       <c r="G50" s="176" t="n"/>
+      <c r="H50" s="176" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="41" t="n"/>
@@ -13442,6 +14300,7 @@
       <c r="E51" s="176" t="n"/>
       <c r="F51" s="176" t="n"/>
       <c r="G51" s="176" t="n"/>
+      <c r="H51" s="176" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="41" t="n"/>
@@ -13451,6 +14310,7 @@
       <c r="E52" s="176" t="n"/>
       <c r="F52" s="176" t="n"/>
       <c r="G52" s="176" t="n"/>
+      <c r="H52" s="176" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="41" t="n"/>
@@ -13460,6 +14320,7 @@
       <c r="E53" s="176" t="n"/>
       <c r="F53" s="176" t="n"/>
       <c r="G53" s="176" t="n"/>
+      <c r="H53" s="176" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="176" t="n"/>
@@ -13469,6 +14330,7 @@
       <c r="E54" s="176" t="n"/>
       <c r="F54" s="176" t="n"/>
       <c r="G54" s="176" t="n"/>
+      <c r="H54" s="176" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="127" t="inlineStr">
@@ -13482,6 +14344,7 @@
       <c r="E55" s="176" t="n"/>
       <c r="F55" s="176" t="n"/>
       <c r="G55" s="176" t="n"/>
+      <c r="H55" s="176" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="206" t="inlineStr">
@@ -13511,6 +14374,11 @@
       </c>
       <c r="F56" s="176" t="n"/>
       <c r="G56" s="176" t="n"/>
+      <c r="H56" s="188" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="16" t="inlineStr">
@@ -13534,11 +14402,16 @@
       </c>
       <c r="F57" s="176" t="n"/>
       <c r="G57" s="176" t="n"/>
+      <c r="H57" s="188" t="inlineStr">
+        <is>
+          <t>Lo: StockAnalysis: LULU EV/EBITDA Hi: StockAnalysis: DECK EV/EBITDA</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="28" customHeight="1">
       <c r="A58" s="68" t="inlineStr">
         <is>
-          <t>DCF exit method (Gordon-implied on FY2030E EBITDA)</t>
+          <t>DCF exit method</t>
         </is>
       </c>
       <c r="B58" s="222">
@@ -13553,6 +14426,7 @@
       <c r="E58" s="176" t="n"/>
       <c r="F58" s="176" t="n"/>
       <c r="G58" s="176" t="n"/>
+      <c r="H58" s="176" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="16" t="inlineStr">
@@ -13576,6 +14450,11 @@
       </c>
       <c r="F59" s="176" t="n"/>
       <c r="G59" s="176" t="n"/>
+      <c r="H59" s="188" t="inlineStr">
+        <is>
+          <t>Lo: StockAnalysis: LULU Forward P/E Hi: StockAnalysis: NKE Forward P/E</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -13595,6 +14474,7 @@
       </c>
       <c r="F60" s="176" t="n"/>
       <c r="G60" s="176" t="n"/>
+      <c r="H60" s="176" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="176" t="n"/>
@@ -13604,6 +14484,7 @@
       <c r="E61" s="176" t="n"/>
       <c r="F61" s="176" t="n"/>
       <c r="G61" s="176" t="n"/>
+      <c r="H61" s="176" t="n"/>
     </row>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
@@ -13619,6 +14500,11 @@
       <c r="E62" s="176" t="n"/>
       <c r="F62" s="176" t="n"/>
       <c r="G62" s="176" t="n"/>
+      <c r="H62" s="188" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="26" t="n"/>
@@ -13628,8 +14514,21 @@
       <c r="E63" s="176" t="n"/>
       <c r="F63" s="176" t="n"/>
       <c r="G63" s="176" t="n"/>
+      <c r="H63" s="176" t="n"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -2555,7 +2555,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2608,7 +2608,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="B4" s="32" t="n">
+      <c r="B4" s="75" t="n">
         <v>0.06</v>
       </c>
       <c r="C4" s="188" t="inlineStr">
@@ -2779,7 +2779,7 @@
           <t>Target Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="75">
         <f>B17/B18</f>
         <v/>
       </c>
@@ -2867,7 +2867,7 @@
           <t>Cost of Equity</t>
         </is>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="130">
         <f>B3+B24*B4</f>
         <v/>
       </c>
@@ -2893,7 +2893,7 @@
           <t>Pre-Tax Cost of Debt</t>
         </is>
       </c>
-      <c r="B30" s="32" t="n">
+      <c r="B30" s="75" t="n">
         <v>0.05</v>
       </c>
       <c r="C30" s="176" t="n"/>
@@ -2904,7 +2904,7 @@
           <t>After-Tax Cost of Debt</t>
         </is>
       </c>
-      <c r="B31" s="31">
+      <c r="B31" s="130">
         <f>B30*(1-B5)</f>
         <v/>
       </c>
@@ -3429,13 +3429,13 @@
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
       </c>
-      <c r="C20" s="32" t="n">
+      <c r="C20" s="75" t="n">
         <v>0.06</v>
       </c>
-      <c r="D20" s="32" t="n">
+      <c r="D20" s="75" t="n">
         <v>0.06</v>
       </c>
-      <c r="E20" s="32" t="n">
+      <c r="E20" s="75" t="n">
         <v>0.06</v>
       </c>
       <c r="F20" s="176" t="n"/>
@@ -10489,7 +10489,7 @@
           <t>Store-channel EBIT (= Rev x store margin)</t>
         </is>
       </c>
-      <c r="B31" s="75">
+      <c r="B31" s="32">
         <f>C31</f>
         <v/>
       </c>
@@ -10521,7 +10521,7 @@
           <t>E-commerce EBIT (= Rev x e-comm margin)</t>
         </is>
       </c>
-      <c r="B32" s="75">
+      <c r="B32" s="32">
         <f>C32</f>
         <v/>
       </c>
@@ -10553,7 +10553,7 @@
           <t>Other-channels EBIT (= Rev x other margin)</t>
         </is>
       </c>
-      <c r="B33" s="75">
+      <c r="B33" s="32">
         <f>C33</f>
         <v/>
       </c>
@@ -10614,7 +10614,7 @@
           <t>EBIT after channel mix</t>
         </is>
       </c>
-      <c r="B35" s="130">
+      <c r="B35" s="31">
         <f>C35</f>
         <v/>
       </c>
@@ -10646,27 +10646,27 @@
           <t>Normalized EBIT (tax base for NOPAT)</t>
         </is>
       </c>
-      <c r="B36" s="31">
+      <c r="B36" s="130">
         <f>B21+B23+B24-B25</f>
         <v/>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="130">
         <f>Scenarios!D45</f>
         <v/>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="130">
         <f>Scenarios!D46</f>
         <v/>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="130">
         <f>Scenarios!D47</f>
         <v/>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="130">
         <f>Scenarios!D48</f>
         <v/>
       </c>
-      <c r="G36" s="31">
+      <c r="G36" s="130">
         <f>Scenarios!D49</f>
         <v/>
       </c>
@@ -10756,24 +10756,27 @@
           <t>Unlevered tax on normalized EBIT</t>
         </is>
       </c>
-      <c r="B40" s="176" t="n"/>
-      <c r="C40" s="32">
+      <c r="B40" s="218">
+        <f>B36*B39</f>
+        <v/>
+      </c>
+      <c r="C40" s="75">
         <f>C36*C39</f>
         <v/>
       </c>
-      <c r="D40" s="32">
+      <c r="D40" s="75">
         <f>D36*D39</f>
         <v/>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="75">
         <f>E36*E39</f>
         <v/>
       </c>
-      <c r="F40" s="32">
+      <c r="F40" s="75">
         <f>F36*F39</f>
         <v/>
       </c>
-      <c r="G40" s="32">
+      <c r="G40" s="75">
         <f>G36*G39</f>
         <v/>
       </c>
@@ -10785,7 +10788,10 @@
           <t>NORMALIZED NOPAT</t>
         </is>
       </c>
-      <c r="B41" s="176" t="n"/>
+      <c r="B41" s="218">
+        <f>B36-B40</f>
+        <v/>
+      </c>
       <c r="C41" s="130">
         <f>C36-C40</f>
         <v/>
@@ -11359,24 +11365,27 @@
           <t>Less: Taxes</t>
         </is>
       </c>
-      <c r="B13" s="176" t="n"/>
-      <c r="C13" s="32">
+      <c r="B13" s="218">
+        <f>-'NOPAT Bridge'!B40</f>
+        <v/>
+      </c>
+      <c r="C13" s="75">
         <f>-'NOPAT Bridge'!C40</f>
         <v/>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="75">
         <f>-'NOPAT Bridge'!D40</f>
         <v/>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="75">
         <f>-'NOPAT Bridge'!E40</f>
         <v/>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="75">
         <f>-'NOPAT Bridge'!F40</f>
         <v/>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="75">
         <f>-'NOPAT Bridge'!G40</f>
         <v/>
       </c>
@@ -11388,7 +11397,10 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="B14" s="176" t="n"/>
+      <c r="B14" s="218">
+        <f>'NOPAT Bridge'!B41</f>
+        <v/>
+      </c>
       <c r="C14" s="130">
         <f>Scenarios!D50</f>
         <v/>
@@ -11462,7 +11474,10 @@
           <t>Plus: D&amp;A</t>
         </is>
       </c>
-      <c r="B17" s="176" t="n"/>
+      <c r="B17" s="218">
+        <f>B15</f>
+        <v/>
+      </c>
       <c r="C17" s="75">
         <f>Scenarios!D55</f>
         <v/>
@@ -11520,7 +11535,10 @@
           <t>Less: Capex</t>
         </is>
       </c>
-      <c r="B19" s="176" t="n"/>
+      <c r="B19" s="218">
+        <f>-680802</f>
+        <v/>
+      </c>
       <c r="C19" s="75">
         <f>Scenarios!D60</f>
         <v/>
@@ -11831,7 +11849,7 @@
           <t>Accrued liabilities (% of revenue)</t>
         </is>
       </c>
-      <c r="B29" s="32">
+      <c r="B29" s="75">
         <f>Scenarios!$D$20</f>
         <v/>
       </c>
@@ -12234,7 +12252,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="B46" s="32">
+      <c r="B46" s="75">
         <f>G36*(1+Scenarios!D10)/(WACC!B36-Scenarios!D10)</f>
         <v/>
       </c>

--- a/LULU/unbeiesgbar_final.xlsx
+++ b/LULU/unbeiesgbar_final.xlsx
@@ -31,7 +31,7 @@
     <numFmt numFmtId="169" formatCode="0.0x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="73">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -450,6 +450,11 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -514,7 +519,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="227">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1097,6 +1102,9 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="71" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="60" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1422,6 +1430,11 @@
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
         <t>FY25 accrued % of revenue.</t>
+      </text>
+    </comment>
+    <comment ref="B27" authorId="0" shapeId="0">
+      <text>
+        <t>Held flat vs FY25 actuals.</t>
       </text>
     </comment>
     <comment ref="B100" authorId="0" shapeId="0">
@@ -2555,7 +2568,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2608,7 +2621,7 @@
           <t>Equity risk premium</t>
         </is>
       </c>
-      <c r="B4" s="75" t="n">
+      <c r="B4" s="32" t="n">
         <v>0.06</v>
       </c>
       <c r="C4" s="188" t="inlineStr">
@@ -2754,24 +2767,34 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
         <is>
-          <t>Total Debt</t>
-        </is>
-      </c>
-      <c r="B17" s="75" t="n">
-        <v>2140000</v>
-      </c>
-      <c r="C17" s="176" t="n"/>
+          <t>Total debt equivalents (for beta unlever)</t>
+        </is>
+      </c>
+      <c r="B17" s="75">
+        <f>B13</f>
+        <v/>
+      </c>
+      <c r="C17" s="176" t="inlineStr">
+        <is>
+          <t>Model: lease debt + funded debt (row 13)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>Market Capitalization</t>
-        </is>
-      </c>
-      <c r="B18" s="75" t="n">
-        <v>11140000</v>
-      </c>
-      <c r="C18" s="176" t="n"/>
+          <t>Market value of equity (for beta unlever)</t>
+        </is>
+      </c>
+      <c r="B18" s="75">
+        <f>B10</f>
+        <v/>
+      </c>
+      <c r="C18" s="176" t="inlineStr">
+        <is>
+          <t>Model: share price × shares (row 10)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -2779,7 +2802,7 @@
           <t>Target Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B19" s="75">
+      <c r="B19" s="28">
         <f>B17/B18</f>
         <v/>
       </c>
@@ -2867,7 +2890,7 @@
           <t>Cost of Equity</t>
         </is>
       </c>
-      <c r="B27" s="130">
+      <c r="B27" s="31">
         <f>B3+B24*B4</f>
         <v/>
       </c>
@@ -2893,7 +2916,7 @@
           <t>Pre-Tax Cost of Debt</t>
         </is>
       </c>
-      <c r="B30" s="75" t="n">
+      <c r="B30" s="32" t="n">
         <v>0.05</v>
       </c>
       <c r="C30" s="176" t="n"/>
@@ -2904,7 +2927,7 @@
           <t>After-Tax Cost of Debt</t>
         </is>
       </c>
-      <c r="B31" s="130">
+      <c r="B31" s="31">
         <f>B30*(1-B5)</f>
         <v/>
       </c>
@@ -2983,7 +3006,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1" showOutlineSymbols="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:H202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3008,6 +3031,7 @@
       <c r="E1" s="184" t="n"/>
       <c r="F1" s="176" t="n"/>
       <c r="G1" s="176" t="n"/>
+      <c r="H1" s="176" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="176" t="n"/>
@@ -3033,6 +3057,7 @@
       </c>
       <c r="F2" s="176" t="n"/>
       <c r="G2" s="176" t="n"/>
+      <c r="H2" s="176" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="127" t="inlineStr">
@@ -3046,6 +3071,7 @@
       <c r="E3" s="176" t="n"/>
       <c r="F3" s="176" t="n"/>
       <c r="G3" s="11" t="n"/>
+      <c r="H3" s="176" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -3069,6 +3095,7 @@
       </c>
       <c r="F4" s="176" t="n"/>
       <c r="G4" s="103" t="n"/>
+      <c r="H4" s="176" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -3092,6 +3119,7 @@
       </c>
       <c r="F5" s="176" t="n"/>
       <c r="G5" s="176" t="n"/>
+      <c r="H5" s="176" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="16" t="inlineStr">
@@ -3115,6 +3143,7 @@
       </c>
       <c r="F6" s="176" t="n"/>
       <c r="G6" s="176" t="n"/>
+      <c r="H6" s="176" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
@@ -3138,6 +3167,7 @@
       </c>
       <c r="F7" s="176" t="n"/>
       <c r="G7" s="176" t="n"/>
+      <c r="H7" s="176" t="n"/>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="16" t="inlineStr">
@@ -3161,6 +3191,7 @@
       </c>
       <c r="F8" s="176" t="n"/>
       <c r="G8" s="176" t="n"/>
+      <c r="H8" s="176" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="16" t="inlineStr">
@@ -3185,6 +3216,7 @@
       </c>
       <c r="F9" s="176" t="n"/>
       <c r="G9" s="176" t="n"/>
+      <c r="H9" s="176" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="16" t="inlineStr">
@@ -3208,6 +3240,7 @@
       </c>
       <c r="F10" s="176" t="n"/>
       <c r="G10" s="176" t="n"/>
+      <c r="H10" s="176" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
@@ -3231,6 +3264,7 @@
       </c>
       <c r="F11" s="176" t="n"/>
       <c r="G11" s="176" t="n"/>
+      <c r="H11" s="176" t="n"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
@@ -3255,6 +3289,7 @@
       </c>
       <c r="F12" s="176" t="n"/>
       <c r="G12" s="176" t="n"/>
+      <c r="H12" s="176" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="16" t="inlineStr">
@@ -3278,6 +3313,7 @@
       </c>
       <c r="F13" s="176" t="n"/>
       <c r="G13" s="176" t="n"/>
+      <c r="H13" s="176" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="16" t="inlineStr">
@@ -3302,6 +3338,7 @@
       </c>
       <c r="F14" s="176" t="n"/>
       <c r="G14" s="176" t="n"/>
+      <c r="H14" s="176" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="16" t="inlineStr">
@@ -3325,6 +3362,7 @@
       </c>
       <c r="F15" s="176" t="n"/>
       <c r="G15" s="176" t="n"/>
+      <c r="H15" s="176" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="16" t="inlineStr">
@@ -3348,6 +3386,7 @@
       </c>
       <c r="F16" s="176" t="n"/>
       <c r="G16" s="176" t="n"/>
+      <c r="H16" s="176" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="16" t="inlineStr">
@@ -3371,6 +3410,7 @@
       </c>
       <c r="F17" s="176" t="n"/>
       <c r="G17" s="176" t="n"/>
+      <c r="H17" s="176" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
@@ -3394,6 +3434,7 @@
       </c>
       <c r="F18" s="176" t="n"/>
       <c r="G18" s="176" t="n"/>
+      <c r="H18" s="176" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
@@ -3417,6 +3458,7 @@
       </c>
       <c r="F19" s="176" t="n"/>
       <c r="G19" s="176" t="n"/>
+      <c r="H19" s="176" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
@@ -3429,17 +3471,18 @@
           <t>LULU FY2025 10-K: Accrued liabilities and other</t>
         </is>
       </c>
-      <c r="C20" s="75" t="n">
+      <c r="C20" s="32" t="n">
         <v>0.06</v>
       </c>
-      <c r="D20" s="75" t="n">
+      <c r="D20" s="32" t="n">
         <v>0.06</v>
       </c>
-      <c r="E20" s="75" t="n">
+      <c r="E20" s="32" t="n">
         <v>0.06</v>
       </c>
       <c r="F20" s="176" t="n"/>
       <c r="G20" s="176" t="n"/>
+      <c r="H20" s="176" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="inlineStr">
@@ -3463,6 +3506,7 @@
       </c>
       <c r="F21" s="176" t="n"/>
       <c r="G21" s="176" t="n"/>
+      <c r="H21" s="176" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
@@ -3486,6 +3530,7 @@
       </c>
       <c r="F22" s="176" t="n"/>
       <c r="G22" s="176" t="n"/>
+      <c r="H22" s="176" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="176" t="n"/>
@@ -3495,24 +3540,46 @@
       <c r="E23" s="176" t="n"/>
       <c r="F23" s="176" t="n"/>
       <c r="G23" s="176" t="n"/>
+      <c r="H23" s="176" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="127" t="inlineStr">
         <is>
-          <t>5-year forecast paths (by scenario)</t>
+          <t>Base case forecast ($000)</t>
         </is>
       </c>
       <c r="B24" s="176" t="n"/>
       <c r="C24" s="176" t="n"/>
-      <c r="D24" s="176" t="n"/>
-      <c r="E24" s="176" t="n"/>
-      <c r="F24" s="176" t="n"/>
-      <c r="G24" s="176" t="n"/>
+      <c r="D24" s="176" t="inlineStr">
+        <is>
+          <t>FY26E</t>
+        </is>
+      </c>
+      <c r="E24" s="176" t="inlineStr">
+        <is>
+          <t>FY27E</t>
+        </is>
+      </c>
+      <c r="F24" s="176" t="inlineStr">
+        <is>
+          <t>FY28E</t>
+        </is>
+      </c>
+      <c r="G24" s="176" t="inlineStr">
+        <is>
+          <t>FY29E</t>
+        </is>
+      </c>
+      <c r="H24" s="176" t="inlineStr">
+        <is>
+          <t>FY30E</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="41" t="inlineStr">
         <is>
-          <t>Rev Y 1</t>
+          <t>Net revenue ($000)</t>
         </is>
       </c>
       <c r="B25" s="176" t="n"/>
@@ -3521,20 +3588,30 @@
         <v/>
       </c>
       <c r="D25" s="75">
-        <f>DCF!$B$6*(1+D4)</f>
+        <f>DCF!C6</f>
         <v/>
       </c>
       <c r="E25" s="75">
-        <f>DCF!$B$6*(1+E4)</f>
-        <v/>
-      </c>
-      <c r="F25" s="176" t="n"/>
-      <c r="G25" s="176" t="n"/>
+        <f>DCF!D6</f>
+        <v/>
+      </c>
+      <c r="F25" s="176">
+        <f>DCF!E6</f>
+        <v/>
+      </c>
+      <c r="G25" s="176">
+        <f>DCF!F6</f>
+        <v/>
+      </c>
+      <c r="H25" s="176">
+        <f>DCF!G6</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="41" t="inlineStr">
         <is>
-          <t>Rev Y 2</t>
+          <t>COGS ($000)</t>
         </is>
       </c>
       <c r="B26" s="176" t="n"/>
@@ -3543,64 +3620,94 @@
         <v/>
       </c>
       <c r="D26" s="75">
-        <f>D25*(1+D5)</f>
+        <f>DCF!C8</f>
         <v/>
       </c>
       <c r="E26" s="75">
-        <f>E25*(1+E5)</f>
-        <v/>
-      </c>
-      <c r="F26" s="176" t="n"/>
-      <c r="G26" s="176" t="n"/>
+        <f>DCF!D8</f>
+        <v/>
+      </c>
+      <c r="F26" s="176">
+        <f>DCF!E8</f>
+        <v/>
+      </c>
+      <c r="G26" s="176">
+        <f>DCF!F8</f>
+        <v/>
+      </c>
+      <c r="H26" s="176">
+        <f>DCF!G8</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="41" t="inlineStr">
         <is>
-          <t>Rev Y 3</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B27" s="176" t="n"/>
-      <c r="C27" s="75">
+      <c r="C27" s="32">
         <f>C26*(1+C5)</f>
         <v/>
       </c>
-      <c r="D27" s="75">
-        <f>D26*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E27" s="75">
-        <f>E26*(1+E5)</f>
-        <v/>
-      </c>
-      <c r="F27" s="176" t="n"/>
-      <c r="G27" s="176" t="n"/>
+      <c r="D27" s="32">
+        <f>DCF!C7</f>
+        <v/>
+      </c>
+      <c r="E27" s="32">
+        <f>DCF!D7</f>
+        <v/>
+      </c>
+      <c r="F27" s="176">
+        <f>DCF!E7</f>
+        <v/>
+      </c>
+      <c r="G27" s="176">
+        <f>DCF!F7</f>
+        <v/>
+      </c>
+      <c r="H27" s="176">
+        <f>DCF!G7</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="41" t="inlineStr">
         <is>
-          <t>Rev Y 4</t>
+          <t>EBIT margin %</t>
         </is>
       </c>
       <c r="B28" s="176" t="n"/>
-      <c r="C28" s="75">
+      <c r="C28" s="32">
         <f>C27*(1+C5)</f>
         <v/>
       </c>
-      <c r="D28" s="75">
-        <f>D27*(1+D5)</f>
-        <v/>
-      </c>
-      <c r="E28" s="75">
-        <f>E27*(1+E5)</f>
-        <v/>
-      </c>
-      <c r="F28" s="176" t="n"/>
-      <c r="G28" s="176" t="n"/>
+      <c r="D28" s="32">
+        <f>DCF!C9</f>
+        <v/>
+      </c>
+      <c r="E28" s="32">
+        <f>DCF!D9</f>
+        <v/>
+      </c>
+      <c r="F28" s="176">
+        <f>DCF!E9</f>
+        <v/>
+      </c>
+      <c r="G28" s="176">
+        <f>DCF!F9</f>
+        <v/>
+      </c>
+      <c r="H28" s="176">
+        <f>DCF!G9</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="41" t="inlineStr">
         <is>
-          <t>Rev Y 5</t>
+          <t>EBIT ($000)</t>
         </is>
       </c>
       <c r="B29" s="176" t="n"/>
@@ -3609,785 +3716,463 @@
         <v/>
       </c>
       <c r="D29" s="75">
-        <f>D28*(1+D5)</f>
+        <f>DCF!C11</f>
         <v/>
       </c>
       <c r="E29" s="75">
-        <f>E28*(1+E5)</f>
-        <v/>
-      </c>
-      <c r="F29" s="176" t="n"/>
-      <c r="G29" s="176" t="n"/>
+        <f>DCF!D11</f>
+        <v/>
+      </c>
+      <c r="F29" s="176">
+        <f>DCF!E11</f>
+        <v/>
+      </c>
+      <c r="G29" s="176">
+        <f>DCF!F11</f>
+        <v/>
+      </c>
+      <c r="H29" s="176">
+        <f>DCF!G11</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="41" t="inlineStr">
         <is>
-          <t>GM% Y 1</t>
+          <t>NOPAT ($000)</t>
         </is>
       </c>
       <c r="B30" s="176" t="n"/>
-      <c r="C30" s="32">
+      <c r="C30" s="75">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D30" s="32">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="E30" s="32">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="F30" s="176" t="n"/>
-      <c r="G30" s="176" t="n"/>
+      <c r="D30" s="75">
+        <f>DCF!C14</f>
+        <v/>
+      </c>
+      <c r="E30" s="75">
+        <f>DCF!D14</f>
+        <v/>
+      </c>
+      <c r="F30" s="176">
+        <f>DCF!E14</f>
+        <v/>
+      </c>
+      <c r="G30" s="176">
+        <f>DCF!F14</f>
+        <v/>
+      </c>
+      <c r="H30" s="176">
+        <f>DCF!G14</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="41" t="inlineStr">
         <is>
-          <t>GM% Y 2</t>
+          <t>D&amp;A ($000)</t>
         </is>
       </c>
       <c r="B31" s="176" t="n"/>
-      <c r="C31" s="32">
+      <c r="C31" s="75">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D31" s="32">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="E31" s="32">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="F31" s="176" t="n"/>
-      <c r="G31" s="176" t="n"/>
+      <c r="D31" s="75">
+        <f>DCF!C17</f>
+        <v/>
+      </c>
+      <c r="E31" s="75">
+        <f>DCF!D17</f>
+        <v/>
+      </c>
+      <c r="F31" s="176">
+        <f>DCF!E17</f>
+        <v/>
+      </c>
+      <c r="G31" s="176">
+        <f>DCF!F17</f>
+        <v/>
+      </c>
+      <c r="H31" s="176">
+        <f>DCF!G17</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="41" t="inlineStr">
         <is>
-          <t>GM% Y 3</t>
+          <t>Capex ($000)</t>
         </is>
       </c>
       <c r="B32" s="176" t="n"/>
-      <c r="C32" s="32">
+      <c r="C32" s="75">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D32" s="32">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="E32" s="32">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="F32" s="176" t="n"/>
-      <c r="G32" s="176" t="n"/>
+      <c r="D32" s="75">
+        <f>DCF!C19</f>
+        <v/>
+      </c>
+      <c r="E32" s="75">
+        <f>DCF!D19</f>
+        <v/>
+      </c>
+      <c r="F32" s="176">
+        <f>DCF!E19</f>
+        <v/>
+      </c>
+      <c r="G32" s="176">
+        <f>DCF!F19</f>
+        <v/>
+      </c>
+      <c r="H32" s="176">
+        <f>DCF!G19</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="41" t="inlineStr">
         <is>
-          <t>GM% Y 4</t>
+          <t>Unlevered FCF ($000)</t>
         </is>
       </c>
       <c r="B33" s="176" t="n"/>
-      <c r="C33" s="32">
+      <c r="C33" s="75">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D33" s="32">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="E33" s="32">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="F33" s="176" t="n"/>
-      <c r="G33" s="176" t="n"/>
+      <c r="D33" s="75">
+        <f>DCF!C36</f>
+        <v/>
+      </c>
+      <c r="E33" s="75">
+        <f>DCF!D36</f>
+        <v/>
+      </c>
+      <c r="F33" s="176">
+        <f>DCF!E36</f>
+        <v/>
+      </c>
+      <c r="G33" s="176">
+        <f>DCF!F36</f>
+        <v/>
+      </c>
+      <c r="H33" s="176">
+        <f>DCF!G36</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="41" t="inlineStr">
-        <is>
-          <t>GM% Y 5</t>
-        </is>
-      </c>
+      <c r="A34" s="41" t="n"/>
       <c r="B34" s="176" t="n"/>
-      <c r="C34" s="32">
-        <f>C14</f>
-        <v/>
-      </c>
-      <c r="D34" s="32">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="E34" s="32">
-        <f>E14</f>
-        <v/>
-      </c>
+      <c r="C34" s="32" t="n"/>
+      <c r="D34" s="32" t="n"/>
+      <c r="E34" s="32" t="n"/>
       <c r="F34" s="176" t="n"/>
       <c r="G34" s="176" t="n"/>
+      <c r="H34" s="176" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="41" t="inlineStr">
-        <is>
-          <t>COGS - year 1</t>
-        </is>
-      </c>
+      <c r="A35" s="41" t="n"/>
       <c r="B35" s="176" t="n"/>
-      <c r="C35" s="75">
-        <f>C25*(1-C30)</f>
-        <v/>
-      </c>
-      <c r="D35" s="75">
-        <f>D25*(1-D30)</f>
-        <v/>
-      </c>
-      <c r="E35" s="75">
-        <f>E25*(1-E30)</f>
-        <v/>
-      </c>
+      <c r="C35" s="75" t="n"/>
+      <c r="D35" s="75" t="n"/>
+      <c r="E35" s="75" t="n"/>
       <c r="F35" s="176" t="n"/>
       <c r="G35" s="176" t="n"/>
+      <c r="H35" s="176" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="41" t="inlineStr">
-        <is>
-          <t>COGS - year 2</t>
-        </is>
-      </c>
+      <c r="A36" s="41" t="n"/>
       <c r="B36" s="176" t="n"/>
-      <c r="C36" s="75">
-        <f>C26*(1-C31)</f>
-        <v/>
-      </c>
-      <c r="D36" s="75">
-        <f>D26*(1-D31)</f>
-        <v/>
-      </c>
-      <c r="E36" s="75">
-        <f>E26*(1-E31)</f>
-        <v/>
-      </c>
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="75" t="n"/>
+      <c r="E36" s="75" t="n"/>
       <c r="F36" s="176" t="n"/>
       <c r="G36" s="176" t="n"/>
+      <c r="H36" s="176" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
-        <is>
-          <t>COGS - year 3</t>
-        </is>
-      </c>
+      <c r="A37" s="41" t="n"/>
       <c r="B37" s="176" t="n"/>
-      <c r="C37" s="75">
-        <f>C27*(1-C32)</f>
-        <v/>
-      </c>
-      <c r="D37" s="75">
-        <f>D27*(1-D32)</f>
-        <v/>
-      </c>
-      <c r="E37" s="75">
-        <f>E27*(1-E32)</f>
-        <v/>
-      </c>
+      <c r="C37" s="75" t="n"/>
+      <c r="D37" s="75" t="n"/>
+      <c r="E37" s="75" t="n"/>
       <c r="F37" s="176" t="n"/>
       <c r="G37" s="176" t="n"/>
+      <c r="H37" s="176" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="41" t="inlineStr">
-        <is>
-          <t>COGS - year 4</t>
-        </is>
-      </c>
+      <c r="A38" s="41" t="n"/>
       <c r="B38" s="176" t="n"/>
-      <c r="C38" s="75">
-        <f>C28*(1-C33)</f>
-        <v/>
-      </c>
-      <c r="D38" s="75">
-        <f>D28*(1-D33)</f>
-        <v/>
-      </c>
-      <c r="E38" s="75">
-        <f>E28*(1-E33)</f>
-        <v/>
-      </c>
+      <c r="C38" s="75" t="n"/>
+      <c r="D38" s="75" t="n"/>
+      <c r="E38" s="75" t="n"/>
       <c r="F38" s="176" t="n"/>
       <c r="G38" s="176" t="n"/>
+      <c r="H38" s="176" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="41" t="inlineStr">
-        <is>
-          <t>COGS - year 5</t>
-        </is>
-      </c>
+      <c r="A39" s="41" t="n"/>
       <c r="B39" s="176" t="n"/>
-      <c r="C39" s="75">
-        <f>C29*(1-C34)</f>
-        <v/>
-      </c>
-      <c r="D39" s="75">
-        <f>D29*(1-D34)</f>
-        <v/>
-      </c>
-      <c r="E39" s="75">
-        <f>E29*(1-E34)</f>
-        <v/>
-      </c>
+      <c r="C39" s="75" t="n"/>
+      <c r="D39" s="75" t="n"/>
+      <c r="E39" s="75" t="n"/>
       <c r="F39" s="176" t="n"/>
       <c r="G39" s="176" t="n"/>
+      <c r="H39" s="176" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Margin Y 1</t>
-        </is>
-      </c>
+      <c r="A40" s="41" t="n"/>
       <c r="B40" s="176" t="n"/>
-      <c r="C40" s="32">
-        <f>C6+(C8-C6)*0/4</f>
-        <v/>
-      </c>
-      <c r="D40" s="32">
-        <f>D6+(D8-D6)*0/4</f>
-        <v/>
-      </c>
-      <c r="E40" s="32">
-        <f>E6+(E8-E6)*0/4</f>
-        <v/>
-      </c>
+      <c r="C40" s="32" t="n"/>
+      <c r="D40" s="32" t="n"/>
+      <c r="E40" s="32" t="n"/>
       <c r="F40" s="176" t="n"/>
       <c r="G40" s="176" t="n"/>
+      <c r="H40" s="176" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Margin Y 2</t>
-        </is>
-      </c>
+      <c r="A41" s="41" t="n"/>
       <c r="B41" s="176" t="n"/>
-      <c r="C41" s="32">
-        <f>C6+(C8-C6)*1/4</f>
-        <v/>
-      </c>
-      <c r="D41" s="32">
-        <f>D6+(D8-D6)*1/4</f>
-        <v/>
-      </c>
-      <c r="E41" s="32">
-        <f>E6+(E8-E6)*1/4</f>
-        <v/>
-      </c>
+      <c r="C41" s="32" t="n"/>
+      <c r="D41" s="32" t="n"/>
+      <c r="E41" s="32" t="n"/>
       <c r="F41" s="176" t="n"/>
       <c r="G41" s="176" t="n"/>
+      <c r="H41" s="176" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Margin Y 3</t>
-        </is>
-      </c>
+      <c r="A42" s="41" t="n"/>
       <c r="B42" s="176" t="n"/>
-      <c r="C42" s="32">
-        <f>C6+(C8-C6)*2/4</f>
-        <v/>
-      </c>
-      <c r="D42" s="32">
-        <f>D6+(D8-D6)*2/4</f>
-        <v/>
-      </c>
-      <c r="E42" s="32">
-        <f>E6+(E8-E6)*2/4</f>
-        <v/>
-      </c>
+      <c r="C42" s="32" t="n"/>
+      <c r="D42" s="32" t="n"/>
+      <c r="E42" s="32" t="n"/>
       <c r="F42" s="176" t="n"/>
       <c r="G42" s="176" t="n"/>
+      <c r="H42" s="176" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Margin Y 4</t>
-        </is>
-      </c>
+      <c r="A43" s="41" t="n"/>
       <c r="B43" s="176" t="n"/>
-      <c r="C43" s="32">
-        <f>C6+(C8-C6)*3/4</f>
-        <v/>
-      </c>
-      <c r="D43" s="32">
-        <f>D6+(D8-D6)*3/4</f>
-        <v/>
-      </c>
-      <c r="E43" s="32">
-        <f>E6+(E8-E6)*3/4</f>
-        <v/>
-      </c>
+      <c r="C43" s="32" t="n"/>
+      <c r="D43" s="32" t="n"/>
+      <c r="E43" s="32" t="n"/>
       <c r="F43" s="176" t="n"/>
       <c r="G43" s="176" t="n"/>
+      <c r="H43" s="176" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Margin Y 5</t>
-        </is>
-      </c>
+      <c r="A44" s="41" t="n"/>
       <c r="B44" s="176" t="n"/>
-      <c r="C44" s="32">
-        <f>C6+(C8-C6)*4/4</f>
-        <v/>
-      </c>
-      <c r="D44" s="32">
-        <f>D6+(D8-D6)*4/4</f>
-        <v/>
-      </c>
-      <c r="E44" s="32">
-        <f>E6+(E8-E6)*4/4</f>
-        <v/>
-      </c>
+      <c r="C44" s="32" t="n"/>
+      <c r="D44" s="32" t="n"/>
+      <c r="E44" s="32" t="n"/>
       <c r="F44" s="176" t="n"/>
       <c r="G44" s="176" t="n"/>
+      <c r="H44" s="176" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Y 1</t>
-        </is>
-      </c>
+      <c r="A45" s="41" t="n"/>
       <c r="B45" s="176" t="n"/>
-      <c r="C45" s="75">
-        <f>C25*C40+C7</f>
-        <v/>
-      </c>
-      <c r="D45" s="75">
-        <f>D25*D40+D7</f>
-        <v/>
-      </c>
-      <c r="E45" s="75">
-        <f>E25*E40+E7</f>
-        <v/>
-      </c>
+      <c r="C45" s="75" t="n"/>
+      <c r="D45" s="75" t="n"/>
+      <c r="E45" s="75" t="n"/>
       <c r="F45" s="176" t="n"/>
       <c r="G45" s="176" t="n"/>
+      <c r="H45" s="176" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Y 2</t>
-        </is>
-      </c>
+      <c r="A46" s="41" t="n"/>
       <c r="B46" s="176" t="n"/>
-      <c r="C46" s="75">
-        <f>C26*C41</f>
-        <v/>
-      </c>
-      <c r="D46" s="75">
-        <f>D26*D41</f>
-        <v/>
-      </c>
-      <c r="E46" s="75">
-        <f>E26*E41</f>
-        <v/>
-      </c>
+      <c r="C46" s="75" t="n"/>
+      <c r="D46" s="75" t="n"/>
+      <c r="E46" s="75" t="n"/>
       <c r="F46" s="176" t="n"/>
       <c r="G46" s="176" t="n"/>
+      <c r="H46" s="176" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Y 3</t>
-        </is>
-      </c>
+      <c r="A47" s="41" t="n"/>
       <c r="B47" s="176" t="n"/>
-      <c r="C47" s="75">
-        <f>C27*C42</f>
-        <v/>
-      </c>
-      <c r="D47" s="75">
-        <f>D27*D42</f>
-        <v/>
-      </c>
-      <c r="E47" s="75">
-        <f>E27*E42</f>
-        <v/>
-      </c>
+      <c r="C47" s="75" t="n"/>
+      <c r="D47" s="75" t="n"/>
+      <c r="E47" s="75" t="n"/>
       <c r="F47" s="176" t="n"/>
       <c r="G47" s="176" t="n"/>
+      <c r="H47" s="176" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Y 4</t>
-        </is>
-      </c>
+      <c r="A48" s="41" t="n"/>
       <c r="B48" s="176" t="n"/>
-      <c r="C48" s="75">
-        <f>C28*C43</f>
-        <v/>
-      </c>
-      <c r="D48" s="75">
-        <f>D28*D43</f>
-        <v/>
-      </c>
-      <c r="E48" s="75">
-        <f>E28*E43</f>
-        <v/>
-      </c>
+      <c r="C48" s="75" t="n"/>
+      <c r="D48" s="75" t="n"/>
+      <c r="E48" s="75" t="n"/>
       <c r="F48" s="176" t="n"/>
       <c r="G48" s="176" t="n"/>
+      <c r="H48" s="176" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="41" t="inlineStr">
-        <is>
-          <t>EBIT Y 5</t>
-        </is>
-      </c>
+      <c r="A49" s="41" t="n"/>
       <c r="B49" s="176" t="n"/>
-      <c r="C49" s="75">
-        <f>C29*C44</f>
-        <v/>
-      </c>
-      <c r="D49" s="75">
-        <f>D29*D44</f>
-        <v/>
-      </c>
-      <c r="E49" s="75">
-        <f>E29*E44</f>
-        <v/>
-      </c>
+      <c r="C49" s="75" t="n"/>
+      <c r="D49" s="75" t="n"/>
+      <c r="E49" s="75" t="n"/>
       <c r="F49" s="176" t="n"/>
       <c r="G49" s="176" t="n"/>
+      <c r="H49" s="176" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="41" t="inlineStr">
-        <is>
-          <t>NOPAT Y 1</t>
-        </is>
-      </c>
+      <c r="A50" s="41" t="n"/>
       <c r="B50" s="176" t="n"/>
-      <c r="C50" s="75">
-        <f>C45*(1-'NOPAT Bridge'!C$39)</f>
-        <v/>
-      </c>
-      <c r="D50" s="75">
-        <f>'NOPAT Bridge'!C41</f>
-        <v/>
-      </c>
-      <c r="E50" s="75">
-        <f>E45*(1-'NOPAT Bridge'!C$39)</f>
-        <v/>
-      </c>
+      <c r="C50" s="75" t="n"/>
+      <c r="D50" s="75" t="n"/>
+      <c r="E50" s="75" t="n"/>
       <c r="F50" s="176" t="n"/>
       <c r="G50" s="176" t="n"/>
+      <c r="H50" s="176" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="41" t="inlineStr">
-        <is>
-          <t>NOPAT Y 2</t>
-        </is>
-      </c>
+      <c r="A51" s="41" t="n"/>
       <c r="B51" s="176" t="n"/>
-      <c r="C51" s="75">
-        <f>C46*(1-'NOPAT Bridge'!D$39)</f>
-        <v/>
-      </c>
-      <c r="D51" s="75">
-        <f>'NOPAT Bridge'!D41</f>
-        <v/>
-      </c>
-      <c r="E51" s="75">
-        <f>E46*(1-'NOPAT Bridge'!D$39)</f>
-        <v/>
-      </c>
+      <c r="C51" s="75" t="n"/>
+      <c r="D51" s="75" t="n"/>
+      <c r="E51" s="75" t="n"/>
       <c r="F51" s="176" t="n"/>
       <c r="G51" s="176" t="n"/>
+      <c r="H51" s="176" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="41" t="inlineStr">
-        <is>
-          <t>NOPAT Y 3</t>
-        </is>
-      </c>
+      <c r="A52" s="41" t="n"/>
       <c r="B52" s="176" t="n"/>
-      <c r="C52" s="75">
-        <f>C47*(1-'NOPAT Bridge'!E$39)</f>
-        <v/>
-      </c>
-      <c r="D52" s="75">
-        <f>'NOPAT Bridge'!E41</f>
-        <v/>
-      </c>
-      <c r="E52" s="75">
-        <f>E47*(1-'NOPAT Bridge'!E$39)</f>
-        <v/>
-      </c>
+      <c r="C52" s="75" t="n"/>
+      <c r="D52" s="75" t="n"/>
+      <c r="E52" s="75" t="n"/>
       <c r="F52" s="176" t="n"/>
       <c r="G52" s="176" t="n"/>
+      <c r="H52" s="176" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="41" t="inlineStr">
-        <is>
-          <t>NOPAT Y 4</t>
-        </is>
-      </c>
+      <c r="A53" s="41" t="n"/>
       <c r="B53" s="176" t="n"/>
-      <c r="C53" s="75">
-        <f>C48*(1-'NOPAT Bridge'!F$39)</f>
-        <v/>
-      </c>
-      <c r="D53" s="75">
-        <f>'NOPAT Bridge'!F41</f>
-        <v/>
-      </c>
-      <c r="E53" s="75">
-        <f>E48*(1-'NOPAT Bridge'!F$39)</f>
-        <v/>
-      </c>
+      <c r="C53" s="75" t="n"/>
+      <c r="D53" s="75" t="n"/>
+      <c r="E53" s="75" t="n"/>
       <c r="F53" s="176" t="n"/>
       <c r="G53" s="176" t="n"/>
+      <c r="H53" s="176" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="41" t="inlineStr">
-        <is>
-          <t>NOPAT Y 5</t>
-        </is>
-      </c>
+      <c r="A54" s="41" t="n"/>
       <c r="B54" s="176" t="n"/>
-      <c r="C54" s="75">
-        <f>C49*(1-'NOPAT Bridge'!G$39)</f>
-        <v/>
-      </c>
-      <c r="D54" s="75">
-        <f>'NOPAT Bridge'!G41</f>
-        <v/>
-      </c>
-      <c r="E54" s="75">
-        <f>E49*(1-'NOPAT Bridge'!G$39)</f>
-        <v/>
-      </c>
+      <c r="C54" s="75" t="n"/>
+      <c r="D54" s="75" t="n"/>
+      <c r="E54" s="75" t="n"/>
       <c r="F54" s="176" t="n"/>
       <c r="G54" s="176" t="n"/>
+      <c r="H54" s="176" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="41" t="inlineStr">
-        <is>
-          <t>D&amp;A Y 1</t>
-        </is>
-      </c>
+      <c r="A55" s="41" t="n"/>
       <c r="B55" s="176" t="n"/>
-      <c r="C55" s="75">
-        <f>C25*C12</f>
-        <v/>
-      </c>
-      <c r="D55" s="75">
-        <f>D25*D12</f>
-        <v/>
-      </c>
-      <c r="E55" s="75">
-        <f>E25*E12</f>
-        <v/>
-      </c>
+      <c r="C55" s="75" t="n"/>
+      <c r="D55" s="75" t="n"/>
+      <c r="E55" s="75" t="n"/>
       <c r="F55" s="176" t="n"/>
       <c r="G55" s="176" t="n"/>
+      <c r="H55" s="176" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="41" t="inlineStr">
-        <is>
-          <t>D&amp;A Y 2</t>
-        </is>
-      </c>
+      <c r="A56" s="41" t="n"/>
       <c r="B56" s="176" t="n"/>
-      <c r="C56" s="75">
-        <f>C26*C12</f>
-        <v/>
-      </c>
-      <c r="D56" s="75">
-        <f>D26*D12</f>
-        <v/>
-      </c>
-      <c r="E56" s="75">
-        <f>E26*E12</f>
-        <v/>
-      </c>
+      <c r="C56" s="75" t="n"/>
+      <c r="D56" s="75" t="n"/>
+      <c r="E56" s="75" t="n"/>
       <c r="F56" s="176" t="n"/>
       <c r="G56" s="176" t="n"/>
+      <c r="H56" s="176" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="41" t="inlineStr">
-        <is>
-          <t>D&amp;A Y 3</t>
-        </is>
-      </c>
+      <c r="A57" s="41" t="n"/>
       <c r="B57" s="176" t="n"/>
-      <c r="C57" s="75">
-        <f>C27*C12</f>
-        <v/>
-      </c>
-      <c r="D57" s="75">
-        <f>D27*D12</f>
-        <v/>
-      </c>
-      <c r="E57" s="75">
-        <f>E27*E12</f>
-        <v/>
-      </c>
+      <c r="C57" s="75" t="n"/>
+      <c r="D57" s="75" t="n"/>
+      <c r="E57" s="75" t="n"/>
       <c r="F57" s="176" t="n"/>
       <c r="G57" s="176" t="n"/>
+      <c r="H57" s="176" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="41" t="inlineStr">
-        <is>
-          <t>D&amp;A Y 4</t>
-        </is>
-      </c>
+      <c r="A58" s="41" t="n"/>
       <c r="B58" s="176" t="n"/>
-      <c r="C58" s="75">
-        <f>C28*C12</f>
-        <v/>
-      </c>
-      <c r="D58" s="75">
-        <f>D28*D12</f>
-        <v/>
-      </c>
-      <c r="E58" s="75">
-        <f>E28*E12</f>
-        <v/>
-      </c>
+      <c r="C58" s="75" t="n"/>
+      <c r="D58" s="75" t="n"/>
+      <c r="E58" s="75" t="n"/>
       <c r="F58" s="176" t="n"/>
       <c r="G58" s="176" t="n"/>
+      <c r="H58" s="176" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="41" t="inlineStr">
-        <is>
-          <t>D&amp;A Y 5</t>
-        </is>
-      </c>
+      <c r="A59" s="41" t="n"/>
       <c r="B59" s="176" t="n"/>
-      <c r="C59" s="75">
-        <f>C29*C12</f>
-        <v/>
-      </c>
-      <c r="D59" s="75">
-        <f>D29*D12</f>
-        <v/>
-      </c>
-      <c r="E59" s="75">
-        <f>E29*E12</f>
-        <v/>
-      </c>
+      <c r="C59" s="75" t="n"/>
+      <c r="D59" s="75" t="n"/>
+      <c r="E59" s="75" t="n"/>
       <c r="F59" s="176" t="n"/>
       <c r="G59" s="176" t="n"/>
+      <c r="H59" s="176" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="41" t="inlineStr">
-        <is>
-          <t>Capex - year 1</t>
-        </is>
-      </c>
+      <c r="A60" s="41" t="n"/>
       <c r="B60" s="176" t="n"/>
-      <c r="C60" s="75">
-        <f>C25*C13</f>
-        <v/>
-      </c>
-      <c r="D60" s="75">
-        <f>D25*D13</f>
-        <v/>
-      </c>
-      <c r="E60" s="75">
-        <f>E25*E13</f>
-        <v/>
-      </c>
+      <c r="C60" s="75" t="n"/>
+      <c r="D60" s="75" t="n"/>
+      <c r="E60" s="75" t="n"/>
       <c r="F60" s="176" t="n"/>
       <c r="G60" s="176" t="n"/>
+      <c r="H60" s="176" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="41" t="inlineStr">
-        <is>
-          <t>Capex - year 2</t>
-        </is>
-      </c>
+      <c r="A61" s="41" t="n"/>
       <c r="B61" s="176" t="n"/>
-      <c r="C61" s="75">
-        <f>C26*C13</f>
-        <v/>
-      </c>
-      <c r="D61" s="75">
-        <f>D26*D13</f>
-        <v/>
-      </c>
-      <c r="E61" s="75">
-        <f>E26*E13</f>
-        <v/>
-      </c>
+      <c r="C61" s="75" t="n"/>
+      <c r="D61" s="75" t="n"/>
+      <c r="E61" s="75" t="n"/>
       <c r="F61" s="176" t="n"/>
       <c r="G61" s="176" t="n"/>
+      <c r="H61" s="176" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="41" t="inlineStr">
-        <is>
-          <t>Capex - year 3</t>
-        </is>
-      </c>
+      <c r="A62" s="41" t="n"/>
       <c r="B62" s="176" t="n"/>
-      <c r="C62" s="75">
-        <f>C27*C13</f>
-        <v/>
-      </c>
-      <c r="D62" s="75">
-        <f>D27*D13</f>
-        <v/>
-      </c>
-      <c r="E62" s="75">
-        <f>E27*E13</f>
-        <v/>
-      </c>
+      <c r="C62" s="75" t="n"/>
+      <c r="D62" s="75" t="n"/>
+      <c r="E62" s="75" t="n"/>
       <c r="F62" s="176" t="n"/>
       <c r="G62" s="176" t="n"/>
+      <c r="H62" s="176" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="41" t="inlineStr">
-        <is>
-          <t>Capex - year 4</t>
-        </is>
-      </c>
+      <c r="A63" s="41" t="n"/>
       <c r="B63" s="176" t="n"/>
-      <c r="C63" s="75">
-        <f>C28*C13</f>
-        <v/>
-      </c>
-      <c r="D63" s="75">
-        <f>D28*D13</f>
-        <v/>
-      </c>
-      <c r="E63" s="75">
-        <f>E28*E13</f>
-        <v/>
-      </c>
+      <c r="C63" s="75" t="n"/>
+      <c r="D63" s="75" t="n"/>
+      <c r="E63" s="75" t="n"/>
       <c r="F63" s="176" t="n"/>
       <c r="G63" s="176" t="n"/>
+      <c r="H63" s="176" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="41" t="inlineStr">
-        <is>
-          <t>Capex - year 5</t>
-        </is>
-      </c>
+      <c r="A64" s="41" t="n"/>
       <c r="B64" s="176" t="n"/>
-      <c r="C64" s="75">
-        <f>C29*C13</f>
-        <v/>
-      </c>
-      <c r="D64" s="75">
-        <f>D29*D13</f>
-        <v/>
-      </c>
-      <c r="E64" s="75">
-        <f>E29*E13</f>
-        <v/>
-      </c>
+      <c r="C64" s="75" t="n"/>
+      <c r="D64" s="75" t="n"/>
+      <c r="E64" s="75" t="n"/>
       <c r="F64" s="176" t="n"/>
       <c r="G64" s="176" t="n"/>
+      <c r="H64" s="176" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="41" t="inlineStr">
@@ -4410,6 +4195,7 @@
       </c>
       <c r="F65" s="176" t="n"/>
       <c r="G65" s="176" t="n"/>
+      <c r="H65" s="176" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="41" t="inlineStr">
@@ -4432,6 +4218,7 @@
       </c>
       <c r="F66" s="176" t="n"/>
       <c r="G66" s="176" t="n"/>
+      <c r="H66" s="176" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="41" t="inlineStr">
@@ -4454,6 +4241,7 @@
       </c>
       <c r="F67" s="176" t="n"/>
       <c r="G67" s="176" t="n"/>
+      <c r="H67" s="176" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="41" t="inlineStr">
@@ -4476,6 +4264,7 @@
       </c>
       <c r="F68" s="176" t="n"/>
       <c r="G68" s="176" t="n"/>
+      <c r="H68" s="176" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="41" t="inlineStr">
@@ -4498,6 +4287,7 @@
       </c>
       <c r="F69" s="176" t="n"/>
       <c r="G69" s="176" t="n"/>
+      <c r="H69" s="176" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="41" t="inlineStr">
@@ -4520,6 +4310,7 @@
       </c>
       <c r="F70" s="176" t="n"/>
       <c r="G70" s="176" t="n"/>
+      <c r="H70" s="176" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="41" t="inlineStr">
@@ -4542,6 +4333,7 @@
       </c>
       <c r="F71" s="176" t="n"/>
       <c r="G71" s="176" t="n"/>
+      <c r="H71" s="176" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="41" t="inlineStr">
@@ -4564,6 +4356,7 @@
       </c>
       <c r="F72" s="176" t="n"/>
       <c r="G72" s="176" t="n"/>
+      <c r="H72" s="176" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="41" t="inlineStr">
@@ -4586,6 +4379,7 @@
       </c>
       <c r="F73" s="176" t="n"/>
       <c r="G73" s="176" t="n"/>
+      <c r="H73" s="176" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="41" t="inlineStr">
@@ -4608,6 +4402,7 @@
       </c>
       <c r="F74" s="176" t="n"/>
       <c r="G74" s="176" t="n"/>
+      <c r="H74" s="176" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="41" t="inlineStr">
@@ -4630,6 +4425,7 @@
       </c>
       <c r="F75" s="176" t="n"/>
       <c r="G75" s="176" t="n"/>
+      <c r="H75" s="176" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="41" t="inlineStr">
@@ -4652,6 +4448,7 @@
       </c>
       <c r="F76" s="176" t="n"/>
       <c r="G76" s="176" t="n"/>
+      <c r="H76" s="176" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="41" t="inlineStr">
@@ -4674,6 +4471,7 @@
       </c>
       <c r="F77" s="176" t="n"/>
       <c r="G77" s="176" t="n"/>
+      <c r="H77" s="176" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="41" t="inlineStr">
@@ -4696,6 +4494,7 @@
       </c>
       <c r="F78" s="176" t="n"/>
       <c r="G78" s="176" t="n"/>
+      <c r="H78" s="176" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="41" t="inlineStr">
@@ -4718,6 +4517,7 @@
       </c>
       <c r="F79" s="176" t="n"/>
       <c r="G79" s="176" t="n"/>
+      <c r="H79" s="176" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="41" t="inlineStr">
@@ -4740,6 +4540,7 @@
       </c>
       <c r="F80" s="176" t="n"/>
       <c r="G80" s="176" t="n"/>
+      <c r="H80" s="176" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="41" t="inlineStr">
@@ -4762,6 +4563,7 @@
       </c>
       <c r="F81" s="176" t="n"/>
       <c r="G81" s="176" t="n"/>
+      <c r="H81" s="176" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="41" t="inlineStr">
@@ -4784,6 +4586,7 @@
       </c>
       <c r="F82" s="176" t="n"/>
       <c r="G82" s="176" t="n"/>
+      <c r="H82" s="176" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="41" t="inlineStr">
@@ -4806,6 +4609,7 @@
       </c>
       <c r="F83" s="176" t="n"/>
       <c r="G83" s="176" t="n"/>
+      <c r="H83" s="176" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="41" t="inlineStr">
@@ -4828,6 +4632,7 @@
       </c>
       <c r="F84" s="176" t="n"/>
       <c r="G84" s="176" t="n"/>
+      <c r="H84" s="176" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="41" t="inlineStr">
@@ -4850,6 +4655,7 @@
       </c>
       <c r="F85" s="176" t="n"/>
       <c r="G85" s="176" t="n"/>
+      <c r="H85" s="176" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="41" t="inlineStr">
@@ -4872,6 +4678,7 @@
       </c>
       <c r="F86" s="176" t="n"/>
       <c r="G86" s="176" t="n"/>
+      <c r="H86" s="176" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="41" t="inlineStr">
@@ -4894,6 +4701,7 @@
       </c>
       <c r="F87" s="176" t="n"/>
       <c r="G87" s="176" t="n"/>
+      <c r="H87" s="176" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="41" t="inlineStr">
@@ -4916,6 +4724,7 @@
       </c>
       <c r="F88" s="176" t="n"/>
       <c r="G88" s="176" t="n"/>
+      <c r="H88" s="176" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="41" t="inlineStr">
@@ -4938,6 +4747,7 @@
       </c>
       <c r="F89" s="176" t="n"/>
       <c r="G89" s="176" t="n"/>
+      <c r="H89" s="176" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="41" t="inlineStr">
@@ -4960,6 +4770,7 @@
       </c>
       <c r="F90" s="176" t="n"/>
       <c r="G90" s="176" t="n"/>
+      <c r="H90" s="176" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="41" t="inlineStr">
@@ -4982,6 +4793,7 @@
       </c>
       <c r="F91" s="176" t="n"/>
       <c r="G91" s="176" t="n"/>
+      <c r="H91" s="176" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="41" t="inlineStr">
@@ -5004,6 +4816,7 @@
       </c>
       <c r="F92" s="176" t="n"/>
       <c r="G92" s="176" t="n"/>
+      <c r="H92" s="176" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="41" t="inlineStr">
@@ -5026,6 +4839,7 @@
       </c>
       <c r="F93" s="176" t="n"/>
       <c r="G93" s="176" t="n"/>
+      <c r="H93" s="176" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="41" t="inlineStr">
@@ -5048,6 +4862,7 @@
       </c>
       <c r="F94" s="176" t="n"/>
       <c r="G94" s="176" t="n"/>
+      <c r="H94" s="176" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="41" t="inlineStr">
@@ -5070,6 +4885,7 @@
       </c>
       <c r="F95" s="176" t="n"/>
       <c r="G95" s="176" t="n"/>
+      <c r="H95" s="176" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="41" t="inlineStr">
@@ -5092,6 +4908,7 @@
       </c>
       <c r="F96" s="176" t="n"/>
       <c r="G96" s="176" t="n"/>
+      <c r="H96" s="176" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="41" t="inlineStr">
@@ -5114,6 +4931,7 @@
       </c>
       <c r="F97" s="176" t="n"/>
       <c r="G97" s="176" t="n"/>
+      <c r="H97" s="176" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="41" t="inlineStr">
@@ -5136,6 +4954,7 @@
       </c>
       <c r="F98" s="176" t="n"/>
       <c r="G98" s="176" t="n"/>
+      <c r="H98" s="176" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="41" t="inlineStr">
@@ -5158,6 +4977,7 @@
       </c>
       <c r="F99" s="176" t="n"/>
       <c r="G99" s="176" t="n"/>
+      <c r="H99" s="176" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="41" t="inlineStr">
@@ -5180,6 +5000,7 @@
       </c>
       <c r="F100" s="176" t="n"/>
       <c r="G100" s="176" t="n"/>
+      <c r="H100" s="176" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="41" t="inlineStr">
@@ -5202,6 +5023,7 @@
       </c>
       <c r="F101" s="176" t="n"/>
       <c r="G101" s="176" t="n"/>
+      <c r="H101" s="176" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="41" t="inlineStr">
@@ -5224,6 +5046,7 @@
       </c>
       <c r="F102" s="176" t="n"/>
       <c r="G102" s="176" t="n"/>
+      <c r="H102" s="176" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="41" t="inlineStr">
@@ -5246,6 +5069,7 @@
       </c>
       <c r="F103" s="176" t="n"/>
       <c r="G103" s="176" t="n"/>
+      <c r="H103" s="176" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="41" t="inlineStr">
@@ -5268,6 +5092,7 @@
       </c>
       <c r="F104" s="176" t="n"/>
       <c r="G104" s="176" t="n"/>
+      <c r="H104" s="176" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="41" t="inlineStr">
@@ -5290,6 +5115,7 @@
       </c>
       <c r="F105" s="176" t="n"/>
       <c r="G105" s="176" t="n"/>
+      <c r="H105" s="176" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="41" t="inlineStr">
@@ -5312,6 +5138,7 @@
       </c>
       <c r="F106" s="176" t="n"/>
       <c r="G106" s="176" t="n"/>
+      <c r="H106" s="176" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="41" t="inlineStr">
@@ -5334,6 +5161,7 @@
       </c>
       <c r="F107" s="176" t="n"/>
       <c r="G107" s="176" t="n"/>
+      <c r="H107" s="176" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="41" t="inlineStr">
@@ -5356,6 +5184,7 @@
       </c>
       <c r="F108" s="176" t="n"/>
       <c r="G108" s="176" t="n"/>
+      <c r="H108" s="176" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="41" t="inlineStr">
@@ -5378,6 +5207,7 @@
       </c>
       <c r="F109" s="176" t="n"/>
       <c r="G109" s="176" t="n"/>
+      <c r="H109" s="176" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="41" t="inlineStr">
@@ -5400,6 +5230,7 @@
       </c>
       <c r="F110" s="176" t="n"/>
       <c r="G110" s="176" t="n"/>
+      <c r="H110" s="176" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="41" t="inlineStr">
@@ -5422,6 +5253,7 @@
       </c>
       <c r="F111" s="176" t="n"/>
       <c r="G111" s="176" t="n"/>
+      <c r="H111" s="176" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="41" t="inlineStr">
@@ -5444,6 +5276,7 @@
       </c>
       <c r="F112" s="176" t="n"/>
       <c r="G112" s="176" t="n"/>
+      <c r="H112" s="176" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="41" t="inlineStr">
@@ -5466,6 +5299,7 @@
       </c>
       <c r="F113" s="176" t="n"/>
       <c r="G113" s="176" t="n"/>
+      <c r="H113" s="176" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="41" t="inlineStr">
@@ -5488,6 +5322,7 @@
       </c>
       <c r="F114" s="176" t="n"/>
       <c r="G114" s="176" t="n"/>
+      <c r="H114" s="176" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="41" t="inlineStr">
@@ -5510,6 +5345,7 @@
       </c>
       <c r="F115" s="176" t="n"/>
       <c r="G115" s="176" t="n"/>
+      <c r="H115" s="176" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="41" t="inlineStr">
@@ -5532,6 +5368,7 @@
       </c>
       <c r="F116" s="176" t="n"/>
       <c r="G116" s="176" t="n"/>
+      <c r="H116" s="176" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="41" t="inlineStr">
@@ -5554,6 +5391,7 @@
       </c>
       <c r="F117" s="176" t="n"/>
       <c r="G117" s="176" t="n"/>
+      <c r="H117" s="176" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="41" t="inlineStr">
@@ -5576,6 +5414,7 @@
       </c>
       <c r="F118" s="176" t="n"/>
       <c r="G118" s="176" t="n"/>
+      <c r="H118" s="176" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="41" t="inlineStr">
@@ -5598,6 +5437,7 @@
       </c>
       <c r="F119" s="176" t="n"/>
       <c r="G119" s="176" t="n"/>
+      <c r="H119" s="176" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="41" t="inlineStr">
@@ -5620,6 +5460,7 @@
       </c>
       <c r="F120" s="176" t="n"/>
       <c r="G120" s="176" t="n"/>
+      <c r="H120" s="176" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="41" t="inlineStr">
@@ -5642,6 +5483,7 @@
       </c>
       <c r="F121" s="176" t="n"/>
       <c r="G121" s="176" t="n"/>
+      <c r="H121" s="176" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="41" t="inlineStr">
@@ -5664,6 +5506,7 @@
       </c>
       <c r="F122" s="176" t="n"/>
       <c r="G122" s="176" t="n"/>
+      <c r="H122" s="176" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="41" t="inlineStr">
@@ -5686,6 +5529,7 @@
       </c>
       <c r="F123" s="176" t="n"/>
       <c r="G123" s="176" t="n"/>
+      <c r="H123" s="176" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="41" t="inlineStr">
@@ -5708,6 +5552,7 @@
       </c>
       <c r="F124" s="176" t="n"/>
       <c r="G124" s="176" t="n"/>
+      <c r="H124" s="176" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="41" t="inlineStr">
@@ -5730,6 +5575,7 @@
       </c>
       <c r="F125" s="176" t="n"/>
       <c r="G125" s="176" t="n"/>
+      <c r="H125" s="176" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="41" t="inlineStr">
@@ -5752,6 +5598,7 @@
       </c>
       <c r="F126" s="176" t="n"/>
       <c r="G126" s="176" t="n"/>
+      <c r="H126" s="176" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="41" t="inlineStr">
@@ -5774,6 +5621,7 @@
       </c>
       <c r="F127" s="176" t="n"/>
       <c r="G127" s="176" t="n"/>
+      <c r="H127" s="176" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="41" t="inlineStr">
@@ -5796,6 +5644,7 @@
       </c>
       <c r="F128" s="176" t="n"/>
       <c r="G128" s="176" t="n"/>
+      <c r="H128" s="176" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="41" t="inlineStr">
@@ -5818,6 +5667,7 @@
       </c>
       <c r="F129" s="176" t="n"/>
       <c r="G129" s="176" t="n"/>
+      <c r="H129" s="176" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="176" t="n"/>
@@ -5827,6 +5677,7 @@
       <c r="E130" s="176" t="n"/>
       <c r="F130" s="176" t="n"/>
       <c r="G130" s="176" t="n"/>
+      <c r="H130" s="176" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="68" t="inlineStr">
@@ -5849,6 +5700,7 @@
       </c>
       <c r="F131" s="176" t="n"/>
       <c r="G131" s="176" t="n"/>
+      <c r="H131" s="176" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="124" t="inlineStr">
@@ -5871,6 +5723,7 @@
       </c>
       <c r="F132" s="176" t="n"/>
       <c r="G132" s="176" t="n"/>
+      <c r="H132" s="176" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="68" t="inlineStr">
@@ -5893,6 +5746,7 @@
       </c>
       <c r="F133" s="176" t="n"/>
       <c r="G133" s="176" t="n"/>
+      <c r="H133" s="176" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="176" t="n"/>
@@ -5902,6 +5756,7 @@
       <c r="E134" s="176" t="n"/>
       <c r="F134" s="176" t="n"/>
       <c r="G134" s="176" t="n"/>
+      <c r="H134" s="176" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="26" t="n"/>
@@ -5911,6 +5766,7 @@
       <c r="E135" s="176" t="n"/>
       <c r="F135" s="176" t="n"/>
       <c r="G135" s="176" t="n"/>
+      <c r="H135" s="176" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="176" t="n"/>
@@ -5920,6 +5776,7 @@
       <c r="E136" s="176" t="n"/>
       <c r="F136" s="176" t="n"/>
       <c r="G136" s="176" t="n"/>
+      <c r="H136" s="176" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="127" t="inlineStr">
@@ -5933,6 +5790,7 @@
       <c r="E137" s="176" t="n"/>
       <c r="F137" s="176" t="n"/>
       <c r="G137" s="176" t="n"/>
+      <c r="H137" s="176" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="41" t="inlineStr">
@@ -5956,6 +5814,7 @@
       </c>
       <c r="F138" s="176" t="n"/>
       <c r="G138" s="176" t="n"/>
+      <c r="H138" s="176" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="41" t="inlineStr">
@@ -5979,6 +5838,7 @@
       </c>
       <c r="F139" s="176" t="n"/>
       <c r="G139" s="176" t="n"/>
+      <c r="H139" s="176" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="41" t="inlineStr">
@@ -6002,6 +5862,7 @@
       </c>
       <c r="F140" s="176" t="n"/>
       <c r="G140" s="176" t="n"/>
+      <c r="H140" s="176" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="41" t="inlineStr">
@@ -6025,6 +5886,7 @@
       </c>
       <c r="F141" s="176" t="n"/>
       <c r="G141" s="176" t="n"/>
+      <c r="H141" s="176" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="41" t="inlineStr">
@@ -6048,6 +5910,7 @@
       </c>
       <c r="F142" s="176" t="n"/>
       <c r="G142" s="176" t="n"/>
+      <c r="H142" s="176" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="41" t="inlineStr">
@@ -6070,6 +5933,7 @@
       </c>
       <c r="F143" s="176" t="n"/>
       <c r="G143" s="176" t="n"/>
+      <c r="H143" s="176" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="41" t="inlineStr">
@@ -6092,6 +5956,7 @@
       </c>
       <c r="F144" s="176" t="n"/>
       <c r="G144" s="176" t="n"/>
+      <c r="H144" s="176" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="41" t="inlineStr">
@@ -6114,6 +5979,7 @@
       </c>
       <c r="F145" s="176" t="n"/>
       <c r="G145" s="176" t="n"/>
+      <c r="H145" s="176" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="41" t="inlineStr">
@@ -6136,6 +6002,7 @@
       </c>
       <c r="F146" s="176" t="n"/>
       <c r="G146" s="176" t="n"/>
+      <c r="H146" s="176" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="41" t="inlineStr">
@@ -6158,6 +6025,7 @@
       </c>
       <c r="F147" s="176" t="n"/>
       <c r="G147" s="176" t="n"/>
+      <c r="H147" s="176" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="41" t="inlineStr">
@@ -6180,6 +6048,7 @@
       </c>
       <c r="F148" s="176" t="n"/>
       <c r="G148" s="176" t="n"/>
+      <c r="H148" s="176" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="41" t="inlineStr">
@@ -6202,6 +6071,7 @@
       </c>
       <c r="F149" s="176" t="n"/>
       <c r="G149" s="176" t="n"/>
+      <c r="H149" s="176" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="41" t="inlineStr">
@@ -6224,6 +6094,7 @@
       </c>
       <c r="F150" s="176" t="n"/>
       <c r="G150" s="176" t="n"/>
+      <c r="H150" s="176" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="41" t="inlineStr">
@@ -6246,6 +6117,7 @@
       </c>
       <c r="F151" s="176" t="n"/>
       <c r="G151" s="176" t="n"/>
+      <c r="H151" s="176" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="41" t="inlineStr">
@@ -6268,6 +6140,7 @@
       </c>
       <c r="F152" s="176" t="n"/>
       <c r="G152" s="176" t="n"/>
+      <c r="H152" s="176" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="41" t="inlineStr">
@@ -6290,6 +6163,7 @@
       </c>
       <c r="F153" s="176" t="n"/>
       <c r="G153" s="176" t="n"/>
+      <c r="H153" s="176" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="41" t="inlineStr">
@@ -6312,6 +6186,7 @@
       </c>
       <c r="F154" s="176" t="n"/>
       <c r="G154" s="176" t="n"/>
+      <c r="H154" s="176" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="41" t="inlineStr">
@@ -6334,6 +6209,7 @@
       </c>
       <c r="F155" s="176" t="n"/>
       <c r="G155" s="176" t="n"/>
+      <c r="H155" s="176" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="41" t="inlineStr">
@@ -6356,6 +6232,7 @@
       </c>
       <c r="F156" s="176" t="n"/>
       <c r="G156" s="176" t="n"/>
+      <c r="H156" s="176" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="41" t="inlineStr">
@@ -6378,6 +6255,7 @@
       </c>
       <c r="F157" s="176" t="n"/>
       <c r="G157" s="176" t="n"/>
+      <c r="H157" s="176" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="41" t="inlineStr">
@@ -6400,6 +6278,7 @@
       </c>
       <c r="F158" s="176" t="n"/>
       <c r="G158" s="176" t="n"/>
+      <c r="H158" s="176" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="41" t="inlineStr">
@@ -6422,6 +6301,7 @@
       </c>
       <c r="F159" s="176" t="n"/>
       <c r="G159" s="176" t="n"/>
+      <c r="H159" s="176" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="41" t="inlineStr">
@@ -6444,6 +6324,7 @@
       </c>
       <c r="F160" s="176" t="n"/>
       <c r="G160" s="176" t="n"/>
+      <c r="H160" s="176" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="41" t="inlineStr">
@@ -6466,6 +6347,7 @@
       </c>
       <c r="F161" s="176" t="n"/>
       <c r="G161" s="176" t="n"/>
+      <c r="H161" s="176" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="41" t="inlineStr">
@@ -6488,6 +6370,7 @@
       </c>
       <c r="F162" s="176" t="n"/>
       <c r="G162" s="176" t="n"/>
+      <c r="H162" s="176" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="41" t="inlineStr">
@@ -6510,6 +6393,7 @@
       </c>
       <c r="F163" s="176" t="n"/>
       <c r="G163" s="176" t="n"/>
+      <c r="H163" s="176" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="41" t="inlineStr">
@@ -6532,6 +6416,7 @@
       </c>
       <c r="F164" s="176" t="n"/>
       <c r="G164" s="176" t="n"/>
+      <c r="H164" s="176" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="41" t="inlineStr">
@@ -6554,6 +6439,7 @@
       </c>
       <c r="F165" s="176" t="n"/>
       <c r="G165" s="176" t="n"/>
+      <c r="H165" s="176" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="41" t="inlineStr">
@@ -6576,6 +6462,7 @@
       </c>
       <c r="F166" s="176" t="n"/>
       <c r="G166" s="176" t="n"/>
+      <c r="H166" s="176" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="41" t="inlineStr">
@@ -6598,6 +6485,7 @@
       </c>
       <c r="F167" s="176" t="n"/>
       <c r="G167" s="176" t="n"/>
+      <c r="H167" s="176" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="41" t="inlineStr">
@@ -6620,6 +6508,7 @@
       </c>
       <c r="F168" s="176" t="n"/>
       <c r="G168" s="176" t="n"/>
+      <c r="H168" s="176" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="41" t="inlineStr">
@@ -6642,6 +6531,7 @@
       </c>
       <c r="F169" s="176" t="n"/>
       <c r="G169" s="176" t="n"/>
+      <c r="H169" s="176" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="41" t="inlineStr">
@@ -6664,6 +6554,7 @@
       </c>
       <c r="F170" s="176" t="n"/>
       <c r="G170" s="176" t="n"/>
+      <c r="H170" s="176" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="41" t="inlineStr">
@@ -6686,6 +6577,7 @@
       </c>
       <c r="F171" s="176" t="n"/>
       <c r="G171" s="176" t="n"/>
+      <c r="H171" s="176" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="41" t="inlineStr">
@@ -6708,6 +6600,7 @@
       </c>
       <c r="F172" s="176" t="n"/>
       <c r="G172" s="176" t="n"/>
+      <c r="H172" s="176" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="41" t="inlineStr">
@@ -6730,6 +6623,7 @@
       </c>
       <c r="F173" s="176" t="n"/>
       <c r="G173" s="176" t="n"/>
+      <c r="H173" s="176" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="41" t="inlineStr">
@@ -6752,6 +6646,7 @@
       </c>
       <c r="F174" s="176" t="n"/>
       <c r="G174" s="176" t="n"/>
+      <c r="H174" s="176" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="41" t="inlineStr">
@@ -6774,6 +6669,7 @@
       </c>
       <c r="F175" s="176" t="n"/>
       <c r="G175" s="176" t="n"/>
+      <c r="H175" s="176" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="41" t="inlineStr">
@@ -6796,6 +6692,7 @@
       </c>
       <c r="F176" s="176" t="n"/>
       <c r="G176" s="176" t="n"/>
+      <c r="H176" s="176" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="41" t="inlineStr">
@@ -6818,6 +6715,7 @@
       </c>
       <c r="F177" s="176" t="n"/>
       <c r="G177" s="176" t="n"/>
+      <c r="H177" s="176" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="41" t="inlineStr">
@@ -6840,6 +6738,7 @@
       </c>
       <c r="F178" s="176" t="n"/>
       <c r="G178" s="176" t="n"/>
+      <c r="H178" s="176" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="41" t="inlineStr">
@@ -6862,6 +6761,7 @@
       </c>
       <c r="F179" s="176" t="n"/>
       <c r="G179" s="176" t="n"/>
+      <c r="H179" s="176" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="41" t="inlineStr">
@@ -6884,6 +6784,7 @@
       </c>
       <c r="F180" s="176" t="n"/>
       <c r="G180" s="176" t="n"/>
+      <c r="H180" s="176" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="41" t="inlineStr">
@@ -6906,6 +6807,7 @@
       </c>
       <c r="F181" s="176" t="n"/>
       <c r="G181" s="176" t="n"/>
+      <c r="H181" s="176" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="41" t="inlineStr">
@@ -6928,6 +6830,7 @@
       </c>
       <c r="F182" s="176" t="n"/>
       <c r="G182" s="176" t="n"/>
+      <c r="H182" s="176" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="41" t="inlineStr">
@@ -6950,6 +6853,7 @@
       </c>
       <c r="F183" s="176" t="n"/>
       <c r="G183" s="176" t="n"/>
+      <c r="H183" s="176" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="41" t="inlineStr">
@@ -6972,6 +6876,7 @@
       </c>
       <c r="F184" s="176" t="n"/>
       <c r="G184" s="176" t="n"/>
+      <c r="H184" s="176" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="41" t="inlineStr">
@@ -6994,6 +6899,7 @@
       </c>
       <c r="F185" s="176" t="n"/>
       <c r="G185" s="176" t="n"/>
+      <c r="H185" s="176" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="41" t="inlineStr">
@@ -7016,6 +6922,7 @@
       </c>
       <c r="F186" s="176" t="n"/>
       <c r="G186" s="176" t="n"/>
+      <c r="H186" s="176" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="41" t="inlineStr">
@@ -7038,6 +6945,7 @@
       </c>
       <c r="F187" s="176" t="n"/>
       <c r="G187" s="176" t="n"/>
+      <c r="H187" s="176" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="41" t="inlineStr">
@@ -7060,6 +6968,7 @@
       </c>
       <c r="F188" s="176" t="n"/>
       <c r="G188" s="176" t="n"/>
+      <c r="H188" s="176" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="41" t="inlineStr">
@@ -7082,6 +6991,7 @@
       </c>
       <c r="F189" s="176" t="n"/>
       <c r="G189" s="176" t="n"/>
+      <c r="H189" s="176" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="41" t="inlineStr">
@@ -7104,6 +7014,7 @@
       </c>
       <c r="F190" s="176" t="n"/>
       <c r="G190" s="176" t="n"/>
+      <c r="H190" s="176" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="41" t="inlineStr">
@@ -7126,6 +7037,7 @@
       </c>
       <c r="F191" s="176" t="n"/>
       <c r="G191" s="176" t="n"/>
+      <c r="H191" s="176" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="41" t="inlineStr">
@@ -7148,6 +7060,7 @@
       </c>
       <c r="F192" s="176" t="n"/>
       <c r="G192" s="176" t="n"/>
+      <c r="H192" s="176" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="26" t="inlineStr">
@@ -7161,6 +7074,7 @@
       <c r="E193" s="176" t="n"/>
       <c r="F193" s="176" t="n"/>
       <c r="G193" s="176" t="n"/>
+      <c r="H193" s="176" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="176" t="inlineStr">
@@ -7176,6 +7090,7 @@
       <c r="E194" s="176" t="n"/>
       <c r="F194" s="176" t="n"/>
       <c r="G194" s="176" t="n"/>
+      <c r="H194" s="176" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="176" t="inlineStr">
@@ -7191,6 +7106,7 @@
       <c r="E195" s="176" t="n"/>
       <c r="F195" s="176" t="n"/>
       <c r="G195" s="176" t="n"/>
+      <c r="H195" s="176" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="176" t="inlineStr">
@@ -7206,6 +7122,7 @@
       <c r="E196" s="176" t="n"/>
       <c r="F196" s="176" t="n"/>
       <c r="G196" s="176" t="n"/>
+      <c r="H196" s="176" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="176" t="inlineStr">
@@ -7221,6 +7138,7 @@
       <c r="E197" s="176" t="n"/>
       <c r="F197" s="176" t="n"/>
       <c r="G197" s="176" t="n"/>
+      <c r="H197" s="176" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="176" t="inlineStr">
@@ -7236,6 +7154,7 @@
       <c r="E198" s="176" t="n"/>
       <c r="F198" s="176" t="n"/>
       <c r="G198" s="176" t="n"/>
+      <c r="H198" s="176" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="176" t="inlineStr">
@@ -7251,6 +7170,7 @@
       <c r="E199" s="176" t="n"/>
       <c r="F199" s="176" t="n"/>
       <c r="G199" s="176" t="n"/>
+      <c r="H199" s="176" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="176" t="inlineStr">
@@ -7266,6 +7186,7 @@
       <c r="E200" s="176" t="n"/>
       <c r="F200" s="176" t="n"/>
       <c r="G200" s="176" t="n"/>
+      <c r="H200" s="176" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="176" t="inlineStr">
@@ -7281,6 +7202,7 @@
       <c r="E201" s="176" t="n"/>
       <c r="F201" s="176" t="n"/>
       <c r="G201" s="176" t="n"/>
+      <c r="H201" s="176" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="176" t="inlineStr">
@@ -7296,6 +7218,7 @@
       <c r="E202" s="176" t="n"/>
       <c r="F202" s="176" t="n"/>
       <c r="G202" s="176" t="n"/>
+      <c r="H202" s="176" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7497,9 +7420,9 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J6" s="185" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: beginning-stores formula</t>
+      <c r="J6" s="169" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: store roll-forward (Item 2)</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7455,7 @@
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>China plus twenty store openings FY26; Americas and RoW open slower.</t>
+          <t>Americas: ~6–8 net new stores/yr (slower than China).</t>
         </is>
       </c>
       <c r="J7" s="185" t="inlineStr">
@@ -7618,9 +7541,9 @@
           <t>Beginning stores plus regional openings minus closures each year.</t>
         </is>
       </c>
-      <c r="J9" s="185" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: ending-stores formula</t>
+      <c r="J9" s="169" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: company-operated store count</t>
         </is>
       </c>
     </row>
@@ -7663,9 +7586,9 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J10" s="185" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: beginning-stores formula</t>
+      <c r="J10" s="169" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: store roll-forward (Item 2)</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7621,7 @@
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>China plus twenty store openings FY26; Americas and RoW open slower.</t>
+          <t>China: ~20 store openings in FY26 (expansion plan).</t>
         </is>
       </c>
       <c r="J11" s="185" t="inlineStr">
@@ -7784,9 +7707,9 @@
           <t>Beginning stores plus regional openings minus closures each year.</t>
         </is>
       </c>
-      <c r="J13" s="185" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: ending-stores formula</t>
+      <c r="J13" s="169" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: company-operated store count</t>
         </is>
       </c>
     </row>
@@ -7829,9 +7752,9 @@
           <t>Beginning stores = last year's ending count. Same.</t>
         </is>
       </c>
-      <c r="J14" s="185" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: beginning-stores formula</t>
+      <c r="J14" s="169" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: store roll-forward (Item 2)</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7787,7 @@
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
-          <t>China plus twenty store openings FY26; Americas and RoW open slower.</t>
+          <t>RoW: ~4–6 net new stores/yr.</t>
         </is>
       </c>
       <c r="J15" s="185" t="inlineStr">
@@ -7950,9 +7873,9 @@
           <t>Beginning stores plus regional openings minus closures each year.</t>
         </is>
       </c>
-      <c r="J17" s="185" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: ending-stores formula</t>
+      <c r="J17" s="169" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: company-operated store count</t>
         </is>
       </c>
     </row>
@@ -7991,9 +7914,9 @@
           <t>Add up Americas + China + RoW ending.</t>
         </is>
       </c>
-      <c r="J18" s="185" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: total-stores formula</t>
+      <c r="J18" s="169" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: total company-operated stores</t>
         </is>
       </c>
     </row>
@@ -8077,9 +8000,9 @@
           <t>Total sq ft equals ending store count times average box size.</t>
         </is>
       </c>
-      <c r="J20" s="185" t="inlineStr">
-        <is>
-          <t>Revenue Drivers: total-sqft formula</t>
+      <c r="J20" s="169" t="inlineStr">
+        <is>
+          <t>LULU FY2025 10-K: sales per square foot &amp; store count</t>
         </is>
       </c>
     </row>
@@ -9335,23 +9258,23 @@
         <v>11102600</v>
       </c>
       <c r="C56" s="75">
-        <f>Scenarios!D25</f>
+        <f>DCF!C6</f>
         <v/>
       </c>
       <c r="D56" s="75">
-        <f>Scenarios!D26</f>
+        <f>DCF!D6</f>
         <v/>
       </c>
       <c r="E56" s="75">
-        <f>Scenarios!D27</f>
+        <f>DCF!E6</f>
         <v/>
       </c>
       <c r="F56" s="75">
-        <f>Scenarios!D28</f>
+        <f>DCF!F6</f>
         <v/>
       </c>
       <c r="G56" s="75">
-        <f>Scenarios!D29</f>
+        <f>DCF!G6</f>
         <v/>
       </c>
       <c r="H56" s="176" t="n"/>
@@ -10047,23 +9970,23 @@
         <v>2210615</v>
       </c>
       <c r="C16" s="75">
-        <f>Scenarios!D45</f>
+        <f>DCF!C11</f>
         <v/>
       </c>
       <c r="D16" s="75">
-        <f>Scenarios!D46</f>
+        <f>DCF!D11</f>
         <v/>
       </c>
       <c r="E16" s="75">
-        <f>Scenarios!D47</f>
+        <f>DCF!E11</f>
         <v/>
       </c>
       <c r="F16" s="75">
-        <f>Scenarios!D48</f>
+        <f>DCF!F11</f>
         <v/>
       </c>
       <c r="G16" s="75">
-        <f>Scenarios!D49</f>
+        <f>DCF!G11</f>
         <v/>
       </c>
       <c r="H16" s="188" t="inlineStr">
@@ -10172,23 +10095,23 @@
         <v>62203</v>
       </c>
       <c r="C20" s="75">
-        <f>Scenarios!C25/DCF!$B$6*$B$20*$B$7</f>
+        <f>IF($B$7=1,DCF!C6*$B$20/DCF!$B$6,0)</f>
         <v/>
       </c>
       <c r="D20" s="75">
-        <f>Scenarios!D25/DCF!$B$6*$B$20*$B$7</f>
+        <f>IF($B$7=1,DCF!D6*$B$20/DCF!$B$6,0)</f>
         <v/>
       </c>
       <c r="E20" s="75">
-        <f>Scenarios!E25/DCF!$B$6*$B$20*$B$7</f>
+        <f>IF($B$7=1,DCF!E6*$B$20/DCF!$B$6,0)</f>
         <v/>
       </c>
       <c r="F20" s="75">
-        <f>Scenarios!F25/DCF!$B$6*$B$20*$B$7</f>
+        <f>IF($B$7=1,DCF!F6*$B$20/DCF!$B$6,0)</f>
         <v/>
       </c>
       <c r="G20" s="75">
-        <f>Scenarios!G25/DCF!$B$6*$B$20*$B$7</f>
+        <f>IF($B$7=1,DCF!G6*$B$20/DCF!$B$6,0)</f>
         <v/>
       </c>
       <c r="H20" s="188" t="inlineStr">
@@ -10250,23 +10173,23 @@
         <v>1028</v>
       </c>
       <c r="C23" s="75">
-        <f>$B$23*(Scenarios!C25/DCF!$B$6)</f>
+        <f>$B$23*(DCF!C6/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="D23" s="75">
-        <f>$B$23*(Scenarios!D25/DCF!$B$6)</f>
+        <f>$B$23*(DCF!D6/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="E23" s="75">
-        <f>$B$23*(Scenarios!E25/DCF!$B$6)</f>
+        <f>$B$23*(DCF!E6/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="F23" s="75">
-        <f>$B$23*(Scenarios!F25/DCF!$B$6)</f>
+        <f>$B$23*(DCF!F6/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="G23" s="75">
-        <f>$B$23*(Scenarios!G25/DCF!$B$6)</f>
+        <f>$B$23*(DCF!G6/DCF!$B$6)</f>
         <v/>
       </c>
       <c r="H23" s="188" t="inlineStr">
@@ -10489,7 +10412,7 @@
           <t>Store-channel EBIT (= Rev x store margin)</t>
         </is>
       </c>
-      <c r="B31" s="32">
+      <c r="B31" s="75">
         <f>C31</f>
         <v/>
       </c>
@@ -10521,7 +10444,7 @@
           <t>E-commerce EBIT (= Rev x e-comm margin)</t>
         </is>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="75">
         <f>C32</f>
         <v/>
       </c>
@@ -10553,7 +10476,7 @@
           <t>Other-channels EBIT (= Rev x other margin)</t>
         </is>
       </c>
-      <c r="B33" s="32">
+      <c r="B33" s="75">
         <f>C33</f>
         <v/>
       </c>
@@ -10614,7 +10537,7 @@
           <t>EBIT after channel mix</t>
         </is>
       </c>
-      <c r="B35" s="31">
+      <c r="B35" s="130">
         <f>C35</f>
         <v/>
       </c>
@@ -10651,23 +10574,23 @@
         <v/>
       </c>
       <c r="C36" s="130">
-        <f>Scenarios!D45</f>
+        <f>DCF!C11</f>
         <v/>
       </c>
       <c r="D36" s="130">
-        <f>Scenarios!D46</f>
+        <f>DCF!D11</f>
         <v/>
       </c>
       <c r="E36" s="130">
-        <f>Scenarios!D47</f>
+        <f>DCF!E11</f>
         <v/>
       </c>
       <c r="F36" s="130">
-        <f>Scenarios!D48</f>
+        <f>DCF!F11</f>
         <v/>
       </c>
       <c r="G36" s="130">
-        <f>Scenarios!D49</f>
+        <f>DCF!G11</f>
         <v/>
       </c>
       <c r="H36" s="176" t="n"/>
@@ -10680,23 +10603,23 @@
       </c>
       <c r="B37" s="176" t="n"/>
       <c r="C37" s="75">
-        <f>C36-Scenarios!D45</f>
+        <f>C36-DCF!C11</f>
         <v/>
       </c>
       <c r="D37" s="75">
-        <f>D36-Scenarios!D46</f>
+        <f>D36-DCF!D11</f>
         <v/>
       </c>
       <c r="E37" s="75">
-        <f>E36-Scenarios!D47</f>
+        <f>E36-DCF!E11</f>
         <v/>
       </c>
       <c r="F37" s="75">
-        <f>F36-Scenarios!D48</f>
+        <f>F36-DCF!F11</f>
         <v/>
       </c>
       <c r="G37" s="75">
-        <f>G36-Scenarios!D49</f>
+        <f>G36-DCF!G11</f>
         <v/>
       </c>
       <c r="H37" s="176" t="n"/>
@@ -11152,23 +11075,23 @@
         <v>11102600</v>
       </c>
       <c r="C6" s="75">
-        <f>Scenarios!D25</f>
+        <f>B6*(1+C5)</f>
         <v/>
       </c>
       <c r="D6" s="75">
-        <f>Scenarios!D26</f>
+        <f>C6*(1+D5)</f>
         <v/>
       </c>
       <c r="E6" s="75">
-        <f>Scenarios!D27</f>
+        <f>D6*(1+E5)</f>
         <v/>
       </c>
       <c r="F6" s="75">
-        <f>Scenarios!D28</f>
+        <f>E6*(1+F5)</f>
         <v/>
       </c>
       <c r="G6" s="75">
-        <f>Scenarios!D29</f>
+        <f>F6*(1+G5)</f>
         <v/>
       </c>
       <c r="H6" s="176" t="n"/>
@@ -11184,23 +11107,23 @@
         <v/>
       </c>
       <c r="C7" s="32">
-        <f>Scenarios!$D$14</f>
+        <f>(C6-C8)/C6</f>
         <v/>
       </c>
       <c r="D7" s="32">
-        <f>Scenarios!$D$14</f>
+        <f>(D6-D8)/D6</f>
         <v/>
       </c>
       <c r="E7" s="32">
-        <f>Scenarios!$D$14</f>
+        <f>(E6-E8)/E6</f>
         <v/>
       </c>
       <c r="F7" s="32">
-        <f>Scenarios!$D$14</f>
+        <f>(F6-F8)/F6</f>
         <v/>
       </c>
       <c r="G7" s="32">
-        <f>Scenarios!$D$14</f>
+        <f>(G6-G8)/G6</f>
         <v/>
       </c>
       <c r="H7" s="176" t="n"/>
@@ -11215,23 +11138,23 @@
         <v>4818468</v>
       </c>
       <c r="C8" s="75">
-        <f>Scenarios!D35</f>
+        <f>C6*(1-Scenarios!$D$14)</f>
         <v/>
       </c>
       <c r="D8" s="75">
-        <f>Scenarios!D36</f>
+        <f>D6*(1-Scenarios!$D$14)</f>
         <v/>
       </c>
       <c r="E8" s="75">
-        <f>Scenarios!D37</f>
+        <f>E6*(1-Scenarios!$D$14)</f>
         <v/>
       </c>
       <c r="F8" s="75">
-        <f>Scenarios!D38</f>
+        <f>F6*(1-Scenarios!$D$14)</f>
         <v/>
       </c>
       <c r="G8" s="75">
-        <f>Scenarios!D39</f>
+        <f>G6*(1-Scenarios!$D$14)</f>
         <v/>
       </c>
       <c r="H8" s="176" t="n"/>
@@ -11244,23 +11167,23 @@
       </c>
       <c r="B9" s="176" t="n"/>
       <c r="C9" s="32">
-        <f>Scenarios!D40</f>
+        <f>C6*C9+C10</f>
         <v/>
       </c>
       <c r="D9" s="32">
-        <f>Scenarios!D41</f>
+        <f>D6*D9</f>
         <v/>
       </c>
       <c r="E9" s="32">
-        <f>Scenarios!D42</f>
+        <f>E6*E9</f>
         <v/>
       </c>
       <c r="F9" s="32">
-        <f>Scenarios!D43</f>
+        <f>F6*F9</f>
         <v/>
       </c>
       <c r="G9" s="32">
-        <f>Scenarios!D44</f>
+        <f>G6*G9</f>
         <v/>
       </c>
       <c r="H9" s="176" t="n"/>
@@ -11306,23 +11229,23 @@
         <v>2210615</v>
       </c>
       <c r="C11" s="130">
-        <f>Scenarios!D45</f>
+        <f>DCF!C11</f>
         <v/>
       </c>
       <c r="D11" s="130">
-        <f>Scenarios!D46</f>
+        <f>DCF!D11</f>
         <v/>
       </c>
       <c r="E11" s="130">
-        <f>Scenarios!D47</f>
+        <f>DCF!E11</f>
         <v/>
       </c>
       <c r="F11" s="130">
-        <f>Scenarios!D48</f>
+        <f>DCF!F11</f>
         <v/>
       </c>
       <c r="G11" s="130">
-        <f>Scenarios!D49</f>
+        <f>DCF!G11</f>
         <v/>
       </c>
       <c r="H11" s="176" t="n"/>
@@ -11338,23 +11261,23 @@
         <v/>
       </c>
       <c r="C12" s="32">
-        <f>C11/C6</f>
+        <f>C9/C6</f>
         <v/>
       </c>
       <c r="D12" s="32">
-        <f>D11/D6</f>
+        <f>D9/D6</f>
         <v/>
       </c>
       <c r="E12" s="32">
-        <f>E11/E6</f>
+        <f>E9/E6</f>
         <v/>
       </c>
       <c r="F12" s="32">
-        <f>F11/F6</f>
+        <f>F9/F6</f>
         <v/>
       </c>
       <c r="G12" s="32">
-        <f>G11/G6</f>
+        <f>G9/G6</f>
         <v/>
       </c>
       <c r="H12" s="176" t="n"/>
@@ -11402,23 +11325,23 @@
         <v/>
       </c>
       <c r="C14" s="130">
-        <f>Scenarios!D50</f>
+        <f>'NOPAT Bridge'!C41</f>
         <v/>
       </c>
       <c r="D14" s="130">
-        <f>Scenarios!D51</f>
+        <f>'NOPAT Bridge'!D41</f>
         <v/>
       </c>
       <c r="E14" s="130">
-        <f>Scenarios!D52</f>
+        <f>'NOPAT Bridge'!E41</f>
         <v/>
       </c>
       <c r="F14" s="130">
-        <f>Scenarios!D53</f>
+        <f>'NOPAT Bridge'!F41</f>
         <v/>
       </c>
       <c r="G14" s="130">
-        <f>Scenarios!D54</f>
+        <f>'NOPAT Bridge'!G41</f>
         <v/>
       </c>
       <c r="H14" s="176" t="n"/>
@@ -11479,23 +11402,23 @@
         <v/>
       </c>
       <c r="C17" s="75">
-        <f>Scenarios!D55</f>
+        <f>C6*Scenarios!$D$12</f>
         <v/>
       </c>
       <c r="D17" s="75">
-        <f>Scenarios!D56</f>
+        <f>D6*Scenarios!$D$12</f>
         <v/>
       </c>
       <c r="E17" s="75">
-        <f>Scenarios!D57</f>
+        <f>E6*Scenarios!$D$12</f>
         <v/>
       </c>
       <c r="F17" s="75">
-        <f>Scenarios!D58</f>
+        <f>F6*Scenarios!$D$12</f>
         <v/>
       </c>
       <c r="G17" s="75">
-        <f>Scenarios!D59</f>
+        <f>G6*Scenarios!$D$12</f>
         <v/>
       </c>
       <c r="H17" s="176" t="n"/>
@@ -11540,23 +11463,23 @@
         <v/>
       </c>
       <c r="C19" s="75">
-        <f>Scenarios!D60</f>
+        <f>-C6*Scenarios!$D$13</f>
         <v/>
       </c>
       <c r="D19" s="75">
-        <f>Scenarios!D61</f>
+        <f>-D6*Scenarios!$D$13</f>
         <v/>
       </c>
       <c r="E19" s="75">
-        <f>Scenarios!D62</f>
+        <f>-E6*Scenarios!$D$13</f>
         <v/>
       </c>
       <c r="F19" s="75">
-        <f>Scenarios!D63</f>
+        <f>-F6*Scenarios!$D$13</f>
         <v/>
       </c>
       <c r="G19" s="75">
-        <f>Scenarios!D64</f>
+        <f>-G6*Scenarios!$D$13</f>
         <v/>
       </c>
       <c r="H19" s="176" t="n"/>
@@ -11586,23 +11509,23 @@
         <v/>
       </c>
       <c r="C21" s="193">
-        <f>Scenarios!D65</f>
+        <f>Scenarios!$D$15</f>
         <v/>
       </c>
       <c r="D21" s="193">
-        <f>Scenarios!D66</f>
+        <f>Scenarios!$D$15</f>
         <v/>
       </c>
       <c r="E21" s="193">
-        <f>Scenarios!D67</f>
+        <f>Scenarios!$D$15</f>
         <v/>
       </c>
       <c r="F21" s="193">
-        <f>Scenarios!D68</f>
+        <f>Scenarios!$D$15</f>
         <v/>
       </c>
       <c r="G21" s="193">
-        <f>Scenarios!D69</f>
+        <f>Scenarios!$D$15</f>
         <v/>
       </c>
       <c r="H21" s="176" t="n"/>
@@ -11617,23 +11540,23 @@
         <v>190657</v>
       </c>
       <c r="C22" s="75">
-        <f>Scenarios!D70</f>
+        <f>C6*C21/365</f>
         <v/>
       </c>
       <c r="D22" s="75">
-        <f>Scenarios!D71</f>
+        <f>D6*D21/365</f>
         <v/>
       </c>
       <c r="E22" s="75">
-        <f>Scenarios!D72</f>
+        <f>E6*E21/365</f>
         <v/>
       </c>
       <c r="F22" s="75">
-        <f>Scenarios!D73</f>
+        <f>F6*F21/365</f>
         <v/>
       </c>
       <c r="G22" s="75">
-        <f>Scenarios!D74</f>
+        <f>G6*G21/365</f>
         <v/>
       </c>
       <c r="H22" s="188" t="inlineStr">
@@ -11653,23 +11576,23 @@
         <v/>
       </c>
       <c r="C23" s="193">
-        <f>Scenarios!D75</f>
+        <f>Scenarios!$D$16-0*Scenarios!$D$17</f>
         <v/>
       </c>
       <c r="D23" s="193">
-        <f>Scenarios!D76</f>
+        <f>Scenarios!$D$16-1*Scenarios!$D$17</f>
         <v/>
       </c>
       <c r="E23" s="193">
-        <f>Scenarios!D77</f>
+        <f>Scenarios!$D$16-2*Scenarios!$D$17</f>
         <v/>
       </c>
       <c r="F23" s="193">
-        <f>Scenarios!D78</f>
+        <f>Scenarios!$D$16-3*Scenarios!$D$17</f>
         <v/>
       </c>
       <c r="G23" s="193">
-        <f>Scenarios!D79</f>
+        <f>Scenarios!$D$16-4*Scenarios!$D$17</f>
         <v/>
       </c>
       <c r="H23" s="176" t="n"/>
@@ -11684,23 +11607,23 @@
         <v>1700753</v>
       </c>
       <c r="C24" s="75">
-        <f>Scenarios!D80</f>
+        <f>C8*C23/365</f>
         <v/>
       </c>
       <c r="D24" s="75">
-        <f>Scenarios!D81</f>
+        <f>D8*D23/365</f>
         <v/>
       </c>
       <c r="E24" s="75">
-        <f>Scenarios!D82</f>
+        <f>E8*E23/365</f>
         <v/>
       </c>
       <c r="F24" s="75">
-        <f>Scenarios!D83</f>
+        <f>F8*F23/365</f>
         <v/>
       </c>
       <c r="G24" s="75">
-        <f>Scenarios!D84</f>
+        <f>G8*G23/365</f>
         <v/>
       </c>
       <c r="H24" s="188" t="inlineStr">
@@ -11720,23 +11643,23 @@
         <v/>
       </c>
       <c r="C25" s="193">
-        <f>Scenarios!D85</f>
+        <f>Scenarios!$D$18</f>
         <v/>
       </c>
       <c r="D25" s="193">
-        <f>Scenarios!D86</f>
+        <f>Scenarios!$D$18</f>
         <v/>
       </c>
       <c r="E25" s="193">
-        <f>Scenarios!D87</f>
+        <f>Scenarios!$D$18</f>
         <v/>
       </c>
       <c r="F25" s="193">
-        <f>Scenarios!D88</f>
+        <f>Scenarios!$D$18</f>
         <v/>
       </c>
       <c r="G25" s="193">
-        <f>Scenarios!D89</f>
+        <f>Scenarios!$D$18</f>
         <v/>
       </c>
       <c r="H25" s="176" t="n"/>
@@ -11751,23 +11674,23 @@
         <v>331421</v>
       </c>
       <c r="C26" s="75">
-        <f>Scenarios!D90</f>
+        <f>C8*C25/365</f>
         <v/>
       </c>
       <c r="D26" s="75">
-        <f>Scenarios!D91</f>
+        <f>D8*D25/365</f>
         <v/>
       </c>
       <c r="E26" s="75">
-        <f>Scenarios!D92</f>
+        <f>E8*E25/365</f>
         <v/>
       </c>
       <c r="F26" s="75">
-        <f>Scenarios!D93</f>
+        <f>F8*F25/365</f>
         <v/>
       </c>
       <c r="G26" s="75">
-        <f>Scenarios!D94</f>
+        <f>G8*G25/365</f>
         <v/>
       </c>
       <c r="H26" s="188" t="inlineStr">
@@ -11818,23 +11741,23 @@
         <v>564089</v>
       </c>
       <c r="C28" s="75">
-        <f>Scenarios!D95</f>
+        <f>C6*C27</f>
         <v/>
       </c>
       <c r="D28" s="75">
-        <f>Scenarios!D96</f>
+        <f>D6*D27</f>
         <v/>
       </c>
       <c r="E28" s="75">
-        <f>Scenarios!D97</f>
+        <f>E6*E27</f>
         <v/>
       </c>
       <c r="F28" s="75">
-        <f>Scenarios!D98</f>
+        <f>F6*F27</f>
         <v/>
       </c>
       <c r="G28" s="75">
-        <f>Scenarios!D99</f>
+        <f>G6*G27</f>
         <v/>
       </c>
       <c r="H28" s="188" t="inlineStr">
@@ -11849,7 +11772,7 @@
           <t>Accrued liabilities (% of revenue)</t>
         </is>
       </c>
-      <c r="B29" s="75">
+      <c r="B29" s="32">
         <f>Scenarios!$D$20</f>
         <v/>
       </c>
@@ -11885,23 +11808,23 @@
         <v>662982</v>
       </c>
       <c r="C30" s="75">
-        <f>Scenarios!D100</f>
+        <f>C6*C29</f>
         <v/>
       </c>
       <c r="D30" s="75">
-        <f>Scenarios!D101</f>
+        <f>D6*D29</f>
         <v/>
       </c>
       <c r="E30" s="75">
-        <f>Scenarios!D102</f>
+        <f>E6*E29</f>
         <v/>
       </c>
       <c r="F30" s="75">
-        <f>Scenarios!D103</f>
+        <f>F6*F29</f>
         <v/>
       </c>
       <c r="G30" s="75">
-        <f>Scenarios!D104</f>
+        <f>G6*G29</f>
         <v/>
       </c>
       <c r="H30" s="188" t="inlineStr">
@@ -11918,23 +11841,23 @@
       </c>
       <c r="B31" s="176" t="n"/>
       <c r="C31" s="75">
-        <f>Scenarios!D105</f>
+        <f>C22+C24+C28</f>
         <v/>
       </c>
       <c r="D31" s="75">
-        <f>Scenarios!D106</f>
+        <f>D22+D24+D28</f>
         <v/>
       </c>
       <c r="E31" s="75">
-        <f>Scenarios!D107</f>
+        <f>E22+E24+E28</f>
         <v/>
       </c>
       <c r="F31" s="75">
-        <f>Scenarios!D108</f>
+        <f>F22+F24+F28</f>
         <v/>
       </c>
       <c r="G31" s="75">
-        <f>Scenarios!D109</f>
+        <f>G22+G24+G28</f>
         <v/>
       </c>
       <c r="H31" s="176" t="n"/>
@@ -11947,23 +11870,23 @@
       </c>
       <c r="B32" s="176" t="n"/>
       <c r="C32" s="75">
-        <f>Scenarios!D110</f>
+        <f>C26+C30</f>
         <v/>
       </c>
       <c r="D32" s="75">
-        <f>Scenarios!D111</f>
+        <f>D26+D30</f>
         <v/>
       </c>
       <c r="E32" s="75">
-        <f>Scenarios!D112</f>
+        <f>E26+E30</f>
         <v/>
       </c>
       <c r="F32" s="75">
-        <f>Scenarios!D113</f>
+        <f>F26+F30</f>
         <v/>
       </c>
       <c r="G32" s="75">
-        <f>Scenarios!D114</f>
+        <f>G26+G30</f>
         <v/>
       </c>
       <c r="H32" s="176" t="n"/>
@@ -11978,23 +11901,23 @@
         <v>1461096</v>
       </c>
       <c r="C33" s="130">
-        <f>Scenarios!D115</f>
+        <f>C31-C32</f>
         <v/>
       </c>
       <c r="D33" s="130">
-        <f>Scenarios!D116</f>
+        <f>D31-D32</f>
         <v/>
       </c>
       <c r="E33" s="130">
-        <f>Scenarios!D117</f>
+        <f>E31-E32</f>
         <v/>
       </c>
       <c r="F33" s="130">
-        <f>Scenarios!D118</f>
+        <f>F31-F32</f>
         <v/>
       </c>
       <c r="G33" s="130">
-        <f>Scenarios!D119</f>
+        <f>G31-G32</f>
         <v/>
       </c>
       <c r="H33" s="188" t="inlineStr">
@@ -12011,23 +11934,23 @@
       </c>
       <c r="B34" s="176" t="n"/>
       <c r="C34" s="130">
-        <f>Scenarios!D120</f>
+        <f>B33-C33</f>
         <v/>
       </c>
       <c r="D34" s="130">
-        <f>Scenarios!D121</f>
+        <f>C33-D33</f>
         <v/>
       </c>
       <c r="E34" s="130">
-        <f>Scenarios!D122</f>
+        <f>D33-E33</f>
         <v/>
       </c>
       <c r="F34" s="130">
-        <f>Scenarios!D123</f>
+        <f>E33-F33</f>
         <v/>
       </c>
       <c r="G34" s="130">
-        <f>Scenarios!D124</f>
+        <f>F33-G33</f>
         <v/>
       </c>
       <c r="H34" s="176" t="n"/>
@@ -12050,23 +11973,23 @@
       </c>
       <c r="B36" s="176" t="n"/>
       <c r="C36" s="200">
-        <f>Scenarios!D125</f>
+        <f>C14+C17+C19+C34</f>
         <v/>
       </c>
       <c r="D36" s="200">
-        <f>Scenarios!D126</f>
+        <f>D14+D17+D19+D34</f>
         <v/>
       </c>
       <c r="E36" s="200">
-        <f>Scenarios!D127</f>
+        <f>E14+E17+E19+E34</f>
         <v/>
       </c>
       <c r="F36" s="200">
-        <f>Scenarios!D128</f>
+        <f>F14+F17+F19+F34</f>
         <v/>
       </c>
       <c r="G36" s="200">
-        <f>Scenarios!D129</f>
+        <f>G14+G17+G19+G34</f>
         <v/>
       </c>
       <c r="H36" s="176" t="n"/>
@@ -12252,7 +12175,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="B46" s="75">
+      <c r="B46" s="32">
         <f>G36*(1+Scenarios!D10)/(WACC!B36-Scenarios!D10)</f>
         <v/>
       </c>
@@ -13192,7 +13115,7 @@
       </c>
       <c r="D95" s="176" t="inlineStr">
         <is>
-          <t>Selected exit is the Gordon identity, so spread should be 0</t>
+          <t>Exit multiple = Gordon-implied (FY30 EBITDA)</t>
         </is>
       </c>
       <c r="E95" s="176" t="n"/>
@@ -13760,7 +13683,7 @@
       </c>
       <c r="H19" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: LULU statistics</t>
         </is>
       </c>
     </row>
@@ -13785,7 +13708,7 @@
       </c>
       <c r="H20" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: UAA statistics</t>
         </is>
       </c>
     </row>
@@ -13810,7 +13733,7 @@
       </c>
       <c r="H21" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: ADS.DE statistics</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13758,7 @@
       </c>
       <c r="H22" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: NKE statistics</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13783,7 @@
       </c>
       <c r="H23" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: DECK statistics</t>
         </is>
       </c>
     </row>
@@ -13885,7 +13808,7 @@
       </c>
       <c r="H24" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: WSM statistics</t>
         </is>
       </c>
     </row>
@@ -13910,7 +13833,7 @@
       </c>
       <c r="H25" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: CROX statistics</t>
         </is>
       </c>
     </row>
@@ -13935,7 +13858,7 @@
       </c>
       <c r="H26" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: MOV statistics</t>
         </is>
       </c>
     </row>
@@ -13960,7 +13883,7 @@
       </c>
       <c r="H27" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: LEVI statistics</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13908,7 @@
       </c>
       <c r="H28" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: LZB statistics</t>
         </is>
       </c>
     </row>
@@ -14010,7 +13933,7 @@
       </c>
       <c r="H29" s="188" t="inlineStr">
         <is>
-          <t>PitchBook Comps Set 04-Sep-2026</t>
+          <t>Yahoo Finance: KTB statistics</t>
         </is>
       </c>
     </row>
@@ -14541,11 +14464,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
